--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -45981,6 +45981,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1984">
+      <c r="A1984" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1984" t="n">
+        <v>10356</v>
+      </c>
+      <c r="C1984" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E1984" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>1.80499994754791</v>
+      </c>
+      <c r="G1984" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46004,6 +46004,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1985">
+      <c r="A1985" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1985" t="n">
+        <v>9346</v>
+      </c>
+      <c r="C1985" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>1.7150000333786</v>
+      </c>
+      <c r="E1985" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G1985" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46027,6 +46027,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1986">
+      <c r="A1986" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1986" t="n">
+        <v>20263</v>
+      </c>
+      <c r="C1986" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>1.72500002384186</v>
+      </c>
+      <c r="E1986" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="G1986" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46035,7 +46035,7 @@
         <v>20263</v>
       </c>
       <c r="C1986" t="n">
-        <v>1.89999997615814</v>
+        <v>1.9099999666214</v>
       </c>
       <c r="D1986" t="n">
         <v>1.72500002384186</v>
@@ -46047,6 +46047,29 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1986" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1987" t="n">
+        <v>9850</v>
+      </c>
+      <c r="C1987" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>1.83500003814697</v>
+      </c>
+      <c r="E1987" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="G1987" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -45891,22 +45891,22 @@
     </row>
     <row r="1980">
       <c r="A1980" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1980" t="n">
-        <v>44450</v>
+        <v>8298</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.5</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="D1980" t="n">
-        <v>2.26999998092651</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="E1980" t="n">
         <v>2.3199999332428</v>
       </c>
       <c r="F1980" t="n">
-        <v>2.32999992370605</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="G1980" t="s">
         <v>7</v>
@@ -45914,22 +45914,22 @@
     </row>
     <row r="1981">
       <c r="A1981" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1981" t="n">
-        <v>29309</v>
+        <v>44450</v>
       </c>
       <c r="C1981" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="E1981" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1981" t="n">
         <v>2.32999992370605</v>
-      </c>
-      <c r="D1981" t="n">
-        <v>2.04999995231628</v>
-      </c>
-      <c r="E1981" t="n">
-        <v>2.27999997138977</v>
-      </c>
-      <c r="F1981" t="n">
-        <v>2.07999992370605</v>
       </c>
       <c r="G1981" t="s">
         <v>7</v>
@@ -45937,22 +45937,22 @@
     </row>
     <row r="1982">
       <c r="A1982" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1982" t="n">
-        <v>40441</v>
+        <v>29309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.03999996185303</v>
+        <v>2.32999992370605</v>
       </c>
       <c r="D1982" t="n">
-        <v>1.91999995708466</v>
+        <v>2.04999995231628</v>
       </c>
       <c r="E1982" t="n">
-        <v>2.03999996185303</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="F1982" t="n">
-        <v>1.95000004768372</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="G1982" t="s">
         <v>7</v>
@@ -45960,22 +45960,22 @@
     </row>
     <row r="1983">
       <c r="A1983" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1983" t="n">
-        <v>14115</v>
+        <v>40441</v>
       </c>
       <c r="C1983" t="n">
-        <v>1.97000002861023</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="D1983" t="n">
-        <v>1.86500000953674</v>
+        <v>1.91999995708466</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.97000002861023</v>
+        <v>2.03999996185303</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.87000000476837</v>
+        <v>1.95000004768372</v>
       </c>
       <c r="G1983" t="s">
         <v>7</v>
@@ -45983,22 +45983,22 @@
     </row>
     <row r="1984">
       <c r="A1984" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1984" t="n">
-        <v>10356</v>
+        <v>14115</v>
       </c>
       <c r="C1984" t="n">
-        <v>1.89999997615814</v>
+        <v>1.97000002861023</v>
       </c>
       <c r="D1984" t="n">
-        <v>1.79999995231628</v>
+        <v>1.86500000953674</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.85000002384186</v>
+        <v>1.97000002861023</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.80499994754791</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="G1984" t="s">
         <v>7</v>
@@ -46006,22 +46006,22 @@
     </row>
     <row r="1985">
       <c r="A1985" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1985" t="n">
-        <v>9346</v>
+        <v>10356</v>
       </c>
       <c r="C1985" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D1985" t="n">
         <v>1.79999995231628</v>
       </c>
-      <c r="D1985" t="n">
-        <v>1.7150000333786</v>
-      </c>
       <c r="E1985" t="n">
-        <v>1.79999995231628</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.75999999046326</v>
+        <v>1.80499994754791</v>
       </c>
       <c r="G1985" t="s">
         <v>7</v>
@@ -46029,22 +46029,22 @@
     </row>
     <row r="1986">
       <c r="A1986" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1986" t="n">
-        <v>20263</v>
+        <v>9346</v>
       </c>
       <c r="C1986" t="n">
-        <v>1.9099999666214</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="D1986" t="n">
-        <v>1.72500002384186</v>
+        <v>1.7150000333786</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.73000001907349</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.9099999666214</v>
+        <v>1.75999999046326</v>
       </c>
       <c r="G1986" t="s">
         <v>7</v>
@@ -46052,24 +46052,47 @@
     </row>
     <row r="1987">
       <c r="A1987" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1987" t="n">
-        <v>9850</v>
+        <v>20263</v>
       </c>
       <c r="C1987" t="n">
-        <v>1.99000000953674</v>
+        <v>1.9099999666214</v>
       </c>
       <c r="D1987" t="n">
-        <v>1.83500003814697</v>
+        <v>1.72500002384186</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.87000000476837</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="F1987" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="G1987" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1988" t="n">
+        <v>9015</v>
+      </c>
+      <c r="C1988" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="E1988" t="n">
         <v>1.97500002384186</v>
       </c>
-      <c r="G1987" t="s">
+      <c r="F1988" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G1988" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108229637146</v>
+        <v>2.88108253479004</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762376785278</v>
+        <v>2.90762400627136</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.37949991226196</v>
       </c>
       <c r="G21" t="n">
-        <v>2.89349699020386</v>
+        <v>2.8934965133667</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392495155334</v>
+        <v>2.89392518997192</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974389076233</v>
+        <v>2.79974412918091</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255313873291</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542967796326</v>
+        <v>2.82542943954468</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035928726196</v>
+        <v>2.76035904884338</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399176597595</v>
+        <v>2.83399152755737</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661381721497</v>
+        <v>2.91661429405212</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385813713074</v>
+        <v>2.95385837554932</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255313873291</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779867172241</v>
+        <v>3.00779819488525</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904938697815</v>
+        <v>3.03904891014099</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489635467529</v>
+        <v>3.30489659309387</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345796585083</v>
+        <v>3.31345844268799</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768544197083</v>
+        <v>3.23768520355225</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309729576111</v>
+        <v>3.25309681892395</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071553230286</v>
+        <v>3.21071577072144</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483025550842</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873642921448</v>
+        <v>3.44873666763306</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098480224609</v>
+        <v>3.61098504066467</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518626213074</v>
+        <v>3.81518578529358</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630454063416</v>
+        <v>3.96630334854126</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293251037598</v>
+        <v>4.04293346405029</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533586502075</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028491973877</v>
+        <v>4.24028539657593</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087991714478</v>
+        <v>4.09087944030762</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.06690645217896</v>
+        <v>4.0669059753418</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128747940063</v>
+        <v>3.98128771781921</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409648895264</v>
+        <v>4.02409696578979</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.93847703933716</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.93847703933716</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279220581055</v>
+        <v>3.91279244422913</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407608985901</v>
+        <v>3.91407632827759</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.0155348777771</v>
+        <v>4.01553440093994</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041044235229</v>
+        <v>3.87041115760803</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330738067627</v>
+        <v>3.96330714225769</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533586502075</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.0583438873291</v>
+        <v>4.05834436416626</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533586502075</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533586502075</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657238006592</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245908737183</v>
+        <v>4.21245861053467</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533586502075</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557350158691</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557350158691</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076435089111</v>
+        <v>7.02076482772827</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671691894531</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109842300415</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109842300415</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109842300415</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919376373291</v>
+        <v>7.14919328689575</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671691894531</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109842300415</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143106460571</v>
+        <v>6.42143154144287</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109842300415</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019359588623</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300212860107</v>
+        <v>6.29300260543823</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019359588623</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557350158691</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70905017852783</v>
+        <v>4.70904922485352</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70905017852783</v>
+        <v>4.70904922485352</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750587463379</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874477386475</v>
+        <v>3.69874453544617</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051532745361</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242046356201</v>
+        <v>2.96242022514343</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432488441467</v>
+        <v>2.53432512283325</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.48295331001282</v>
+        <v>2.4829535484314</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971641540527</v>
+        <v>4.10971593856812</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533586502075</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299169540405</v>
+        <v>3.73299217224121</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038217544556</v>
+        <v>3.51038241386414</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593457221985</v>
+        <v>3.65593481063843</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881087303162</v>
+        <v>3.63881063461304</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750587463379</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.41620135307312</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.41620135307312</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449689865112</v>
+        <v>3.66449666023254</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004881858826</v>
+        <v>3.8100483417511</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285902023315</v>
+        <v>3.85285878181458</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329662322998</v>
+        <v>4.74329710006714</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356435775757</v>
+        <v>4.50356340408325</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G375" t="n">
-        <v>4.46931648254395</v>
+        <v>4.46931600570679</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082025527954</v>
+        <v>4.4008207321167</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657238006592</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.2723913192749</v>
+        <v>4.27239227294922</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055490493774</v>
+        <v>4.64055347442627</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838346481323</v>
+        <v>5.30838298797607</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577299118042</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838346481323</v>
+        <v>5.30838298797607</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028764724731</v>
+        <v>4.88028717041016</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20563983917236</v>
+        <v>5.20564031600952</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.06864976882935</v>
+        <v>5.0686502456665</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577299118042</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.06864976882935</v>
+        <v>5.0686502456665</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06864976882935</v>
+        <v>5.0686502456665</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152606964111</v>
+        <v>5.0515251159668</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550621032715</v>
+        <v>5.32550668716431</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577299118042</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988819122314</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988819122314</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023851394653</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763734817505</v>
+        <v>5.16763687133789</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.13283824920654</v>
+        <v>5.13283777236938</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.13283824920654</v>
+        <v>5.13283777236938</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.83704710006714</v>
+        <v>4.83704662322998</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744937896729</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744937896729</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165822982788</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425987243652</v>
+        <v>4.45425939559937</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>4.36726188659668</v>
+        <v>4.36726236343384</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.34986305236816</v>
+        <v>4.34986257553101</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887052536011</v>
+        <v>4.08887147903442</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5</v>
       </c>
       <c r="G498" t="n">
-        <v>4.34986305236816</v>
+        <v>4.34986257553101</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.14106941223145</v>
+        <v>4.1410698890686</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456792831421</v>
+        <v>4.18456840515137</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785261154175</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165822982788</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785261154175</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785261154175</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525144577026</v>
+        <v>4.71525096893311</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744937896729</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525144577026</v>
+        <v>4.71525096893311</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.4020619392395</v>
+        <v>4.40206098556519</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744937896729</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.13283824920654</v>
+        <v>5.13283777236938</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.13283824920654</v>
+        <v>5.13283777236938</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.13283824920654</v>
+        <v>5.13283777236938</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023851394653</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39383029937744</v>
+        <v>5.39382982254028</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>5.68962097167969</v>
+        <v>5.68962049484253</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68962097167969</v>
+        <v>5.68962049484253</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.63742208480835</v>
+        <v>5.63742256164551</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122961044312</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122961044312</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661752700806</v>
+        <v>5.7766170501709</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881546020508</v>
+        <v>5.82881641387939</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801233291626</v>
+        <v>5.9680118560791</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>6.30562353134155</v>
+        <v>6.30562305450439</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.50156116485596</v>
+        <v>6.5015606880188</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031089782715</v>
+        <v>7.00031042098999</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718584060669</v>
+        <v>7.10718536376953</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G625" t="n">
-        <v>6.89343547821045</v>
+        <v>6.89343500137329</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468591690063</v>
+        <v>6.96468544006348</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562274932861</v>
+        <v>6.87562322616577</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>7.0893726348877</v>
+        <v>7.08937311172485</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.4812479019165</v>
+        <v>7.48124742507935</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874814987183</v>
+        <v>7.90874671936035</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.1403112411499</v>
+        <v>8.14031028747559</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343521118164</v>
+        <v>9.17343616485596</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>9.97499656677246</v>
+        <v>9.97499752044678</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890434265137</v>
+        <v>9.12890338897705</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702972412109</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437252044678</v>
+        <v>9.08437347412109</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718444824219</v>
+        <v>8.81718349456787</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937362670898</v>
+        <v>8.79937267303467</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G644" t="n">
-        <v>8.62124824523926</v>
+        <v>8.62124729156494</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624809265137</v>
+        <v>8.90624713897705</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702972412109</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453102111816</v>
+        <v>11.8453092575073</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671848297119</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562475204468</v>
+        <v>11.7562456130981</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671848297119</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.8594512939453</v>
+        <v>11.859450340271</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363958358765</v>
+        <v>10.7363967895508</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.410228729248</v>
+        <v>11.4102296829224</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.8145275115967</v>
+        <v>11.8145294189453</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535938262939</v>
+        <v>12.3535947799683</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868036270142</v>
+        <v>13.3868045806885</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>14.3301696777344</v>
+        <v>14.3301706314087</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719760894775</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.834098815918</v>
+        <v>17.8341007232666</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.834098815918</v>
+        <v>17.8341007232666</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239444732666</v>
+        <v>17.9239406585693</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>17.5645656585693</v>
+        <v>17.5645637512207</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227544784546</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>17.5645656585693</v>
+        <v>17.5645637512207</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5645656585693</v>
+        <v>17.5645637512207</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153430938721</v>
+        <v>17.1153411865234</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922895431519</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372142791748</v>
+        <v>16.0372104644775</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372142791748</v>
+        <v>16.0372104644775</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719760894775</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864349365234</v>
+        <v>16.4864330291748</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661224365234</v>
+        <v>16.6661205291748</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387701034546</v>
+        <v>15.138768196106</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.3184566497803</v>
+        <v>15.318455696106</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040035247803</v>
+        <v>15.004002571106</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864349365234</v>
+        <v>16.4864330291748</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922895431519</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719760894775</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227544784546</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.75</v>
       </c>
       <c r="G782" t="n">
-        <v>15.9473676681519</v>
+        <v>15.9473657608032</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922895431519</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227544784546</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227544784546</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126020431519</v>
+        <v>15.8126010894775</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922895431519</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024448394775</v>
+        <v>15.9024467468262</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227544784546</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.3184566497803</v>
+        <v>15.318455696106</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286128997803</v>
+        <v>15.2286138534546</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879917144775</v>
+        <v>15.5879898071289</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141578674316</v>
+        <v>14.914158821106</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387701034546</v>
+        <v>15.138768196106</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>13.5215702056885</v>
+        <v>13.5215711593628</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.554780960083</v>
+        <v>14.5547819137573</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.5997037887573</v>
+        <v>14.599702835083</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504802703857</v>
+        <v>14.1504812240601</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055593490601</v>
+        <v>14.1055583953857</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461814880371</v>
+        <v>13.7461824417114</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477373123169</v>
+        <v>12.8477382659912</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129716873169</v>
+        <v>12.7129707336426</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680507659912</v>
+        <v>12.6680498123169</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>12.5</v>
       </c>
       <c r="G836" t="n">
-        <v>11.2305402755737</v>
+        <v>11.230541229248</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.2305402755737</v>
+        <v>11.230541229248</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578935623169</v>
+        <v>12.7578945159912</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172714233398</v>
+        <v>13.1172723770142</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723485946655</v>
+        <v>13.0723495483398</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969608306885</v>
+        <v>13.2969598770142</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911033630371</v>
+        <v>13.7911043167114</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766609191895</v>
+        <v>15.7766618728638</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>16.118070602417</v>
+        <v>16.1180725097656</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563522338867</v>
+        <v>15.9563503265381</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407255172729</v>
+        <v>15.7407245635986</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250997543335</v>
+        <v>15.5250988006592</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454103469849</v>
+        <v>15.3454113006592</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602523803711</v>
+        <v>14.8602514266968</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368127822876</v>
+        <v>14.5368118286133</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.7344694137573</v>
+        <v>14.734468460083</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135290145874</v>
+        <v>14.8135280609131</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G891" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501482009888</v>
+        <v>14.8501491546631</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>14</v>
       </c>
       <c r="G906" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824361801147</v>
+        <v>12.9824371337891</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345291137695</v>
+        <v>12.6345300674438</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908824920654</v>
+        <v>12.8908815383911</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429744720459</v>
+        <v>12.5429735183716</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711521148682</v>
+        <v>12.6711511611938</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>13.0190591812134</v>
+        <v>13.0190582275391</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14</v>
       </c>
       <c r="G922" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>14</v>
       </c>
       <c r="G924" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894626617432</v>
+        <v>12.6894617080688</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359508514404</v>
+        <v>12.8359489440918</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739917755127</v>
+        <v>13.0739908218384</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>14</v>
       </c>
       <c r="G934" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923013687134</v>
+        <v>13.092303276062</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>13.1106128692627</v>
+        <v>13.110613822937</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923013687134</v>
+        <v>13.092303276062</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402839660645</v>
+        <v>14.7402849197388</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501482009888</v>
+        <v>14.8501491546631</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613605499268</v>
+        <v>13.8613615036011</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346046447754</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951419830322</v>
+        <v>13.4951429367065</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303451538086</v>
+        <v>13.3303442001343</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>13.7331838607788</v>
+        <v>13.7331848144531</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796701431274</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>15</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7331838607788</v>
+        <v>13.7331848144531</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G996" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726455688477</v>
+        <v>14.1726446151733</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613605499268</v>
+        <v>13.8613615036011</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796701431274</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.081090927124</v>
+        <v>14.0810918807983</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6670417785645</v>
+        <v>14.6670408248901</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726455688477</v>
+        <v>14.1726446151733</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726455688477</v>
+        <v>14.1726446151733</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1056" t="n">
-        <v>14.6304178237915</v>
+        <v>14.6304187774658</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>14.2458896636963</v>
+        <v>14.2458906173706</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>15.051570892334</v>
+        <v>15.0515699386597</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473840713501</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>17</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.5642757415771</v>
+        <v>15.5642738342285</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.5642757415771</v>
+        <v>15.5642738342285</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699550628662</v>
+        <v>16.3699531555176</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -52112,6 +52112,32 @@
         <v>1.9099999666214</v>
       </c>
       <c r="H1990" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1991" t="n">
+        <v>13005</v>
+      </c>
+      <c r="C1991" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G1991" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="H1991" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108253479004</v>
+        <v>2.88108205795288</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248680114746</v>
+        <v>2.90248703956604</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441948890686</v>
+        <v>2.83441925048828</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.37949991226196</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8934965133667</v>
+        <v>2.89349675178528</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974412918091</v>
+        <v>2.79974389076233</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255313873291</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601166725159</v>
+        <v>2.81601142883301</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549625396729</v>
+        <v>2.76549649238586</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035904884338</v>
+        <v>2.76035952568054</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368394851685</v>
+        <v>2.85368371009827</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661429405212</v>
+        <v>2.91661381721497</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255313873291</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379132270813</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379132270813</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379132270813</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904891014099</v>
+        <v>3.03904914855957</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256887435913</v>
+        <v>3.34256911277771</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787263870239</v>
+        <v>3.19787216186523</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345844268799</v>
+        <v>3.31345820426941</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768520355225</v>
+        <v>3.2376856803894</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309681892395</v>
+        <v>3.25309705734253</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071577072144</v>
+        <v>3.21071553230286</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36482977867126</v>
+        <v>3.36483001708984</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.40763926506042</v>
+        <v>3.407639503479</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873666763306</v>
+        <v>3.44873642921448</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630334854126</v>
+        <v>3.96630382537842</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293346405029</v>
+        <v>4.04293298721313</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533586502075</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028539657593</v>
+        <v>4.24028491973877</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087944030762</v>
+        <v>4.09087896347046</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0669059753418</v>
+        <v>4.06690692901611</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128771781921</v>
+        <v>3.98128724098206</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279244422913</v>
+        <v>3.91279220581055</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553440093994</v>
+        <v>4.01553535461426</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0082573890686</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041115760803</v>
+        <v>3.87041091918945</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330714225769</v>
+        <v>3.96330761909485</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533586502075</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834436416626</v>
+        <v>4.05834341049194</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533586502075</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533586502075</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245861053467</v>
+        <v>4.21245813369751</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533586502075</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076482772827</v>
+        <v>7.02076435089111</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828893661499</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671644210815</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919328689575</v>
+        <v>7.14919424057007</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671644210815</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828893661499</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143154144287</v>
+        <v>6.42143106460571</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862110137939</v>
+        <v>6.37862205505371</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G220" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G221" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G244" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>6.16457319259644</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209825515747</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209825515747</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490678787231</v>
+        <v>5.864905834198</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209825515747</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995500564575</v>
+        <v>5.17995452880859</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904922485352</v>
+        <v>4.70904970169067</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904922485352</v>
+        <v>4.70904970169067</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383113861084</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750587463379</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874453544617</v>
+        <v>3.69874477386475</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051532745361</v>
+        <v>3.39051580429077</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242022514343</v>
+        <v>2.96241998672485</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432512283325</v>
+        <v>2.53432488441467</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158173561096</v>
+        <v>2.43158149719238</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971593856812</v>
+        <v>4.10971641540527</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533586502075</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723957061768</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299217224121</v>
+        <v>3.73299241065979</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038241386414</v>
+        <v>3.51038217544556</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743953704834</v>
+        <v>3.58743929862976</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593481063843</v>
+        <v>3.65593457221985</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881063461304</v>
+        <v>3.63881087303162</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750587463379</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620135307312</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620135307312</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861090660095</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723957061768</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861090660095</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.8100483417511</v>
+        <v>3.81004929542542</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.8785445690155</v>
+        <v>3.87854480743408</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329710006714</v>
+        <v>4.74329662322998</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.4008207321167</v>
+        <v>4.40081977844238</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383113861084</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239227294922</v>
+        <v>4.2723913192749</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055347442627</v>
+        <v>4.64055442810059</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838251113892</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577394485474</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303079605103</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838251113892</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015449523926</v>
+        <v>5.00015497207642</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015449523926</v>
+        <v>5.00015497207642</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20564031600952</v>
+        <v>5.20563983917236</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.0686502456665</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577394485474</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.0686502456665</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303079605103</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.0686502456665</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.0515251159668</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577394485474</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988771438599</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988771438599</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.2024359703064</v>
+        <v>5.20243549346924</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023851394653</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543846130371</v>
+        <v>5.11543893814087</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0980396270752</v>
+        <v>5.09803915023804</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763687133789</v>
+        <v>5.16763782501221</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.83704662322998</v>
+        <v>4.8370475769043</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.7674503326416</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.7674503326416</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165870666504</v>
+        <v>4.47165822982788</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286649703979</v>
+        <v>4.26286602020264</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286649703979</v>
+        <v>4.26286602020264</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.1410698890686</v>
+        <v>4.14107036590576</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497020721436</v>
+        <v>4.11497068405151</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286649703979</v>
+        <v>4.26286602020264</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506395339966</v>
+        <v>4.31506443023682</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.30636405944824</v>
+        <v>4.3063645362854</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43686056137085</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G514" t="n">
-        <v>4.54125642776489</v>
+        <v>4.54125690460205</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165870666504</v>
+        <v>4.47165822982788</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43686056137085</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525096893311</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825489044189</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.7674503326416</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825489044189</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525096893311</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43686056137085</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G559" t="n">
-        <v>4.54125642776489</v>
+        <v>4.54125690460205</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.7674503326416</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203416824341</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023851394653</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203416824341</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>5.68962049484253</v>
+        <v>5.68962097167969</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68962049484253</v>
+        <v>5.68962097167969</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.5678243637085</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082733154297</v>
+        <v>5.48082685470581</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.5678243637085</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.7766170501709</v>
+        <v>5.77661752700806</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.9680118560791</v>
+        <v>5.96801233291626</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437356948853</v>
+        <v>6.23437309265137</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031042098999</v>
+        <v>7.00031089782715</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562322616577</v>
+        <v>6.87562370300293</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>7.08937311172485</v>
+        <v>7.0893726348877</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968402862549</v>
+        <v>7.81968450546265</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249599456787</v>
+        <v>9.26249694824219</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249599456787</v>
+        <v>9.26249694824219</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437347412109</v>
+        <v>9.08437252044678</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718349456787</v>
+        <v>8.81718444824219</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062232971191</v>
+        <v>9.4406213760376</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671848297119</v>
+        <v>11.6671838760376</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335903167725</v>
+        <v>11.5335893630981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562456130981</v>
+        <v>11.7562465667725</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671848297119</v>
+        <v>11.6671838760376</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.4102296829224</v>
+        <v>11.410228729248</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.8341007232666</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.8341007232666</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227544784546</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051887512207</v>
+        <v>17.2051868438721</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>18.25</v>
       </c>
       <c r="G753" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356555938721</v>
+        <v>16.9356575012207</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>18.25</v>
       </c>
       <c r="G760" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415111541748</v>
+        <v>16.4415130615234</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.318455696106</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.004002571106</v>
+        <v>15.0040035247803</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532251358032</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>18.25</v>
       </c>
       <c r="G773" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227544784546</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.75</v>
       </c>
       <c r="G782" t="n">
-        <v>15.9473657608032</v>
+        <v>15.9473676681519</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227544784546</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227544784546</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981470108032</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981470108032</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126010894775</v>
+        <v>15.8126020431519</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>15.3633794784546</v>
+        <v>15.3633804321289</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024467468262</v>
+        <v>15.9024457931519</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981470108032</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227544784546</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.318455696106</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532251358032</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>14.689546585083</v>
+        <v>14.6895475387573</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098581314087</v>
+        <v>14.5098571777344</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129707336426</v>
+        <v>12.7129716873169</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172723770142</v>
+        <v>13.1172714233398</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664939880371</v>
+        <v>13.5664930343628</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>13.6563367843628</v>
+        <v>13.6563358306885</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012596130371</v>
+        <v>13.7012605667114</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532251358032</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532251358032</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>15.3633794784546</v>
+        <v>15.3633804321289</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766618728638</v>
+        <v>15.7766628265381</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407245635986</v>
+        <v>15.7407264709473</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250988006592</v>
+        <v>15.5250997543335</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602514266968</v>
+        <v>14.8602504730225</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>15.0149478912354</v>
+        <v>15.014946937561</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G903" t="n">
-        <v>14.6121082305908</v>
+        <v>14.6121072769165</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824371337891</v>
+        <v>12.9824361801147</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345300674438</v>
+        <v>12.6345291137695</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G912" t="n">
-        <v>12.6528396606445</v>
+        <v>12.6528406143188</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429735183716</v>
+        <v>12.5429744720459</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>13.0190582275391</v>
+        <v>13.0190591812134</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G920" t="n">
-        <v>13.3852767944336</v>
+        <v>13.3852758407593</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514207839966</v>
+        <v>12.4514217376709</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359489440918</v>
+        <v>12.8359498977661</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739908218384</v>
+        <v>13.0739917755127</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.092303276062</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>13.110613822937</v>
+        <v>13.1106128692627</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.092303276062</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346046447754</v>
+        <v>13.9346055984497</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951429367065</v>
+        <v>13.4951419830322</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>14.0994024276733</v>
+        <v>14.099401473999</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796701431274</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G981" t="n">
-        <v>14.2092685699463</v>
+        <v>14.209267616272</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G985" t="n">
-        <v>14.154335975647</v>
+        <v>14.1543350219727</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G989" t="n">
-        <v>14.2092685699463</v>
+        <v>14.209267616272</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>14.0994024276733</v>
+        <v>14.099401473999</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514963150024</v>
+        <v>13.7514953613281</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712266921997</v>
+        <v>13.9712257385254</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796701431274</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.9417037963867</v>
+        <v>14.941704750061</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909580230713</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0994024276733</v>
+        <v>14.099401473999</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909580230713</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909580230713</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1058" t="n">
-        <v>14.6121082305908</v>
+        <v>14.6121072769165</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1084" t="n">
-        <v>15.0149478912354</v>
+        <v>15.014946937561</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>15.0149478912354</v>
+        <v>15.014946937561</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.161434173584</v>
+        <v>15.1614351272583</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>15.0515699386597</v>
+        <v>15.051570892334</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4361000061035</v>
+        <v>15.4360990524292</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1094" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825862884521</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473840713501</v>
+        <v>15.7473850250244</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825862884521</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>17</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.5642738342285</v>
+        <v>15.5642757415771</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8023176193237</v>
+        <v>15.802318572998</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.5642738342285</v>
+        <v>15.5642757415771</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572492599487</v>
+        <v>15.8572483062744</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290735244751</v>
+        <v>15.7290725708008</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319141387939</v>
+        <v>16.1319122314453</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -52138,6 +52138,32 @@
         <v>1.94000005722046</v>
       </c>
       <c r="H1991" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1992" t="n">
+        <v>5355</v>
+      </c>
+      <c r="C1992" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="G1992" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="H1992" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441925048828</v>
+        <v>2.83441948890686</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863395690918</v>
+        <v>2.8986337184906</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601142883301</v>
+        <v>2.81601119041443</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.84426593780518</v>
+        <v>2.8442656993866</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542943954468</v>
+        <v>2.82542967796326</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035952568054</v>
+        <v>2.76035928726196</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399152755737</v>
+        <v>2.83399128913879</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368371009827</v>
+        <v>2.85368394851685</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661381721497</v>
+        <v>2.91661405563354</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823916435242</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904914855957</v>
+        <v>3.03904938697815</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256911277771</v>
+        <v>3.34256863594055</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787216186523</v>
+        <v>3.19787263870239</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489659309387</v>
+        <v>3.30489635467529</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626792907715</v>
+        <v>3.35626816749573</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.2376856803894</v>
+        <v>3.23768544197083</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483001708984</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873642921448</v>
+        <v>3.44873666763306</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757316589355</v>
+        <v>3.4675726890564</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518578529358</v>
+        <v>3.81518626213074</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630382537842</v>
+        <v>3.96630430221558</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028491973877</v>
+        <v>4.24028539657593</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087896347046</v>
+        <v>4.09087991714478</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.06690692901611</v>
+        <v>4.06690645217896</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128724098206</v>
+        <v>3.98128771781921</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553535461426</v>
+        <v>4.0155348777771</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566779136658</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.00825786590576</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041091918945</v>
+        <v>3.87041044235229</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566779136658</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493272781372</v>
+        <v>3.9149329662323</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834341049194</v>
+        <v>4.05834484100342</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245813369751</v>
+        <v>4.21245861053467</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938234329224</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938234329224</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938234329224</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376384735107</v>
+        <v>4.32376337051392</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.60804986953735</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424007415771</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>6.67828893661499</v>
+        <v>6.67828845977783</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233541488647</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514537811279</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233541488647</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266948699951</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919424057007</v>
+        <v>7.14919328689575</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638427734375</v>
+        <v>7.10638332366943</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638427734375</v>
+        <v>7.10638332366943</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514537811279</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233541488647</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.67828893661499</v>
+        <v>6.67828845977783</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266948699951</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862205505371</v>
+        <v>6.37862157821655</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424007415771</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019359588623</v>
+        <v>6.25019311904907</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300260543823</v>
+        <v>6.29300308227539</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019359588623</v>
+        <v>6.25019311904907</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.60804986953735</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.864905834198</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.60804986953735</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.60804986953735</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.60804986953735</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995452880859</v>
+        <v>5.17995405197144</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383113861084</v>
+        <v>4.26383066177368</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750587463379</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874477386475</v>
+        <v>3.69874429702759</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051556587219</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857252120972</v>
+        <v>2.56857228279114</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158149719238</v>
+        <v>2.43158173561096</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971641540527</v>
+        <v>4.10971593856812</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710618019104</v>
+        <v>3.88710641860962</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723957061768</v>
+        <v>3.76723980903625</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299241065979</v>
+        <v>3.73299217224121</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743929862976</v>
+        <v>3.58743953704834</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476344108582</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593457221985</v>
+        <v>3.65593528747559</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881087303162</v>
+        <v>3.63881134986877</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894426345825</v>
+        <v>3.51894402503967</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750587463379</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757316589355</v>
+        <v>3.4675726890564</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.41620135307312</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.41620135307312</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476344108582</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757316589355</v>
+        <v>3.4675726890564</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723957061768</v>
+        <v>3.76723980903625</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004929542542</v>
+        <v>3.81004905700684</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854480743408</v>
+        <v>3.87854433059692</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285878181458</v>
+        <v>3.852858543396</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356340408325</v>
+        <v>4.50356388092041</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40081977844238</v>
+        <v>4.40082120895386</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383113861084</v>
+        <v>4.26383066177368</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.2723913192749</v>
+        <v>4.27239227294922</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577394485474</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015497207642</v>
+        <v>5.0001540184021</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015497207642</v>
+        <v>5.0001540184021</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577394485474</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550668716431</v>
+        <v>5.32550621032715</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413463592529</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577394485474</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988723754883</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413463592529</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988723754883</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.20243549346924</v>
+        <v>5.2024359703064</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763782501221</v>
+        <v>5.16763734817505</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08063936233521</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08063936233521</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.13283777236938</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.13283777236938</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005054473877</v>
+        <v>4.75005006790161</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165822982788</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.34986257553101</v>
+        <v>4.34986305236816</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896474838257</v>
+        <v>4.28896522521973</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416564941406</v>
+        <v>4.25416612625122</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5</v>
       </c>
       <c r="G498" t="n">
-        <v>4.34986257553101</v>
+        <v>4.34986305236816</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.14107036590576</v>
+        <v>4.1410698890686</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456840515137</v>
+        <v>4.18456888198853</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.43686056137085</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165822982788</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>4.43686056137085</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825489044189</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825489044189</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>4.43686056137085</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08063936233521</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.13283777236938</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.13283777236938</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203369140625</v>
+        <v>5.27203321456909</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.13283777236938</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203369140625</v>
+        <v>5.27203321456909</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.41122961044312</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.41122961044312</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>5.81141710281372</v>
+        <v>5.81141662597656</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661752700806</v>
+        <v>5.77661800384521</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>5.81141710281372</v>
+        <v>5.81141662597656</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437261581421</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.5015606880188</v>
+        <v>6.50156116485596</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G625" t="n">
-        <v>6.89343500137329</v>
+        <v>6.89343547821045</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562370300293</v>
+        <v>6.87562322616577</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>7.0893726348877</v>
+        <v>7.08937311172485</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.48124742507935</v>
+        <v>7.4812479019165</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874671936035</v>
+        <v>7.90874767303467</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968450546265</v>
+        <v>7.81968545913696</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.14031028747559</v>
+        <v>8.14030933380127</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343616485596</v>
+        <v>9.17343521118164</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>9.97499752044678</v>
+        <v>9.97499656677246</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890338897705</v>
+        <v>9.12890434265137</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437252044678</v>
+        <v>9.08437061309814</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718444824219</v>
+        <v>8.8171854019165</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G643" t="n">
-        <v>8.69249820709229</v>
+        <v>8.69249725341797</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624713897705</v>
+        <v>8.90624809265137</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.4406213760376</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046569824219</v>
+        <v>9.93046474456787</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453092575073</v>
+        <v>11.845308303833</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.859450340271</v>
+        <v>11.8594512939453</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.455150604248</v>
+        <v>11.4551515579224</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.8145294189453</v>
+        <v>11.814528465271</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868045806885</v>
+        <v>13.3868036270142</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>14.3301706314087</v>
+        <v>14.3301696777344</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719760894775</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501125335693</v>
+        <v>17.2501106262207</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180870056152</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239406585693</v>
+        <v>17.923942565918</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.7442531585693</v>
+        <v>17.744255065918</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>17.3848781585693</v>
+        <v>17.3848762512207</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>17.3848781585693</v>
+        <v>17.3848762512207</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501125335693</v>
+        <v>17.2501106262207</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153411865234</v>
+        <v>17.1153430938721</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372104644775</v>
+        <v>16.0372123718262</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372104644775</v>
+        <v>16.0372123718262</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719760894775</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864330291748</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040035247803</v>
+        <v>15.004002571106</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864330291748</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719760894775</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270580291748</v>
+        <v>16.1270561218262</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981470108032</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981470108032</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981470108032</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879898071289</v>
+        <v>15.5879907608032</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.914158821106</v>
+        <v>14.9141578674316</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200124740601</v>
+        <v>14.4200134277344</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129716873169</v>
+        <v>12.7129726409912</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332832336426</v>
+        <v>12.5332822799683</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578945159912</v>
+        <v>12.7578935623169</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>13.6563358306885</v>
+        <v>13.6563367843628</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.2196283340454</v>
+        <v>15.219630241394</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657209396362</v>
+        <v>15.1657228469849</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407264709473</v>
+        <v>15.7407274246216</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602504730225</v>
+        <v>14.8602514266968</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.734468460083</v>
+        <v>14.7344694137573</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G879" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -52164,6 +52164,32 @@
         <v>1.93499994277954</v>
       </c>
       <c r="H1992" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1993" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C1993" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="G1993" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="H1993" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -629,7 +629,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762400627136</v>
+        <v>2.90762424468994</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392518997192</v>
+        <v>2.89392471313477</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8986337184906</v>
+        <v>2.89863395690918</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601119041443</v>
+        <v>2.81601142883301</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549649238586</v>
+        <v>2.76549601554871</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.8442656993866</v>
+        <v>2.84426593780518</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035928726196</v>
+        <v>2.76035904884338</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399128913879</v>
+        <v>2.83399176597595</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368394851685</v>
+        <v>2.85368347167969</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256863594055</v>
+        <v>3.34256911277771</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345820426941</v>
+        <v>3.31345844268799</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309705734253</v>
+        <v>3.25309681892395</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071553230286</v>
+        <v>3.21071529388428</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873666763306</v>
+        <v>3.44873642921448</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630430221558</v>
+        <v>3.96630382537842</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087991714478</v>
+        <v>4.09088039398193</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.06690645217896</v>
+        <v>4.0669059753418</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128771781921</v>
+        <v>3.98128724098206</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409696578979</v>
+        <v>4.02409648895264</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847823143005</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847823143005</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279220581055</v>
+        <v>3.91279172897339</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407632827759</v>
+        <v>3.91407561302185</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.0155348777771</v>
+        <v>4.01553535461426</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.9564573764801</v>
+        <v>3.95645761489868</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566779136658</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825786590576</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041044235229</v>
+        <v>3.87041068077087</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330761909485</v>
+        <v>3.96330738067627</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566779136658</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.9149329662323</v>
+        <v>3.91493248939514</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.67749977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>4.00483226776123</v>
+        <v>4.00483179092407</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834484100342</v>
+        <v>4.0583438873291</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376337051392</v>
+        <v>4.32376384735107</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424007415771</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076435089111</v>
+        <v>7.02076482772827</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828798294067</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671691894531</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233541488647</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514537811279</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233541488647</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638332366943</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638332366943</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514537811279</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233541488647</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671691894531</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828798294067</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143106460571</v>
+        <v>6.42143058776855</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424007415771</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300308227539</v>
+        <v>6.29300260543823</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995405197144</v>
+        <v>5.17995452880859</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874429702759</v>
+        <v>3.69874453544617</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051556587219</v>
+        <v>3.39051580429077</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96241998672485</v>
+        <v>2.96242022514343</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560145378113</v>
+        <v>3.95560121536255</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710641860962</v>
+        <v>3.88710594177246</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299217224121</v>
+        <v>3.73299169540405</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038217544556</v>
+        <v>3.51038241386414</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743953704834</v>
+        <v>3.58743977546692</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593528747559</v>
+        <v>3.65593433380127</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881134986877</v>
+        <v>3.63881063461304</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894402503967</v>
+        <v>3.51894474029541</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620111465454</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620111465454</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449666023254</v>
+        <v>3.66449689865112</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004905700684</v>
+        <v>3.81004858016968</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.852858543396</v>
+        <v>3.85285830497742</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329662322998</v>
+        <v>4.7432975769043</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G375" t="n">
-        <v>4.46931600570679</v>
+        <v>4.46931552886963</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082120895386</v>
+        <v>4.4008207321167</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239227294922</v>
+        <v>4.27239179611206</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055442810059</v>
+        <v>4.64055395126343</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139291763306</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.0001540184021</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.0001540184021</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028717041016</v>
+        <v>4.88028764724731</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139291763306</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139291763306</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550621032715</v>
+        <v>5.32550716400146</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139291763306</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988771438599</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988771438599</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139291763306</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.2024359703064</v>
+        <v>5.20243644714355</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943252563477</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943252563477</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023708343506</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543893814087</v>
+        <v>5.11543941497803</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803915023804</v>
+        <v>5.09803867340088</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763734817505</v>
+        <v>5.16763687133789</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>4.95884323120117</v>
+        <v>4.95884370803833</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>5.04584121704102</v>
+        <v>5.04584074020386</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>4.95884323120117</v>
+        <v>4.95884370803833</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265027999878</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005006790161</v>
+        <v>4.75005102157593</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265027999878</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425939559937</v>
+        <v>4.45425891876221</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896522521973</v>
+        <v>4.28896474838257</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887147903442</v>
+        <v>4.08887100219727</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716861724854</v>
+        <v>4.16716814041138</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416612625122</v>
+        <v>4.25416564941406</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497068405151</v>
+        <v>4.11497020721436</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506443023682</v>
+        <v>4.3150634765625</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456888198853</v>
+        <v>4.18456840515137</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G514" t="n">
-        <v>4.54125690460205</v>
+        <v>4.54125642776489</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385663986206</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G559" t="n">
-        <v>4.54125690460205</v>
+        <v>4.54125642776489</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.87184619903564</v>
+        <v>4.8718466758728</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.95884323120117</v>
+        <v>4.95884370803833</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943252563477</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943252563477</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203321456909</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023708343506</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203321456909</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.63742256164551</v>
+        <v>5.63742208480835</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.56782388687134</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082685470581</v>
+        <v>5.48082828521729</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.56782388687134</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661800384521</v>
+        <v>5.7766170501709</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881641387939</v>
+        <v>5.82881593704224</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801233291626</v>
+        <v>5.9680118560791</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>6.30562305450439</v>
+        <v>6.30562257766724</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437261581421</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031089782715</v>
+        <v>7.00031042098999</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468544006348</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562322616577</v>
+        <v>6.87562274932861</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874767303467</v>
+        <v>7.90874862670898</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968545913696</v>
+        <v>7.8196849822998</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.14030933380127</v>
+        <v>8.14031028747559</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.47874736785889</v>
+        <v>8.4787483215332</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>9.97499656677246</v>
+        <v>9.97499847412109</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249694824219</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249694824219</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890434265137</v>
+        <v>9.12890338897705</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437061309814</v>
+        <v>9.08437252044678</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937267303467</v>
+        <v>8.79937171936035</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G643" t="n">
-        <v>8.69249725341797</v>
+        <v>8.69249820709229</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046474456787</v>
+        <v>9.93046569824219</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093717575073</v>
+        <v>10.5093727111816</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781202316284</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781202316284</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781202316284</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335893630981</v>
+        <v>11.5335903167725</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.4551515579224</v>
+        <v>11.455150604248</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363967895508</v>
+        <v>10.7363958358765</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.410228729248</v>
+        <v>11.4102296829224</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.7696075439453</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.7696075439453</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868036270142</v>
+        <v>13.3868045806885</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.8340969085693</v>
+        <v>17.8341007232666</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.8340969085693</v>
+        <v>17.8341007232666</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.744255065918</v>
+        <v>17.7442531585693</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>17.7891750335693</v>
+        <v>17.789176940918</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051868438721</v>
+        <v>17.2051887512207</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356575012207</v>
+        <v>16.9356555938721</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661205291748</v>
+        <v>16.6661224365234</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415130615234</v>
+        <v>16.4415111541748</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.138768196106</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.3184566497803</v>
+        <v>15.318455696106</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>17</v>
       </c>
       <c r="G769" t="n">
-        <v>15.2735357284546</v>
+        <v>15.2735366821289</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676792144775</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.75</v>
       </c>
       <c r="G782" t="n">
-        <v>15.9473676681519</v>
+        <v>15.9473657608032</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126020431519</v>
+        <v>15.8126010894775</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676792144775</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676792144775</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>15.3633804321289</v>
+        <v>15.3633794784546</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.3184566497803</v>
+        <v>15.318455696106</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879907608032</v>
+        <v>15.5879898071289</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.138768196106</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.1836910247803</v>
+        <v>15.1836891174316</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098571777344</v>
+        <v>14.5098581314087</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.5547819137573</v>
+        <v>14.554780960083</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504812240601</v>
+        <v>14.1504802703857</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200134277344</v>
+        <v>14.4200124740601</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461824417114</v>
+        <v>13.7461814880371</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129726409912</v>
+        <v>12.7129716873169</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680498123169</v>
+        <v>12.6680507659912</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>12.5</v>
       </c>
       <c r="G836" t="n">
-        <v>11.230541229248</v>
+        <v>11.2305402755737</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.230541229248</v>
+        <v>11.2305402755737</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332822799683</v>
+        <v>12.5332832336426</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>13.3418827056885</v>
+        <v>13.3418817520142</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>13.6563367843628</v>
+        <v>13.6563377380371</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012605667114</v>
+        <v>13.7012586593628</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.2735357284546</v>
+        <v>15.2735366821289</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.219630241394</v>
+        <v>15.2196292877197</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.399317741394</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657228469849</v>
+        <v>15.1657199859619</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>15.3633804321289</v>
+        <v>15.3633794784546</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766628265381</v>
+        <v>15.7766618728638</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>16.1180725097656</v>
+        <v>16.118070602417</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563503265381</v>
+        <v>15.956353187561</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407274246216</v>
+        <v>15.7407264709473</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250997543335</v>
+        <v>15.5250988006592</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602514266968</v>
+        <v>14.8602523803711</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>14.644624710083</v>
+        <v>14.6446237564087</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9500951766968</v>
+        <v>14.9500961303711</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368118286133</v>
+        <v>14.5368127822876</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G874" t="n">
-        <v>14.6086874008179</v>
+        <v>14.6086864471436</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>14.644624710083</v>
+        <v>14.6446237564087</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.7344694137573</v>
+        <v>14.734468460083</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G880" t="n">
-        <v>14.3923778533936</v>
+        <v>14.3923768997192</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>14.8318395614624</v>
+        <v>14.8318386077881</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G896" t="n">
-        <v>14.996636390686</v>
+        <v>14.9966373443604</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G900" t="n">
-        <v>14.996636390686</v>
+        <v>14.9966373443604</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G905" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908815383911</v>
+        <v>12.8908824920654</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G912" t="n">
-        <v>12.6528406143188</v>
+        <v>12.6528396606445</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429744720459</v>
+        <v>12.5429754257202</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G919" t="n">
-        <v>12.7443952560425</v>
+        <v>12.7443943023682</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G920" t="n">
-        <v>13.3852758407593</v>
+        <v>13.3852767944336</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G930" t="n">
-        <v>13.0373687744141</v>
+        <v>13.0373697280884</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739917755127</v>
+        <v>13.0739908218384</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G933" t="n">
-        <v>12.7443952560425</v>
+        <v>12.7443943023682</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G938" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>13.8979825973511</v>
+        <v>13.8979816436768</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G949" t="n">
-        <v>14.227578163147</v>
+        <v>14.2275791168213</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346046447754</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951419830322</v>
+        <v>13.4951429367065</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G960" t="n">
-        <v>13.5134534835815</v>
+        <v>13.5134544372559</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G965" t="n">
-        <v>13.6782512664795</v>
+        <v>13.6782503128052</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G969" t="n">
-        <v>13.7148723602295</v>
+        <v>13.7148733139038</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599407196045</v>
+        <v>13.6599397659302</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G971" t="n">
-        <v>13.7148723602295</v>
+        <v>13.7148733139038</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G974" t="n">
-        <v>14.227578163147</v>
+        <v>14.2275791168213</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G976" t="n">
-        <v>13.8979825973511</v>
+        <v>13.8979816436768</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>13.9162931442261</v>
+        <v>13.9162921905518</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G981" t="n">
-        <v>14.209267616272</v>
+        <v>14.2092685699463</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G989" t="n">
-        <v>14.209267616272</v>
+        <v>14.2092685699463</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726455688477</v>
+        <v>14.172646522522</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.8979825973511</v>
+        <v>13.8979816436768</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6670408248901</v>
+        <v>14.6670417785645</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1011" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726455688477</v>
+        <v>14.172646522522</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1017" t="n">
-        <v>13.9162931442261</v>
+        <v>13.9162921905518</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1026" t="n">
-        <v>14.4106874465942</v>
+        <v>14.4106884002686</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.8318395614624</v>
+        <v>14.8318386077881</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726455688477</v>
+        <v>14.172646522522</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1057" t="n">
-        <v>14.7036619186401</v>
+        <v>14.7036628723145</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1064" t="n">
-        <v>14.5022430419922</v>
+        <v>14.5022420883179</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1065" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>14.2458906173706</v>
+        <v>14.2458896636963</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1084" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="n">
-        <v>15.0698804855347</v>
+        <v>15.0698795318604</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.960015296936</v>
+        <v>14.9600162506104</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4360990524292</v>
+        <v>15.4361000061035</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473859786987</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1101" t="n">
-        <v>15.6375188827515</v>
+        <v>15.6375179290771</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>16.2600898742676</v>
+        <v>16.2600917816162</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319122314453</v>
+        <v>16.1319141387939</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699531555176</v>
+        <v>16.3699550628662</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309246063232</v>
+        <v>17.7309226989746</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641819000244</v>
+        <v>16.9641799926758</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683395385742</v>
+        <v>16.8683376312256</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -52190,6 +52190,32 @@
         <v>1.98500001430511</v>
       </c>
       <c r="H1993" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1994" t="n">
+        <v>8872</v>
+      </c>
+      <c r="C1994" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1994" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -629,7 +629,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762376785278</v>
+        <v>2.90762400627136</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863395690918</v>
+        <v>2.8986337184906</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974365234375</v>
+        <v>2.79974389076233</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255313873291</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549625396729</v>
+        <v>2.76549649238586</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.8442656993866</v>
+        <v>2.84426617622375</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035904884338</v>
+        <v>2.76035928726196</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399152755737</v>
+        <v>2.83399176597595</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255313873291</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779819488525</v>
+        <v>3.00779867172241</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256935119629</v>
+        <v>3.34256887435913</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787287712097</v>
+        <v>3.19787263870239</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768544197083</v>
+        <v>3.2376856803894</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36482954025269</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873666763306</v>
+        <v>3.44873642921448</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098504066467</v>
+        <v>3.61098456382751</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518650054932</v>
+        <v>3.81518602371216</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630430221558</v>
+        <v>3.96630382537842</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293346405029</v>
+        <v>4.04293298721313</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028491973877</v>
+        <v>4.24028539657593</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087944030762</v>
+        <v>4.09087991714478</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128771781921</v>
+        <v>3.9812867641449</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.93847751617432</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.93847751617432</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279196739197</v>
+        <v>3.91279172897339</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407632827759</v>
+        <v>3.91407608985901</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.0155348777771</v>
+        <v>4.01553440093994</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.95645785331726</v>
+        <v>3.95645761489868</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566874504089</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0082573890686</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330761909485</v>
+        <v>3.96330738067627</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566874504089</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.0583438873291</v>
+        <v>4.05834436416626</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657381057739</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245908737183</v>
+        <v>4.21245813369751</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638332366943</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638332366943</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54985904693604</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862205505371</v>
+        <v>6.37862157821655</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019359588623</v>
+        <v>6.25019264221191</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019359588623</v>
+        <v>6.25019264221191</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176370620728</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895565032959</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995452880859</v>
+        <v>5.17995500564575</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874429702759</v>
+        <v>3.69874477386475</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432464599609</v>
+        <v>2.53432488441467</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158197402954</v>
+        <v>2.43158173561096</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>3.23640155792236</v>
+        <v>3.23640131950378</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560145378113</v>
+        <v>3.95560121536255</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710594177246</v>
+        <v>3.88710641860962</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723980903625</v>
+        <v>3.76724004745483</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743953704834</v>
+        <v>3.5874400138855</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593481063843</v>
+        <v>3.65593528747559</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881063461304</v>
+        <v>3.63881087303162</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449689865112</v>
+        <v>3.66449666023254</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861066818237</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723980903625</v>
+        <v>3.76724004745483</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861066818237</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.8785445690155</v>
+        <v>3.87854480743408</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.852858543396</v>
+        <v>3.85285878181458</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082120895386</v>
+        <v>4.4008207321167</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657381057739</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239227294922</v>
+        <v>4.2723913192749</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838251113892</v>
+        <v>5.30838203430176</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838251113892</v>
+        <v>5.30838203430176</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426969528198</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426969528198</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550621032715</v>
+        <v>5.32550668716431</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426969528198</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426969528198</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426969528198</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426969528198</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.2024359703064</v>
+        <v>5.20243644714355</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023708343506</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803867340088</v>
+        <v>5.09803915023804</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763782501221</v>
+        <v>5.16763687133789</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>5.04584074020386</v>
+        <v>5.0458402633667</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.8370475769043</v>
+        <v>4.83704710006714</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404413223267</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404413223267</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75004959106445</v>
+        <v>4.75005054473877</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165822982788</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425891876221</v>
+        <v>4.45425939559937</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896427154541</v>
+        <v>4.28896474838257</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887100219727</v>
+        <v>4.08887052536011</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416564941406</v>
+        <v>4.2541651725769</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497068405151</v>
+        <v>4.11497020721436</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456792831421</v>
+        <v>4.18456840515137</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G514" t="n">
-        <v>4.54125690460205</v>
+        <v>4.54125642776489</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165822982788</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525192260742</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525192260742</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206146240234</v>
+        <v>4.40206098556519</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G559" t="n">
-        <v>4.54125690460205</v>
+        <v>4.54125642776489</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.87184619903564</v>
+        <v>4.8718466758728</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723554611206</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023708343506</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723554611206</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723554611206</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39382982254028</v>
+        <v>5.39382934570312</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.63742256164551</v>
+        <v>5.63742208480835</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881593704224</v>
+        <v>5.82881641387939</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.5015606880188</v>
+        <v>6.50156116485596</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031089782715</v>
+        <v>7.00031042098999</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.83999824523926</v>
+        <v>6.8399977684021</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718488693237</v>
+        <v>7.10718536376953</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468496322632</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562322616577</v>
+        <v>6.87562274932861</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.48124742507935</v>
+        <v>7.48124694824219</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968450546265</v>
+        <v>7.8196849822998</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.14031028747559</v>
+        <v>8.14030933380127</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.47874641418457</v>
+        <v>8.4787483215332</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343616485596</v>
+        <v>9.17343521118164</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249694824219</v>
+        <v>9.2624979019165</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249694824219</v>
+        <v>9.2624979019165</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890243530273</v>
+        <v>9.12890434265137</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702877044678</v>
+        <v>9.30702781677246</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718444824219</v>
+        <v>8.8171854019165</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937267303467</v>
+        <v>8.79937171936035</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702877044678</v>
+        <v>9.30702781677246</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.4406213760376</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093727111816</v>
+        <v>10.5093717575073</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109331130981</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453092575073</v>
+        <v>11.845308303833</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671829223633</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109331130981</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335893630981</v>
+        <v>11.5335903167725</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671829223633</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899171829224</v>
+        <v>11.589916229248</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>11.0957746505737</v>
+        <v>11.0957736968994</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.410228729248</v>
+        <v>11.4102296829224</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899171829224</v>
+        <v>11.589916229248</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899171829224</v>
+        <v>11.589916229248</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.814528465271</v>
+        <v>11.8145275115967</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449962615967</v>
+        <v>11.5449953079224</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868036270142</v>
+        <v>13.3868045806885</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.8340969085693</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.8340969085693</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.923942565918</v>
+        <v>17.9239444732666</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.744255065918</v>
+        <v>17.7442531585693</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>17.7891750335693</v>
+        <v>17.789176940918</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372123718262</v>
+        <v>16.0372104644775</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372123718262</v>
+        <v>16.0372104644775</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356575012207</v>
+        <v>16.9356555938721</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661205291748</v>
+        <v>16.6661224365234</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415130615234</v>
+        <v>16.4415111541748</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.138768196106</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.004002571106</v>
+        <v>15.0040016174316</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676792144775</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126020431519</v>
+        <v>15.8125991821289</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676792144775</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676792144775</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>15.3633804321289</v>
+        <v>15.3633794784546</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286138534546</v>
+        <v>15.2286128997803</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879907608032</v>
+        <v>15.5879878997803</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141578674316</v>
+        <v>14.914158821106</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.138768196106</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.1836910247803</v>
+        <v>15.1836891174316</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>14.6895475387573</v>
+        <v>14.689546585083</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.5547819137573</v>
+        <v>14.554780960083</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461824417114</v>
+        <v>13.7461814880371</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129726409912</v>
+        <v>12.7129716873169</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680498123169</v>
+        <v>12.6680507659912</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>12.0391387939453</v>
+        <v>12.039137840271</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>12.5</v>
       </c>
       <c r="G836" t="n">
-        <v>11.230541229248</v>
+        <v>11.2305402755737</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.230541229248</v>
+        <v>11.2305402755737</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899171829224</v>
+        <v>11.589916229248</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332822799683</v>
+        <v>12.5332832336426</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>13.3418827056885</v>
+        <v>13.3418817520142</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012605667114</v>
+        <v>13.7012596130371</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>15.5</v>
       </c>
       <c r="G851" t="n">
-        <v>13.9258699417114</v>
+        <v>13.9258708953857</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.219630241394</v>
+        <v>15.2196283340454</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.399317741394</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657228469849</v>
+        <v>15.1657209396362</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>15.3633804321289</v>
+        <v>15.3633794784546</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766628265381</v>
+        <v>15.7766618728638</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563503265381</v>
+        <v>15.956353187561</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407274246216</v>
+        <v>15.7407264709473</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250997543335</v>
+        <v>15.5250988006592</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454113006592</v>
+        <v>15.3454093933105</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602514266968</v>
+        <v>14.8602523803711</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.7344694137573</v>
+        <v>14.734468460083</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G880" t="n">
-        <v>14.3923778533936</v>
+        <v>14.3923768997192</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>14.8318395614624</v>
+        <v>14.8318386077881</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G896" t="n">
-        <v>14.996636390686</v>
+        <v>14.9966373443604</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G900" t="n">
-        <v>14.996636390686</v>
+        <v>14.9966373443604</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G905" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908815383911</v>
+        <v>12.8908824920654</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G912" t="n">
-        <v>12.6528406143188</v>
+        <v>12.6528396606445</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429744720459</v>
+        <v>12.5429754257202</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G919" t="n">
-        <v>12.7443952560425</v>
+        <v>12.7443943023682</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G920" t="n">
-        <v>13.3852758407593</v>
+        <v>13.3852767944336</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G930" t="n">
-        <v>13.0373687744141</v>
+        <v>13.0373697280884</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739917755127</v>
+        <v>13.0739908218384</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G933" t="n">
-        <v>12.7443952560425</v>
+        <v>12.7443943023682</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G938" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>13.8979825973511</v>
+        <v>13.8979816436768</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G949" t="n">
-        <v>14.227578163147</v>
+        <v>14.2275791168213</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346046447754</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951419830322</v>
+        <v>13.4951429367065</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G960" t="n">
-        <v>13.5134534835815</v>
+        <v>13.5134544372559</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G965" t="n">
-        <v>13.6782512664795</v>
+        <v>13.6782503128052</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G969" t="n">
-        <v>13.7148723602295</v>
+        <v>13.7148733139038</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599407196045</v>
+        <v>13.6599397659302</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G971" t="n">
-        <v>13.7148723602295</v>
+        <v>13.7148733139038</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G974" t="n">
-        <v>14.227578163147</v>
+        <v>14.2275791168213</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G976" t="n">
-        <v>13.8979825973511</v>
+        <v>13.8979816436768</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>13.9162931442261</v>
+        <v>13.9162921905518</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G981" t="n">
-        <v>14.209267616272</v>
+        <v>14.2092685699463</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G989" t="n">
-        <v>14.209267616272</v>
+        <v>14.2092685699463</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726455688477</v>
+        <v>14.172646522522</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.8979825973511</v>
+        <v>13.8979816436768</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6670408248901</v>
+        <v>14.6670417785645</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1011" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726455688477</v>
+        <v>14.172646522522</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1017" t="n">
-        <v>13.9162931442261</v>
+        <v>13.9162921905518</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1026" t="n">
-        <v>14.4106874465942</v>
+        <v>14.4106884002686</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.8318395614624</v>
+        <v>14.8318386077881</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726455688477</v>
+        <v>14.172646522522</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1057" t="n">
-        <v>14.7036619186401</v>
+        <v>14.7036628723145</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656219482422</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1064" t="n">
-        <v>14.5022430419922</v>
+        <v>14.5022420883179</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1065" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>14.2458906173706</v>
+        <v>14.2458896636963</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1084" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="n">
-        <v>15.0698804855347</v>
+        <v>15.0698795318604</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.960015296936</v>
+        <v>14.9600162506104</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4360990524292</v>
+        <v>15.4361000061035</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473859786987</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1101" t="n">
-        <v>15.6375188827515</v>
+        <v>15.6375179290771</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>16.2600898742676</v>
+        <v>16.2600917816162</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319122314453</v>
+        <v>16.1319141387939</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699531555176</v>
+        <v>16.3699550628662</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309246063232</v>
+        <v>17.7309226989746</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641819000244</v>
+        <v>16.9641799926758</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683395385742</v>
+        <v>16.8683376312256</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -52268,6 +52268,32 @@
         <v>1.98500001430511</v>
       </c>
       <c r="H1996" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1997" t="n">
+        <v>23626</v>
+      </c>
+      <c r="C1997" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>1.87999999523163</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>1.87999999523163</v>
+      </c>
+      <c r="H1997" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46365,8 +46365,31 @@
       <c r="E2000" t="n">
         <v>1.81500005722046</v>
       </c>
-      <c r="F2000"/>
+      <c r="F2000" t="n">
+        <v>1.81500005722046</v>
+      </c>
       <c r="G2000" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2001" t="n">
+        <v>4611</v>
+      </c>
+      <c r="C2001" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>1.7849999666214</v>
+      </c>
+      <c r="F2001"/>
+      <c r="G2001" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46388,8 +46388,31 @@
       <c r="E2001" t="n">
         <v>1.7849999666214</v>
       </c>
-      <c r="F2001"/>
+      <c r="F2001" t="n">
+        <v>1.8400000333786</v>
+      </c>
       <c r="G2001" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2002" t="n">
+        <v>1527</v>
+      </c>
+      <c r="C2002" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="F2002"/>
+      <c r="G2002" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46411,8 +46411,31 @@
       <c r="E2002" t="n">
         <v>1.8400000333786</v>
       </c>
-      <c r="F2002"/>
+      <c r="F2002" t="n">
+        <v>1.86000001430511</v>
+      </c>
       <c r="G2002" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2003" t="n">
+        <v>1515</v>
+      </c>
+      <c r="C2003" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="F2003"/>
+      <c r="G2003" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46434,8 +46434,31 @@
       <c r="E2003" t="n">
         <v>1.86000001430511</v>
       </c>
-      <c r="F2003"/>
+      <c r="F2003" t="n">
+        <v>1.82500004768372</v>
+      </c>
       <c r="G2003" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2004" t="n">
+        <v>1291</v>
+      </c>
+      <c r="C2004" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="F2004"/>
+      <c r="G2004" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -46464,6 +46464,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2005">
+      <c r="A2005" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2005" t="n">
+        <v>7980</v>
+      </c>
+      <c r="C2005" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>1.7849999666214</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="G2005" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108229637146</v>
+        <v>2.88108205795288</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676808357239</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762376785278</v>
+        <v>2.90762424468994</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676808357239</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676808357239</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441972732544</v>
+        <v>2.83441948890686</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.37949991226196</v>
       </c>
       <c r="G21" t="n">
-        <v>2.89349699020386</v>
+        <v>2.89349675178528</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392471313477</v>
+        <v>2.89392518997192</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8986337184906</v>
+        <v>2.89863419532776</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255361557007</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601142883301</v>
+        <v>2.81601166725159</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.84426617622375</v>
+        <v>2.84426593780518</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542991638184</v>
+        <v>2.82542943954468</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823892593384</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368371009827</v>
+        <v>2.85368418693542</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385813713074</v>
+        <v>2.9538586139679</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255361557007</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823892593384</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823892593384</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823892593384</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779867172241</v>
+        <v>3.00779843330383</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626769065857</v>
+        <v>3.35626816749573</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768544197083</v>
+        <v>3.2376856803894</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309729576111</v>
+        <v>3.25309681892395</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071553230286</v>
+        <v>3.21071577072144</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.407639503479</v>
+        <v>3.40763902664185</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873666763306</v>
+        <v>3.44873642921448</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098480224609</v>
+        <v>3.61098527908325</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293298721313</v>
+        <v>4.04293346405029</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028539657593</v>
+        <v>4.24028444290161</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128700256348</v>
+        <v>3.98128724098206</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279268264771</v>
+        <v>3.91279220581055</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.0155348777771</v>
+        <v>4.01553535461426</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.95645689964294</v>
+        <v>3.95645785331726</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566802978516</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0082573890686</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041044235229</v>
+        <v>3.87041091918945</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330738067627</v>
+        <v>3.96330714225769</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566802978516</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493225097656</v>
+        <v>3.91493272781372</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12684059143066</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834436416626</v>
+        <v>4.05834484100342</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12684059143066</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657381057739</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245861053467</v>
+        <v>4.21245908737183</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938234329224</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938234329224</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938234329224</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500131607056</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500131607056</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219087600708</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871562957764</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871562957764</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871562957764</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871562957764</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076482772827</v>
+        <v>7.02076435089111</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671739578247</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266948699951</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919376373291</v>
+        <v>7.14919281005859</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671739578247</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266948699951</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143106460571</v>
+        <v>6.42143154144287</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862110137939</v>
+        <v>6.37862157821655</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614473342896</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614473342896</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614473342896</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614473342896</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70904922485352</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70904922485352</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874429702759</v>
+        <v>3.69874453544617</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051556587219</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242046356201</v>
+        <v>2.96241998672485</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857204437256</v>
+        <v>2.56857228279114</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432464599609</v>
+        <v>2.53432488441467</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158149719238</v>
+        <v>2.43158197402954</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4829535484314</v>
+        <v>2.48295378684998</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560145378113</v>
+        <v>3.95560121536255</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710594177246</v>
+        <v>3.88710641860962</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299169540405</v>
+        <v>3.73299241065979</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038241386414</v>
+        <v>3.51038217544556</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593481063843</v>
+        <v>3.65593528747559</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.6388111114502</v>
+        <v>3.63881087303162</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.41620111465454</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.41620111465454</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004905700684</v>
+        <v>3.81004858016968</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854433059692</v>
+        <v>3.87854480743408</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285878181458</v>
+        <v>3.85285902023315</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G373" t="n">
-        <v>4.8289155960083</v>
+        <v>4.82891654968262</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.4008207321167</v>
+        <v>4.40082120895386</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657381057739</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.2723913192749</v>
+        <v>4.27239179611206</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838346481323</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838346481323</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028764724731</v>
+        <v>4.88028717041016</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20563983917236</v>
+        <v>5.20564031600952</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152654647827</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413558959961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988771438599</v>
+        <v>5.2398886680603</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413558959961</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988771438599</v>
+        <v>5.2398886680603</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543846130371</v>
+        <v>5.11543941497803</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763734817505</v>
+        <v>5.16763687133789</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08064031600952</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08064031600952</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844095230103</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.8370475769043</v>
+        <v>4.83704710006714</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404413223267</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404413223267</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>4.36726188659668</v>
+        <v>4.36726236343384</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.34986305236816</v>
+        <v>4.34986257553101</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896427154541</v>
+        <v>4.28896474838257</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716909408569</v>
+        <v>4.16716861724854</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5</v>
       </c>
       <c r="G498" t="n">
-        <v>4.34986305236816</v>
+        <v>4.34986257553101</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.1410698890686</v>
+        <v>4.14106941223145</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.1149697303772</v>
+        <v>4.11497068405151</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286554336548</v>
+        <v>4.26286649703979</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506443023682</v>
+        <v>4.3150634765625</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.43686056137085</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385663986206</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905801773071</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>4.43686056137085</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905801773071</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345579147339</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905801773071</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905801773071</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206098556519</v>
+        <v>4.40206146240234</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>4.43686056137085</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905801773071</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08064031600952</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664577484131</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844095230103</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844095230103</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664577484131</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203416824341</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203416824341</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.56782388687134</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.56782388687134</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661800384521</v>
+        <v>5.77661752700806</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>5.79401683807373</v>
+        <v>5.79401731491089</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801233291626</v>
+        <v>5.96801280975342</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.5015606880188</v>
+        <v>6.50156116485596</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718584060669</v>
+        <v>7.10718536376953</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468639373779</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562274932861</v>
+        <v>6.87562227249146</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.4812479019165</v>
+        <v>7.48124694824219</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874719619751</v>
+        <v>7.90874767303467</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249599456787</v>
+        <v>9.2624979019165</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249599456787</v>
+        <v>9.2624979019165</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890434265137</v>
+        <v>9.12890338897705</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437347412109</v>
+        <v>9.08437061309814</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G644" t="n">
-        <v>8.62124824523926</v>
+        <v>8.62124729156494</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093727111816</v>
+        <v>10.5093717575073</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109340667725</v>
+        <v>11.3109350204468</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453102111816</v>
+        <v>11.8453092575073</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109340667725</v>
+        <v>11.3109350204468</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335903167725</v>
+        <v>11.5335893630981</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.455150604248</v>
+        <v>11.4551515579224</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363958358765</v>
+        <v>10.7363967895508</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.410228729248</v>
+        <v>11.4102296829224</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.8145275115967</v>
+        <v>11.814528465271</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535938262939</v>
+        <v>12.3535947799683</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621923446655</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868036270142</v>
+        <v>13.3868045806885</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>17.6544094085693</v>
+        <v>17.6544075012207</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239444732666</v>
+        <v>17.9239406585693</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.7442531585693</v>
+        <v>17.744255065918</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>17.5645656585693</v>
+        <v>17.5645637512207</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>17.5645656585693</v>
+        <v>17.5645637512207</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5645656585693</v>
+        <v>17.5645637512207</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153430938721</v>
+        <v>17.1153411865234</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922876358032</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372142791748</v>
+        <v>16.0372104644775</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372142791748</v>
+        <v>16.0372104644775</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110443115234</v>
+        <v>16.7110424041748</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>18.25</v>
       </c>
       <c r="G753" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>18.25</v>
       </c>
       <c r="G760" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415111541748</v>
+        <v>16.4415092468262</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387701034546</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.3184566497803</v>
+        <v>15.318455696106</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040035247803</v>
+        <v>15.0040016174316</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>18.25</v>
       </c>
       <c r="G773" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922876358032</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270580291748</v>
+        <v>16.1270561218262</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922876358032</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981441497803</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981441497803</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126020431519</v>
+        <v>15.8126010894775</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922876358032</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981441497803</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.3184566497803</v>
+        <v>15.318455696106</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879917144775</v>
+        <v>15.5879898071289</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387701034546</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.1836910247803</v>
+        <v>15.183690071106</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590797424316</v>
+        <v>14.959080696106</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>13.5215702056885</v>
+        <v>13.5215711593628</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.5997037887573</v>
+        <v>14.5997018814087</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504802703857</v>
+        <v>14.1504812240601</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200124740601</v>
+        <v>14.4200134277344</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055593490601</v>
+        <v>14.1055574417114</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461814880371</v>
+        <v>13.7461824417114</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621923446655</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477373123169</v>
+        <v>12.8477382659912</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680507659912</v>
+        <v>12.6680498123169</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>12.0391387939453</v>
+        <v>12.0391397476196</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172714233398</v>
+        <v>13.1172723770142</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723485946655</v>
+        <v>13.0723495483398</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621923446655</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969608306885</v>
+        <v>13.2969589233398</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664939880371</v>
+        <v>13.5664930343628</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012596130371</v>
+        <v>13.7012586593628</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911033630371</v>
+        <v>13.7911043167114</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954040527344</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.3993186950684</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532251358032</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766609191895</v>
+        <v>15.7766618728638</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407255172729</v>
+        <v>15.7407264709473</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250997543335</v>
+        <v>15.5250978469849</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454103469849</v>
+        <v>15.3454113006592</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368127822876</v>
+        <v>14.5368118286133</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.7344694137573</v>
+        <v>14.734468460083</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135290145874</v>
+        <v>14.8135280609131</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G887" t="n">
-        <v>14.4289999008179</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G891" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G893" t="n">
-        <v>14.4289999008179</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G896" t="n">
-        <v>14.996636390686</v>
+        <v>14.9966373443604</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501482009888</v>
+        <v>14.8501491546631</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G900" t="n">
-        <v>14.996636390686</v>
+        <v>14.9966373443604</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>14</v>
       </c>
       <c r="G906" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824361801147</v>
+        <v>12.9824371337891</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345291137695</v>
+        <v>12.6345300674438</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908824920654</v>
+        <v>12.8908815383911</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711521148682</v>
+        <v>12.6711511611938</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>13.0007476806641</v>
+        <v>13.0007467269897</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>13.0007476806641</v>
+        <v>13.0007467269897</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>13.0007476806641</v>
+        <v>13.0007467269897</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14</v>
       </c>
       <c r="G922" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.0007476806641</v>
+        <v>13.0007467269897</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>14</v>
       </c>
       <c r="G924" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G927" t="n">
-        <v>12.6162185668945</v>
+        <v>12.6162176132202</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359508514404</v>
+        <v>12.8359489440918</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G930" t="n">
-        <v>13.0373687744141</v>
+        <v>13.0373697280884</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739917755127</v>
+        <v>13.0739908218384</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>14</v>
       </c>
       <c r="G934" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>13.0007476806641</v>
+        <v>13.0007467269897</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>13.0007476806641</v>
+        <v>13.0007467269897</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G949" t="n">
-        <v>14.227578163147</v>
+        <v>14.2275791168213</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402839660645</v>
+        <v>14.7402849197388</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501482009888</v>
+        <v>14.8501491546631</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G953" t="n">
-        <v>14.4289999008179</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613605499268</v>
+        <v>13.8613615036011</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346036911011</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G960" t="n">
-        <v>13.5134534835815</v>
+        <v>13.5134544372559</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>13.5500755310059</v>
+        <v>13.5500745773315</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>13.5500755310059</v>
+        <v>13.5500745773315</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303451538086</v>
+        <v>13.3303442001343</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599407196045</v>
+        <v>13.6599397659302</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G974" t="n">
-        <v>14.227578163147</v>
+        <v>14.2275791168213</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>13.7331838607788</v>
+        <v>13.7331848144531</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>15</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7331838607788</v>
+        <v>13.7331848144531</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G985" t="n">
-        <v>14.154335975647</v>
+        <v>14.1543350219727</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G992" t="n">
-        <v>14.4289999008179</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G996" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613605499268</v>
+        <v>13.8613615036011</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.081090927124</v>
+        <v>14.0810918807983</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1011" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.4289999008179</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.4839315414429</v>
+        <v>14.4839305877686</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1055" t="n">
-        <v>14.4289999008179</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1061" t="n">
-        <v>14.4839315414429</v>
+        <v>14.4839305877686</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1065" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>14.5937967300415</v>
+        <v>14.5937957763672</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="n">
-        <v>15.0698804855347</v>
+        <v>15.0698795318604</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.960015296936</v>
+        <v>14.9600162506104</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473859786987</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319141387939</v>
+        <v>16.1319160461426</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699550628662</v>
+        <v>16.3699531555176</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309246063232</v>
+        <v>17.7309226989746</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641819000244</v>
+        <v>16.9641799926758</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683395385742</v>
+        <v>16.8683376312256</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -52554,6 +52554,32 @@
         <v>1.80999994277954</v>
       </c>
       <c r="H2007" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2008" t="n">
+        <v>1465</v>
+      </c>
+      <c r="C2008" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H2008" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108205795288</v>
+        <v>2.8810818195343</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762424468994</v>
+        <v>2.90762376785278</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441948890686</v>
+        <v>2.83441925048828</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392518997192</v>
+        <v>2.89392495155334</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863419532776</v>
+        <v>2.89863395690918</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601166725159</v>
+        <v>2.81601142883301</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549649238586</v>
+        <v>2.76549625396729</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.84426593780518</v>
+        <v>2.8442656993866</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368418693542</v>
+        <v>2.85368394851685</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9538586139679</v>
+        <v>2.95385837554932</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779843330383</v>
+        <v>3.00779819488525</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379132270813</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904914855957</v>
+        <v>3.03904938697815</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256887435913</v>
+        <v>3.34256911277771</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489635467529</v>
+        <v>3.30489659309387</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345820426941</v>
+        <v>3.31345844268799</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309681892395</v>
+        <v>3.25309705734253</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071577072144</v>
+        <v>3.21071529388428</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483001708984</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.40763902664185</v>
+        <v>3.407639503479</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098527908325</v>
+        <v>3.61098480224609</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.966304063797</v>
+        <v>3.96630334854126</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028444290161</v>
+        <v>4.24028539657593</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0669059753418</v>
+        <v>4.06690692901611</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409696578979</v>
+        <v>4.02409648895264</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407632827759</v>
+        <v>3.91407585144043</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553535461426</v>
+        <v>4.0155348777771</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493272781372</v>
+        <v>3.91493225097656</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.67749977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>4.00483179092407</v>
+        <v>4.00483274459839</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834484100342</v>
+        <v>4.05834436416626</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376337051392</v>
+        <v>4.32376384735107</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871562957764</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828798294067</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671644210815</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919281005859</v>
+        <v>7.14919376373291</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671644210815</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828798294067</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143154144287</v>
+        <v>6.42143058776855</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862157821655</v>
+        <v>6.37862110137939</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G220" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G221" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614473342896</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G244" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176370620728</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614473342896</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614473342896</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614473342896</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995500564575</v>
+        <v>5.17995452880859</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904922485352</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904922485352</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26383066177368</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750587463379</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432488441467</v>
+        <v>2.53432512283325</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158197402954</v>
+        <v>2.43158149719238</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.48295378684998</v>
+        <v>2.48295331001282</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>3.23640108108521</v>
+        <v>3.23640155792236</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971546173096</v>
+        <v>4.10971641540527</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710641860962</v>
+        <v>3.8871066570282</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743953704834</v>
+        <v>3.58743977546692</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593528747559</v>
+        <v>3.65593457221985</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881087303162</v>
+        <v>3.63881063461304</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894426345825</v>
+        <v>3.51894450187683</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750587463379</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861066818237</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861066818237</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004858016968</v>
+        <v>3.81004905700684</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854480743408</v>
+        <v>3.87854433059692</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285902023315</v>
+        <v>3.85285878181458</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329662322998</v>
+        <v>4.74329710006714</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356340408325</v>
+        <v>4.50356435775757</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G375" t="n">
-        <v>4.46931600570679</v>
+        <v>4.46931552886963</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082120895386</v>
+        <v>4.4008207321167</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26383066177368</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838346481323</v>
+        <v>5.30838203430176</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838346481323</v>
+        <v>5.30838203430176</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.06864976882935</v>
+        <v>5.0686502456665</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.06864976882935</v>
+        <v>5.0686502456665</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06864976882935</v>
+        <v>5.0686502456665</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152654647827</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550621032715</v>
+        <v>5.32550668716431</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577346801758</v>
+        <v>5.08577299118042</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.2398886680603</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.2398886680603</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543941497803</v>
+        <v>5.11543893814087</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803915023804</v>
+        <v>5.09803867340088</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.97624349594116</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763687133789</v>
+        <v>5.16763782501221</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844095230103</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.97624349594116</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404413223267</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404413223267</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744985580444</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005006790161</v>
+        <v>4.75005054473877</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744985580444</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286649703979</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286649703979</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497068405151</v>
+        <v>4.11497020721436</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286649703979</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.3150634765625</v>
+        <v>4.31506395339966</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905801773071</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905801773071</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345579147339</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744985580444</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905801773071</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905801773071</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206146240234</v>
+        <v>4.40206050872803</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905801773071</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744985580444</v>
+        <v>4.7674503326416</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.97624349594116</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.97624349594116</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664577484131</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844095230103</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844095230103</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664577484131</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.97624349594116</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>5.6722207069397</v>
+        <v>5.67222118377686</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782388687134</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082733154297</v>
+        <v>5.48082780838013</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782388687134</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>5.81141710281372</v>
+        <v>5.81141662597656</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>5.81141710281372</v>
+        <v>5.81141662597656</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801280975342</v>
+        <v>5.96801233291626</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437356948853</v>
+        <v>6.23437309265137</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.50156116485596</v>
+        <v>6.5015606880188</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.8399977684021</v>
+        <v>6.83999729156494</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468591690063</v>
+        <v>6.96468544006348</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562227249146</v>
+        <v>6.87562274932861</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>7.08937311172485</v>
+        <v>7.0893726348877</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.48124694824219</v>
+        <v>7.48124742507935</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874767303467</v>
+        <v>7.90874671936035</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968450546265</v>
+        <v>7.8196849822998</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.1403112411499</v>
+        <v>8.14030933380127</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.4787483215332</v>
+        <v>8.47874736785889</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343521118164</v>
+        <v>9.17343425750732</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>9.97499656677246</v>
+        <v>9.97499752044678</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.2624979019165</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.2624979019165</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437061309814</v>
+        <v>9.08437156677246</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937267303467</v>
+        <v>8.79937171936035</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G643" t="n">
-        <v>8.69249820709229</v>
+        <v>8.69249725341797</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093717575073</v>
+        <v>10.5093727111816</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109350204468</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>11.3999967575073</v>
+        <v>11.3999977111816</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109350204468</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562475204468</v>
+        <v>11.7562456130981</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.8594512939453</v>
+        <v>11.859450340271</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363967895508</v>
+        <v>10.7363958358765</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.4102296829224</v>
+        <v>11.410228729248</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.814528465271</v>
+        <v>11.8145294189453</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535947799683</v>
+        <v>12.3535938262939</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621923446655</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>14.3301696777344</v>
+        <v>14.3301706314087</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>17.6544075012207</v>
+        <v>17.6544094085693</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>16.8907337188721</v>
+        <v>16.8907318115234</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>17.879020690918</v>
+        <v>17.8790225982666</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239406585693</v>
+        <v>17.923942565918</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.744255065918</v>
+        <v>17.7442531585693</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399524688721</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.8907337188721</v>
+        <v>16.8907318115234</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051887512207</v>
+        <v>17.2051868438721</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399524688721</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153411865234</v>
+        <v>17.1153430938721</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399524688721</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922876358032</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110424041748</v>
+        <v>16.7110443115234</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>18.25</v>
       </c>
       <c r="G753" t="n">
-        <v>16.3965892791748</v>
+        <v>16.3965873718262</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356555938721</v>
+        <v>16.9356575012207</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>16.3516674041748</v>
+        <v>16.3516654968262</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661224365234</v>
+        <v>16.6661205291748</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>18.25</v>
       </c>
       <c r="G760" t="n">
-        <v>16.3965892791748</v>
+        <v>16.3965873718262</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415092468262</v>
+        <v>16.4415111541748</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.318455696106</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040016174316</v>
+        <v>15.0040035247803</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>18.25</v>
       </c>
       <c r="G773" t="n">
-        <v>16.3965892791748</v>
+        <v>16.3965873718262</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922876358032</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270561218262</v>
+        <v>16.1270580291748</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922876358032</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981441497803</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981441497803</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>15.4083013534546</v>
+        <v>15.4083003997803</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126010894775</v>
+        <v>15.8126001358032</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922876358032</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329116821289</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329116821289</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024448394775</v>
+        <v>15.9024457931519</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981441497803</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.318455696106</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286128997803</v>
+        <v>15.2286138534546</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879898071289</v>
+        <v>15.5879907608032</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329116821289</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329116821289</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098581314087</v>
+        <v>14.509859085083</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.5997018814087</v>
+        <v>14.599702835083</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055574417114</v>
+        <v>14.1055593490601</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461824417114</v>
+        <v>13.7461814880371</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621923446655</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129716873169</v>
+        <v>12.7129726409912</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>12.0391397476196</v>
+        <v>12.0391387939453</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578935623169</v>
+        <v>12.7578945159912</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621923446655</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664930343628</v>
+        <v>13.5664920806885</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012586593628</v>
+        <v>13.7012605667114</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911043167114</v>
+        <v>13.7911033630371</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954040527344</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329116821289</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993186950684</v>
+        <v>15.3993167877197</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657209396362</v>
+        <v>15.1657218933105</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766618728638</v>
+        <v>15.7766628265381</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407264709473</v>
+        <v>15.7407274246216</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250978469849</v>
+        <v>15.5251007080078</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454113006592</v>
+        <v>15.3454093933105</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602523803711</v>
+        <v>14.8602514266968</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.734468460083</v>
+        <v>14.7344694137573</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G879" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>14.9233922958374</v>
+        <v>14.9233932495117</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135280609131</v>
+        <v>14.8135290145874</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>14.5937957763672</v>
+        <v>14.5937967300415</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G887" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289999008179</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G891" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G893" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289999008179</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G896" t="n">
-        <v>14.9966373443604</v>
+        <v>14.996636390686</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>14.9233922958374</v>
+        <v>14.9233932495117</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G900" t="n">
-        <v>14.9966373443604</v>
+        <v>14.996636390686</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>14</v>
       </c>
       <c r="G906" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824371337891</v>
+        <v>12.9824361801147</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345300674438</v>
+        <v>12.6345291137695</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908815383911</v>
+        <v>12.8908824920654</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711511611938</v>
+        <v>12.6711521148682</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>13.0007467269897</v>
+        <v>13.0007476806641</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>13.0007467269897</v>
+        <v>13.0007476806641</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>13.0007467269897</v>
+        <v>13.0007476806641</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14</v>
       </c>
       <c r="G922" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.0007467269897</v>
+        <v>13.0007476806641</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>14</v>
       </c>
       <c r="G924" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514207839966</v>
+        <v>12.4514217376709</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G927" t="n">
-        <v>12.6162176132202</v>
+        <v>12.6162185668945</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359489440918</v>
+        <v>12.8359508514404</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G930" t="n">
-        <v>13.0373697280884</v>
+        <v>13.0373687744141</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739908218384</v>
+        <v>13.0739917755127</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>14</v>
       </c>
       <c r="G934" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>13.0007467269897</v>
+        <v>13.0007476806641</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>13.0007467269897</v>
+        <v>13.0007476806641</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923023223877</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923023223877</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G949" t="n">
-        <v>14.2275791168213</v>
+        <v>14.227578163147</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402849197388</v>
+        <v>14.7402839660645</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9233922958374</v>
+        <v>14.9233932495117</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G953" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289999008179</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346036911011</v>
+        <v>13.9346055984497</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G960" t="n">
-        <v>13.5134544372559</v>
+        <v>13.5134534835815</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>13.5500745773315</v>
+        <v>13.5500755310059</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G963" t="n">
-        <v>13.5500745773315</v>
+        <v>13.5500755310059</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303442001343</v>
+        <v>13.3303451538086</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599397659302</v>
+        <v>13.6599407196045</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G974" t="n">
-        <v>14.2275791168213</v>
+        <v>14.227578163147</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>13.7331848144531</v>
+        <v>13.7331838607788</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796710968018</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>15</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7331848144531</v>
+        <v>13.7331838607788</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G985" t="n">
-        <v>14.1543350219727</v>
+        <v>14.154335975647</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G992" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289999008179</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G996" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514963150024</v>
+        <v>13.7514953613281</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712266921997</v>
+        <v>13.9712257385254</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796710968018</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.0810918807983</v>
+        <v>14.081090927124</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.9417037963867</v>
+        <v>14.941704750061</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1011" t="n">
-        <v>14.5937957763672</v>
+        <v>14.5937967300415</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289999008179</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.4839305877686</v>
+        <v>14.4839315414429</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1055" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289999008179</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1061" t="n">
-        <v>14.4839305877686</v>
+        <v>14.4839315414429</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1065" t="n">
-        <v>14.5937957763672</v>
+        <v>14.5937967300415</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>14.5937957763672</v>
+        <v>14.5937967300415</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.161434173584</v>
+        <v>15.1614351272583</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="n">
-        <v>15.0698795318604</v>
+        <v>15.0698804855347</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.9600162506104</v>
+        <v>14.960015296936</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473859786987</v>
+        <v>15.7473850250244</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8023176193237</v>
+        <v>15.802318572998</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572492599487</v>
+        <v>15.8572483062744</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290735244751</v>
+        <v>15.7290725708008</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319160461426</v>
+        <v>16.1319141387939</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699531555176</v>
+        <v>16.3699550628662</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.060022354126</v>
+        <v>17.0600242614746</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.395471572876</v>
+        <v>17.3954734802246</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309226989746</v>
+        <v>17.7309246063232</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392360687256</v>
+        <v>17.5392379760742</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392360687256</v>
+        <v>17.5392379760742</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.395471572876</v>
+        <v>17.3954734802246</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.395471572876</v>
+        <v>17.3954734802246</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.060022354126</v>
+        <v>17.0600242614746</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641799926758</v>
+        <v>16.9641819000244</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.060022354126</v>
+        <v>17.0600242614746</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683376312256</v>
+        <v>16.8683395385742</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -52580,6 +52580,32 @@
         <v>1.79999995231628</v>
       </c>
       <c r="H2008" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2009" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2009" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H2009" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H3" t="n">
         <v>13950</v>
@@ -485,7 +485,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H4" t="n">
         <v>7200</v>
@@ -514,7 +514,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248656272888</v>
+        <v>2.90248680114746</v>
       </c>
       <c r="H5" t="n">
         <v>8550</v>
@@ -543,7 +543,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H6" t="n">
         <v>1350</v>
@@ -572,7 +572,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H7" t="n">
         <v>7200</v>
@@ -601,7 +601,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H8" t="n">
         <v>2700</v>
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H9" t="n">
         <v>1350</v>
@@ -688,7 +688,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H11" t="n">
         <v>450</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H12" t="n">
         <v>1800</v>
@@ -746,7 +746,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H13" t="n">
         <v>3600</v>
@@ -775,7 +775,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441972732544</v>
+        <v>2.83441948890686</v>
       </c>
       <c r="H20" t="n">
         <v>900</v>
@@ -1007,7 +1007,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392471313477</v>
+        <v>2.89392495155334</v>
       </c>
       <c r="H22" t="n">
         <v>450</v>
@@ -1065,7 +1065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H24" t="n">
         <v>450</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863395690918</v>
+        <v>2.8986337184906</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1152,7 +1152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255361557007</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H27" t="n">
         <v>450</v>
@@ -1239,7 +1239,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549625396729</v>
+        <v>2.76549601554871</v>
       </c>
       <c r="H30" t="n">
         <v>3150</v>
@@ -1268,7 +1268,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H31" t="n">
         <v>4950</v>
@@ -1297,7 +1297,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.84426546096802</v>
+        <v>2.84426593780518</v>
       </c>
       <c r="H32" t="n">
         <v>2700</v>
@@ -1355,7 +1355,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035904884338</v>
+        <v>2.76035952568054</v>
       </c>
       <c r="H34" t="n">
         <v>1800</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1442,7 +1442,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H37" t="n">
         <v>5400</v>
@@ -1471,7 +1471,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368394851685</v>
+        <v>2.85368371009827</v>
       </c>
       <c r="H38" t="n">
         <v>6300</v>
@@ -1500,7 +1500,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661429405212</v>
+        <v>2.91661405563354</v>
       </c>
       <c r="H39" t="n">
         <v>19350</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385837554932</v>
+        <v>2.95385813713074</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255361557007</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779795646667</v>
+        <v>3.00779819488525</v>
       </c>
       <c r="H46" t="n">
         <v>7650</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1906,7 +1906,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904938697815</v>
+        <v>3.03904914855957</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256887435913</v>
+        <v>3.34256911277771</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -1964,7 +1964,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787287712097</v>
+        <v>3.19787263870239</v>
       </c>
       <c r="H55" t="n">
         <v>63900</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489635467529</v>
+        <v>3.30489659309387</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2022,7 +2022,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626816749573</v>
+        <v>3.35626792907715</v>
       </c>
       <c r="H57" t="n">
         <v>20250</v>
@@ -2051,7 +2051,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345844268799</v>
+        <v>3.31345796585083</v>
       </c>
       <c r="H58" t="n">
         <v>4500</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768591880798</v>
+        <v>3.23768544197083</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2109,7 +2109,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309681892395</v>
+        <v>3.25309705734253</v>
       </c>
       <c r="H60" t="n">
         <v>5400</v>
@@ -2138,7 +2138,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071577072144</v>
+        <v>3.21071553230286</v>
       </c>
       <c r="H61" t="n">
         <v>11700</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.40763926506042</v>
+        <v>3.407639503479</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518602371216</v>
+        <v>3.81518626213074</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630454063416</v>
+        <v>3.966304063797</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2370,7 +2370,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293346405029</v>
+        <v>4.04293298721313</v>
       </c>
       <c r="H69" t="n">
         <v>51750</v>
@@ -2399,7 +2399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H70" t="n">
         <v>59850</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2457,7 +2457,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028491973877</v>
+        <v>4.24028444290161</v>
       </c>
       <c r="H72" t="n">
         <v>10800</v>
@@ -2486,7 +2486,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087991714478</v>
+        <v>4.09087944030762</v>
       </c>
       <c r="H73" t="n">
         <v>33300</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.9812867641449</v>
+        <v>3.98128700256348</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2573,7 +2573,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409696578979</v>
+        <v>4.02409648895264</v>
       </c>
       <c r="H76" t="n">
         <v>450</v>
@@ -2602,7 +2602,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847751617432</v>
       </c>
       <c r="H77" t="n">
         <v>5850</v>
@@ -2631,7 +2631,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847751617432</v>
       </c>
       <c r="H78" t="n">
         <v>18900</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279220581055</v>
+        <v>3.91279196739197</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2689,7 +2689,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407632827759</v>
+        <v>3.91407585144043</v>
       </c>
       <c r="H80" t="n">
         <v>4950</v>
@@ -2718,7 +2718,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553535461426</v>
+        <v>4.0155348777771</v>
       </c>
       <c r="H81" t="n">
         <v>1800</v>
@@ -2747,7 +2747,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.95645761489868</v>
+        <v>3.9564573764801</v>
       </c>
       <c r="H82" t="n">
         <v>2250</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825786590576</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041115760803</v>
+        <v>3.87041139602661</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330714225769</v>
+        <v>3.96330785751343</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493201255798</v>
+        <v>3.91493272781372</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H93" t="n">
         <v>10350</v>
@@ -3153,7 +3153,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H96" t="n">
         <v>12600</v>
@@ -3182,7 +3182,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.0583438873291</v>
+        <v>4.05834436416626</v>
       </c>
       <c r="H97" t="n">
         <v>900</v>
@@ -3327,7 +3327,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H102" t="n">
         <v>4050</v>
@@ -3356,7 +3356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H103" t="n">
         <v>2250</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H104" t="n">
         <v>9450</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H108" t="n">
         <v>11250</v>
@@ -3530,7 +3530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H109" t="n">
         <v>27450</v>
@@ -3588,7 +3588,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H111" t="n">
         <v>4500</v>
@@ -3617,7 +3617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H112" t="n">
         <v>13950</v>
@@ -3675,7 +3675,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3704,7 +3704,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245908737183</v>
+        <v>4.21245861053467</v>
       </c>
       <c r="H115" t="n">
         <v>22950</v>
@@ -3733,7 +3733,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H116" t="n">
         <v>900</v>
@@ -3762,7 +3762,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H117" t="n">
         <v>5400</v>
@@ -3791,7 +3791,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H118" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H120" t="n">
         <v>11700</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4023,7 +4023,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376337051392</v>
+        <v>4.32376384735107</v>
       </c>
       <c r="H126" t="n">
         <v>900</v>
@@ -4052,7 +4052,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H127" t="n">
         <v>10800</v>
@@ -4081,7 +4081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H128" t="n">
         <v>8100</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4139,7 +4139,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H130" t="n">
         <v>1350</v>
@@ -4168,7 +4168,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500131607056</v>
       </c>
       <c r="H131" t="n">
         <v>4950</v>
@@ -4255,7 +4255,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H134" t="n">
         <v>7200</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4313,7 +4313,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H136" t="n">
         <v>35100</v>
@@ -4429,7 +4429,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H140" t="n">
         <v>33750</v>
@@ -4458,7 +4458,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H141" t="n">
         <v>21150</v>
@@ -4545,7 +4545,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H144" t="n">
         <v>1350</v>
@@ -4574,7 +4574,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H145" t="n">
         <v>8550</v>
@@ -4603,7 +4603,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H146" t="n">
         <v>11250</v>
@@ -4632,7 +4632,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H147" t="n">
         <v>1350</v>
@@ -4777,7 +4777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H152" t="n">
         <v>13500</v>
@@ -4806,7 +4806,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H153" t="n">
         <v>3150</v>
@@ -4864,7 +4864,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H155" t="n">
         <v>27000</v>
@@ -4893,7 +4893,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H156" t="n">
         <v>1800</v>
@@ -4922,7 +4922,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H159" t="n">
         <v>2250</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52242994308472</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H163" t="n">
         <v>7650</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5328,7 +5328,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52242994308472</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H171" t="n">
         <v>8100</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5647,7 +5647,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076435089111</v>
+        <v>7.02076482772827</v>
       </c>
       <c r="H182" t="n">
         <v>31050</v>
@@ -5705,7 +5705,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671739578247</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H184" t="n">
         <v>3600</v>
@@ -5734,7 +5734,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H185" t="n">
         <v>15750</v>
@@ -5763,7 +5763,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H186" t="n">
         <v>4050</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514537811279</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266901016235</v>
+        <v>6.59266948699951</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -5937,7 +5937,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H192" t="n">
         <v>4950</v>
@@ -5966,7 +5966,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H194" t="n">
         <v>4050</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6082,7 +6082,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638332366943</v>
+        <v>7.10638380050659</v>
       </c>
       <c r="H197" t="n">
         <v>15750</v>
@@ -6111,7 +6111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638332366943</v>
+        <v>7.10638380050659</v>
       </c>
       <c r="H198" t="n">
         <v>10800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514537811279</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6198,7 +6198,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671739578247</v>
+        <v>6.80671644210815</v>
       </c>
       <c r="H201" t="n">
         <v>11250</v>
@@ -6227,7 +6227,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H202" t="n">
         <v>5400</v>
@@ -6256,7 +6256,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H203" t="n">
         <v>2250</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266901016235</v>
+        <v>6.59266948699951</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6459,7 +6459,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143154144287</v>
+        <v>6.42143106460571</v>
       </c>
       <c r="H210" t="n">
         <v>6300</v>
@@ -6488,7 +6488,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H211" t="n">
         <v>13050</v>
@@ -6517,7 +6517,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H212" t="n">
         <v>4050</v>
@@ -6546,7 +6546,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H213" t="n">
         <v>3150</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986047744751</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6807,7 +6807,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.2073826789856</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H222" t="n">
         <v>7042</v>
@@ -6865,7 +6865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H224" t="n">
         <v>6100</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7039,7 +7039,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H230" t="n">
         <v>49999</v>
@@ -7068,7 +7068,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.2073826789856</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H231" t="n">
         <v>55223</v>
@@ -7097,7 +7097,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019264221191</v>
       </c>
       <c r="H232" t="n">
         <v>20785</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300308227539</v>
+        <v>6.29300212860107</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7155,7 +7155,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H234" t="n">
         <v>15656</v>
@@ -7213,7 +7213,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H236" t="n">
         <v>20646</v>
@@ -7271,7 +7271,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019264221191</v>
       </c>
       <c r="H238" t="n">
         <v>4610</v>
@@ -7300,7 +7300,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H239" t="n">
         <v>7153</v>
@@ -7329,7 +7329,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.2073826789856</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H240" t="n">
         <v>10587</v>
@@ -7358,7 +7358,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H241" t="n">
         <v>2766</v>
@@ -7387,7 +7387,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H243" t="n">
         <v>3750</v>
@@ -7532,7 +7532,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H247" t="n">
         <v>3650</v>
@@ -7561,7 +7561,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H248" t="n">
         <v>751</v>
@@ -7590,7 +7590,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H249" t="n">
         <v>5546</v>
@@ -7619,7 +7619,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052528381348</v>
       </c>
       <c r="H250" t="n">
         <v>4710</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7909,7 +7909,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H260" t="n">
         <v>10941</v>
@@ -7938,7 +7938,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H261" t="n">
         <v>2202</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8025,7 +8025,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052528381348</v>
       </c>
       <c r="H264" t="n">
         <v>1575</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8141,7 +8141,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052528381348</v>
       </c>
       <c r="H268" t="n">
         <v>2072</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8402,7 +8402,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209730148315</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H277" t="n">
         <v>1002</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8518,7 +8518,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H281" t="n">
         <v>14397</v>
@@ -8547,7 +8547,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052528381348</v>
       </c>
       <c r="H282" t="n">
         <v>3735</v>
@@ -8576,7 +8576,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052528381348</v>
       </c>
       <c r="H283" t="n">
         <v>5807</v>
@@ -8605,7 +8605,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052528381348</v>
       </c>
       <c r="H284" t="n">
         <v>498</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209730148315</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H285" t="n">
         <v>5658</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8924,7 +8924,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209730148315</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H295" t="n">
         <v>3196</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9475,7 +9475,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52242994308472</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H314" t="n">
         <v>1549</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9620,7 +9620,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557397842407</v>
       </c>
       <c r="H319" t="n">
         <v>5941</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995405197144</v>
+        <v>5.17995452880859</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H322" t="n">
         <v>7516</v>
@@ -9736,7 +9736,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70905017852783</v>
+        <v>4.70904970169067</v>
       </c>
       <c r="H323" t="n">
         <v>13319</v>
@@ -9765,7 +9765,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70905017852783</v>
+        <v>4.70904970169067</v>
       </c>
       <c r="H324" t="n">
         <v>7596</v>
@@ -9794,7 +9794,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H325" t="n">
         <v>7622</v>
@@ -9823,7 +9823,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H326" t="n">
         <v>6905</v>
@@ -9852,7 +9852,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H327" t="n">
         <v>5844</v>
@@ -9910,7 +9910,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874453544617</v>
+        <v>3.69874429702759</v>
       </c>
       <c r="H329" t="n">
         <v>7210</v>
@@ -9997,7 +9997,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H332" t="n">
         <v>17685</v>
@@ -10055,7 +10055,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432488441467</v>
+        <v>2.53432464599609</v>
       </c>
       <c r="H334" t="n">
         <v>25142</v>
@@ -10258,7 +10258,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H341" t="n">
         <v>24606</v>
@@ -10287,7 +10287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971546173096</v>
+        <v>4.10971641540527</v>
       </c>
       <c r="H342" t="n">
         <v>27229</v>
@@ -10316,7 +10316,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H343" t="n">
         <v>19120</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723957061768</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10432,7 +10432,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038217544556</v>
+        <v>3.51038241386414</v>
       </c>
       <c r="H347" t="n">
         <v>4841</v>
@@ -10461,7 +10461,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743929862976</v>
+        <v>3.58743977546692</v>
       </c>
       <c r="H348" t="n">
         <v>5375</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476344108582</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593504905701</v>
+        <v>3.65593481063843</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881158828735</v>
+        <v>3.63881063461304</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10635,7 +10635,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894402503967</v>
+        <v>3.51894426345825</v>
       </c>
       <c r="H354" t="n">
         <v>4650</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476344108582</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10838,7 +10838,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449666023254</v>
+        <v>3.66449689865112</v>
       </c>
       <c r="H361" t="n">
         <v>16600</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723957061768</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10954,7 +10954,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004929542542</v>
+        <v>3.81004881858826</v>
       </c>
       <c r="H365" t="n">
         <v>3480</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854433059692</v>
+        <v>3.87854480743408</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11041,7 +11041,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329662322998</v>
+        <v>4.74329710006714</v>
       </c>
       <c r="H368" t="n">
         <v>77313</v>
@@ -11070,7 +11070,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356340408325</v>
+        <v>4.50356388092041</v>
       </c>
       <c r="H369" t="n">
         <v>65581</v>
@@ -11157,7 +11157,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="n">
         <v>50751</v>
@@ -11273,7 +11273,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082025527954</v>
+        <v>4.4008207321167</v>
       </c>
       <c r="H376" t="n">
         <v>38510</v>
@@ -11302,7 +11302,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H377" t="n">
         <v>13190</v>
@@ -11331,7 +11331,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H378" t="n">
         <v>10379</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239274978638</v>
+        <v>4.27239179611206</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11447,7 +11447,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838251113892</v>
+        <v>5.30838346481323</v>
       </c>
       <c r="H382" t="n">
         <v>137190</v>
@@ -11476,7 +11476,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577299118042</v>
+        <v>5.08577394485474</v>
       </c>
       <c r="H383" t="n">
         <v>75589</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11563,7 +11563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="n">
         <v>87258</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838251113892</v>
+        <v>5.30838346481323</v>
       </c>
       <c r="H387" t="n">
         <v>39972</v>
@@ -11621,7 +11621,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H388" t="n">
         <v>21205</v>
@@ -11650,7 +11650,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H389" t="n">
         <v>10104</v>
@@ -11708,7 +11708,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H391" t="n">
         <v>16426</v>
@@ -11737,7 +11737,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H392" t="n">
         <v>5797</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11824,7 +11824,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H395" t="n">
         <v>6353</v>
@@ -11853,7 +11853,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20564031600952</v>
+        <v>5.20563983917236</v>
       </c>
       <c r="H396" t="n">
         <v>4787</v>
@@ -11882,7 +11882,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H397" t="n">
         <v>5833</v>
@@ -11911,7 +11911,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.06864976882935</v>
+        <v>5.06864929199219</v>
       </c>
       <c r="H398" t="n">
         <v>11452</v>
@@ -11940,7 +11940,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577299118042</v>
+        <v>5.08577394485474</v>
       </c>
       <c r="H399" t="n">
         <v>4802</v>
@@ -12027,7 +12027,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.06864976882935</v>
+        <v>5.06864929199219</v>
       </c>
       <c r="H402" t="n">
         <v>4910</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12114,7 +12114,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H405" t="n">
         <v>961</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12201,7 +12201,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H408" t="n">
         <v>8938</v>
@@ -12259,7 +12259,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06864976882935</v>
+        <v>5.06864929199219</v>
       </c>
       <c r="H410" t="n">
         <v>5073</v>
@@ -12288,7 +12288,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H411" t="n">
         <v>1244</v>
@@ -12346,7 +12346,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H413" t="n">
         <v>3640</v>
@@ -12491,7 +12491,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H418" t="n">
         <v>1185</v>
@@ -12578,7 +12578,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H421" t="n">
         <v>10486</v>
@@ -12607,7 +12607,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H422" t="n">
         <v>7415</v>
@@ -12694,7 +12694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H425" t="n">
         <v>3416</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12897,7 +12897,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577299118042</v>
+        <v>5.08577394485474</v>
       </c>
       <c r="H432" t="n">
         <v>1500</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12955,7 +12955,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H434" t="n">
         <v>528</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13042,7 +13042,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988819122314</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H437" t="n">
         <v>7970</v>
@@ -13071,7 +13071,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H438" t="n">
         <v>8401</v>
@@ -13100,7 +13100,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988819122314</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H439" t="n">
         <v>4505</v>
@@ -13216,7 +13216,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H443" t="n">
         <v>260</v>
@@ -13390,7 +13390,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851661682129</v>
       </c>
       <c r="H449" t="n">
         <v>2920</v>
@@ -13448,7 +13448,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H451" t="n">
         <v>650</v>
@@ -13477,7 +13477,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H452" t="n">
         <v>930</v>
@@ -13535,7 +13535,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023851394653</v>
       </c>
       <c r="H454" t="n">
         <v>900</v>
@@ -13564,7 +13564,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H455" t="n">
         <v>845</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803915023804</v>
+        <v>5.0980396270752</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13709,7 +13709,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H460" t="n">
         <v>2330</v>
@@ -13738,7 +13738,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763687133789</v>
+        <v>5.16763734817505</v>
       </c>
       <c r="H461" t="n">
         <v>2800</v>
@@ -13767,7 +13767,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08064031600952</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H462" t="n">
         <v>2675</v>
@@ -13796,7 +13796,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08064031600952</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H463" t="n">
         <v>1000</v>
@@ -13999,7 +13999,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H470" t="n">
         <v>4279</v>
@@ -14086,7 +14086,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.83704662322998</v>
+        <v>4.83704710006714</v>
       </c>
       <c r="H473" t="n">
         <v>2696</v>
@@ -14115,7 +14115,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404508590698</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H474" t="n">
         <v>6712</v>
@@ -14144,7 +14144,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404508590698</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005054473877</v>
+        <v>4.75005006790161</v>
       </c>
       <c r="H477" t="n">
         <v>1841</v>
@@ -14318,7 +14318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H481" t="n">
         <v>6191</v>
@@ -14376,7 +14376,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H483" t="n">
         <v>6872</v>
@@ -14405,7 +14405,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H484" t="n">
         <v>2940</v>
@@ -14434,7 +14434,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H485" t="n">
         <v>672</v>
@@ -14463,7 +14463,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H486" t="n">
         <v>200</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H487" t="n">
         <v>537</v>
@@ -14724,7 +14724,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716909408569</v>
+        <v>4.16716861724854</v>
       </c>
       <c r="H495" t="n">
         <v>20644</v>
@@ -14782,7 +14782,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416564941406</v>
+        <v>4.25416612625122</v>
       </c>
       <c r="H497" t="n">
         <v>1064</v>
@@ -14840,7 +14840,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.14106941223145</v>
+        <v>4.1410698890686</v>
       </c>
       <c r="H499" t="n">
         <v>11007</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497020721436</v>
+        <v>4.11497068405151</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14927,7 +14927,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.3150634765625</v>
+        <v>4.31506443023682</v>
       </c>
       <c r="H502" t="n">
         <v>4690</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456840515137</v>
+        <v>4.18456792831421</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -14985,7 +14985,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.3063645362854</v>
+        <v>4.30636405944824</v>
       </c>
       <c r="H504" t="n">
         <v>10900</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15101,7 +15101,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H508" t="n">
         <v>14843</v>
@@ -15130,7 +15130,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H509" t="n">
         <v>6520</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15217,7 +15217,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H512" t="n">
         <v>2873</v>
@@ -15304,7 +15304,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H515" t="n">
         <v>2290</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H517" t="n">
         <v>3170</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H518" t="n">
         <v>1170</v>
@@ -15420,7 +15420,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H519" t="n">
         <v>2418</v>
@@ -15449,7 +15449,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H520" t="n">
         <v>140</v>
@@ -15478,7 +15478,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H523" t="n">
         <v>6233</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H524" t="n">
         <v>1255</v>
@@ -15652,7 +15652,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H527" t="n">
         <v>920</v>
@@ -15681,7 +15681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H528" t="n">
         <v>1750</v>
@@ -15768,7 +15768,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H531" t="n">
         <v>7058</v>
@@ -15797,7 +15797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H532" t="n">
         <v>16579</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15971,7 +15971,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H538" t="n">
         <v>1392</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16058,7 +16058,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H541" t="n">
         <v>1369</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16116,7 +16116,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525096893311</v>
+        <v>4.71525049209595</v>
       </c>
       <c r="H543" t="n">
         <v>300</v>
@@ -16174,7 +16174,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H545" t="n">
         <v>1820</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H549" t="n">
         <v>1333</v>
@@ -16319,7 +16319,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525096893311</v>
+        <v>4.71525049209595</v>
       </c>
       <c r="H550" t="n">
         <v>3677</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16406,7 +16406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H553" t="n">
         <v>12566</v>
@@ -16435,7 +16435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H554" t="n">
         <v>4021</v>
@@ -16464,7 +16464,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H555" t="n">
         <v>3530</v>
@@ -16493,7 +16493,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H556" t="n">
         <v>4770</v>
@@ -16609,7 +16609,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H560" t="n">
         <v>3592</v>
@@ -16638,7 +16638,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H561" t="n">
         <v>8531</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16783,7 +16783,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08064031600952</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H566" t="n">
         <v>45160</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16899,7 +16899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H570" t="n">
         <v>4750</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.87184619903564</v>
+        <v>4.8718466758728</v>
       </c>
       <c r="H572" t="n">
         <v>14439</v>
@@ -16986,7 +16986,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H573" t="n">
         <v>11120</v>
@@ -17015,7 +17015,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H574" t="n">
         <v>10615</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17276,7 +17276,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H583" t="n">
         <v>68126</v>
@@ -17363,7 +17363,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H586" t="n">
         <v>26713</v>
@@ -17450,7 +17450,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H589" t="n">
         <v>6920</v>
@@ -17537,7 +17537,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503618240356</v>
       </c>
       <c r="H592" t="n">
         <v>6452</v>
@@ -17595,7 +17595,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H594" t="n">
         <v>12574</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17653,7 +17653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023851394653</v>
       </c>
       <c r="H596" t="n">
         <v>9629</v>
@@ -17711,7 +17711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H598" t="n">
         <v>15675</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H600" t="n">
         <v>2830</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39382934570312</v>
+        <v>5.39382982254028</v>
       </c>
       <c r="H601" t="n">
         <v>124984</v>
@@ -17943,7 +17943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.56782388687134</v>
       </c>
       <c r="H606" t="n">
         <v>11629</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18001,7 +18001,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082733154297</v>
+        <v>5.48082780838013</v>
       </c>
       <c r="H608" t="n">
         <v>8454</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18059,7 +18059,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.56782388687134</v>
       </c>
       <c r="H610" t="n">
         <v>163362</v>
@@ -18088,7 +18088,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>5.81141662597656</v>
+        <v>5.81141710281372</v>
       </c>
       <c r="H611" t="n">
         <v>67041</v>
@@ -18117,7 +18117,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661800384521</v>
+        <v>5.77661752700806</v>
       </c>
       <c r="H612" t="n">
         <v>36365</v>
@@ -18204,7 +18204,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>5.81141662597656</v>
+        <v>5.81141710281372</v>
       </c>
       <c r="H615" t="n">
         <v>25918</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281095504761</v>
+        <v>6.00281143188477</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281095504761</v>
+        <v>6.00281143188477</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468544006348</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562274932861</v>
+        <v>6.87562322616577</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18610,7 +18610,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.4812479019165</v>
+        <v>7.48124694824219</v>
       </c>
       <c r="H629" t="n">
         <v>152384</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874862670898</v>
+        <v>7.90874814987183</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968593597412</v>
+        <v>7.8196849822998</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18697,7 +18697,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.14031028747559</v>
+        <v>8.1403112411499</v>
       </c>
       <c r="H632" t="n">
         <v>59783</v>
@@ -18871,7 +18871,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890434265137</v>
+        <v>9.12890338897705</v>
       </c>
       <c r="H638" t="n">
         <v>117220</v>
@@ -18900,7 +18900,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702781677246</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H639" t="n">
         <v>47607</v>
@@ -18958,7 +18958,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.8171854019165</v>
+        <v>8.81718444824219</v>
       </c>
       <c r="H641" t="n">
         <v>40921</v>
@@ -18987,7 +18987,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937171936035</v>
+        <v>8.79937267303467</v>
       </c>
       <c r="H642" t="n">
         <v>24861</v>
@@ -19103,7 +19103,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702781677246</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H646" t="n">
         <v>97578</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19161,7 +19161,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046474456787</v>
+        <v>9.93046569824219</v>
       </c>
       <c r="H648" t="n">
         <v>98237</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781202316284</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19335,7 +19335,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.845308303833</v>
+        <v>11.8453092575073</v>
       </c>
       <c r="H654" t="n">
         <v>47177</v>
@@ -19364,7 +19364,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671848297119</v>
+        <v>11.6671838760376</v>
       </c>
       <c r="H655" t="n">
         <v>87639</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781202316284</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781202316284</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19596,7 +19596,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671848297119</v>
+        <v>11.6671838760376</v>
       </c>
       <c r="H663" t="n">
         <v>11952</v>
@@ -19625,7 +19625,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H664" t="n">
         <v>25174</v>
@@ -19683,7 +19683,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H666" t="n">
         <v>12852</v>
@@ -19712,7 +19712,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H667" t="n">
         <v>20242</v>
@@ -19741,7 +19741,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H668" t="n">
         <v>9685</v>
@@ -19828,7 +19828,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H671" t="n">
         <v>3415</v>
@@ -19857,7 +19857,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.455150604248</v>
+        <v>11.4551515579224</v>
       </c>
       <c r="H672" t="n">
         <v>11052</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363977432251</v>
+        <v>10.7363967895508</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -19944,7 +19944,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.4102296829224</v>
+        <v>11.410228729248</v>
       </c>
       <c r="H675" t="n">
         <v>30625</v>
@@ -20002,7 +20002,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H677" t="n">
         <v>9507</v>
@@ -20031,7 +20031,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H678" t="n">
         <v>18194</v>
@@ -20060,7 +20060,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H679" t="n">
         <v>7332</v>
@@ -20118,7 +20118,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H681" t="n">
         <v>6945</v>
@@ -20147,7 +20147,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H682" t="n">
         <v>3572</v>
@@ -20205,7 +20205,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.7696056365967</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H684" t="n">
         <v>11051</v>
@@ -20234,7 +20234,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.7696056365967</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H685" t="n">
         <v>9237</v>
@@ -20292,7 +20292,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H687" t="n">
         <v>8053</v>
@@ -20321,7 +20321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449962615967</v>
+        <v>11.5449953079224</v>
       </c>
       <c r="H688" t="n">
         <v>8002</v>
@@ -20350,7 +20350,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H689" t="n">
         <v>10841</v>
@@ -20437,7 +20437,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H692" t="n">
         <v>140958</v>
@@ -20466,7 +20466,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868045806885</v>
+        <v>13.3868036270142</v>
       </c>
       <c r="H693" t="n">
         <v>49176</v>
@@ -20553,7 +20553,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>17.6544075012207</v>
+        <v>17.6544094085693</v>
       </c>
       <c r="H696" t="n">
         <v>330825</v>
@@ -20611,7 +20611,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H698" t="n">
         <v>59019</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180870056152</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20756,7 +20756,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239406585693</v>
+        <v>17.923942565918</v>
       </c>
       <c r="H703" t="n">
         <v>17675</v>
@@ -20785,7 +20785,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H704" t="n">
         <v>50153</v>
@@ -20814,7 +20814,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.7442531585693</v>
+        <v>17.7442512512207</v>
       </c>
       <c r="H705" t="n">
         <v>29563</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -20988,7 +20988,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H711" t="n">
         <v>7977</v>
@@ -21075,7 +21075,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H714" t="n">
         <v>56021</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21162,7 +21162,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H717" t="n">
         <v>48881</v>
@@ -21191,7 +21191,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051887512207</v>
+        <v>17.2051868438721</v>
       </c>
       <c r="H718" t="n">
         <v>51474</v>
@@ -21249,7 +21249,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H720" t="n">
         <v>23381</v>
@@ -21278,7 +21278,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H721" t="n">
         <v>30310</v>
@@ -21365,7 +21365,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5645637512207</v>
+        <v>17.5645656585693</v>
       </c>
       <c r="H724" t="n">
         <v>21861</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H728" t="n">
         <v>20822</v>
@@ -21597,7 +21597,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H732" t="n">
         <v>11380</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21655,7 +21655,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H734" t="n">
         <v>15613</v>
@@ -21713,7 +21713,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H736" t="n">
         <v>10110</v>
@@ -21742,7 +21742,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H737" t="n">
         <v>15411</v>
@@ -21800,7 +21800,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H739" t="n">
         <v>9553</v>
@@ -21858,7 +21858,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H741" t="n">
         <v>81245</v>
@@ -21887,7 +21887,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H742" t="n">
         <v>26368</v>
@@ -21945,7 +21945,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H744" t="n">
         <v>13809</v>
@@ -22003,7 +22003,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H746" t="n">
         <v>42523</v>
@@ -22061,7 +22061,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372104644775</v>
+        <v>16.0372123718262</v>
       </c>
       <c r="H748" t="n">
         <v>6624</v>
@@ -22090,7 +22090,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372104644775</v>
+        <v>16.0372123718262</v>
       </c>
       <c r="H749" t="n">
         <v>4575</v>
@@ -22148,7 +22148,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864330291748</v>
+        <v>16.4864311218262</v>
       </c>
       <c r="H751" t="n">
         <v>22548</v>
@@ -22177,7 +22177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110443115234</v>
+        <v>16.7110462188721</v>
       </c>
       <c r="H752" t="n">
         <v>38381</v>
@@ -22264,7 +22264,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H755" t="n">
         <v>10473</v>
@@ -22438,7 +22438,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H761" t="n">
         <v>15074</v>
@@ -22612,7 +22612,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.318455696106</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H767" t="n">
         <v>6092</v>
@@ -22641,7 +22641,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040016174316</v>
+        <v>15.004002571106</v>
       </c>
       <c r="H768" t="n">
         <v>16692</v>
@@ -22757,7 +22757,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864330291748</v>
+        <v>16.4864311218262</v>
       </c>
       <c r="H772" t="n">
         <v>30917</v>
@@ -22931,7 +22931,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H778" t="n">
         <v>8343</v>
@@ -23018,7 +23018,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H781" t="n">
         <v>3445</v>
@@ -23076,7 +23076,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H783" t="n">
         <v>3772</v>
@@ -23105,7 +23105,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H784" t="n">
         <v>9640</v>
@@ -23134,7 +23134,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H785" t="n">
         <v>2827</v>
@@ -23279,7 +23279,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126029968262</v>
+        <v>15.8126020431519</v>
       </c>
       <c r="H790" t="n">
         <v>9326</v>
@@ -23337,7 +23337,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922895431519</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H792" t="n">
         <v>6586</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024467468262</v>
+        <v>15.9024457931519</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227563858032</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H800" t="n">
         <v>4924</v>
@@ -23598,7 +23598,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.318455696106</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H801" t="n">
         <v>17725</v>
@@ -23888,7 +23888,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590797424316</v>
+        <v>14.9590787887573</v>
       </c>
       <c r="H811" t="n">
         <v>1809</v>
@@ -23946,7 +23946,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098581314087</v>
+        <v>14.5098571777344</v>
       </c>
       <c r="H813" t="n">
         <v>12514</v>
@@ -23975,7 +23975,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H814" t="n">
         <v>10409</v>
@@ -24091,7 +24091,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H818" t="n">
         <v>34207</v>
@@ -24120,7 +24120,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H819" t="n">
         <v>15464</v>
@@ -24178,7 +24178,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.599702835083</v>
+        <v>14.5997037887573</v>
       </c>
       <c r="H821" t="n">
         <v>12526</v>
@@ -24265,7 +24265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055574417114</v>
+        <v>14.1055583953857</v>
       </c>
       <c r="H824" t="n">
         <v>35205</v>
@@ -24294,7 +24294,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461824417114</v>
+        <v>13.7461814880371</v>
       </c>
       <c r="H825" t="n">
         <v>7453</v>
@@ -24352,7 +24352,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H827" t="n">
         <v>23439</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680498123169</v>
+        <v>12.6680507659912</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24584,7 +24584,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>12.0391397476196</v>
+        <v>12.0391387939453</v>
       </c>
       <c r="H835" t="n">
         <v>9700</v>
@@ -24671,7 +24671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H838" t="n">
         <v>13270</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332832336426</v>
+        <v>12.5332841873169</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24758,7 +24758,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578945159912</v>
+        <v>12.7578935623169</v>
       </c>
       <c r="H841" t="n">
         <v>18683</v>
@@ -24787,7 +24787,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172723770142</v>
+        <v>13.1172714233398</v>
       </c>
       <c r="H842" t="n">
         <v>4865</v>
@@ -24845,7 +24845,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H844" t="n">
         <v>6802</v>
@@ -24874,7 +24874,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969598770142</v>
+        <v>13.2969608306885</v>
       </c>
       <c r="H845" t="n">
         <v>4249</v>
@@ -25077,7 +25077,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954030990601</v>
+        <v>14.1954021453857</v>
       </c>
       <c r="H852" t="n">
         <v>6891</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.3993158340454</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25396,7 +25396,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766618728638</v>
+        <v>15.7766628265381</v>
       </c>
       <c r="H863" t="n">
         <v>44798</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407264709473</v>
+        <v>15.7407255172729</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25512,7 +25512,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250988006592</v>
+        <v>15.5250997543335</v>
       </c>
       <c r="H867" t="n">
         <v>7118</v>
@@ -25541,7 +25541,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454113006592</v>
+        <v>15.3454103469849</v>
       </c>
       <c r="H868" t="n">
         <v>4337</v>
@@ -25599,7 +25599,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>14.6446256637573</v>
+        <v>14.644624710083</v>
       </c>
       <c r="H870" t="n">
         <v>3094</v>
@@ -25744,7 +25744,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>14.6446256637573</v>
+        <v>14.644624710083</v>
       </c>
       <c r="H875" t="n">
         <v>7498</v>
@@ -25773,7 +25773,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>14.734468460083</v>
+        <v>14.7344694137573</v>
       </c>
       <c r="H876" t="n">
         <v>2092</v>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108205795288</v>
+        <v>2.88108229637146</v>
       </c>
       <c r="H2" t="n">
         <v>41400</v>
@@ -456,7 +456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H3" t="n">
         <v>13950</v>
@@ -514,7 +514,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248680114746</v>
+        <v>2.90248703956604</v>
       </c>
       <c r="H5" t="n">
         <v>8550</v>
@@ -543,7 +543,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H6" t="n">
         <v>1350</v>
@@ -572,7 +572,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H7" t="n">
         <v>7200</v>
@@ -601,7 +601,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H8" t="n">
         <v>2700</v>
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H9" t="n">
         <v>1350</v>
@@ -659,7 +659,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762400627136</v>
+        <v>2.90762376785278</v>
       </c>
       <c r="H10" t="n">
         <v>2250</v>
@@ -688,7 +688,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H11" t="n">
         <v>450</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H12" t="n">
         <v>1800</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>3.37949991226196</v>
       </c>
       <c r="G21" t="n">
-        <v>2.89349675178528</v>
+        <v>2.89349699020386</v>
       </c>
       <c r="H21" t="n">
         <v>450</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1065,7 +1065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H24" t="n">
         <v>450</v>
@@ -1123,7 +1123,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974389076233</v>
+        <v>2.79974412918091</v>
       </c>
       <c r="H26" t="n">
         <v>1800</v>
@@ -1181,7 +1181,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601166725159</v>
+        <v>2.81601142883301</v>
       </c>
       <c r="H28" t="n">
         <v>450</v>
@@ -1239,7 +1239,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549601554871</v>
+        <v>2.76549625396729</v>
       </c>
       <c r="H30" t="n">
         <v>3150</v>
@@ -1268,7 +1268,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H31" t="n">
         <v>4950</v>
@@ -1326,7 +1326,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542967796326</v>
+        <v>2.82542943954468</v>
       </c>
       <c r="H33" t="n">
         <v>2250</v>
@@ -1355,7 +1355,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035952568054</v>
+        <v>2.76035904884338</v>
       </c>
       <c r="H34" t="n">
         <v>1800</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1442,7 +1442,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H37" t="n">
         <v>5400</v>
@@ -1471,7 +1471,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368371009827</v>
+        <v>2.85368394851685</v>
       </c>
       <c r="H38" t="n">
         <v>6300</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385813713074</v>
+        <v>2.95385789871216</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779819488525</v>
+        <v>3.00779795646667</v>
       </c>
       <c r="H46" t="n">
         <v>7650</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666786193848</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256911277771</v>
+        <v>3.34256887435913</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489659309387</v>
+        <v>3.30489635467529</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2051,7 +2051,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345796585083</v>
+        <v>3.31345844268799</v>
       </c>
       <c r="H58" t="n">
         <v>4500</v>
@@ -2138,7 +2138,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071553230286</v>
+        <v>3.21071577072144</v>
       </c>
       <c r="H61" t="n">
         <v>11700</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483001708984</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.407639503479</v>
+        <v>3.40763926506042</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2283,7 +2283,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098504066467</v>
+        <v>3.61098480224609</v>
       </c>
       <c r="H66" t="n">
         <v>38250</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.966304063797</v>
+        <v>3.96630454063416</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2370,7 +2370,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293298721313</v>
+        <v>4.04293346405029</v>
       </c>
       <c r="H69" t="n">
         <v>51750</v>
@@ -2399,7 +2399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H70" t="n">
         <v>59850</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.2809534072876</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0669059753418</v>
+        <v>4.06690549850464</v>
       </c>
       <c r="H74" t="n">
         <v>18450</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128700256348</v>
+        <v>3.98128747940063</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2573,7 +2573,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409648895264</v>
+        <v>4.02409601211548</v>
       </c>
       <c r="H76" t="n">
         <v>450</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279196739197</v>
+        <v>3.91279220581055</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041139602661</v>
+        <v>3.87041068077087</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330785751343</v>
+        <v>3.96330738067627</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2921,7 +2921,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493272781372</v>
+        <v>3.91493248939514</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -2950,7 +2950,7 @@
         <v>4.67749977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>4.00483226776123</v>
+        <v>4.00483274459839</v>
       </c>
       <c r="H89" t="n">
         <v>17550</v>
@@ -2979,7 +2979,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H90" t="n">
         <v>17550</v>
@@ -3008,7 +3008,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H91" t="n">
         <v>4950</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H93" t="n">
         <v>10350</v>
@@ -3182,7 +3182,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834436416626</v>
+        <v>4.05834484100342</v>
       </c>
       <c r="H97" t="n">
         <v>900</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H98" t="n">
         <v>8100</v>
@@ -3298,7 +3298,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H101" t="n">
         <v>4050</v>
@@ -3356,7 +3356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H103" t="n">
         <v>2250</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H104" t="n">
         <v>9450</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.2809534072876</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.2809534072876</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.2809534072876</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H108" t="n">
         <v>11250</v>
@@ -3617,7 +3617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H112" t="n">
         <v>13950</v>
@@ -3704,7 +3704,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245861053467</v>
+        <v>4.21245908737183</v>
       </c>
       <c r="H115" t="n">
         <v>22950</v>
@@ -3733,7 +3733,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H116" t="n">
         <v>900</v>
@@ -3762,7 +3762,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H117" t="n">
         <v>5400</v>
@@ -3791,7 +3791,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H118" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H120" t="n">
         <v>11700</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.2809534072876</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4052,7 +4052,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500131607056</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H127" t="n">
         <v>10800</v>
@@ -4081,7 +4081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H128" t="n">
         <v>8100</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4168,7 +4168,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500131607056</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H131" t="n">
         <v>4950</v>
@@ -4255,7 +4255,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219135284424</v>
       </c>
       <c r="H134" t="n">
         <v>7200</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4313,7 +4313,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H136" t="n">
         <v>35100</v>
@@ -4342,7 +4342,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H137" t="n">
         <v>69750</v>
@@ -4371,7 +4371,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H138" t="n">
         <v>18000</v>
@@ -4400,7 +4400,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H139" t="n">
         <v>3150</v>
@@ -4429,7 +4429,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H140" t="n">
         <v>33750</v>
@@ -4458,7 +4458,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H141" t="n">
         <v>21150</v>
@@ -4487,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H142" t="n">
         <v>9900</v>
@@ -4545,7 +4545,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H144" t="n">
         <v>1350</v>
@@ -4574,7 +4574,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H145" t="n">
         <v>8550</v>
@@ -4603,7 +4603,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H146" t="n">
         <v>11250</v>
@@ -4632,7 +4632,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H147" t="n">
         <v>1350</v>
@@ -4661,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H148" t="n">
         <v>1350</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H149" t="n">
         <v>6750</v>
@@ -4719,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H151" t="n">
         <v>1800</v>
@@ -4777,7 +4777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H152" t="n">
         <v>13500</v>
@@ -4806,7 +4806,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H153" t="n">
         <v>3150</v>
@@ -4835,7 +4835,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H154" t="n">
         <v>3150</v>
@@ -4864,7 +4864,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H155" t="n">
         <v>27000</v>
@@ -4893,7 +4893,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H156" t="n">
         <v>1800</v>
@@ -4922,7 +4922,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H158" t="n">
         <v>1800</v>
@@ -4980,7 +4980,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433460235596</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H159" t="n">
         <v>2250</v>
@@ -5009,7 +5009,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H160" t="n">
         <v>7650</v>
@@ -5067,7 +5067,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H162" t="n">
         <v>20250</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5183,7 +5183,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H166" t="n">
         <v>10800</v>
@@ -5212,7 +5212,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H167" t="n">
         <v>14850</v>
@@ -5241,7 +5241,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56523942947388</v>
       </c>
       <c r="H168" t="n">
         <v>10800</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5386,7 +5386,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H173" t="n">
         <v>26100</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771579742432</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5647,7 +5647,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076482772827</v>
+        <v>7.02076435089111</v>
       </c>
       <c r="H182" t="n">
         <v>31050</v>
@@ -5705,7 +5705,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671644210815</v>
+        <v>6.80671739578247</v>
       </c>
       <c r="H184" t="n">
         <v>3600</v>
@@ -5734,7 +5734,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H185" t="n">
         <v>15750</v>
@@ -5763,7 +5763,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H186" t="n">
         <v>4050</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5937,7 +5937,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H192" t="n">
         <v>4950</v>
@@ -5966,7 +5966,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H194" t="n">
         <v>4050</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919376373291</v>
+        <v>7.14919328689575</v>
       </c>
       <c r="H196" t="n">
         <v>13950</v>
@@ -6082,7 +6082,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638380050659</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H197" t="n">
         <v>15750</v>
@@ -6111,7 +6111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638380050659</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H198" t="n">
         <v>10800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6198,7 +6198,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671644210815</v>
+        <v>6.80671739578247</v>
       </c>
       <c r="H201" t="n">
         <v>11250</v>
@@ -6227,7 +6227,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H202" t="n">
         <v>5400</v>
@@ -6256,7 +6256,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H203" t="n">
         <v>2250</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6459,7 +6459,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143106460571</v>
+        <v>6.42143154144287</v>
       </c>
       <c r="H210" t="n">
         <v>6300</v>
@@ -6488,7 +6488,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H211" t="n">
         <v>13050</v>
@@ -6517,7 +6517,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H212" t="n">
         <v>4050</v>
@@ -6546,7 +6546,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390790939331</v>
       </c>
       <c r="H213" t="n">
         <v>3150</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54986047744751</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862157821655</v>
+        <v>6.37862110137939</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -6952,7 +6952,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56523942947388</v>
       </c>
       <c r="H227" t="n">
         <v>19965</v>
@@ -6981,7 +6981,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H228" t="n">
         <v>3719</v>
@@ -7039,7 +7039,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H230" t="n">
         <v>49999</v>
@@ -7097,7 +7097,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019264221191</v>
+        <v>6.25019311904907</v>
       </c>
       <c r="H232" t="n">
         <v>20785</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300212860107</v>
+        <v>6.29300165176392</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7155,7 +7155,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H234" t="n">
         <v>15656</v>
@@ -7213,7 +7213,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H236" t="n">
         <v>20646</v>
@@ -7271,7 +7271,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019264221191</v>
+        <v>6.25019311904907</v>
       </c>
       <c r="H238" t="n">
         <v>4610</v>
@@ -7358,7 +7358,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H241" t="n">
         <v>2766</v>
@@ -7387,7 +7387,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H247" t="n">
         <v>3650</v>
@@ -7561,7 +7561,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176418304443</v>
+        <v>6.12176465988159</v>
       </c>
       <c r="H248" t="n">
         <v>751</v>
@@ -7619,7 +7619,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052528381348</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H250" t="n">
         <v>4710</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771579742432</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771579742432</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771579742432</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8025,7 +8025,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052528381348</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H264" t="n">
         <v>1575</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8141,7 +8141,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052528381348</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H268" t="n">
         <v>2072</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771579742432</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8402,7 +8402,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H277" t="n">
         <v>1002</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8547,7 +8547,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052528381348</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H282" t="n">
         <v>3735</v>
@@ -8576,7 +8576,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052528381348</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H283" t="n">
         <v>5807</v>
@@ -8605,7 +8605,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052528381348</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H284" t="n">
         <v>498</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H285" t="n">
         <v>5658</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771579742432</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8924,7 +8924,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209825515747</v>
       </c>
       <c r="H295" t="n">
         <v>3196</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9040,7 +9040,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H299" t="n">
         <v>2360</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9098,7 +9098,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H301" t="n">
         <v>2357</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9243,7 +9243,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H306" t="n">
         <v>6889</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H309" t="n">
         <v>714</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9388,7 +9388,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H311" t="n">
         <v>1072</v>
@@ -9417,7 +9417,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56523942947388</v>
       </c>
       <c r="H312" t="n">
         <v>1448</v>
@@ -9446,7 +9446,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56523942947388</v>
       </c>
       <c r="H313" t="n">
         <v>8895</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366836547852</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9562,7 +9562,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H317" t="n">
         <v>4780</v>
@@ -9591,7 +9591,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H318" t="n">
         <v>25735</v>
@@ -9620,7 +9620,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557397842407</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H319" t="n">
         <v>5941</v>
@@ -9649,7 +9649,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H320" t="n">
         <v>9329</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995452880859</v>
+        <v>5.17995500564575</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H322" t="n">
         <v>7516</v>
@@ -9852,7 +9852,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H327" t="n">
         <v>5844</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051556587219</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -9997,7 +9997,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104912757874</v>
       </c>
       <c r="H332" t="n">
         <v>17685</v>
@@ -10026,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857228279114</v>
+        <v>2.56857252120972</v>
       </c>
       <c r="H333" t="n">
         <v>13836</v>
@@ -10287,7 +10287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971641540527</v>
+        <v>4.10971546173096</v>
       </c>
       <c r="H342" t="n">
         <v>27229</v>
@@ -10316,7 +10316,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533538818359</v>
       </c>
       <c r="H343" t="n">
         <v>19120</v>
@@ -10345,7 +10345,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.8871066570282</v>
+        <v>3.88710641860962</v>
       </c>
       <c r="H344" t="n">
         <v>14534</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723909378052</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299217224121</v>
+        <v>3.73299193382263</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10432,7 +10432,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038241386414</v>
+        <v>3.51038217544556</v>
       </c>
       <c r="H347" t="n">
         <v>4841</v>
@@ -10461,7 +10461,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743977546692</v>
+        <v>3.58743953704834</v>
       </c>
       <c r="H348" t="n">
         <v>5375</v>
@@ -10490,7 +10490,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H349" t="n">
         <v>8462</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593481063843</v>
+        <v>3.65593457221985</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881063461304</v>
+        <v>3.63881087303162</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10606,7 +10606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H353" t="n">
         <v>1950</v>
@@ -10635,7 +10635,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894426345825</v>
+        <v>3.51894450187683</v>
       </c>
       <c r="H354" t="n">
         <v>4650</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10722,7 +10722,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.41620111465454</v>
+        <v>3.41620135307312</v>
       </c>
       <c r="H357" t="n">
         <v>4102</v>
@@ -10751,7 +10751,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.41620111465454</v>
+        <v>3.41620135307312</v>
       </c>
       <c r="H358" t="n">
         <v>4270</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10867,7 +10867,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861162185669</v>
       </c>
       <c r="H362" t="n">
         <v>19084</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723909378052</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861162185669</v>
       </c>
       <c r="H364" t="n">
         <v>2419</v>
@@ -10954,7 +10954,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004881858826</v>
+        <v>3.81004905700684</v>
       </c>
       <c r="H365" t="n">
         <v>3480</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854480743408</v>
+        <v>3.8785445690155</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285830497742</v>
+        <v>3.85285878181458</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11099,7 +11099,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H370" t="n">
         <v>55309</v>
@@ -11128,7 +11128,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H371" t="n">
         <v>176118</v>
@@ -11186,7 +11186,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G373" t="n">
-        <v>4.82891607284546</v>
+        <v>4.8289155960083</v>
       </c>
       <c r="H373" t="n">
         <v>122121</v>
@@ -11273,7 +11273,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.4008207321167</v>
+        <v>4.40082120895386</v>
       </c>
       <c r="H376" t="n">
         <v>38510</v>
@@ -11331,7 +11331,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H378" t="n">
         <v>10379</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239179611206</v>
+        <v>4.2723913192749</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11447,7 +11447,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838346481323</v>
+        <v>5.30838298797607</v>
       </c>
       <c r="H382" t="n">
         <v>137190</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303079605103</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838346481323</v>
+        <v>5.30838298797607</v>
       </c>
       <c r="H387" t="n">
         <v>39972</v>
@@ -11621,7 +11621,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H388" t="n">
         <v>21205</v>
@@ -11679,7 +11679,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H390" t="n">
         <v>18684</v>
@@ -11708,7 +11708,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015449523926</v>
+        <v>5.00015497207642</v>
       </c>
       <c r="H391" t="n">
         <v>16426</v>
@@ -11737,7 +11737,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015449523926</v>
+        <v>5.00015497207642</v>
       </c>
       <c r="H392" t="n">
         <v>5797</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11853,7 +11853,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20563983917236</v>
+        <v>5.20564031600952</v>
       </c>
       <c r="H396" t="n">
         <v>4787</v>
@@ -11882,7 +11882,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H397" t="n">
         <v>5833</v>
@@ -11969,7 +11969,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H400" t="n">
         <v>1473</v>
@@ -11998,7 +11998,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H401" t="n">
         <v>1401</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303079605103</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12114,7 +12114,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H405" t="n">
         <v>961</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12201,7 +12201,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H408" t="n">
         <v>8938</v>
@@ -12288,7 +12288,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H411" t="n">
         <v>1244</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12346,7 +12346,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H413" t="n">
         <v>3640</v>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H417" t="n">
         <v>3912</v>
@@ -12520,7 +12520,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550621032715</v>
+        <v>5.32550668716431</v>
       </c>
       <c r="H419" t="n">
         <v>44555</v>
@@ -12578,7 +12578,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H421" t="n">
         <v>10486</v>
@@ -12665,7 +12665,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H424" t="n">
         <v>970</v>
@@ -12694,7 +12694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H425" t="n">
         <v>3416</v>
@@ -12723,7 +12723,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H426" t="n">
         <v>4511</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13042,7 +13042,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988771438599</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H437" t="n">
         <v>7970</v>
@@ -13100,7 +13100,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988771438599</v>
+        <v>5.23988723754883</v>
       </c>
       <c r="H439" t="n">
         <v>4505</v>
@@ -13129,7 +13129,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H440" t="n">
         <v>592</v>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H441" t="n">
         <v>915</v>
@@ -13245,7 +13245,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H444" t="n">
         <v>1100</v>
@@ -13274,7 +13274,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H445" t="n">
         <v>4470</v>
@@ -13303,7 +13303,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H446" t="n">
         <v>504</v>
@@ -13332,7 +13332,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H447" t="n">
         <v>2883</v>
@@ -13361,7 +13361,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H448" t="n">
         <v>7543</v>
@@ -13390,7 +13390,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851661682129</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H449" t="n">
         <v>2920</v>
@@ -13448,7 +13448,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H451" t="n">
         <v>650</v>
@@ -13477,7 +13477,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H452" t="n">
         <v>930</v>
@@ -13506,7 +13506,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H453" t="n">
         <v>7910</v>
@@ -13535,7 +13535,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023851394653</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H454" t="n">
         <v>900</v>
@@ -13564,7 +13564,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H455" t="n">
         <v>845</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0980396270752</v>
+        <v>5.09803915023804</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104211807251</v>
+        <v>5.01104259490967</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13709,7 +13709,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H460" t="n">
         <v>2330</v>
@@ -13825,7 +13825,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H464" t="n">
         <v>4200</v>
@@ -13912,7 +13912,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H467" t="n">
         <v>500</v>
@@ -13999,7 +13999,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H470" t="n">
         <v>4279</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.73265075683594</v>
+        <v>4.73265027999878</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14057,7 +14057,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H472" t="n">
         <v>10358</v>
@@ -14086,7 +14086,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.83704710006714</v>
+        <v>4.8370475769043</v>
       </c>
       <c r="H473" t="n">
         <v>2696</v>
@@ -14173,7 +14173,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H476" t="n">
         <v>4010</v>
@@ -14202,7 +14202,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005006790161</v>
+        <v>4.75005054473877</v>
       </c>
       <c r="H477" t="n">
         <v>1841</v>
@@ -14231,7 +14231,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H478" t="n">
         <v>2892</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.73265075683594</v>
+        <v>4.73265027999878</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14376,7 +14376,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H483" t="n">
         <v>6872</v>
@@ -14579,7 +14579,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>4.36726236343384</v>
+        <v>4.36726188659668</v>
       </c>
       <c r="H490" t="n">
         <v>1100</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.34986257553101</v>
+        <v>4.34986305236816</v>
       </c>
       <c r="H491" t="n">
         <v>11245</v>
@@ -14637,7 +14637,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286506652832</v>
       </c>
       <c r="H492" t="n">
         <v>21336</v>
@@ -14695,7 +14695,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887100219727</v>
+        <v>4.08887052536011</v>
       </c>
       <c r="H494" t="n">
         <v>1610</v>
@@ -14753,7 +14753,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286506652832</v>
       </c>
       <c r="H496" t="n">
         <v>3677</v>
@@ -14782,7 +14782,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416612625122</v>
+        <v>4.25416564941406</v>
       </c>
       <c r="H497" t="n">
         <v>1064</v>
@@ -14811,7 +14811,7 @@
         <v>5</v>
       </c>
       <c r="G498" t="n">
-        <v>4.34986257553101</v>
+        <v>4.34986305236816</v>
       </c>
       <c r="H498" t="n">
         <v>1568</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497068405151</v>
+        <v>4.1149697303772</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14898,7 +14898,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286506652832</v>
       </c>
       <c r="H501" t="n">
         <v>2104</v>
@@ -14927,7 +14927,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506443023682</v>
+        <v>4.31506395339966</v>
       </c>
       <c r="H502" t="n">
         <v>4690</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15217,7 +15217,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H512" t="n">
         <v>2873</v>
@@ -15304,7 +15304,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H515" t="n">
         <v>2290</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15420,7 +15420,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H519" t="n">
         <v>2418</v>
@@ -15449,7 +15449,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H520" t="n">
         <v>140</v>
@@ -15478,7 +15478,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H527" t="n">
         <v>920</v>
@@ -15681,7 +15681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H528" t="n">
         <v>1750</v>
@@ -15768,7 +15768,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H531" t="n">
         <v>7058</v>
@@ -15797,7 +15797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H532" t="n">
         <v>16579</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15971,7 +15971,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H538" t="n">
         <v>1392</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16116,7 +16116,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525049209595</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H543" t="n">
         <v>300</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825393676758</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16203,7 +16203,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H546" t="n">
         <v>8745</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825393676758</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H549" t="n">
         <v>1333</v>
@@ -16319,7 +16319,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525049209595</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H550" t="n">
         <v>3677</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16464,7 +16464,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H555" t="n">
         <v>3530</v>
@@ -16493,7 +16493,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H556" t="n">
         <v>4770</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206098556519</v>
+        <v>4.40206146240234</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16609,7 +16609,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H560" t="n">
         <v>3592</v>
@@ -16638,7 +16638,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H561" t="n">
         <v>8531</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16696,7 +16696,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H563" t="n">
         <v>7869</v>
@@ -16725,7 +16725,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H564" t="n">
         <v>16117</v>
@@ -16754,7 +16754,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H565" t="n">
         <v>4770</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16841,7 +16841,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H568" t="n">
         <v>22400</v>
@@ -16870,7 +16870,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H569" t="n">
         <v>16615</v>
@@ -16899,7 +16899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H570" t="n">
         <v>4750</v>
@@ -16928,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H571" t="n">
         <v>855</v>
@@ -16986,7 +16986,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H573" t="n">
         <v>11120</v>
@@ -17015,7 +17015,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H574" t="n">
         <v>10615</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104211807251</v>
+        <v>5.01104259490967</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17276,7 +17276,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H583" t="n">
         <v>68126</v>
@@ -17305,7 +17305,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H584" t="n">
         <v>21315</v>
@@ -17334,7 +17334,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H585" t="n">
         <v>18151</v>
@@ -17363,7 +17363,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H586" t="n">
         <v>26713</v>
@@ -17392,7 +17392,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H587" t="n">
         <v>4942</v>
@@ -17421,7 +17421,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H588" t="n">
         <v>10524</v>
@@ -17450,7 +17450,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H589" t="n">
         <v>6920</v>
@@ -17479,7 +17479,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H590" t="n">
         <v>6044</v>
@@ -17537,7 +17537,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503618240356</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H592" t="n">
         <v>6452</v>
@@ -17566,7 +17566,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H593" t="n">
         <v>3697</v>
@@ -17595,7 +17595,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H594" t="n">
         <v>12574</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17653,7 +17653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023851394653</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H596" t="n">
         <v>9629</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983528137207</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H597" t="n">
         <v>33122</v>
@@ -17711,7 +17711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H598" t="n">
         <v>15675</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H600" t="n">
         <v>2830</v>
@@ -17943,7 +17943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782388687134</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H606" t="n">
         <v>11629</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.41122913360596</v>
+        <v>5.4112286567688</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.41122913360596</v>
+        <v>5.4112286567688</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18059,7 +18059,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782388687134</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H610" t="n">
         <v>163362</v>
@@ -18088,7 +18088,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>5.81141710281372</v>
+        <v>5.81141757965088</v>
       </c>
       <c r="H611" t="n">
         <v>67041</v>
@@ -18175,7 +18175,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881641387939</v>
+        <v>5.82881593704224</v>
       </c>
       <c r="H614" t="n">
         <v>16210</v>
@@ -18204,7 +18204,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>5.81141710281372</v>
+        <v>5.81141757965088</v>
       </c>
       <c r="H615" t="n">
         <v>25918</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281143188477</v>
+        <v>6.00281047821045</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281143188477</v>
+        <v>6.00281047821045</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437356948853</v>
+        <v>6.23437309265137</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031042098999</v>
+        <v>7.00031089782715</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18436,7 +18436,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.83999824523926</v>
+        <v>6.8399977684021</v>
       </c>
       <c r="H623" t="n">
         <v>76240</v>
@@ -18465,7 +18465,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718536376953</v>
+        <v>7.10718584060669</v>
       </c>
       <c r="H624" t="n">
         <v>102683</v>
@@ -18494,7 +18494,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G625" t="n">
-        <v>6.89343500137329</v>
+        <v>6.89343547821045</v>
       </c>
       <c r="H625" t="n">
         <v>84822</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468591690063</v>
+        <v>6.96468639373779</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562322616577</v>
+        <v>6.87562274932861</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18610,7 +18610,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.48124694824219</v>
+        <v>7.4812479019165</v>
       </c>
       <c r="H629" t="n">
         <v>152384</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874814987183</v>
+        <v>7.90874719619751</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.8196849822998</v>
+        <v>7.81968450546265</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18726,7 +18726,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.47874736785889</v>
+        <v>8.4787483215332</v>
       </c>
       <c r="H633" t="n">
         <v>83403</v>
@@ -18871,7 +18871,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890338897705</v>
+        <v>9.12890434265137</v>
       </c>
       <c r="H638" t="n">
         <v>117220</v>
@@ -18929,7 +18929,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437252044678</v>
+        <v>9.08437347412109</v>
       </c>
       <c r="H640" t="n">
         <v>42073</v>
@@ -19016,7 +19016,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G643" t="n">
-        <v>8.69249725341797</v>
+        <v>8.69249820709229</v>
       </c>
       <c r="H643" t="n">
         <v>30205</v>
@@ -19045,7 +19045,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G644" t="n">
-        <v>8.62124729156494</v>
+        <v>8.62124824523926</v>
       </c>
       <c r="H644" t="n">
         <v>31463</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062232971191</v>
+        <v>9.44062328338623</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19190,7 +19190,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093717575073</v>
+        <v>10.5093727111816</v>
       </c>
       <c r="H649" t="n">
         <v>113895</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781202316284</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19335,7 +19335,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453092575073</v>
+        <v>11.8453102111816</v>
       </c>
       <c r="H654" t="n">
         <v>47177</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781202316284</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781202316284</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19567,7 +19567,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562456130981</v>
+        <v>11.7562475204468</v>
       </c>
       <c r="H662" t="n">
         <v>64255</v>
@@ -19625,7 +19625,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H664" t="n">
         <v>25174</v>
@@ -19654,7 +19654,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.859450340271</v>
+        <v>11.8594512939453</v>
       </c>
       <c r="H665" t="n">
         <v>38062</v>
@@ -19683,7 +19683,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H666" t="n">
         <v>12852</v>
@@ -19857,7 +19857,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.4551515579224</v>
+        <v>11.455150604248</v>
       </c>
       <c r="H672" t="n">
         <v>11052</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363967895508</v>
+        <v>10.7363958358765</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -20118,7 +20118,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H681" t="n">
         <v>6945</v>
@@ -20147,7 +20147,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H682" t="n">
         <v>3572</v>
@@ -20263,7 +20263,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.814528465271</v>
+        <v>11.8145275115967</v>
       </c>
       <c r="H686" t="n">
         <v>31688</v>
@@ -20321,7 +20321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449953079224</v>
+        <v>11.5449962615967</v>
       </c>
       <c r="H688" t="n">
         <v>8002</v>
@@ -20350,7 +20350,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H689" t="n">
         <v>10841</v>
@@ -20379,7 +20379,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535947799683</v>
+        <v>12.3535938262939</v>
       </c>
       <c r="H690" t="n">
         <v>194061</v>
@@ -20408,7 +20408,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H691" t="n">
         <v>55853</v>
@@ -20437,7 +20437,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H692" t="n">
         <v>140958</v>
@@ -20524,7 +20524,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H695" t="n">
         <v>297213</v>
@@ -20611,7 +20611,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501125335693</v>
+        <v>17.2501106262207</v>
       </c>
       <c r="H698" t="n">
         <v>59019</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180850982666</v>
+        <v>18.4180870056152</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20756,7 +20756,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.923942565918</v>
+        <v>17.9239444732666</v>
       </c>
       <c r="H703" t="n">
         <v>17675</v>
@@ -20814,7 +20814,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.7442512512207</v>
+        <v>17.7442531585693</v>
       </c>
       <c r="H705" t="n">
         <v>29563</v>
@@ -20843,7 +20843,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H706" t="n">
         <v>37684</v>
@@ -20872,7 +20872,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399524688721</v>
       </c>
       <c r="H707" t="n">
         <v>16206</v>
@@ -21017,7 +21017,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H712" t="n">
         <v>12956</v>
@@ -21191,7 +21191,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051868438721</v>
+        <v>17.2051887512207</v>
       </c>
       <c r="H718" t="n">
         <v>51474</v>
@@ -21307,7 +21307,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H722" t="n">
         <v>31177</v>
@@ -21539,7 +21539,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399524688721</v>
       </c>
       <c r="H730" t="n">
         <v>22860</v>
@@ -21655,7 +21655,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501125335693</v>
+        <v>17.2501106262207</v>
       </c>
       <c r="H734" t="n">
         <v>15613</v>
@@ -21684,7 +21684,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153411865234</v>
+        <v>17.1153430938721</v>
       </c>
       <c r="H735" t="n">
         <v>6538</v>
@@ -21771,7 +21771,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399524688721</v>
       </c>
       <c r="H738" t="n">
         <v>18846</v>
@@ -22003,7 +22003,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H746" t="n">
         <v>42523</v>
@@ -22032,7 +22032,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0821342468262</v>
+        <v>16.0821323394775</v>
       </c>
       <c r="H747" t="n">
         <v>11492</v>
@@ -22061,7 +22061,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372123718262</v>
+        <v>16.0372142791748</v>
       </c>
       <c r="H748" t="n">
         <v>6624</v>
@@ -22090,7 +22090,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372123718262</v>
+        <v>16.0372142791748</v>
       </c>
       <c r="H749" t="n">
         <v>4575</v>
@@ -22119,7 +22119,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H750" t="n">
         <v>10298</v>
@@ -22148,7 +22148,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864311218262</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H751" t="n">
         <v>22548</v>
@@ -22177,7 +22177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110462188721</v>
+        <v>16.7110443115234</v>
       </c>
       <c r="H752" t="n">
         <v>38381</v>
@@ -22206,7 +22206,7 @@
         <v>18.25</v>
       </c>
       <c r="G753" t="n">
-        <v>16.3965892791748</v>
+        <v>16.3965873718262</v>
       </c>
       <c r="H753" t="n">
         <v>19504</v>
@@ -22293,7 +22293,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H756" t="n">
         <v>13943</v>
@@ -22380,7 +22380,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661205291748</v>
+        <v>16.6661224365234</v>
       </c>
       <c r="H759" t="n">
         <v>32049</v>
@@ -22409,7 +22409,7 @@
         <v>18.25</v>
       </c>
       <c r="G760" t="n">
-        <v>16.3965892791748</v>
+        <v>16.3965873718262</v>
       </c>
       <c r="H760" t="n">
         <v>10784</v>
@@ -22496,7 +22496,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H763" t="n">
         <v>17084</v>
@@ -22554,7 +22554,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778364181519</v>
+        <v>15.6778354644775</v>
       </c>
       <c r="H765" t="n">
         <v>16640</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22641,7 +22641,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.004002571106</v>
+        <v>15.0040035247803</v>
       </c>
       <c r="H768" t="n">
         <v>16692</v>
@@ -22670,7 +22670,7 @@
         <v>17</v>
       </c>
       <c r="G769" t="n">
-        <v>15.273533821106</v>
+        <v>15.2735357284546</v>
       </c>
       <c r="H769" t="n">
         <v>16809</v>
@@ -22699,7 +22699,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H770" t="n">
         <v>5930</v>
@@ -22728,7 +22728,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676773071289</v>
       </c>
       <c r="H771" t="n">
         <v>8915</v>
@@ -22757,7 +22757,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864311218262</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H772" t="n">
         <v>30917</v>
@@ -22786,7 +22786,7 @@
         <v>18.25</v>
       </c>
       <c r="G773" t="n">
-        <v>16.3965892791748</v>
+        <v>16.3965873718262</v>
       </c>
       <c r="H773" t="n">
         <v>27383</v>
@@ -22815,7 +22815,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H774" t="n">
         <v>3354</v>
@@ -22844,7 +22844,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H775" t="n">
         <v>13090</v>
@@ -22902,7 +22902,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>16.0821342468262</v>
+        <v>16.0821323394775</v>
       </c>
       <c r="H777" t="n">
         <v>6129</v>
@@ -22931,7 +22931,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H778" t="n">
         <v>8343</v>
@@ -22960,7 +22960,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H779" t="n">
         <v>4290</v>
@@ -22989,7 +22989,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270561218262</v>
+        <v>16.1270580291748</v>
       </c>
       <c r="H780" t="n">
         <v>2753</v>
@@ -23076,7 +23076,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H783" t="n">
         <v>3772</v>
@@ -23163,7 +23163,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H786" t="n">
         <v>2004</v>
@@ -23221,7 +23221,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H788" t="n">
         <v>14768</v>
@@ -23308,7 +23308,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676773071289</v>
       </c>
       <c r="H791" t="n">
         <v>2124</v>
@@ -23337,7 +23337,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H792" t="n">
         <v>6586</v>
@@ -23366,7 +23366,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676773071289</v>
       </c>
       <c r="H793" t="n">
         <v>7639</v>
@@ -23395,7 +23395,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H794" t="n">
         <v>4856</v>
@@ -23424,7 +23424,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H795" t="n">
         <v>3584</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024457931519</v>
+        <v>15.9024448394775</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23511,7 +23511,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H798" t="n">
         <v>13711</v>
@@ -23540,7 +23540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778364181519</v>
+        <v>15.6778354644775</v>
       </c>
       <c r="H799" t="n">
         <v>4638</v>
@@ -23627,7 +23627,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286148071289</v>
+        <v>15.2286128997803</v>
       </c>
       <c r="H802" t="n">
         <v>5534</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879898071289</v>
+        <v>15.5879917144775</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23714,7 +23714,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H805" t="n">
         <v>5836</v>
@@ -23743,7 +23743,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H806" t="n">
         <v>7842</v>
@@ -23772,7 +23772,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141597747803</v>
+        <v>14.9141578674316</v>
       </c>
       <c r="H807" t="n">
         <v>18172</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -23830,7 +23830,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H809" t="n">
         <v>1995</v>
@@ -23859,7 +23859,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.183690071106</v>
+        <v>15.1836910247803</v>
       </c>
       <c r="H810" t="n">
         <v>3859</v>
@@ -23888,7 +23888,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590787887573</v>
+        <v>14.9590797424316</v>
       </c>
       <c r="H811" t="n">
         <v>1809</v>
@@ -23917,7 +23917,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>14.6895475387573</v>
+        <v>14.689546585083</v>
       </c>
       <c r="H812" t="n">
         <v>4915</v>
@@ -23946,7 +23946,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098571777344</v>
+        <v>14.5098581314087</v>
       </c>
       <c r="H813" t="n">
         <v>12514</v>
@@ -24033,7 +24033,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>13.5215711593628</v>
+        <v>13.5215702056885</v>
       </c>
       <c r="H816" t="n">
         <v>17349</v>
@@ -24149,7 +24149,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H820" t="n">
         <v>14476</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504812240601</v>
+        <v>14.1504802703857</v>
       </c>
       <c r="H822" t="n">
         <v>17003</v>
@@ -24265,7 +24265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055583953857</v>
+        <v>14.1055593490601</v>
       </c>
       <c r="H824" t="n">
         <v>35205</v>
@@ -24352,7 +24352,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H827" t="n">
         <v>23439</v>
@@ -24381,7 +24381,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H828" t="n">
         <v>13048</v>
@@ -24410,7 +24410,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H829" t="n">
         <v>7670</v>
@@ -24439,7 +24439,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H830" t="n">
         <v>25666</v>
@@ -24468,7 +24468,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477392196655</v>
+        <v>12.8477373123169</v>
       </c>
       <c r="H831" t="n">
         <v>15063</v>
@@ -24555,7 +24555,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H834" t="n">
         <v>12679</v>
@@ -24700,7 +24700,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H839" t="n">
         <v>33921</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332841873169</v>
+        <v>12.5332832336426</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24816,7 +24816,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723495483398</v>
+        <v>13.0723485946655</v>
       </c>
       <c r="H843" t="n">
         <v>3970</v>
@@ -24845,7 +24845,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H844" t="n">
         <v>6802</v>
@@ -24932,7 +24932,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664930343628</v>
+        <v>13.5664939880371</v>
       </c>
       <c r="H847" t="n">
         <v>9274</v>
@@ -25106,7 +25106,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H853" t="n">
         <v>10148</v>
@@ -25135,7 +25135,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.273533821106</v>
+        <v>15.2735357284546</v>
       </c>
       <c r="H854" t="n">
         <v>51860</v>
@@ -25164,7 +25164,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H855" t="n">
         <v>45677</v>
@@ -25222,7 +25222,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H857" t="n">
         <v>10279</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993158340454</v>
+        <v>15.3993167877197</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25309,7 +25309,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H860" t="n">
         <v>4992</v>
@@ -25396,7 +25396,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766628265381</v>
+        <v>15.7766609191895</v>
       </c>
       <c r="H863" t="n">
         <v>44798</v>
@@ -25570,7 +25570,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602514266968</v>
+        <v>14.8602523803711</v>
       </c>
       <c r="H869" t="n">
         <v>12585</v>
@@ -25657,7 +25657,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368118286133</v>
+        <v>14.5368127822876</v>
       </c>
       <c r="H872" t="n">
         <v>5468</v>
@@ -25831,7 +25831,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H878" t="n">
         <v>3239</v>
@@ -25947,7 +25947,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135280609131</v>
+        <v>14.8135290145874</v>
       </c>
       <c r="H882" t="n">
         <v>7029</v>
@@ -25976,7 +25976,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H883" t="n">
         <v>869</v>
@@ -26005,7 +26005,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H884" t="n">
         <v>2276</v>
@@ -26034,7 +26034,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H885" t="n">
         <v>1989</v>
@@ -26121,7 +26121,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H888" t="n">
         <v>3111</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H890" t="n">
         <v>4619</v>
@@ -26208,7 +26208,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G891" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H891" t="n">
         <v>3839</v>
@@ -26411,7 +26411,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H898" t="n">
         <v>9737</v>
@@ -26643,7 +26643,7 @@
         <v>14</v>
       </c>
       <c r="G906" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H906" t="n">
         <v>8483</v>
@@ -26672,7 +26672,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824371337891</v>
+        <v>12.9824361801147</v>
       </c>
       <c r="H907" t="n">
         <v>3998</v>
@@ -26701,7 +26701,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345300674438</v>
+        <v>12.6345291137695</v>
       </c>
       <c r="H908" t="n">
         <v>11680</v>
@@ -26759,7 +26759,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908815383911</v>
+        <v>12.8908824920654</v>
       </c>
       <c r="H910" t="n">
         <v>845</v>
@@ -26846,7 +26846,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429735183716</v>
+        <v>12.5429744720459</v>
       </c>
       <c r="H913" t="n">
         <v>3259</v>
@@ -26875,7 +26875,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711511611938</v>
+        <v>12.6711521148682</v>
       </c>
       <c r="H914" t="n">
         <v>2839</v>
@@ -26991,7 +26991,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>13.0190582275391</v>
+        <v>13.0190591812134</v>
       </c>
       <c r="H918" t="n">
         <v>2344</v>
@@ -27107,7 +27107,7 @@
         <v>14</v>
       </c>
       <c r="G922" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H922" t="n">
         <v>4016</v>
@@ -27165,7 +27165,7 @@
         <v>14</v>
       </c>
       <c r="G924" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H924" t="n">
         <v>6097</v>
@@ -27194,7 +27194,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894617080688</v>
+        <v>12.6894626617432</v>
       </c>
       <c r="H925" t="n">
         <v>776</v>
@@ -27223,7 +27223,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514207839966</v>
+        <v>12.4514217376709</v>
       </c>
       <c r="H926" t="n">
         <v>3020</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359489440918</v>
+        <v>12.8359508514404</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27368,7 +27368,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739908218384</v>
+        <v>13.0739917755127</v>
       </c>
       <c r="H931" t="n">
         <v>824</v>
@@ -27455,7 +27455,7 @@
         <v>14</v>
       </c>
       <c r="G934" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H934" t="n">
         <v>399</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.092303276062</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27658,7 +27658,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>13.110613822937</v>
+        <v>13.1106128692627</v>
       </c>
       <c r="H941" t="n">
         <v>991</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.092303276062</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27774,7 +27774,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H945" t="n">
         <v>3109</v>
@@ -27861,7 +27861,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H948" t="n">
         <v>4180</v>
@@ -27919,7 +27919,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402849197388</v>
+        <v>14.7402839660645</v>
       </c>
       <c r="H950" t="n">
         <v>5635</v>
@@ -27948,7 +27948,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H951" t="n">
         <v>10192</v>
@@ -28035,7 +28035,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H954" t="n">
         <v>5306</v>
@@ -28064,7 +28064,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346046447754</v>
+        <v>13.9346055984497</v>
       </c>
       <c r="H955" t="n">
         <v>1552</v>
@@ -28151,7 +28151,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H958" t="n">
         <v>840</v>
@@ -28180,7 +28180,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951429367065</v>
+        <v>13.4951419830322</v>
       </c>
       <c r="H959" t="n">
         <v>2351</v>
@@ -28325,7 +28325,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H964" t="n">
         <v>2199</v>
@@ -28441,7 +28441,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303442001343</v>
+        <v>13.3303451538086</v>
       </c>
       <c r="H968" t="n">
         <v>853</v>
@@ -28644,7 +28644,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>13.7331848144531</v>
+        <v>13.7331838607788</v>
       </c>
       <c r="H975" t="n">
         <v>3867</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796701431274</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28760,7 +28760,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H979" t="n">
         <v>548</v>
@@ -28847,7 +28847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H982" t="n">
         <v>1433</v>
@@ -28876,7 +28876,7 @@
         <v>15</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7331848144531</v>
+        <v>13.7331838607788</v>
       </c>
       <c r="H983" t="n">
         <v>3489</v>
@@ -28905,7 +28905,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H984" t="n">
         <v>2674</v>
@@ -29166,7 +29166,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H993" t="n">
         <v>3823</v>
@@ -29224,7 +29224,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H995" t="n">
         <v>776</v>
@@ -29253,7 +29253,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G996" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H996" t="n">
         <v>786</v>
@@ -29282,7 +29282,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H997" t="n">
         <v>1556</v>
@@ -29311,7 +29311,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H998" t="n">
         <v>2430</v>
@@ -29340,7 +29340,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514963150024</v>
+        <v>13.7514953613281</v>
       </c>
       <c r="H999" t="n">
         <v>1949</v>
@@ -29369,7 +29369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1000" t="n">
         <v>1623</v>
@@ -29427,7 +29427,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712266921997</v>
+        <v>13.9712257385254</v>
       </c>
       <c r="H1002" t="n">
         <v>3350</v>
@@ -29456,7 +29456,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1003" t="n">
         <v>748</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796701431274</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29514,7 +29514,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.0810918807983</v>
+        <v>14.081090927124</v>
       </c>
       <c r="H1005" t="n">
         <v>1238</v>
@@ -29543,7 +29543,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1006" t="n">
         <v>626</v>
@@ -29572,7 +29572,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1007" t="n">
         <v>1460</v>
@@ -29630,7 +29630,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.9417037963867</v>
+        <v>14.941704750061</v>
       </c>
       <c r="H1009" t="n">
         <v>11362</v>
@@ -29659,7 +29659,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6670408248901</v>
+        <v>14.6670417785645</v>
       </c>
       <c r="H1010" t="n">
         <v>14618</v>
@@ -29717,7 +29717,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H1012" t="n">
         <v>11964</v>
@@ -29746,7 +29746,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H1013" t="n">
         <v>8822</v>
@@ -29775,7 +29775,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1014" t="n">
         <v>801</v>
@@ -29804,7 +29804,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1015" t="n">
         <v>6837</v>
@@ -29833,7 +29833,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H1016" t="n">
         <v>3081</v>
@@ -29978,7 +29978,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H1021" t="n">
         <v>924</v>
@@ -30326,7 +30326,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1033" t="n">
         <v>1202</v>
@@ -30384,7 +30384,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1035" t="n">
         <v>7293</v>
@@ -30558,7 +30558,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H1041" t="n">
         <v>3209</v>
@@ -30761,7 +30761,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H1048" t="n">
         <v>3540</v>
@@ -30993,7 +30993,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1056" t="n">
-        <v>14.6304187774658</v>
+        <v>14.6304178237915</v>
       </c>
       <c r="H1056" t="n">
         <v>9312</v>
@@ -31080,7 +31080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1059" t="n">
         <v>2147</v>
@@ -31399,7 +31399,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1070" t="n">
         <v>4599</v>
@@ -31428,7 +31428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1071" t="n">
         <v>15327</v>
@@ -31515,7 +31515,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1074" t="n">
         <v>4278</v>
@@ -31544,7 +31544,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>14.2458906173706</v>
+        <v>14.2458896636963</v>
       </c>
       <c r="H1075" t="n">
         <v>4709</v>
@@ -31573,7 +31573,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1076" t="n">
         <v>5561</v>
@@ -31602,7 +31602,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H1077" t="n">
         <v>8530</v>
@@ -31631,7 +31631,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1078" t="n">
         <v>11008</v>
@@ -31718,7 +31718,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1081" t="n">
         <v>104130</v>
@@ -31776,7 +31776,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H1083" t="n">
         <v>10646</v>
@@ -31892,7 +31892,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.161434173584</v>
+        <v>15.1614351272583</v>
       </c>
       <c r="H1087" t="n">
         <v>6067</v>
@@ -31921,7 +31921,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>15.0515699386597</v>
+        <v>15.051570892334</v>
       </c>
       <c r="H1088" t="n">
         <v>8528</v>
@@ -32008,7 +32008,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1091" t="n">
         <v>9320</v>
@@ -32124,7 +32124,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473840713501</v>
+        <v>15.7473850250244</v>
       </c>
       <c r="H1095" t="n">
         <v>11814</v>
@@ -32211,7 +32211,7 @@
         <v>17</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.5642738342285</v>
+        <v>15.5642757415771</v>
       </c>
       <c r="H1098" t="n">
         <v>8931</v>
@@ -32240,7 +32240,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8023176193237</v>
+        <v>15.802318572998</v>
       </c>
       <c r="H1099" t="n">
         <v>6086</v>
@@ -32356,7 +32356,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1103" t="n">
         <v>5347</v>
@@ -32385,7 +32385,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.5642738342285</v>
+        <v>15.5642757415771</v>
       </c>
       <c r="H1104" t="n">
         <v>4079</v>
@@ -32414,7 +32414,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572492599487</v>
+        <v>15.8572483062744</v>
       </c>
       <c r="H1105" t="n">
         <v>21663</v>
@@ -32443,7 +32443,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290735244751</v>
+        <v>15.7290725708008</v>
       </c>
       <c r="H1106" t="n">
         <v>5698</v>
@@ -32617,7 +32617,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699531555176</v>
+        <v>16.3699550628662</v>
       </c>
       <c r="H1112" t="n">
         <v>28938</v>
@@ -58665,6 +58665,64 @@
         <v>4200</v>
       </c>
       <c r="I2010" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2011" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2011" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="H2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2011" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2012" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2012" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>1.70500004291534</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="H2012" t="n">
+        <v>5095</v>
+      </c>
+      <c r="I2012" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H3" t="n">
         <v>13950</v>
@@ -485,7 +485,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H4" t="n">
         <v>7200</v>
@@ -514,7 +514,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248703956604</v>
+        <v>2.90248680114746</v>
       </c>
       <c r="H5" t="n">
         <v>8550</v>
@@ -543,7 +543,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H6" t="n">
         <v>1350</v>
@@ -572,7 +572,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H7" t="n">
         <v>7200</v>
@@ -601,7 +601,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H8" t="n">
         <v>2700</v>
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H9" t="n">
         <v>1350</v>
@@ -659,7 +659,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762376785278</v>
+        <v>2.90762400627136</v>
       </c>
       <c r="H10" t="n">
         <v>2250</v>
@@ -688,7 +688,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H11" t="n">
         <v>450</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H12" t="n">
         <v>1800</v>
@@ -746,7 +746,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H13" t="n">
         <v>3600</v>
@@ -775,7 +775,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>3.37949991226196</v>
       </c>
       <c r="G21" t="n">
-        <v>2.89349699020386</v>
+        <v>2.8934965133667</v>
       </c>
       <c r="H21" t="n">
         <v>450</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062021255493</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1065,7 +1065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H24" t="n">
         <v>450</v>
@@ -1152,7 +1152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255361557007</v>
       </c>
       <c r="H27" t="n">
         <v>450</v>
@@ -1268,7 +1268,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H31" t="n">
         <v>4950</v>
@@ -1297,7 +1297,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.84426593780518</v>
+        <v>2.8442656993866</v>
       </c>
       <c r="H32" t="n">
         <v>2700</v>
@@ -1326,7 +1326,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542943954468</v>
+        <v>2.82542991638184</v>
       </c>
       <c r="H33" t="n">
         <v>2250</v>
@@ -1355,7 +1355,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035904884338</v>
+        <v>2.76035928726196</v>
       </c>
       <c r="H34" t="n">
         <v>1800</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1442,7 +1442,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H37" t="n">
         <v>5400</v>
@@ -1500,7 +1500,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661405563354</v>
+        <v>2.91661429405212</v>
       </c>
       <c r="H39" t="n">
         <v>19350</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385789871216</v>
+        <v>2.95385837554932</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255361557007</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1906,7 +1906,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904914855957</v>
+        <v>3.03904938697815</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256887435913</v>
+        <v>3.34256863594055</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -2022,7 +2022,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626792907715</v>
+        <v>3.35626816749573</v>
       </c>
       <c r="H57" t="n">
         <v>20250</v>
@@ -2051,7 +2051,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345844268799</v>
+        <v>3.31345820426941</v>
       </c>
       <c r="H58" t="n">
         <v>4500</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768544197083</v>
+        <v>3.2376856803894</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2109,7 +2109,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309705734253</v>
+        <v>3.25309681892395</v>
       </c>
       <c r="H60" t="n">
         <v>5400</v>
@@ -2138,7 +2138,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071577072144</v>
+        <v>3.21071553230286</v>
       </c>
       <c r="H61" t="n">
         <v>11700</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36482977867126</v>
+        <v>3.36483001708984</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.40763926506042</v>
+        <v>3.407639503479</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757245063782</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2283,7 +2283,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098480224609</v>
+        <v>3.61098504066467</v>
       </c>
       <c r="H66" t="n">
         <v>38250</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518626213074</v>
+        <v>3.81518602371216</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2370,7 +2370,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293346405029</v>
+        <v>4.04293298721313</v>
       </c>
       <c r="H69" t="n">
         <v>51750</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.2809534072876</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2457,7 +2457,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028444290161</v>
+        <v>4.24028539657593</v>
       </c>
       <c r="H72" t="n">
         <v>10800</v>
@@ -2486,7 +2486,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087944030762</v>
+        <v>4.09087991714478</v>
       </c>
       <c r="H73" t="n">
         <v>33300</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.06690549850464</v>
+        <v>4.0669059753418</v>
       </c>
       <c r="H74" t="n">
         <v>18450</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128747940063</v>
+        <v>3.98128724098206</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2573,7 +2573,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409601211548</v>
+        <v>4.02409696578979</v>
       </c>
       <c r="H76" t="n">
         <v>450</v>
@@ -2602,7 +2602,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.93847751617432</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H77" t="n">
         <v>5850</v>
@@ -2631,7 +2631,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.93847751617432</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H78" t="n">
         <v>18900</v>
@@ -2689,7 +2689,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407585144043</v>
+        <v>3.91407632827759</v>
       </c>
       <c r="H80" t="n">
         <v>4950</v>
@@ -2718,7 +2718,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.0155348777771</v>
+        <v>4.01553535461426</v>
       </c>
       <c r="H81" t="n">
         <v>1800</v>
@@ -2747,7 +2747,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.9564573764801</v>
+        <v>3.95645761489868</v>
       </c>
       <c r="H82" t="n">
         <v>2250</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566802978516</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0082573890686</v>
+        <v>4.00825786590576</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041068077087</v>
+        <v>3.87041044235229</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330738067627</v>
+        <v>3.96330714225769</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566802978516</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493248939514</v>
+        <v>3.9149329662323</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -2950,7 +2950,7 @@
         <v>4.67749977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>4.00483274459839</v>
+        <v>4.00483226776123</v>
       </c>
       <c r="H89" t="n">
         <v>17550</v>
@@ -2979,7 +2979,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H90" t="n">
         <v>17550</v>
@@ -3008,7 +3008,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H91" t="n">
         <v>4950</v>
@@ -3037,7 +3037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H92" t="n">
         <v>6750</v>
@@ -3095,7 +3095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H96" t="n">
         <v>12600</v>
@@ -3182,7 +3182,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834484100342</v>
+        <v>4.05834436416626</v>
       </c>
       <c r="H97" t="n">
         <v>900</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H98" t="n">
         <v>8100</v>
@@ -3240,7 +3240,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H99" t="n">
         <v>8550</v>
@@ -3269,7 +3269,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H101" t="n">
         <v>4050</v>
@@ -3327,7 +3327,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H102" t="n">
         <v>4050</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.2809534072876</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.2809534072876</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.2809534072876</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H108" t="n">
         <v>11250</v>
@@ -3530,7 +3530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H109" t="n">
         <v>27450</v>
@@ -3588,7 +3588,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H111" t="n">
         <v>4500</v>
@@ -3617,7 +3617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H112" t="n">
         <v>13950</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3675,7 +3675,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3762,7 +3762,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H117" t="n">
         <v>5400</v>
@@ -3791,7 +3791,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H118" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H120" t="n">
         <v>11700</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.2809534072876</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4023,7 +4023,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376384735107</v>
+        <v>4.32376337051392</v>
       </c>
       <c r="H126" t="n">
         <v>900</v>
@@ -4052,7 +4052,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H127" t="n">
         <v>10800</v>
@@ -4081,7 +4081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H128" t="n">
         <v>8100</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4139,7 +4139,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H130" t="n">
         <v>1350</v>
@@ -4168,7 +4168,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H131" t="n">
         <v>4950</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4255,7 +4255,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219135284424</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H134" t="n">
         <v>7200</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4487,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H142" t="n">
         <v>9900</v>
@@ -4545,7 +4545,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H144" t="n">
         <v>1350</v>
@@ -4603,7 +4603,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H146" t="n">
         <v>11250</v>
@@ -4661,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H148" t="n">
         <v>1350</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H149" t="n">
         <v>6750</v>
@@ -4719,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H152" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H154" t="n">
         <v>3150</v>
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H158" t="n">
         <v>1800</v>
@@ -4980,7 +4980,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H159" t="n">
         <v>2250</v>
@@ -5009,7 +5009,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H160" t="n">
         <v>7650</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H163" t="n">
         <v>7650</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5183,7 +5183,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H166" t="n">
         <v>10800</v>
@@ -5212,7 +5212,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H167" t="n">
         <v>14850</v>
@@ -5241,7 +5241,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523942947388</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="n">
         <v>10800</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5328,7 +5328,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H171" t="n">
         <v>8100</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5386,7 +5386,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H173" t="n">
         <v>26100</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771579742432</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547945022583</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5734,7 +5734,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H185" t="n">
         <v>15750</v>
@@ -5763,7 +5763,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H186" t="n">
         <v>4050</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233541488647</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514490127563</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233541488647</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266948699951</v>
+        <v>6.5926685333252</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -5937,7 +5937,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H192" t="n">
         <v>4950</v>
@@ -5966,7 +5966,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H194" t="n">
         <v>4050</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919328689575</v>
+        <v>7.14919376373291</v>
       </c>
       <c r="H196" t="n">
         <v>13950</v>
@@ -6082,7 +6082,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638427734375</v>
+        <v>7.10638380050659</v>
       </c>
       <c r="H197" t="n">
         <v>15750</v>
@@ -6111,7 +6111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638427734375</v>
+        <v>7.10638380050659</v>
       </c>
       <c r="H198" t="n">
         <v>10800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514490127563</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233541488647</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6227,7 +6227,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H202" t="n">
         <v>5400</v>
@@ -6256,7 +6256,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H203" t="n">
         <v>2250</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547945022583</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266948699951</v>
+        <v>6.5926685333252</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6459,7 +6459,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143154144287</v>
+        <v>6.42143106460571</v>
       </c>
       <c r="H210" t="n">
         <v>6300</v>
@@ -6488,7 +6488,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109794616699</v>
+        <v>6.72109746932983</v>
       </c>
       <c r="H211" t="n">
         <v>13050</v>
@@ -6517,7 +6517,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H212" t="n">
         <v>4050</v>
@@ -6546,7 +6546,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390790939331</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H213" t="n">
         <v>3150</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862110137939</v>
+        <v>6.37862157821655</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6865,7 +6865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H224" t="n">
         <v>6100</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -6952,7 +6952,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523942947388</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="n">
         <v>19965</v>
@@ -6981,7 +6981,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H228" t="n">
         <v>3719</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7039,7 +7039,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G230" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H230" t="n">
         <v>49999</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300165176392</v>
+        <v>6.29300308227539</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7155,7 +7155,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H234" t="n">
         <v>15656</v>
@@ -7184,7 +7184,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H235" t="n">
         <v>2494</v>
@@ -7213,7 +7213,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H236" t="n">
         <v>20646</v>
@@ -7300,7 +7300,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H239" t="n">
         <v>7153</v>
@@ -7358,7 +7358,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H241" t="n">
         <v>2766</v>
@@ -7387,7 +7387,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H243" t="n">
         <v>3750</v>
@@ -7532,7 +7532,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G247" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H247" t="n">
         <v>3650</v>
@@ -7561,7 +7561,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>6.12176465988159</v>
+        <v>6.12176418304443</v>
       </c>
       <c r="H248" t="n">
         <v>751</v>
@@ -7590,7 +7590,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H249" t="n">
         <v>5546</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771579742432</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771579742432</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7909,7 +7909,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H260" t="n">
         <v>10941</v>
@@ -7938,7 +7938,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H261" t="n">
         <v>2202</v>
@@ -7967,7 +7967,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H262" t="n">
         <v>2060</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771579742432</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8054,7 +8054,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H265" t="n">
         <v>998</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8199,7 +8199,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H270" t="n">
         <v>12160</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771579742432</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8402,7 +8402,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209825515747</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H277" t="n">
         <v>1002</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8518,7 +8518,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H281" t="n">
         <v>14397</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209825515747</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H285" t="n">
         <v>5658</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771579742432</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8924,7 +8924,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209825515747</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H295" t="n">
         <v>3196</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9040,7 +9040,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H299" t="n">
         <v>2360</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9098,7 +9098,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H301" t="n">
         <v>2357</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9243,7 +9243,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H306" t="n">
         <v>6889</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H309" t="n">
         <v>714</v>
@@ -9388,7 +9388,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H311" t="n">
         <v>1072</v>
@@ -9417,7 +9417,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523942947388</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="n">
         <v>1448</v>
@@ -9446,7 +9446,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523942947388</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="n">
         <v>8895</v>
@@ -9475,7 +9475,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H314" t="n">
         <v>1549</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366836547852</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9562,7 +9562,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085887908936</v>
+        <v>5.65085983276367</v>
       </c>
       <c r="H317" t="n">
         <v>4780</v>
@@ -9591,7 +9591,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H318" t="n">
         <v>25735</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995500564575</v>
+        <v>5.17995405197144</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9736,7 +9736,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H323" t="n">
         <v>13319</v>
@@ -9765,7 +9765,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70905017852783</v>
       </c>
       <c r="H324" t="n">
         <v>7596</v>
@@ -9794,7 +9794,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H325" t="n">
         <v>7622</v>
@@ -9823,7 +9823,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H326" t="n">
         <v>6905</v>
@@ -9852,7 +9852,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26383066177368</v>
       </c>
       <c r="H327" t="n">
         <v>5844</v>
@@ -9910,7 +9910,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874429702759</v>
+        <v>3.69874453544617</v>
       </c>
       <c r="H329" t="n">
         <v>7210</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051556587219</v>
+        <v>3.39051580429077</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -9968,7 +9968,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242022514343</v>
+        <v>2.96241998672485</v>
       </c>
       <c r="H331" t="n">
         <v>25097</v>
@@ -9997,7 +9997,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104912757874</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H332" t="n">
         <v>17685</v>
@@ -10026,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857252120972</v>
+        <v>2.56857204437256</v>
       </c>
       <c r="H333" t="n">
         <v>13836</v>
@@ -10055,7 +10055,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>2.53432464599609</v>
+        <v>2.53432488441467</v>
       </c>
       <c r="H334" t="n">
         <v>25142</v>
@@ -10084,7 +10084,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158173561096</v>
+        <v>2.43158197402954</v>
       </c>
       <c r="H335" t="n">
         <v>3740</v>
@@ -10229,7 +10229,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560097694397</v>
+        <v>3.95560145378113</v>
       </c>
       <c r="H340" t="n">
         <v>40606</v>
@@ -10258,7 +10258,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062124252319</v>
       </c>
       <c r="H341" t="n">
         <v>24606</v>
@@ -10287,7 +10287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971546173096</v>
+        <v>4.10971593856812</v>
       </c>
       <c r="H342" t="n">
         <v>27229</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723909378052</v>
+        <v>3.76723980903625</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299193382263</v>
+        <v>3.73299241065979</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593457221985</v>
+        <v>3.65593528747559</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881087303162</v>
+        <v>3.63881134986877</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10635,7 +10635,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894450187683</v>
+        <v>3.51894402503967</v>
       </c>
       <c r="H354" t="n">
         <v>4650</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757245063782</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757245063782</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10838,7 +10838,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449689865112</v>
+        <v>3.66449642181396</v>
       </c>
       <c r="H361" t="n">
         <v>16600</v>
@@ -10867,7 +10867,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861162185669</v>
+        <v>3.81861090660095</v>
       </c>
       <c r="H362" t="n">
         <v>19084</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723909378052</v>
+        <v>3.76723980903625</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861162185669</v>
+        <v>3.81861090660095</v>
       </c>
       <c r="H364" t="n">
         <v>2419</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.8785445690155</v>
+        <v>3.87854433059692</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285878181458</v>
+        <v>3.852858543396</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11041,7 +11041,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329710006714</v>
+        <v>4.74329614639282</v>
       </c>
       <c r="H368" t="n">
         <v>77313</v>
@@ -11157,7 +11157,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H372" t="n">
         <v>50751</v>
@@ -11186,7 +11186,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G373" t="n">
-        <v>4.8289155960083</v>
+        <v>4.82891607284546</v>
       </c>
       <c r="H373" t="n">
         <v>122121</v>
@@ -11273,7 +11273,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082120895386</v>
+        <v>4.4008207321167</v>
       </c>
       <c r="H376" t="n">
         <v>38510</v>
@@ -11302,7 +11302,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H377" t="n">
         <v>13190</v>
@@ -11331,7 +11331,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26383066177368</v>
       </c>
       <c r="H378" t="n">
         <v>10379</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.2723913192749</v>
+        <v>4.27239274978638</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11418,7 +11418,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055395126343</v>
+        <v>4.64055442810059</v>
       </c>
       <c r="H381" t="n">
         <v>28041</v>
@@ -11476,7 +11476,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>5.08577394485474</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H383" t="n">
         <v>75589</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11563,7 +11563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H386" t="n">
         <v>87258</v>
@@ -11679,7 +11679,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H390" t="n">
         <v>18684</v>
@@ -11708,7 +11708,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015497207642</v>
+        <v>5.0001540184021</v>
       </c>
       <c r="H391" t="n">
         <v>16426</v>
@@ -11737,7 +11737,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015497207642</v>
+        <v>5.0001540184021</v>
       </c>
       <c r="H392" t="n">
         <v>5797</v>
@@ -11766,7 +11766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028764724731</v>
+        <v>4.88028717041016</v>
       </c>
       <c r="H393" t="n">
         <v>8696</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11853,7 +11853,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20564031600952</v>
+        <v>5.20563983917236</v>
       </c>
       <c r="H396" t="n">
         <v>4787</v>
@@ -11911,7 +11911,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H398" t="n">
         <v>11452</v>
@@ -11940,7 +11940,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.08577394485474</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H399" t="n">
         <v>4802</v>
@@ -11969,7 +11969,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H400" t="n">
         <v>1473</v>
@@ -11998,7 +11998,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H401" t="n">
         <v>1401</v>
@@ -12027,7 +12027,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H402" t="n">
         <v>4910</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12259,7 +12259,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.06864929199219</v>
+        <v>5.06864976882935</v>
       </c>
       <c r="H410" t="n">
         <v>5073</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H417" t="n">
         <v>3912</v>
@@ -12665,7 +12665,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H424" t="n">
         <v>970</v>
@@ -12723,7 +12723,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H426" t="n">
         <v>4511</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12897,7 +12897,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>5.08577394485474</v>
+        <v>5.08577346801758</v>
       </c>
       <c r="H432" t="n">
         <v>1500</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13042,7 +13042,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>5.23988723754883</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H437" t="n">
         <v>7970</v>
@@ -13100,7 +13100,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>5.23988723754883</v>
+        <v>5.23988771438599</v>
       </c>
       <c r="H439" t="n">
         <v>4505</v>
@@ -13129,7 +13129,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H440" t="n">
         <v>592</v>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H441" t="n">
         <v>915</v>
@@ -13245,7 +13245,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H444" t="n">
         <v>1100</v>
@@ -13274,7 +13274,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H445" t="n">
         <v>4470</v>
@@ -13303,7 +13303,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H446" t="n">
         <v>504</v>
@@ -13332,7 +13332,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H447" t="n">
         <v>2883</v>
@@ -13361,7 +13361,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714408874512</v>
       </c>
       <c r="H448" t="n">
         <v>7543</v>
@@ -13448,7 +13448,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H451" t="n">
         <v>650</v>
@@ -13477,7 +13477,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H452" t="n">
         <v>930</v>
@@ -13593,7 +13593,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543846130371</v>
+        <v>5.11543893814087</v>
       </c>
       <c r="H456" t="n">
         <v>3723</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13709,7 +13709,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H460" t="n">
         <v>2330</v>
@@ -13767,7 +13767,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08063936233521</v>
       </c>
       <c r="H462" t="n">
         <v>2675</v>
@@ -13796,7 +13796,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08063936233521</v>
       </c>
       <c r="H463" t="n">
         <v>1000</v>
@@ -13825,7 +13825,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H464" t="n">
         <v>4200</v>
@@ -13854,7 +13854,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H465" t="n">
         <v>3199</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H466" t="n">
         <v>2015</v>
@@ -13912,7 +13912,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H467" t="n">
         <v>500</v>
@@ -13970,7 +13970,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H469" t="n">
         <v>1484</v>
@@ -13999,7 +13999,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H470" t="n">
         <v>4279</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.73265027999878</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14057,7 +14057,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H472" t="n">
         <v>10358</v>
@@ -14173,7 +14173,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H476" t="n">
         <v>4010</v>
@@ -14202,7 +14202,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005054473877</v>
+        <v>4.75005006790161</v>
       </c>
       <c r="H477" t="n">
         <v>1841</v>
@@ -14231,7 +14231,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H478" t="n">
         <v>2892</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.73265027999878</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14318,7 +14318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H481" t="n">
         <v>6191</v>
@@ -14376,7 +14376,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H483" t="n">
         <v>6872</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H487" t="n">
         <v>537</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14579,7 +14579,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>4.36726188659668</v>
+        <v>4.36726236343384</v>
       </c>
       <c r="H490" t="n">
         <v>1100</v>
@@ -14637,7 +14637,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286506652832</v>
+        <v>4.26286602020264</v>
       </c>
       <c r="H492" t="n">
         <v>21336</v>
@@ -14666,7 +14666,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896474838257</v>
+        <v>4.28896522521973</v>
       </c>
       <c r="H493" t="n">
         <v>5774</v>
@@ -14695,7 +14695,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887052536011</v>
+        <v>4.08887147903442</v>
       </c>
       <c r="H494" t="n">
         <v>1610</v>
@@ -14753,7 +14753,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286506652832</v>
+        <v>4.26286602020264</v>
       </c>
       <c r="H496" t="n">
         <v>3677</v>
@@ -14782,7 +14782,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416564941406</v>
+        <v>4.25416612625122</v>
       </c>
       <c r="H497" t="n">
         <v>1064</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.1149697303772</v>
+        <v>4.11497068405151</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14898,7 +14898,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286506652832</v>
+        <v>4.26286602020264</v>
       </c>
       <c r="H501" t="n">
         <v>2104</v>
@@ -14927,7 +14927,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506395339966</v>
+        <v>4.31506443023682</v>
       </c>
       <c r="H502" t="n">
         <v>4690</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456792831421</v>
+        <v>4.18456888198853</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -14985,7 +14985,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.30636405944824</v>
+        <v>4.3063645362854</v>
       </c>
       <c r="H504" t="n">
         <v>10900</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15217,7 +15217,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H512" t="n">
         <v>2873</v>
@@ -15304,7 +15304,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H515" t="n">
         <v>2290</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H517" t="n">
         <v>3170</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H518" t="n">
         <v>1170</v>
@@ -15420,7 +15420,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H519" t="n">
         <v>2418</v>
@@ -15449,7 +15449,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H520" t="n">
         <v>140</v>
@@ -15478,7 +15478,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H523" t="n">
         <v>6233</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H524" t="n">
         <v>1255</v>
@@ -15681,7 +15681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H528" t="n">
         <v>1750</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15797,7 +15797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H532" t="n">
         <v>16579</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15971,7 +15971,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H538" t="n">
         <v>1392</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16203,7 +16203,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H546" t="n">
         <v>8745</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H549" t="n">
         <v>1333</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206146240234</v>
+        <v>4.40206098556519</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16638,7 +16638,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H561" t="n">
         <v>8531</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16696,7 +16696,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H563" t="n">
         <v>7869</v>
@@ -16725,7 +16725,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H564" t="n">
         <v>16117</v>
@@ -16754,7 +16754,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H565" t="n">
         <v>4770</v>
@@ -16783,7 +16783,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08063936233521</v>
       </c>
       <c r="H566" t="n">
         <v>45160</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16870,7 +16870,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H569" t="n">
         <v>16615</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.8718466758728</v>
+        <v>4.87184619903564</v>
       </c>
       <c r="H572" t="n">
         <v>14439</v>
@@ -16986,7 +16986,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H573" t="n">
         <v>11120</v>
@@ -17015,7 +17015,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H574" t="n">
         <v>10615</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17102,7 +17102,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H577" t="n">
         <v>6090</v>
@@ -17131,7 +17131,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H578" t="n">
         <v>11230</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H579" t="n">
         <v>3281</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17276,7 +17276,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H583" t="n">
         <v>68126</v>
@@ -17334,7 +17334,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H585" t="n">
         <v>18151</v>
@@ -17363,7 +17363,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H586" t="n">
         <v>26713</v>
@@ -17392,7 +17392,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H587" t="n">
         <v>4942</v>
@@ -17421,7 +17421,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H588" t="n">
         <v>10524</v>
@@ -17450,7 +17450,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H589" t="n">
         <v>6920</v>
@@ -17508,7 +17508,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203369140625</v>
+        <v>5.27203321456909</v>
       </c>
       <c r="H591" t="n">
         <v>2345</v>
@@ -17566,7 +17566,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.1328387260437</v>
+        <v>5.13283824920654</v>
       </c>
       <c r="H593" t="n">
         <v>3697</v>
@@ -17595,7 +17595,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624254226685</v>
       </c>
       <c r="H594" t="n">
         <v>12574</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17711,7 +17711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H598" t="n">
         <v>15675</v>
@@ -17740,7 +17740,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203369140625</v>
+        <v>5.27203321456909</v>
       </c>
       <c r="H599" t="n">
         <v>16071</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.2372350692749</v>
+        <v>5.23723459243774</v>
       </c>
       <c r="H600" t="n">
         <v>2830</v>
@@ -17827,7 +17827,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>5.68962049484253</v>
+        <v>5.68962097167969</v>
       </c>
       <c r="H602" t="n">
         <v>98090</v>
@@ -17885,7 +17885,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68962049484253</v>
+        <v>5.68962097167969</v>
       </c>
       <c r="H604" t="n">
         <v>14365</v>
@@ -17914,7 +17914,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.63742208480835</v>
+        <v>5.63742256164551</v>
       </c>
       <c r="H605" t="n">
         <v>23583</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18001,7 +18001,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082780838013</v>
+        <v>5.48082685470581</v>
       </c>
       <c r="H608" t="n">
         <v>8454</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18088,7 +18088,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>5.81141757965088</v>
+        <v>5.81141662597656</v>
       </c>
       <c r="H611" t="n">
         <v>67041</v>
@@ -18117,7 +18117,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661752700806</v>
+        <v>5.77661800384521</v>
       </c>
       <c r="H612" t="n">
         <v>36365</v>
@@ -18146,7 +18146,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>5.79401683807373</v>
+        <v>5.79401731491089</v>
       </c>
       <c r="H613" t="n">
         <v>17964</v>
@@ -18175,7 +18175,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881593704224</v>
+        <v>5.82881641387939</v>
       </c>
       <c r="H614" t="n">
         <v>16210</v>
@@ -18204,7 +18204,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>5.81141757965088</v>
+        <v>5.81141662597656</v>
       </c>
       <c r="H615" t="n">
         <v>25918</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.9680118560791</v>
+        <v>5.96801233291626</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437261581421</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18378,7 +18378,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.5015606880188</v>
+        <v>6.50156116485596</v>
       </c>
       <c r="H621" t="n">
         <v>31678</v>
@@ -18465,7 +18465,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718584060669</v>
+        <v>7.10718536376953</v>
       </c>
       <c r="H624" t="n">
         <v>102683</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468639373779</v>
+        <v>6.96468544006348</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562274932861</v>
+        <v>6.87562322616577</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874719619751</v>
+        <v>7.90874767303467</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968450546265</v>
+        <v>7.81968545913696</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18697,7 +18697,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.1403112411499</v>
+        <v>8.14030933380127</v>
       </c>
       <c r="H632" t="n">
         <v>59783</v>
@@ -18726,7 +18726,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.4787483215332</v>
+        <v>8.47874736785889</v>
       </c>
       <c r="H633" t="n">
         <v>83403</v>
@@ -18813,7 +18813,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249599456787</v>
+        <v>9.26249694824219</v>
       </c>
       <c r="H636" t="n">
         <v>208819</v>
@@ -18842,7 +18842,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249599456787</v>
+        <v>9.26249694824219</v>
       </c>
       <c r="H637" t="n">
         <v>116116</v>
@@ -18929,7 +18929,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437347412109</v>
+        <v>9.08437061309814</v>
       </c>
       <c r="H640" t="n">
         <v>42073</v>
@@ -18958,7 +18958,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718444824219</v>
+        <v>8.8171854019165</v>
       </c>
       <c r="H641" t="n">
         <v>40921</v>
@@ -19016,7 +19016,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G643" t="n">
-        <v>8.69249820709229</v>
+        <v>8.69249725341797</v>
       </c>
       <c r="H643" t="n">
         <v>30205</v>
@@ -19045,7 +19045,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G644" t="n">
-        <v>8.62124824523926</v>
+        <v>8.62124729156494</v>
       </c>
       <c r="H644" t="n">
         <v>31463</v>
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624713897705</v>
+        <v>8.90624809265137</v>
       </c>
       <c r="H645" t="n">
         <v>112321</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19161,7 +19161,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046569824219</v>
+        <v>9.93046474456787</v>
       </c>
       <c r="H648" t="n">
         <v>98237</v>
@@ -19190,7 +19190,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093727111816</v>
+        <v>10.5093717575073</v>
       </c>
       <c r="H649" t="n">
         <v>113895</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19335,7 +19335,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453102111816</v>
+        <v>11.845308303833</v>
       </c>
       <c r="H654" t="n">
         <v>47177</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19538,7 +19538,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335903167725</v>
+        <v>11.5335893630981</v>
       </c>
       <c r="H661" t="n">
         <v>13950</v>
@@ -19567,7 +19567,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562475204468</v>
+        <v>11.7562465667725</v>
       </c>
       <c r="H662" t="n">
         <v>64255</v>
@@ -19712,7 +19712,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H667" t="n">
         <v>20242</v>
@@ -19741,7 +19741,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H668" t="n">
         <v>9685</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19828,7 +19828,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H671" t="n">
         <v>3415</v>
@@ -19857,7 +19857,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.455150604248</v>
+        <v>11.4551515579224</v>
       </c>
       <c r="H672" t="n">
         <v>11052</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363958358765</v>
+        <v>10.7363967895508</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20002,7 +20002,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H677" t="n">
         <v>9507</v>
@@ -20031,7 +20031,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H678" t="n">
         <v>18194</v>
@@ -20060,7 +20060,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H679" t="n">
         <v>7332</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20205,7 +20205,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H684" t="n">
         <v>11051</v>
@@ -20234,7 +20234,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H685" t="n">
         <v>9237</v>
@@ -20263,7 +20263,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>11.8145275115967</v>
+        <v>11.814528465271</v>
       </c>
       <c r="H686" t="n">
         <v>31688</v>
@@ -20292,7 +20292,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H687" t="n">
         <v>8053</v>
@@ -20379,7 +20379,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535938262939</v>
+        <v>12.3535947799683</v>
       </c>
       <c r="H690" t="n">
         <v>194061</v>
@@ -20524,7 +20524,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H695" t="n">
         <v>297213</v>
@@ -20582,7 +20582,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H697" t="n">
         <v>248766</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180870056152</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20727,7 +20727,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H702" t="n">
         <v>62036</v>
@@ -20756,7 +20756,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239444732666</v>
+        <v>17.923942565918</v>
       </c>
       <c r="H703" t="n">
         <v>17675</v>
@@ -20814,7 +20814,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.7442531585693</v>
+        <v>17.744255065918</v>
       </c>
       <c r="H705" t="n">
         <v>29563</v>
@@ -20843,7 +20843,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H706" t="n">
         <v>37684</v>
@@ -20872,7 +20872,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H707" t="n">
         <v>16206</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -21017,7 +21017,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H712" t="n">
         <v>12956</v>
@@ -21075,7 +21075,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H714" t="n">
         <v>56021</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21191,7 +21191,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051887512207</v>
+        <v>17.2051868438721</v>
       </c>
       <c r="H718" t="n">
         <v>51474</v>
@@ -21307,7 +21307,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H722" t="n">
         <v>31177</v>
@@ -21539,7 +21539,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H730" t="n">
         <v>22860</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21771,7 +21771,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399524688721</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H738" t="n">
         <v>18846</v>
@@ -21974,7 +21974,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H745" t="n">
         <v>15308</v>
@@ -22032,7 +22032,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H747" t="n">
         <v>11492</v>
@@ -22061,7 +22061,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>16.0372142791748</v>
+        <v>16.0372123718262</v>
       </c>
       <c r="H748" t="n">
         <v>6624</v>
@@ -22090,7 +22090,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>16.0372142791748</v>
+        <v>16.0372123718262</v>
       </c>
       <c r="H749" t="n">
         <v>4575</v>
@@ -22119,7 +22119,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H750" t="n">
         <v>10298</v>
@@ -22206,7 +22206,7 @@
         <v>18.25</v>
       </c>
       <c r="G753" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H753" t="n">
         <v>19504</v>
@@ -22235,7 +22235,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356555938721</v>
+        <v>16.9356575012207</v>
       </c>
       <c r="H754" t="n">
         <v>36349</v>
@@ -22293,7 +22293,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H756" t="n">
         <v>13943</v>
@@ -22351,7 +22351,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H758" t="n">
         <v>8367</v>
@@ -22380,7 +22380,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661224365234</v>
+        <v>16.6661205291748</v>
       </c>
       <c r="H759" t="n">
         <v>32049</v>
@@ -22409,7 +22409,7 @@
         <v>18.25</v>
       </c>
       <c r="G760" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H760" t="n">
         <v>10784</v>
@@ -22496,7 +22496,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H763" t="n">
         <v>17084</v>
@@ -22525,7 +22525,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415111541748</v>
+        <v>16.4415130615234</v>
       </c>
       <c r="H764" t="n">
         <v>5046</v>
@@ -22554,7 +22554,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H765" t="n">
         <v>16640</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387701034546</v>
+        <v>15.138768196106</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22641,7 +22641,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040035247803</v>
+        <v>15.004002571106</v>
       </c>
       <c r="H768" t="n">
         <v>16692</v>
@@ -22699,7 +22699,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H770" t="n">
         <v>5930</v>
@@ -22728,7 +22728,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H771" t="n">
         <v>8915</v>
@@ -22786,7 +22786,7 @@
         <v>18.25</v>
       </c>
       <c r="G773" t="n">
-        <v>16.3965873718262</v>
+        <v>16.3965892791748</v>
       </c>
       <c r="H773" t="n">
         <v>27383</v>
@@ -22815,7 +22815,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H774" t="n">
         <v>3354</v>
@@ -22844,7 +22844,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067436218262</v>
+        <v>16.3067455291748</v>
       </c>
       <c r="H775" t="n">
         <v>13090</v>
@@ -22873,7 +22873,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H776" t="n">
         <v>3032</v>
@@ -22902,7 +22902,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H777" t="n">
         <v>6129</v>
@@ -22960,7 +22960,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H779" t="n">
         <v>4290</v>
@@ -22989,7 +22989,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270580291748</v>
+        <v>16.1270561218262</v>
       </c>
       <c r="H780" t="n">
         <v>2753</v>
@@ -23018,7 +23018,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H781" t="n">
         <v>3445</v>
@@ -23105,7 +23105,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H784" t="n">
         <v>9640</v>
@@ -23134,7 +23134,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H785" t="n">
         <v>2827</v>
@@ -23192,7 +23192,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H787" t="n">
         <v>1452</v>
@@ -23308,7 +23308,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H791" t="n">
         <v>2124</v>
@@ -23366,7 +23366,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676773071289</v>
+        <v>15.7676782608032</v>
       </c>
       <c r="H793" t="n">
         <v>7639</v>
@@ -23395,7 +23395,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H794" t="n">
         <v>4856</v>
@@ -23424,7 +23424,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H795" t="n">
         <v>3584</v>
@@ -23453,7 +23453,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>15.3633794784546</v>
+        <v>15.3633804321289</v>
       </c>
       <c r="H796" t="n">
         <v>8529</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024448394775</v>
+        <v>15.9024457931519</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23540,7 +23540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H799" t="n">
         <v>4638</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H800" t="n">
         <v>4924</v>
@@ -23627,7 +23627,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286128997803</v>
+        <v>15.2286138534546</v>
       </c>
       <c r="H802" t="n">
         <v>5534</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879917144775</v>
+        <v>15.5879907608032</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23685,7 +23685,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H804" t="n">
         <v>6910</v>
@@ -23714,7 +23714,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H805" t="n">
         <v>5836</v>
@@ -23743,7 +23743,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H806" t="n">
         <v>7842</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387701034546</v>
+        <v>15.138768196106</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -23830,7 +23830,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H809" t="n">
         <v>1995</v>
@@ -23917,7 +23917,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>14.689546585083</v>
+        <v>14.6895475387573</v>
       </c>
       <c r="H812" t="n">
         <v>4915</v>
@@ -23946,7 +23946,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098581314087</v>
+        <v>14.5098571777344</v>
       </c>
       <c r="H813" t="n">
         <v>12514</v>
@@ -24004,7 +24004,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H815" t="n">
         <v>21544</v>
@@ -24033,7 +24033,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>13.5215702056885</v>
+        <v>13.5215711593628</v>
       </c>
       <c r="H816" t="n">
         <v>17349</v>
@@ -24062,7 +24062,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.554780960083</v>
+        <v>14.5547819137573</v>
       </c>
       <c r="H817" t="n">
         <v>53993</v>
@@ -24178,7 +24178,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.5997037887573</v>
+        <v>14.599702835083</v>
       </c>
       <c r="H821" t="n">
         <v>12526</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504802703857</v>
+        <v>14.1504812240601</v>
       </c>
       <c r="H822" t="n">
         <v>17003</v>
@@ -24236,7 +24236,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200124740601</v>
+        <v>14.4200134277344</v>
       </c>
       <c r="H823" t="n">
         <v>6212</v>
@@ -24265,7 +24265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055593490601</v>
+        <v>14.1055583953857</v>
       </c>
       <c r="H824" t="n">
         <v>35205</v>
@@ -24294,7 +24294,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461814880371</v>
+        <v>13.7461824417114</v>
       </c>
       <c r="H825" t="n">
         <v>7453</v>
@@ -24323,7 +24323,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H826" t="n">
         <v>4142</v>
@@ -24468,7 +24468,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477373123169</v>
+        <v>12.8477382659912</v>
       </c>
       <c r="H831" t="n">
         <v>15063</v>
@@ -24497,7 +24497,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129716873169</v>
+        <v>12.7129726409912</v>
       </c>
       <c r="H832" t="n">
         <v>7112</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680507659912</v>
+        <v>12.6680498123169</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24613,7 +24613,7 @@
         <v>12.5</v>
       </c>
       <c r="G836" t="n">
-        <v>11.2305402755737</v>
+        <v>11.230541229248</v>
       </c>
       <c r="H836" t="n">
         <v>26240</v>
@@ -24642,7 +24642,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.2305402755737</v>
+        <v>11.230541229248</v>
       </c>
       <c r="H837" t="n">
         <v>20126</v>
@@ -24671,7 +24671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H838" t="n">
         <v>13270</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332832336426</v>
+        <v>12.5332822799683</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24816,7 +24816,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723485946655</v>
+        <v>13.0723495483398</v>
       </c>
       <c r="H843" t="n">
         <v>3970</v>
@@ -24874,7 +24874,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969608306885</v>
+        <v>13.2969598770142</v>
       </c>
       <c r="H845" t="n">
         <v>4249</v>
@@ -24932,7 +24932,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664939880371</v>
+        <v>13.5664930343628</v>
       </c>
       <c r="H847" t="n">
         <v>9274</v>
@@ -24990,7 +24990,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012596130371</v>
+        <v>13.7012605667114</v>
       </c>
       <c r="H849" t="n">
         <v>4278</v>
@@ -25019,7 +25019,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911033630371</v>
+        <v>13.7911043167114</v>
       </c>
       <c r="H850" t="n">
         <v>2038</v>
@@ -25164,7 +25164,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329126358032</v>
+        <v>15.6329135894775</v>
       </c>
       <c r="H855" t="n">
         <v>45677</v>
@@ -25193,7 +25193,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.2196283340454</v>
+        <v>15.219630241394</v>
       </c>
       <c r="H856" t="n">
         <v>17742</v>
@@ -25222,7 +25222,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H857" t="n">
         <v>10279</v>
@@ -25280,7 +25280,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H859" t="n">
         <v>25099</v>
@@ -25309,7 +25309,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532241821289</v>
+        <v>15.4532260894775</v>
       </c>
       <c r="H860" t="n">
         <v>4992</v>
@@ -25338,7 +25338,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657209396362</v>
+        <v>15.1657228469849</v>
       </c>
       <c r="H861" t="n">
         <v>7654</v>
@@ -25367,7 +25367,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>15.3633794784546</v>
+        <v>15.3633804321289</v>
       </c>
       <c r="H862" t="n">
         <v>17177</v>
@@ -25396,7 +25396,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766609191895</v>
+        <v>15.7766628265381</v>
       </c>
       <c r="H863" t="n">
         <v>44798</v>
@@ -25425,7 +25425,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>16.118070602417</v>
+        <v>16.1180725097656</v>
       </c>
       <c r="H864" t="n">
         <v>30261</v>
@@ -25454,7 +25454,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563522338867</v>
+        <v>15.9563503265381</v>
       </c>
       <c r="H865" t="n">
         <v>11649</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407255172729</v>
+        <v>15.7407274246216</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25541,7 +25541,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454103469849</v>
+        <v>15.3454113006592</v>
       </c>
       <c r="H868" t="n">
         <v>4337</v>
@@ -25570,7 +25570,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G869" t="n">
-        <v>14.8602523803711</v>
+        <v>14.8602514266968</v>
       </c>
       <c r="H869" t="n">
         <v>12585</v>
@@ -25657,7 +25657,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368127822876</v>
+        <v>14.5368118286133</v>
       </c>
       <c r="H872" t="n">
         <v>5468</v>
@@ -25686,7 +25686,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H873" t="n">
         <v>5894</v>
@@ -25860,7 +25860,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G879" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H879" t="n">
         <v>8701</v>
@@ -25947,7 +25947,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135290145874</v>
+        <v>14.8135280609131</v>
       </c>
       <c r="H882" t="n">
         <v>7029</v>
@@ -26005,7 +26005,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H884" t="n">
         <v>2276</v>
@@ -26121,7 +26121,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H888" t="n">
         <v>3111</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H890" t="n">
         <v>4619</v>
@@ -26208,7 +26208,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G891" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H891" t="n">
         <v>3839</v>
@@ -26411,7 +26411,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501482009888</v>
+        <v>14.8501491546631</v>
       </c>
       <c r="H898" t="n">
         <v>9737</v>
@@ -26527,7 +26527,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>15.0149478912354</v>
+        <v>15.014946937561</v>
       </c>
       <c r="H902" t="n">
         <v>2675</v>
@@ -26556,7 +26556,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G903" t="n">
-        <v>14.6121082305908</v>
+        <v>14.6121072769165</v>
       </c>
       <c r="H903" t="n">
         <v>7365</v>
@@ -26643,7 +26643,7 @@
         <v>14</v>
       </c>
       <c r="G906" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H906" t="n">
         <v>8483</v>
@@ -26759,7 +26759,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908824920654</v>
+        <v>12.8908815383911</v>
       </c>
       <c r="H910" t="n">
         <v>845</v>
@@ -26817,7 +26817,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G912" t="n">
-        <v>12.6528396606445</v>
+        <v>12.6528406143188</v>
       </c>
       <c r="H912" t="n">
         <v>8775</v>
@@ -26875,7 +26875,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711521148682</v>
+        <v>12.6711511611938</v>
       </c>
       <c r="H914" t="n">
         <v>2839</v>
@@ -27049,7 +27049,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G920" t="n">
-        <v>13.3852767944336</v>
+        <v>13.3852758407593</v>
       </c>
       <c r="H920" t="n">
         <v>4325</v>
@@ -27107,7 +27107,7 @@
         <v>14</v>
       </c>
       <c r="G922" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H922" t="n">
         <v>4016</v>
@@ -27165,7 +27165,7 @@
         <v>14</v>
       </c>
       <c r="G924" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H924" t="n">
         <v>6097</v>
@@ -27194,7 +27194,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894626617432</v>
+        <v>12.6894617080688</v>
       </c>
       <c r="H925" t="n">
         <v>776</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359508514404</v>
+        <v>12.8359498977661</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27455,7 +27455,7 @@
         <v>14</v>
       </c>
       <c r="G934" t="n">
-        <v>12.8176383972168</v>
+        <v>12.8176393508911</v>
       </c>
       <c r="H934" t="n">
         <v>399</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27861,7 +27861,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H948" t="n">
         <v>4180</v>
@@ -27919,7 +27919,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402839660645</v>
+        <v>14.7402849197388</v>
       </c>
       <c r="H950" t="n">
         <v>5635</v>
@@ -27948,7 +27948,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501482009888</v>
+        <v>14.8501491546631</v>
       </c>
       <c r="H951" t="n">
         <v>10192</v>
@@ -28441,7 +28441,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303451538086</v>
+        <v>13.3303442001343</v>
       </c>
       <c r="H968" t="n">
         <v>853</v>
@@ -28586,7 +28586,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>14.0994024276733</v>
+        <v>14.099401473999</v>
       </c>
       <c r="H973" t="n">
         <v>4167</v>
@@ -28644,7 +28644,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>13.7331838607788</v>
+        <v>13.7331848144531</v>
       </c>
       <c r="H975" t="n">
         <v>3867</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28760,7 +28760,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H979" t="n">
         <v>548</v>
@@ -28818,7 +28818,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G981" t="n">
-        <v>14.2092685699463</v>
+        <v>14.209267616272</v>
       </c>
       <c r="H981" t="n">
         <v>3919</v>
@@ -28876,7 +28876,7 @@
         <v>15</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7331838607788</v>
+        <v>13.7331848144531</v>
       </c>
       <c r="H983" t="n">
         <v>3489</v>
@@ -28934,7 +28934,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G985" t="n">
-        <v>14.154335975647</v>
+        <v>14.1543350219727</v>
       </c>
       <c r="H985" t="n">
         <v>2097</v>
@@ -29050,7 +29050,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G989" t="n">
-        <v>14.2092685699463</v>
+        <v>14.209267616272</v>
       </c>
       <c r="H989" t="n">
         <v>1773</v>
@@ -29195,7 +29195,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>14.0994024276733</v>
+        <v>14.099401473999</v>
       </c>
       <c r="H994" t="n">
         <v>968</v>
@@ -29224,7 +29224,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H995" t="n">
         <v>776</v>
@@ -29253,7 +29253,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G996" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H996" t="n">
         <v>786</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29514,7 +29514,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.081090927124</v>
+        <v>14.0810918807983</v>
       </c>
       <c r="H1005" t="n">
         <v>1238</v>
@@ -29543,7 +29543,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1006" t="n">
         <v>626</v>
@@ -29572,7 +29572,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1007" t="n">
         <v>1460</v>
@@ -29659,7 +29659,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6670417785645</v>
+        <v>14.6670408248901</v>
       </c>
       <c r="H1010" t="n">
         <v>14618</v>
@@ -29717,7 +29717,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H1012" t="n">
         <v>11964</v>
@@ -29746,7 +29746,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.3374433517456</v>
+        <v>14.3374443054199</v>
       </c>
       <c r="H1013" t="n">
         <v>8822</v>
@@ -29775,7 +29775,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1014" t="n">
         <v>801</v>
@@ -29891,7 +29891,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909580230713</v>
       </c>
       <c r="H1018" t="n">
         <v>2476</v>
@@ -29978,7 +29978,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H1021" t="n">
         <v>924</v>
@@ -30065,7 +30065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0994024276733</v>
+        <v>14.099401473999</v>
       </c>
       <c r="H1024" t="n">
         <v>1162</v>
@@ -30094,7 +30094,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909580230713</v>
       </c>
       <c r="H1025" t="n">
         <v>1900</v>
@@ -30181,7 +30181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909580230713</v>
       </c>
       <c r="H1028" t="n">
         <v>5343</v>
@@ -30384,7 +30384,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1035" t="n">
         <v>7293</v>
@@ -30587,7 +30587,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1042" t="n">
         <v>8372</v>
@@ -30616,7 +30616,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1043" t="n">
         <v>2854</v>
@@ -30645,7 +30645,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1044" t="n">
         <v>1046</v>
@@ -30993,7 +30993,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1056" t="n">
-        <v>14.6304178237915</v>
+        <v>14.6304187774658</v>
       </c>
       <c r="H1056" t="n">
         <v>9312</v>
@@ -31051,7 +31051,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1058" t="n">
-        <v>14.6121082305908</v>
+        <v>14.6121072769165</v>
       </c>
       <c r="H1058" t="n">
         <v>10801</v>
@@ -31080,7 +31080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1059" t="n">
         <v>2147</v>
@@ -31399,7 +31399,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1070" t="n">
         <v>4599</v>
@@ -31428,7 +31428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1071" t="n">
         <v>15327</v>
@@ -31486,7 +31486,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>14.2825117111206</v>
+        <v>14.2825126647949</v>
       </c>
       <c r="H1073" t="n">
         <v>15777</v>
@@ -31515,7 +31515,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1074" t="n">
         <v>4278</v>
@@ -31544,7 +31544,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>14.2458896636963</v>
+        <v>14.2458906173706</v>
       </c>
       <c r="H1075" t="n">
         <v>4709</v>
@@ -31573,7 +31573,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1076" t="n">
         <v>5561</v>
@@ -31602,7 +31602,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.0444707870483</v>
+        <v>14.044469833374</v>
       </c>
       <c r="H1077" t="n">
         <v>8530</v>
@@ -31631,7 +31631,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1078" t="n">
         <v>11008</v>
@@ -31776,7 +31776,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H1083" t="n">
         <v>10646</v>
@@ -31805,7 +31805,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1084" t="n">
-        <v>15.0149478912354</v>
+        <v>15.014946937561</v>
       </c>
       <c r="H1084" t="n">
         <v>7700</v>
@@ -31834,7 +31834,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>15.0149478912354</v>
+        <v>15.014946937561</v>
       </c>
       <c r="H1085" t="n">
         <v>7742</v>
@@ -32066,7 +32066,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4361000061035</v>
+        <v>15.4360990524292</v>
       </c>
       <c r="H1093" t="n">
         <v>8188</v>
@@ -32095,7 +32095,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1094" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825862884521</v>
       </c>
       <c r="H1094" t="n">
         <v>4974</v>
@@ -32182,7 +32182,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825862884521</v>
       </c>
       <c r="H1097" t="n">
         <v>6511</v>
@@ -32588,7 +32588,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319141387939</v>
+        <v>16.1319122314453</v>
       </c>
       <c r="H1111" t="n">
         <v>48202</v>
@@ -32617,7 +32617,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699550628662</v>
+        <v>16.3699531555176</v>
       </c>
       <c r="H1112" t="n">
         <v>28938</v>
@@ -58723,6 +58723,35 @@
         <v>5095</v>
       </c>
       <c r="I2012" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2013" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2013" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>1.61500000953674</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="H2013" t="n">
+        <v>9259</v>
+      </c>
+      <c r="I2013" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108229637146</v>
+        <v>2.88108205795288</v>
       </c>
       <c r="H2" t="n">
         <v>41400</v>
@@ -659,7 +659,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762400627136</v>
+        <v>2.90762376785278</v>
       </c>
       <c r="H10" t="n">
         <v>2250</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441948890686</v>
+        <v>2.83441972732544</v>
       </c>
       <c r="H20" t="n">
         <v>900</v>
@@ -978,7 +978,7 @@
         <v>3.37949991226196</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8934965133667</v>
+        <v>2.89349675178528</v>
       </c>
       <c r="H21" t="n">
         <v>450</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062021255493</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8986337184906</v>
+        <v>2.89863395690918</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1123,7 +1123,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974412918091</v>
+        <v>2.79974389076233</v>
       </c>
       <c r="H26" t="n">
         <v>1800</v>
@@ -1210,7 +1210,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H29" t="n">
         <v>1800</v>
@@ -1326,7 +1326,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542991638184</v>
+        <v>2.82542967796326</v>
       </c>
       <c r="H33" t="n">
         <v>2250</v>
@@ -1384,7 +1384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399152755737</v>
+        <v>2.83399176597595</v>
       </c>
       <c r="H35" t="n">
         <v>7650</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1471,7 +1471,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368394851685</v>
+        <v>2.85368418693542</v>
       </c>
       <c r="H38" t="n">
         <v>6300</v>
@@ -1500,7 +1500,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661429405212</v>
+        <v>2.9166145324707</v>
       </c>
       <c r="H39" t="n">
         <v>19350</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779795646667</v>
+        <v>3.00779843330383</v>
       </c>
       <c r="H46" t="n">
         <v>7650</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1906,7 +1906,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904938697815</v>
+        <v>3.03904914855957</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256863594055</v>
+        <v>3.34256887435913</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -1964,7 +1964,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787263870239</v>
+        <v>3.19787240028381</v>
       </c>
       <c r="H55" t="n">
         <v>63900</v>
@@ -2022,7 +2022,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626816749573</v>
+        <v>3.35626792907715</v>
       </c>
       <c r="H57" t="n">
         <v>20250</v>
@@ -2051,7 +2051,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345820426941</v>
+        <v>3.31345796585083</v>
       </c>
       <c r="H58" t="n">
         <v>4500</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.407639503479</v>
+        <v>3.40763926506042</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2225,7 +2225,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873666763306</v>
+        <v>3.44873690605164</v>
       </c>
       <c r="H64" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757245063782</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518602371216</v>
+        <v>3.81518626213074</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630454063416</v>
+        <v>3.966304063797</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2399,7 +2399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H70" t="n">
         <v>59850</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2457,7 +2457,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028539657593</v>
+        <v>4.24028491973877</v>
       </c>
       <c r="H72" t="n">
         <v>10800</v>
@@ -2486,7 +2486,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087991714478</v>
+        <v>4.09087944030762</v>
       </c>
       <c r="H73" t="n">
         <v>33300</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0669059753418</v>
+        <v>4.06690645217896</v>
       </c>
       <c r="H74" t="n">
         <v>18450</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128724098206</v>
+        <v>3.98128652572632</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2573,7 +2573,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409696578979</v>
+        <v>4.02409648895264</v>
       </c>
       <c r="H76" t="n">
         <v>450</v>
@@ -2602,7 +2602,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847751617432</v>
       </c>
       <c r="H77" t="n">
         <v>5850</v>
@@ -2631,7 +2631,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847751617432</v>
       </c>
       <c r="H78" t="n">
         <v>18900</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279220581055</v>
+        <v>3.91279244422913</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2689,7 +2689,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407632827759</v>
+        <v>3.91407585144043</v>
       </c>
       <c r="H80" t="n">
         <v>4950</v>
@@ -2718,7 +2718,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553535461426</v>
+        <v>4.01553440093994</v>
       </c>
       <c r="H81" t="n">
         <v>1800</v>
@@ -2747,7 +2747,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.95645761489868</v>
+        <v>3.9564573764801</v>
       </c>
       <c r="H82" t="n">
         <v>2250</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566779136658</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825786590576</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041044235229</v>
+        <v>3.87041139602661</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330714225769</v>
+        <v>3.96330738067627</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566779136658</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.9149329662323</v>
+        <v>3.91493320465088</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -2950,7 +2950,7 @@
         <v>4.67749977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>4.00483226776123</v>
+        <v>4.00483179092407</v>
       </c>
       <c r="H89" t="n">
         <v>17550</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H93" t="n">
         <v>10350</v>
@@ -3356,7 +3356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H103" t="n">
         <v>2250</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H104" t="n">
         <v>9450</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H108" t="n">
         <v>11250</v>
@@ -3559,7 +3559,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H110" t="n">
         <v>21150</v>
@@ -3617,7 +3617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H112" t="n">
         <v>13950</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3704,7 +3704,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245908737183</v>
+        <v>4.21245861053467</v>
       </c>
       <c r="H115" t="n">
         <v>22950</v>
@@ -3733,7 +3733,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H116" t="n">
         <v>900</v>
@@ -3762,7 +3762,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H117" t="n">
         <v>5400</v>
@@ -3791,7 +3791,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H118" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H120" t="n">
         <v>11700</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4081,7 +4081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H128" t="n">
         <v>8100</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4197,7 +4197,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H132" t="n">
         <v>4050</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4255,7 +4255,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H134" t="n">
         <v>7200</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4313,7 +4313,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H136" t="n">
         <v>35100</v>
@@ -4429,7 +4429,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H140" t="n">
         <v>33750</v>
@@ -4458,7 +4458,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H141" t="n">
         <v>21150</v>
@@ -4487,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H142" t="n">
         <v>9900</v>
@@ -4516,7 +4516,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H143" t="n">
         <v>2250</v>
@@ -4574,7 +4574,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H145" t="n">
         <v>8550</v>
@@ -4632,7 +4632,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H147" t="n">
         <v>1350</v>
@@ -4661,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H148" t="n">
         <v>1350</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H149" t="n">
         <v>6750</v>
@@ -4719,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H153" t="n">
         <v>3150</v>
@@ -4835,7 +4835,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H154" t="n">
         <v>3150</v>
@@ -4864,7 +4864,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H155" t="n">
         <v>27000</v>
@@ -4893,7 +4893,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H156" t="n">
         <v>1800</v>
@@ -4922,7 +4922,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H158" t="n">
         <v>1800</v>
@@ -5009,7 +5009,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H160" t="n">
         <v>7650</v>
@@ -5038,7 +5038,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H161" t="n">
         <v>102150</v>
@@ -5067,7 +5067,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H162" t="n">
         <v>20250</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H163" t="n">
         <v>7650</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.60804986953735</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5183,7 +5183,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H166" t="n">
         <v>10800</v>
@@ -5212,7 +5212,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H167" t="n">
         <v>14850</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5328,7 +5328,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H171" t="n">
         <v>8100</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5386,7 +5386,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H173" t="n">
         <v>26100</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547801971436</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5734,7 +5734,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H185" t="n">
         <v>15750</v>
@@ -5763,7 +5763,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H186" t="n">
         <v>4050</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233541488647</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514490127563</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233541488647</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.5926685333252</v>
+        <v>6.59266948699951</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -5937,7 +5937,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G192" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H192" t="n">
         <v>4950</v>
@@ -5966,7 +5966,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G194" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H194" t="n">
         <v>4050</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919376373291</v>
+        <v>7.14919328689575</v>
       </c>
       <c r="H196" t="n">
         <v>13950</v>
@@ -6082,7 +6082,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638380050659</v>
+        <v>7.10638284683228</v>
       </c>
       <c r="H197" t="n">
         <v>15750</v>
@@ -6111,7 +6111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638380050659</v>
+        <v>7.10638284683228</v>
       </c>
       <c r="H198" t="n">
         <v>10800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514490127563</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233541488647</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6227,7 +6227,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H202" t="n">
         <v>5400</v>
@@ -6256,7 +6256,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H203" t="n">
         <v>2250</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547849655151</v>
+        <v>6.63547801971436</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.5926685333252</v>
+        <v>6.59266948699951</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6488,7 +6488,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>6.72109746932983</v>
+        <v>6.72109794616699</v>
       </c>
       <c r="H211" t="n">
         <v>13050</v>
@@ -6517,7 +6517,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H212" t="n">
         <v>4050</v>
@@ -6546,7 +6546,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H213" t="n">
         <v>3150</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862157821655</v>
+        <v>6.37862110137939</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -6981,7 +6981,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H228" t="n">
         <v>3719</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7097,7 +7097,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019264221191</v>
       </c>
       <c r="H232" t="n">
         <v>20785</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300308227539</v>
+        <v>6.29300212860107</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7184,7 +7184,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H235" t="n">
         <v>2494</v>
@@ -7271,7 +7271,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019264221191</v>
       </c>
       <c r="H238" t="n">
         <v>4610</v>
@@ -7619,7 +7619,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H250" t="n">
         <v>4710</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.60804986953735</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7967,7 +7967,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H262" t="n">
         <v>2060</v>
@@ -8025,7 +8025,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H264" t="n">
         <v>1575</v>
@@ -8054,7 +8054,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H265" t="n">
         <v>998</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8141,7 +8141,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H268" t="n">
         <v>2072</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8199,7 +8199,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H270" t="n">
         <v>12160</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8547,7 +8547,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H282" t="n">
         <v>3735</v>
@@ -8576,7 +8576,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H283" t="n">
         <v>5807</v>
@@ -8605,7 +8605,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052576065063</v>
+        <v>5.95052623748779</v>
       </c>
       <c r="H284" t="n">
         <v>498</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9040,7 +9040,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H299" t="n">
         <v>2360</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9098,7 +9098,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H301" t="n">
         <v>2357</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.60804986953735</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9243,7 +9243,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H306" t="n">
         <v>6889</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.60804986953735</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H309" t="n">
         <v>714</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.60804986953735</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9388,7 +9388,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H311" t="n">
         <v>1072</v>
@@ -9475,7 +9475,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H314" t="n">
         <v>1549</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9562,7 +9562,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085983276367</v>
+        <v>5.65085935592651</v>
       </c>
       <c r="H317" t="n">
         <v>4780</v>
@@ -9591,7 +9591,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H318" t="n">
         <v>25735</v>
@@ -9620,7 +9620,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H319" t="n">
         <v>5941</v>
@@ -9649,7 +9649,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H320" t="n">
         <v>9329</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995405197144</v>
+        <v>5.17995452880859</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H322" t="n">
         <v>7516</v>
@@ -9736,7 +9736,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70905017852783</v>
+        <v>4.70904970169067</v>
       </c>
       <c r="H323" t="n">
         <v>13319</v>
@@ -9765,7 +9765,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70905017852783</v>
+        <v>4.70904970169067</v>
       </c>
       <c r="H324" t="n">
         <v>7596</v>
@@ -9852,7 +9852,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383066177368</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H327" t="n">
         <v>5844</v>
@@ -9881,7 +9881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750563621521</v>
       </c>
       <c r="H328" t="n">
         <v>14468</v>
@@ -9968,7 +9968,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96241998672485</v>
+        <v>2.96242046356201</v>
       </c>
       <c r="H331" t="n">
         <v>25097</v>
@@ -10026,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857204437256</v>
+        <v>2.56857252120972</v>
       </c>
       <c r="H333" t="n">
         <v>13836</v>
@@ -10142,7 +10142,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H337" t="n">
         <v>1910</v>
@@ -10171,7 +10171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533538818359</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H343" t="n">
         <v>19120</v>
@@ -10345,7 +10345,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710641860962</v>
+        <v>3.88710618019104</v>
       </c>
       <c r="H344" t="n">
         <v>14534</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299241065979</v>
+        <v>3.73299193382263</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10461,7 +10461,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743953704834</v>
+        <v>3.58743929862976</v>
       </c>
       <c r="H348" t="n">
         <v>5375</v>
@@ -10490,7 +10490,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H349" t="n">
         <v>8462</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593528747559</v>
+        <v>3.65593457221985</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881134986877</v>
+        <v>3.6388111114502</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10606,7 +10606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H353" t="n">
         <v>1950</v>
@@ -10664,7 +10664,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750563621521</v>
       </c>
       <c r="H355" t="n">
         <v>3470</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757245063782</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757245063782</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10838,7 +10838,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449642181396</v>
+        <v>3.66449666023254</v>
       </c>
       <c r="H361" t="n">
         <v>16600</v>
@@ -10867,7 +10867,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861090660095</v>
+        <v>3.81861162185669</v>
       </c>
       <c r="H362" t="n">
         <v>19084</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861090660095</v>
+        <v>3.81861162185669</v>
       </c>
       <c r="H364" t="n">
         <v>2419</v>
@@ -10954,7 +10954,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004905700684</v>
+        <v>3.81004929542542</v>
       </c>
       <c r="H365" t="n">
         <v>3480</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.852858543396</v>
+        <v>3.85285830497742</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11041,7 +11041,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329614639282</v>
+        <v>4.74329662322998</v>
       </c>
       <c r="H368" t="n">
         <v>77313</v>
@@ -11070,7 +11070,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356388092041</v>
+        <v>4.50356435775757</v>
       </c>
       <c r="H369" t="n">
         <v>65581</v>
@@ -11099,7 +11099,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H370" t="n">
         <v>55309</v>
@@ -11128,7 +11128,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400196075439</v>
+        <v>5.39400243759155</v>
       </c>
       <c r="H371" t="n">
         <v>176118</v>
@@ -11157,7 +11157,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="n">
         <v>50751</v>
@@ -11215,7 +11215,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H374" t="n">
         <v>82279</v>
@@ -11331,7 +11331,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383066177368</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H378" t="n">
         <v>10379</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239274978638</v>
+        <v>4.27239179611206</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11418,7 +11418,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055442810059</v>
+        <v>4.64055395126343</v>
       </c>
       <c r="H381" t="n">
         <v>28041</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11534,7 +11534,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H385" t="n">
         <v>40025</v>
@@ -11563,7 +11563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="n">
         <v>87258</v>
@@ -11679,7 +11679,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H390" t="n">
         <v>18684</v>
@@ -11708,7 +11708,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.0001540184021</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H391" t="n">
         <v>16426</v>
@@ -11737,7 +11737,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.0001540184021</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H392" t="n">
         <v>5797</v>
@@ -11766,7 +11766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028717041016</v>
+        <v>4.88028764724731</v>
       </c>
       <c r="H393" t="n">
         <v>8696</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11969,7 +11969,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H400" t="n">
         <v>1473</v>
@@ -11998,7 +11998,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H401" t="n">
         <v>1401</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12114,7 +12114,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H405" t="n">
         <v>961</v>
@@ -12143,7 +12143,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H406" t="n">
         <v>2647</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12201,7 +12201,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H408" t="n">
         <v>8938</v>
@@ -12230,7 +12230,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H409" t="n">
         <v>4265</v>
@@ -12288,7 +12288,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H411" t="n">
         <v>1244</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12346,7 +12346,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152606964111</v>
+        <v>5.05152559280396</v>
       </c>
       <c r="H413" t="n">
         <v>3640</v>
@@ -12375,7 +12375,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H414" t="n">
         <v>1971</v>
@@ -12404,7 +12404,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H415" t="n">
         <v>4635</v>
@@ -12433,7 +12433,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H416" t="n">
         <v>12743</v>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H417" t="n">
         <v>3912</v>
@@ -12549,7 +12549,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H420" t="n">
         <v>11461</v>
@@ -12636,7 +12636,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H423" t="n">
         <v>4800</v>
@@ -12665,7 +12665,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H424" t="n">
         <v>970</v>
@@ -12723,7 +12723,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H426" t="n">
         <v>4511</v>
@@ -12752,7 +12752,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H427" t="n">
         <v>5140</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12839,7 +12839,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H430" t="n">
         <v>1010</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13129,7 +13129,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H440" t="n">
         <v>592</v>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H441" t="n">
         <v>915</v>
@@ -13187,7 +13187,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H442" t="n">
         <v>1564</v>
@@ -13245,7 +13245,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H444" t="n">
         <v>1100</v>
@@ -13274,7 +13274,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H445" t="n">
         <v>4470</v>
@@ -13303,7 +13303,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H446" t="n">
         <v>504</v>
@@ -13332,7 +13332,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289669036865</v>
       </c>
       <c r="H447" t="n">
         <v>2883</v>
@@ -13361,7 +13361,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714408874512</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H448" t="n">
         <v>7543</v>
@@ -13419,7 +13419,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.2024359703064</v>
+        <v>5.20243549346924</v>
       </c>
       <c r="H450" t="n">
         <v>2913</v>
@@ -13506,7 +13506,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H453" t="n">
         <v>7910</v>
@@ -13535,7 +13535,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023803710938</v>
       </c>
       <c r="H454" t="n">
         <v>900</v>
@@ -13593,7 +13593,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543893814087</v>
+        <v>5.11543846130371</v>
       </c>
       <c r="H456" t="n">
         <v>3723</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803915023804</v>
+        <v>5.0980396270752</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104211807251</v>
+        <v>5.01104259490967</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13709,7 +13709,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H460" t="n">
         <v>2330</v>
@@ -13767,7 +13767,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H462" t="n">
         <v>2675</v>
@@ -13796,7 +13796,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H463" t="n">
         <v>1000</v>
@@ -13854,7 +13854,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>4.95884323120117</v>
+        <v>4.95884370803833</v>
       </c>
       <c r="H465" t="n">
         <v>3199</v>
@@ -13941,7 +13941,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>5.04584121704102</v>
+        <v>5.04584074020386</v>
       </c>
       <c r="H468" t="n">
         <v>7558</v>
@@ -13970,7 +13970,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>4.95884323120117</v>
+        <v>4.95884370803833</v>
       </c>
       <c r="H469" t="n">
         <v>1484</v>
@@ -13999,7 +13999,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H470" t="n">
         <v>4279</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265075683594</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14057,7 +14057,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H472" t="n">
         <v>10358</v>
@@ -14115,7 +14115,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404508590698</v>
       </c>
       <c r="H474" t="n">
         <v>6712</v>
@@ -14144,7 +14144,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404508590698</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265075683594</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14318,7 +14318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H481" t="n">
         <v>6191</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H487" t="n">
         <v>537</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.34986305236816</v>
+        <v>4.34986257553101</v>
       </c>
       <c r="H491" t="n">
         <v>11245</v>
@@ -14637,7 +14637,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H492" t="n">
         <v>21336</v>
@@ -14695,7 +14695,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887147903442</v>
+        <v>4.08887052536011</v>
       </c>
       <c r="H494" t="n">
         <v>1610</v>
@@ -14753,7 +14753,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H496" t="n">
         <v>3677</v>
@@ -14782,7 +14782,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416612625122</v>
+        <v>4.25416564941406</v>
       </c>
       <c r="H497" t="n">
         <v>1064</v>
@@ -14811,7 +14811,7 @@
         <v>5</v>
       </c>
       <c r="G498" t="n">
-        <v>4.34986305236816</v>
+        <v>4.34986257553101</v>
       </c>
       <c r="H498" t="n">
         <v>1568</v>
@@ -14840,7 +14840,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.1410698890686</v>
+        <v>4.14106941223145</v>
       </c>
       <c r="H499" t="n">
         <v>11007</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497068405151</v>
+        <v>4.11497020721436</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14898,7 +14898,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>4.26286602020264</v>
+        <v>4.26286554336548</v>
       </c>
       <c r="H501" t="n">
         <v>2104</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456888198853</v>
+        <v>4.18456792831421</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785261154175</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15043,7 +15043,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.50645780563354</v>
+        <v>4.50645732879639</v>
       </c>
       <c r="H506" t="n">
         <v>5490</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H517" t="n">
         <v>3170</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H518" t="n">
         <v>1170</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H523" t="n">
         <v>6233</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H524" t="n">
         <v>1255</v>
@@ -15594,7 +15594,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.50645780563354</v>
+        <v>4.50645732879639</v>
       </c>
       <c r="H525" t="n">
         <v>2013</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.50645780563354</v>
+        <v>4.50645732879639</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H527" t="n">
         <v>920</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15768,7 +15768,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H531" t="n">
         <v>7058</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15942,7 +15942,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.50645780563354</v>
+        <v>4.50645732879639</v>
       </c>
       <c r="H537" t="n">
         <v>8283</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785261154175</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785261154175</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16116,7 +16116,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525144577026</v>
+        <v>4.71525096893311</v>
       </c>
       <c r="H543" t="n">
         <v>300</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16319,7 +16319,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525144577026</v>
+        <v>4.71525096893311</v>
       </c>
       <c r="H550" t="n">
         <v>3677</v>
@@ -16464,7 +16464,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H555" t="n">
         <v>3530</v>
@@ -16493,7 +16493,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H556" t="n">
         <v>4770</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206098556519</v>
+        <v>4.40206146240234</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16609,7 +16609,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905849456787</v>
+        <v>4.48905897140503</v>
       </c>
       <c r="H560" t="n">
         <v>3592</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305255889893</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16696,7 +16696,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H563" t="n">
         <v>7869</v>
@@ -16754,7 +16754,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H565" t="n">
         <v>4770</v>
@@ -16783,7 +16783,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08063936233521</v>
+        <v>5.08063983917236</v>
       </c>
       <c r="H566" t="n">
         <v>45160</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16841,7 +16841,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H568" t="n">
         <v>22400</v>
@@ -16928,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H571" t="n">
         <v>855</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.87184619903564</v>
+        <v>4.8718466758728</v>
       </c>
       <c r="H572" t="n">
         <v>14439</v>
@@ -16986,7 +16986,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H573" t="n">
         <v>11120</v>
@@ -17015,7 +17015,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H574" t="n">
         <v>10615</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.95884323120117</v>
+        <v>4.95884370803833</v>
       </c>
       <c r="H579" t="n">
         <v>3281</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104211807251</v>
+        <v>5.01104259490967</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17305,7 +17305,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H584" t="n">
         <v>21315</v>
@@ -17479,7 +17479,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H590" t="n">
         <v>6044</v>
@@ -17508,7 +17508,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203321456909</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H591" t="n">
         <v>2345</v>
@@ -17595,7 +17595,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.97624254226685</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H594" t="n">
         <v>12574</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324052810669</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17653,7 +17653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023803710938</v>
       </c>
       <c r="H596" t="n">
         <v>9629</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H597" t="n">
         <v>33122</v>
@@ -17740,7 +17740,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203321456909</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H599" t="n">
         <v>16071</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39382982254028</v>
+        <v>5.39383029937744</v>
       </c>
       <c r="H601" t="n">
         <v>124984</v>
@@ -17827,7 +17827,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>5.68962097167969</v>
+        <v>5.68962049484253</v>
       </c>
       <c r="H602" t="n">
         <v>98090</v>
@@ -17885,7 +17885,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68962097167969</v>
+        <v>5.68962049484253</v>
       </c>
       <c r="H604" t="n">
         <v>14365</v>
@@ -17914,7 +17914,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.63742256164551</v>
+        <v>5.63742208480835</v>
       </c>
       <c r="H605" t="n">
         <v>23583</v>
@@ -17943,7 +17943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H606" t="n">
         <v>11629</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.41122913360596</v>
+        <v>5.4112286567688</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18001,7 +18001,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082685470581</v>
+        <v>5.48082733154297</v>
       </c>
       <c r="H608" t="n">
         <v>8454</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.41122913360596</v>
+        <v>5.4112286567688</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18059,7 +18059,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H610" t="n">
         <v>163362</v>
@@ -18146,7 +18146,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>5.79401731491089</v>
+        <v>5.79401683807373</v>
       </c>
       <c r="H613" t="n">
         <v>17964</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801233291626</v>
+        <v>5.9680118560791</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18320,7 +18320,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>6.30562305450439</v>
+        <v>6.30562353134155</v>
       </c>
       <c r="H619" t="n">
         <v>24808</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437261581421</v>
+        <v>6.23437309265137</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18378,7 +18378,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.50156116485596</v>
+        <v>6.5015606880188</v>
       </c>
       <c r="H621" t="n">
         <v>31678</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031089782715</v>
+        <v>7.00031042098999</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18436,7 +18436,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.8399977684021</v>
+        <v>6.83999824523926</v>
       </c>
       <c r="H623" t="n">
         <v>76240</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468544006348</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562322616577</v>
+        <v>6.87562274932861</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18610,7 +18610,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.4812479019165</v>
+        <v>7.48124742507935</v>
       </c>
       <c r="H629" t="n">
         <v>152384</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874767303467</v>
+        <v>7.90874814987183</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968545913696</v>
+        <v>7.81968593597412</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18697,7 +18697,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.14030933380127</v>
+        <v>8.1403112411499</v>
       </c>
       <c r="H632" t="n">
         <v>59783</v>
@@ -18755,7 +18755,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343521118164</v>
+        <v>9.17343425750732</v>
       </c>
       <c r="H634" t="n">
         <v>112604</v>
@@ -18813,7 +18813,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249694824219</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H636" t="n">
         <v>208819</v>
@@ -18842,7 +18842,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249694824219</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H637" t="n">
         <v>116116</v>
@@ -18929,7 +18929,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437061309814</v>
+        <v>9.08437252044678</v>
       </c>
       <c r="H640" t="n">
         <v>42073</v>
@@ -18987,7 +18987,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937267303467</v>
+        <v>8.79937171936035</v>
       </c>
       <c r="H642" t="n">
         <v>24861</v>
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624809265137</v>
+        <v>8.90624713897705</v>
       </c>
       <c r="H645" t="n">
         <v>112321</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062232971191</v>
+        <v>9.44062328338623</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19219,7 +19219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109340667725</v>
+        <v>11.3109350204468</v>
       </c>
       <c r="H650" t="n">
         <v>160231</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19422,7 +19422,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>11.3999967575073</v>
+        <v>11.399995803833</v>
       </c>
       <c r="H657" t="n">
         <v>25340</v>
@@ -19451,7 +19451,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109340667725</v>
+        <v>11.3109350204468</v>
       </c>
       <c r="H658" t="n">
         <v>11498</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19538,7 +19538,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335893630981</v>
+        <v>11.5335903167725</v>
       </c>
       <c r="H661" t="n">
         <v>13950</v>
@@ -19567,7 +19567,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562465667725</v>
+        <v>11.7562456130981</v>
       </c>
       <c r="H662" t="n">
         <v>64255</v>
@@ -19625,7 +19625,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H664" t="n">
         <v>25174</v>
@@ -19654,7 +19654,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.8594512939453</v>
+        <v>11.859450340271</v>
       </c>
       <c r="H665" t="n">
         <v>38062</v>
@@ -19683,7 +19683,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H666" t="n">
         <v>12852</v>
@@ -19712,7 +19712,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H667" t="n">
         <v>20242</v>
@@ -19741,7 +19741,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H668" t="n">
         <v>9685</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19828,7 +19828,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H671" t="n">
         <v>3415</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20002,7 +20002,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H677" t="n">
         <v>9507</v>
@@ -20031,7 +20031,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H678" t="n">
         <v>18194</v>
@@ -20060,7 +20060,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H679" t="n">
         <v>7332</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20118,7 +20118,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H681" t="n">
         <v>6945</v>
@@ -20147,7 +20147,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H682" t="n">
         <v>3572</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20205,7 +20205,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.7696075439453</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H684" t="n">
         <v>11051</v>
@@ -20234,7 +20234,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.7696075439453</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H685" t="n">
         <v>9237</v>
@@ -20292,7 +20292,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H687" t="n">
         <v>8053</v>
@@ -20321,7 +20321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449962615967</v>
+        <v>11.5449953079224</v>
       </c>
       <c r="H688" t="n">
         <v>8002</v>
@@ -20350,7 +20350,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797618865967</v>
+        <v>11.6797609329224</v>
       </c>
       <c r="H689" t="n">
         <v>10841</v>
@@ -20408,7 +20408,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="n">
         <v>55853</v>
@@ -20437,7 +20437,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H692" t="n">
         <v>140958</v>
@@ -20582,7 +20582,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.8340969085693</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H697" t="n">
         <v>248766</v>
@@ -20611,7 +20611,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H698" t="n">
         <v>59019</v>
@@ -20727,7 +20727,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.8340969085693</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H702" t="n">
         <v>62036</v>
@@ -20814,7 +20814,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.744255065918</v>
+        <v>17.7442512512207</v>
       </c>
       <c r="H705" t="n">
         <v>29563</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -21075,7 +21075,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H714" t="n">
         <v>56021</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21655,7 +21655,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501106262207</v>
+        <v>17.2501125335693</v>
       </c>
       <c r="H734" t="n">
         <v>15613</v>
@@ -21684,7 +21684,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153430938721</v>
+        <v>17.1153411865234</v>
       </c>
       <c r="H735" t="n">
         <v>6538</v>
@@ -21974,7 +21974,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H745" t="n">
         <v>15308</v>
@@ -22003,7 +22003,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H746" t="n">
         <v>42523</v>
@@ -22148,7 +22148,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864349365234</v>
+        <v>16.4864311218262</v>
       </c>
       <c r="H751" t="n">
         <v>22548</v>
@@ -22177,7 +22177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110443115234</v>
+        <v>16.7110462188721</v>
       </c>
       <c r="H752" t="n">
         <v>38381</v>
@@ -22235,7 +22235,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356575012207</v>
+        <v>16.9356555938721</v>
       </c>
       <c r="H754" t="n">
         <v>36349</v>
@@ -22351,7 +22351,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H758" t="n">
         <v>8367</v>
@@ -22525,7 +22525,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>16.4415130615234</v>
+        <v>16.4415111541748</v>
       </c>
       <c r="H764" t="n">
         <v>5046</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.138768196106</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22670,7 +22670,7 @@
         <v>17</v>
       </c>
       <c r="G769" t="n">
-        <v>15.2735357284546</v>
+        <v>15.273533821106</v>
       </c>
       <c r="H769" t="n">
         <v>16809</v>
@@ -22699,7 +22699,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532232284546</v>
       </c>
       <c r="H770" t="n">
         <v>5930</v>
@@ -22757,7 +22757,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864349365234</v>
+        <v>16.4864311218262</v>
       </c>
       <c r="H772" t="n">
         <v>30917</v>
@@ -22873,7 +22873,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H776" t="n">
         <v>3032</v>
@@ -22931,7 +22931,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H778" t="n">
         <v>8343</v>
@@ -23018,7 +23018,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H781" t="n">
         <v>3445</v>
@@ -23076,7 +23076,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H783" t="n">
         <v>3772</v>
@@ -23105,7 +23105,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H784" t="n">
         <v>9640</v>
@@ -23134,7 +23134,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H785" t="n">
         <v>2827</v>
@@ -23163,7 +23163,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H786" t="n">
         <v>2004</v>
@@ -23192,7 +23192,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H787" t="n">
         <v>1452</v>
@@ -23221,7 +23221,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H788" t="n">
         <v>14768</v>
@@ -23337,7 +23337,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H792" t="n">
         <v>6586</v>
@@ -23395,7 +23395,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H794" t="n">
         <v>4856</v>
@@ -23424,7 +23424,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H795" t="n">
         <v>3584</v>
@@ -23453,7 +23453,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>15.3633804321289</v>
+        <v>15.3633794784546</v>
       </c>
       <c r="H796" t="n">
         <v>8529</v>
@@ -23511,7 +23511,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H798" t="n">
         <v>13711</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H800" t="n">
         <v>4924</v>
@@ -23627,7 +23627,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286138534546</v>
+        <v>15.2286148071289</v>
       </c>
       <c r="H802" t="n">
         <v>5534</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879907608032</v>
+        <v>15.5879898071289</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23685,7 +23685,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H804" t="n">
         <v>6910</v>
@@ -23714,7 +23714,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H805" t="n">
         <v>5836</v>
@@ -23743,7 +23743,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H806" t="n">
         <v>7842</v>
@@ -23772,7 +23772,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141578674316</v>
+        <v>14.9141597747803</v>
       </c>
       <c r="H807" t="n">
         <v>18172</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.138768196106</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -23830,7 +23830,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532232284546</v>
       </c>
       <c r="H809" t="n">
         <v>1995</v>
@@ -23859,7 +23859,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.1836910247803</v>
+        <v>15.183690071106</v>
       </c>
       <c r="H810" t="n">
         <v>3859</v>
@@ -23888,7 +23888,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590797424316</v>
+        <v>14.9590787887573</v>
       </c>
       <c r="H811" t="n">
         <v>1809</v>
@@ -24004,7 +24004,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H815" t="n">
         <v>21544</v>
@@ -24062,7 +24062,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.5547819137573</v>
+        <v>14.554780960083</v>
       </c>
       <c r="H817" t="n">
         <v>53993</v>
@@ -24149,7 +24149,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H820" t="n">
         <v>14476</v>
@@ -24178,7 +24178,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.599702835083</v>
+        <v>14.5997037887573</v>
       </c>
       <c r="H821" t="n">
         <v>12526</v>
@@ -24236,7 +24236,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200134277344</v>
+        <v>14.4200124740601</v>
       </c>
       <c r="H823" t="n">
         <v>6212</v>
@@ -24294,7 +24294,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>13.7461824417114</v>
+        <v>13.7461814880371</v>
       </c>
       <c r="H825" t="n">
         <v>7453</v>
@@ -24323,7 +24323,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H826" t="n">
         <v>4142</v>
@@ -24352,7 +24352,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H827" t="n">
         <v>23439</v>
@@ -24381,7 +24381,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H828" t="n">
         <v>13048</v>
@@ -24410,7 +24410,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H829" t="n">
         <v>7670</v>
@@ -24439,7 +24439,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H830" t="n">
         <v>25666</v>
@@ -24468,7 +24468,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477382659912</v>
+        <v>12.8477392196655</v>
       </c>
       <c r="H831" t="n">
         <v>15063</v>
@@ -24497,7 +24497,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129726409912</v>
+        <v>12.7129716873169</v>
       </c>
       <c r="H832" t="n">
         <v>7112</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680498123169</v>
+        <v>12.6680507659912</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24555,7 +24555,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H834" t="n">
         <v>12679</v>
@@ -24613,7 +24613,7 @@
         <v>12.5</v>
       </c>
       <c r="G836" t="n">
-        <v>11.230541229248</v>
+        <v>11.2305402755737</v>
       </c>
       <c r="H836" t="n">
         <v>26240</v>
@@ -24642,7 +24642,7 @@
         <v>12.5</v>
       </c>
       <c r="G837" t="n">
-        <v>11.230541229248</v>
+        <v>11.2305402755737</v>
       </c>
       <c r="H837" t="n">
         <v>20126</v>
@@ -24671,7 +24671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899171829224</v>
+        <v>11.5899181365967</v>
       </c>
       <c r="H838" t="n">
         <v>13270</v>
@@ -24700,7 +24700,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766483306885</v>
+        <v>13.4766492843628</v>
       </c>
       <c r="H839" t="n">
         <v>33921</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332822799683</v>
+        <v>12.5332841873169</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24845,7 +24845,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621932983398</v>
+        <v>13.1621942520142</v>
       </c>
       <c r="H844" t="n">
         <v>6802</v>
@@ -24874,7 +24874,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969598770142</v>
+        <v>13.2969608306885</v>
       </c>
       <c r="H845" t="n">
         <v>4249</v>
@@ -24990,7 +24990,7 @@
         <v>15.25</v>
       </c>
       <c r="G849" t="n">
-        <v>13.7012605667114</v>
+        <v>13.7012596130371</v>
       </c>
       <c r="H849" t="n">
         <v>4278</v>
@@ -25019,7 +25019,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911043167114</v>
+        <v>13.7911033630371</v>
       </c>
       <c r="H850" t="n">
         <v>2038</v>
@@ -25106,7 +25106,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H853" t="n">
         <v>10148</v>
@@ -25135,7 +25135,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.2735357284546</v>
+        <v>15.273533821106</v>
       </c>
       <c r="H854" t="n">
         <v>51860</v>
@@ -25164,7 +25164,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329135894775</v>
+        <v>15.6329107284546</v>
       </c>
       <c r="H855" t="n">
         <v>45677</v>
@@ -25193,7 +25193,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.219630241394</v>
+        <v>15.2196283340454</v>
       </c>
       <c r="H856" t="n">
         <v>17742</v>
@@ -25222,7 +25222,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532232284546</v>
       </c>
       <c r="H857" t="n">
         <v>10279</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.3993158340454</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25280,7 +25280,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H859" t="n">
         <v>25099</v>
@@ -25309,7 +25309,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532260894775</v>
+        <v>15.4532232284546</v>
       </c>
       <c r="H860" t="n">
         <v>4992</v>
@@ -25338,7 +25338,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657228469849</v>
+        <v>15.1657209396362</v>
       </c>
       <c r="H861" t="n">
         <v>7654</v>
@@ -25367,7 +25367,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>15.3633804321289</v>
+        <v>15.3633794784546</v>
       </c>
       <c r="H862" t="n">
         <v>17177</v>
@@ -25425,7 +25425,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>16.1180725097656</v>
+        <v>16.118070602417</v>
       </c>
       <c r="H864" t="n">
         <v>30261</v>
@@ -25454,7 +25454,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563503265381</v>
+        <v>15.9563522338867</v>
       </c>
       <c r="H865" t="n">
         <v>11649</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407274246216</v>
+        <v>15.7407255172729</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25541,7 +25541,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454113006592</v>
+        <v>15.3454103469849</v>
       </c>
       <c r="H868" t="n">
         <v>4337</v>
@@ -25686,7 +25686,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289979934692</v>
       </c>
       <c r="H873" t="n">
         <v>5894</v>
@@ -25831,7 +25831,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H878" t="n">
         <v>3239</v>
@@ -25860,7 +25860,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G879" t="n">
-        <v>14.4289989471436</v>
+        <v>14.4289979934692</v>
       </c>
       <c r="H879" t="n">
         <v>8701</v>
@@ -25976,7 +25976,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H883" t="n">
         <v>869</v>
@@ -26034,7 +26034,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H885" t="n">
         <v>1989</v>
@@ -26527,7 +26527,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H902" t="n">
         <v>2675</v>
@@ -26556,7 +26556,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G903" t="n">
-        <v>14.6121072769165</v>
+        <v>14.6121082305908</v>
       </c>
       <c r="H903" t="n">
         <v>7365</v>
@@ -26672,7 +26672,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824361801147</v>
+        <v>12.9824371337891</v>
       </c>
       <c r="H907" t="n">
         <v>3998</v>
@@ -26701,7 +26701,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345291137695</v>
+        <v>12.6345300674438</v>
       </c>
       <c r="H908" t="n">
         <v>11680</v>
@@ -26817,7 +26817,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G912" t="n">
-        <v>12.6528406143188</v>
+        <v>12.6528396606445</v>
       </c>
       <c r="H912" t="n">
         <v>8775</v>
@@ -26846,7 +26846,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429744720459</v>
+        <v>12.5429735183716</v>
       </c>
       <c r="H913" t="n">
         <v>3259</v>
@@ -26991,7 +26991,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>13.0190591812134</v>
+        <v>13.0190582275391</v>
       </c>
       <c r="H918" t="n">
         <v>2344</v>
@@ -27049,7 +27049,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G920" t="n">
-        <v>13.3852758407593</v>
+        <v>13.3852767944336</v>
       </c>
       <c r="H920" t="n">
         <v>4325</v>
@@ -27223,7 +27223,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="n">
         <v>3020</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359498977661</v>
+        <v>12.8359489440918</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27368,7 +27368,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739917755127</v>
+        <v>13.0739908218384</v>
       </c>
       <c r="H931" t="n">
         <v>824</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923023223877</v>
+        <v>13.092303276062</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27658,7 +27658,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>13.1106128692627</v>
+        <v>13.110613822937</v>
       </c>
       <c r="H941" t="n">
         <v>991</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923023223877</v>
+        <v>13.092303276062</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27774,7 +27774,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H945" t="n">
         <v>3109</v>
@@ -28035,7 +28035,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613605499268</v>
+        <v>13.8613615036011</v>
       </c>
       <c r="H954" t="n">
         <v>5306</v>
@@ -28064,7 +28064,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346046447754</v>
       </c>
       <c r="H955" t="n">
         <v>1552</v>
@@ -28151,7 +28151,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H958" t="n">
         <v>840</v>
@@ -28180,7 +28180,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951419830322</v>
+        <v>13.4951429367065</v>
       </c>
       <c r="H959" t="n">
         <v>2351</v>
@@ -28325,7 +28325,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H964" t="n">
         <v>2199</v>
@@ -28586,7 +28586,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H973" t="n">
         <v>4167</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796710968018</v>
+        <v>13.8796701431274</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28818,7 +28818,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G981" t="n">
-        <v>14.209267616272</v>
+        <v>14.2092685699463</v>
       </c>
       <c r="H981" t="n">
         <v>3919</v>
@@ -28847,7 +28847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H982" t="n">
         <v>1433</v>
@@ -28905,7 +28905,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H984" t="n">
         <v>2674</v>
@@ -28934,7 +28934,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G985" t="n">
-        <v>14.1543350219727</v>
+        <v>14.154335975647</v>
       </c>
       <c r="H985" t="n">
         <v>2097</v>
@@ -29050,7 +29050,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G989" t="n">
-        <v>14.209267616272</v>
+        <v>14.2092685699463</v>
       </c>
       <c r="H989" t="n">
         <v>1773</v>
@@ -29166,7 +29166,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H993" t="n">
         <v>3823</v>
@@ -29195,7 +29195,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H994" t="n">
         <v>968</v>
@@ -29282,7 +29282,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726455688477</v>
+        <v>14.1726446151733</v>
       </c>
       <c r="H997" t="n">
         <v>1556</v>
@@ -29311,7 +29311,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613605499268</v>
+        <v>13.8613615036011</v>
       </c>
       <c r="H998" t="n">
         <v>2430</v>
@@ -29340,7 +29340,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="n">
         <v>1949</v>
@@ -29369,7 +29369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H1000" t="n">
         <v>1623</v>
@@ -29427,7 +29427,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="n">
         <v>3350</v>
@@ -29456,7 +29456,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247394561768</v>
+        <v>13.8247385025024</v>
       </c>
       <c r="H1003" t="n">
         <v>748</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796710968018</v>
+        <v>13.8796701431274</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29630,7 +29630,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="n">
         <v>11362</v>
@@ -29804,7 +29804,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H1015" t="n">
         <v>6837</v>
@@ -29833,7 +29833,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726455688477</v>
+        <v>14.1726446151733</v>
       </c>
       <c r="H1016" t="n">
         <v>3081</v>
@@ -29891,7 +29891,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1018" t="n">
         <v>2476</v>
@@ -30065,7 +30065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.099401473999</v>
+        <v>14.0994024276733</v>
       </c>
       <c r="H1024" t="n">
         <v>1162</v>
@@ -30094,7 +30094,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1025" t="n">
         <v>1900</v>
@@ -30181,7 +30181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.1909580230713</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1028" t="n">
         <v>5343</v>
@@ -30326,7 +30326,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895372390747</v>
+        <v>13.9895362854004</v>
       </c>
       <c r="H1033" t="n">
         <v>1202</v>
@@ -30558,7 +30558,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487302780151</v>
+        <v>14.6487293243408</v>
       </c>
       <c r="H1041" t="n">
         <v>3209</v>
@@ -30587,7 +30587,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1042" t="n">
         <v>8372</v>
@@ -30616,7 +30616,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1043" t="n">
         <v>2854</v>
@@ -30645,7 +30645,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1044" t="n">
         <v>1046</v>
@@ -30761,7 +30761,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726455688477</v>
+        <v>14.1726446151733</v>
       </c>
       <c r="H1048" t="n">
         <v>3540</v>
@@ -31051,7 +31051,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1058" t="n">
-        <v>14.6121072769165</v>
+        <v>14.6121082305908</v>
       </c>
       <c r="H1058" t="n">
         <v>10801</v>
@@ -31486,7 +31486,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>14.2825126647949</v>
+        <v>14.2825117111206</v>
       </c>
       <c r="H1073" t="n">
         <v>15777</v>
@@ -31718,7 +31718,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1081" t="n">
         <v>104130</v>
@@ -31805,7 +31805,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1084" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H1084" t="n">
         <v>7700</v>
@@ -31834,7 +31834,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>15.014946937561</v>
+        <v>15.0149478912354</v>
       </c>
       <c r="H1085" t="n">
         <v>7742</v>
@@ -31892,7 +31892,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="n">
         <v>6067</v>
@@ -31921,7 +31921,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>15.051570892334</v>
+        <v>15.0515699386597</v>
       </c>
       <c r="H1088" t="n">
         <v>8528</v>
@@ -32008,7 +32008,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1091" t="n">
         <v>9320</v>
@@ -32066,7 +32066,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4360990524292</v>
+        <v>15.4361000061035</v>
       </c>
       <c r="H1093" t="n">
         <v>8188</v>
@@ -32095,7 +32095,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1094" t="n">
-        <v>15.5825862884521</v>
+        <v>15.5825872421265</v>
       </c>
       <c r="H1094" t="n">
         <v>4974</v>
@@ -32124,7 +32124,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473840713501</v>
       </c>
       <c r="H1095" t="n">
         <v>11814</v>
@@ -32182,7 +32182,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.5825862884521</v>
+        <v>15.5825872421265</v>
       </c>
       <c r="H1097" t="n">
         <v>6511</v>
@@ -32211,7 +32211,7 @@
         <v>17</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.5642757415771</v>
+        <v>15.5642738342285</v>
       </c>
       <c r="H1098" t="n">
         <v>8931</v>
@@ -32240,7 +32240,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="n">
         <v>6086</v>
@@ -32356,7 +32356,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896127700806</v>
+        <v>15.2896118164062</v>
       </c>
       <c r="H1103" t="n">
         <v>5347</v>
@@ -32385,7 +32385,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.5642757415771</v>
+        <v>15.5642738342285</v>
       </c>
       <c r="H1104" t="n">
         <v>4079</v>
@@ -32414,7 +32414,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="n">
         <v>21663</v>
@@ -32443,7 +32443,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="n">
         <v>5698</v>
@@ -32588,7 +32588,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.1319122314453</v>
+        <v>16.1319141387939</v>
       </c>
       <c r="H1111" t="n">
         <v>48202</v>
@@ -58752,6 +58752,35 @@
         <v>9259</v>
       </c>
       <c r="I2013" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2014" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2014" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>1.66499996185303</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>1.66499996185303</v>
+      </c>
+      <c r="H2014" t="n">
+        <v>11289</v>
+      </c>
+      <c r="I2014" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108205795288</v>
+        <v>2.8810818195343</v>
       </c>
       <c r="H2" t="n">
         <v>41400</v>
@@ -456,7 +456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H3" t="n">
         <v>13950</v>
@@ -543,7 +543,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H6" t="n">
         <v>1350</v>
@@ -572,7 +572,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H7" t="n">
         <v>7200</v>
@@ -601,7 +601,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H8" t="n">
         <v>2700</v>
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H9" t="n">
         <v>1350</v>
@@ -688,7 +688,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H11" t="n">
         <v>450</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H12" t="n">
         <v>1800</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441972732544</v>
+        <v>2.83441948890686</v>
       </c>
       <c r="H20" t="n">
         <v>900</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1065,7 +1065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H24" t="n">
         <v>450</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863395690918</v>
+        <v>2.8986337184906</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1152,7 +1152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255361557007</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H27" t="n">
         <v>450</v>
@@ -1210,7 +1210,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H29" t="n">
         <v>1800</v>
@@ -1239,7 +1239,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549625396729</v>
+        <v>2.76549601554871</v>
       </c>
       <c r="H30" t="n">
         <v>3150</v>
@@ -1268,7 +1268,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H31" t="n">
         <v>4950</v>
@@ -1384,7 +1384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399176597595</v>
+        <v>2.83399152755737</v>
       </c>
       <c r="H35" t="n">
         <v>7650</v>
@@ -1442,7 +1442,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H37" t="n">
         <v>5400</v>
@@ -1471,7 +1471,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368418693542</v>
+        <v>2.85368394851685</v>
       </c>
       <c r="H38" t="n">
         <v>6300</v>
@@ -1500,7 +1500,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.9166145324707</v>
+        <v>2.91661429405212</v>
       </c>
       <c r="H39" t="n">
         <v>19350</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255361557007</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1703,7 +1703,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779843330383</v>
+        <v>3.00779819488525</v>
       </c>
       <c r="H46" t="n">
         <v>7650</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1906,7 +1906,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904914855957</v>
+        <v>3.03904938697815</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1964,7 +1964,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787240028381</v>
+        <v>3.19787263870239</v>
       </c>
       <c r="H55" t="n">
         <v>63900</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489635467529</v>
+        <v>3.30489611625671</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2022,7 +2022,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626792907715</v>
+        <v>3.35626816749573</v>
       </c>
       <c r="H57" t="n">
         <v>20250</v>
@@ -2051,7 +2051,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G58" t="n">
-        <v>3.31345796585083</v>
+        <v>3.31345820426941</v>
       </c>
       <c r="H58" t="n">
         <v>4500</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.2376856803894</v>
+        <v>3.23768544197083</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483001708984</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.40763926506042</v>
+        <v>3.407639503479</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2225,7 +2225,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873690605164</v>
+        <v>3.44873642921448</v>
       </c>
       <c r="H64" t="n">
         <v>13500</v>
@@ -2283,7 +2283,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098504066467</v>
+        <v>3.61098480224609</v>
       </c>
       <c r="H66" t="n">
         <v>38250</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518626213074</v>
+        <v>3.81518602371216</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.966304063797</v>
+        <v>3.96630477905273</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2399,7 +2399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H70" t="n">
         <v>59850</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2457,7 +2457,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028491973877</v>
+        <v>4.24028539657593</v>
       </c>
       <c r="H72" t="n">
         <v>10800</v>
@@ -2486,7 +2486,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087944030762</v>
+        <v>4.09087991714478</v>
       </c>
       <c r="H73" t="n">
         <v>33300</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128652572632</v>
+        <v>3.98128771781921</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2573,7 +2573,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409648895264</v>
+        <v>4.02409696578979</v>
       </c>
       <c r="H76" t="n">
         <v>450</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279244422913</v>
+        <v>3.91279196739197</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2689,7 +2689,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407585144043</v>
+        <v>3.91407561302185</v>
       </c>
       <c r="H80" t="n">
         <v>4950</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566779136658</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041139602661</v>
+        <v>3.87041068077087</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330738067627</v>
+        <v>3.96330761909485</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566779136658</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493320465088</v>
+        <v>3.91493225097656</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -2950,7 +2950,7 @@
         <v>4.67749977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>4.00483179092407</v>
+        <v>4.00483226776123</v>
       </c>
       <c r="H89" t="n">
         <v>17550</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H93" t="n">
         <v>10350</v>
@@ -3153,7 +3153,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H96" t="n">
         <v>12600</v>
@@ -3182,7 +3182,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834436416626</v>
+        <v>4.0583438873291</v>
       </c>
       <c r="H97" t="n">
         <v>900</v>
@@ -3327,7 +3327,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H102" t="n">
         <v>4050</v>
@@ -3356,7 +3356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H103" t="n">
         <v>2250</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H104" t="n">
         <v>9450</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3530,7 +3530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H109" t="n">
         <v>27450</v>
@@ -3559,7 +3559,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H110" t="n">
         <v>21150</v>
@@ -3588,7 +3588,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H111" t="n">
         <v>4500</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3675,7 +3675,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3733,7 +3733,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H116" t="n">
         <v>900</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095388412476</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4052,7 +4052,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H127" t="n">
         <v>10800</v>
@@ -4139,7 +4139,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H130" t="n">
         <v>1350</v>
@@ -4168,7 +4168,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H131" t="n">
         <v>4950</v>
@@ -4197,7 +4197,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H132" t="n">
         <v>4050</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4313,7 +4313,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H136" t="n">
         <v>35100</v>
@@ -4487,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H142" t="n">
         <v>9900</v>
@@ -4516,7 +4516,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H143" t="n">
         <v>2250</v>
@@ -4545,7 +4545,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H144" t="n">
         <v>1350</v>
@@ -4574,7 +4574,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H145" t="n">
         <v>8550</v>
@@ -4603,7 +4603,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H146" t="n">
         <v>11250</v>
@@ -4632,7 +4632,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H147" t="n">
         <v>1350</v>
@@ -4661,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H148" t="n">
         <v>1350</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H149" t="n">
         <v>6750</v>
@@ -4719,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H152" t="n">
         <v>13500</v>
@@ -4806,7 +4806,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H153" t="n">
         <v>3150</v>
@@ -4835,7 +4835,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H154" t="n">
         <v>3150</v>
@@ -4864,7 +4864,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G155" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H155" t="n">
         <v>27000</v>
@@ -4893,7 +4893,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H156" t="n">
         <v>1800</v>
@@ -4922,7 +4922,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H158" t="n">
         <v>1800</v>
@@ -4980,7 +4980,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433555603027</v>
       </c>
       <c r="H159" t="n">
         <v>2250</v>
@@ -5009,7 +5009,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H160" t="n">
         <v>7650</v>
@@ -5038,7 +5038,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H161" t="n">
         <v>102150</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H163" t="n">
         <v>7650</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5328,7 +5328,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H171" t="n">
         <v>8100</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547801971436</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5705,7 +5705,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671739578247</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H184" t="n">
         <v>3600</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266948699951</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6198,7 +6198,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671739578247</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H201" t="n">
         <v>11250</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547801971436</v>
+        <v>6.63547897338867</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266948699951</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862110137939</v>
+        <v>6.37862157821655</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6807,7 +6807,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H222" t="n">
         <v>7042</v>
@@ -6865,7 +6865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H224" t="n">
         <v>6100</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424102783203</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7068,7 +7068,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H231" t="n">
         <v>55223</v>
@@ -7097,7 +7097,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019264221191</v>
+        <v>6.25019311904907</v>
       </c>
       <c r="H232" t="n">
         <v>20785</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300212860107</v>
+        <v>6.29300308227539</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7271,7 +7271,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019264221191</v>
+        <v>6.25019311904907</v>
       </c>
       <c r="H238" t="n">
         <v>4610</v>
@@ -7300,7 +7300,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H239" t="n">
         <v>7153</v>
@@ -7329,7 +7329,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H240" t="n">
         <v>10587</v>
@@ -7416,7 +7416,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H243" t="n">
         <v>3750</v>
@@ -7590,7 +7590,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H249" t="n">
         <v>5546</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7909,7 +7909,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H260" t="n">
         <v>10941</v>
@@ -7938,7 +7938,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H261" t="n">
         <v>2202</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8402,7 +8402,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209730148315</v>
       </c>
       <c r="H277" t="n">
         <v>1002</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8518,7 +8518,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895469665527</v>
+        <v>6.07895421981812</v>
       </c>
       <c r="H281" t="n">
         <v>14397</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209730148315</v>
       </c>
       <c r="H285" t="n">
         <v>5658</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8924,7 +8924,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209777832031</v>
+        <v>5.82209730148315</v>
       </c>
       <c r="H295" t="n">
         <v>3196</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928829193115</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9475,7 +9475,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52243089675903</v>
       </c>
       <c r="H314" t="n">
         <v>1549</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9591,7 +9591,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H318" t="n">
         <v>25735</v>
@@ -9707,7 +9707,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H322" t="n">
         <v>7516</v>
@@ -9794,7 +9794,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H325" t="n">
         <v>7622</v>
@@ -9823,7 +9823,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H326" t="n">
         <v>6905</v>
@@ -9881,7 +9881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750563621521</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H328" t="n">
         <v>14468</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051556587219</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -9968,7 +9968,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242046356201</v>
+        <v>2.96242022514343</v>
       </c>
       <c r="H331" t="n">
         <v>25097</v>
@@ -9997,7 +9997,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104888916016</v>
+        <v>2.91104865074158</v>
       </c>
       <c r="H332" t="n">
         <v>17685</v>
@@ -10026,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857252120972</v>
+        <v>2.56857228279114</v>
       </c>
       <c r="H333" t="n">
         <v>13836</v>
@@ -10084,7 +10084,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158197402954</v>
+        <v>2.43158173561096</v>
       </c>
       <c r="H335" t="n">
         <v>3740</v>
@@ -10113,7 +10113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4829535484314</v>
+        <v>2.48295331001282</v>
       </c>
       <c r="H336" t="n">
         <v>8502</v>
@@ -10142,7 +10142,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H337" t="n">
         <v>1910</v>
@@ -10171,7 +10171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>3.23640131950378</v>
+        <v>3.23640108108521</v>
       </c>
       <c r="H339" t="n">
         <v>2830</v>
@@ -10258,7 +10258,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062124252319</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H341" t="n">
         <v>24606</v>
@@ -10316,7 +10316,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H343" t="n">
         <v>19120</v>
@@ -10345,7 +10345,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710618019104</v>
+        <v>3.88710594177246</v>
       </c>
       <c r="H344" t="n">
         <v>14534</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299193382263</v>
+        <v>3.73299217224121</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476367950439</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593457221985</v>
+        <v>3.65593528747559</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.6388111114502</v>
+        <v>3.63881134986877</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10664,7 +10664,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750563621521</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H355" t="n">
         <v>3470</v>
@@ -10722,7 +10722,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.41620135307312</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H357" t="n">
         <v>4102</v>
@@ -10751,7 +10751,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.41620135307312</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H358" t="n">
         <v>4270</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476367950439</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10838,7 +10838,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449666023254</v>
+        <v>3.66449689865112</v>
       </c>
       <c r="H361" t="n">
         <v>16600</v>
@@ -10867,7 +10867,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861162185669</v>
+        <v>3.81861114501953</v>
       </c>
       <c r="H362" t="n">
         <v>19084</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861162185669</v>
+        <v>3.81861114501953</v>
       </c>
       <c r="H364" t="n">
         <v>2419</v>
@@ -10954,7 +10954,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004929542542</v>
+        <v>3.81004881858826</v>
       </c>
       <c r="H365" t="n">
         <v>3480</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854433059692</v>
+        <v>3.87854480743408</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285830497742</v>
+        <v>3.85285806655884</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11157,7 +11157,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H372" t="n">
         <v>50751</v>
@@ -11215,7 +11215,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.62343072891235</v>
+        <v>4.6234302520752</v>
       </c>
       <c r="H374" t="n">
         <v>82279</v>
@@ -11244,7 +11244,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G375" t="n">
-        <v>4.46931600570679</v>
+        <v>4.46931552886963</v>
       </c>
       <c r="H375" t="n">
         <v>55699</v>
@@ -11302,7 +11302,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H377" t="n">
         <v>13190</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239179611206</v>
+        <v>4.27239274978638</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781080245972</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11418,7 +11418,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055395126343</v>
+        <v>4.64055442810059</v>
       </c>
       <c r="H381" t="n">
         <v>28041</v>
@@ -11447,7 +11447,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838251113892</v>
       </c>
       <c r="H382" t="n">
         <v>137190</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11534,7 +11534,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H385" t="n">
         <v>40025</v>
@@ -11563,7 +11563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.3426308631897</v>
+        <v>5.34263038635254</v>
       </c>
       <c r="H386" t="n">
         <v>87258</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838251113892</v>
       </c>
       <c r="H387" t="n">
         <v>39972</v>
@@ -11621,7 +11621,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H388" t="n">
         <v>21205</v>
@@ -11679,7 +11679,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H390" t="n">
         <v>18684</v>
@@ -11766,7 +11766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028764724731</v>
+        <v>4.880286693573</v>
       </c>
       <c r="H393" t="n">
         <v>8696</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11882,7 +11882,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H397" t="n">
         <v>5833</v>
@@ -11969,7 +11969,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H400" t="n">
         <v>1473</v>
@@ -11998,7 +11998,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H401" t="n">
         <v>1401</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12114,7 +12114,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H405" t="n">
         <v>961</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12201,7 +12201,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H408" t="n">
         <v>8938</v>
@@ -12288,7 +12288,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H411" t="n">
         <v>1244</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12346,7 +12346,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G413" t="n">
-        <v>5.05152559280396</v>
+        <v>5.05152606964111</v>
       </c>
       <c r="H413" t="n">
         <v>3640</v>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H417" t="n">
         <v>3912</v>
@@ -12549,7 +12549,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H420" t="n">
         <v>11461</v>
@@ -12578,7 +12578,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H421" t="n">
         <v>10486</v>
@@ -12607,7 +12607,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413463592529</v>
       </c>
       <c r="H422" t="n">
         <v>7415</v>
@@ -12636,7 +12636,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H423" t="n">
         <v>4800</v>
@@ -12665,7 +12665,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H424" t="n">
         <v>970</v>
@@ -12694,7 +12694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H425" t="n">
         <v>3416</v>
@@ -12723,7 +12723,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H426" t="n">
         <v>4511</v>
@@ -12752,7 +12752,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H427" t="n">
         <v>5140</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440237045288</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426874160767</v>
+        <v>5.15426826477051</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13071,7 +13071,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413463592529</v>
       </c>
       <c r="H438" t="n">
         <v>8401</v>
@@ -13129,7 +13129,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H440" t="n">
         <v>592</v>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H441" t="n">
         <v>915</v>
@@ -13245,7 +13245,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H444" t="n">
         <v>1100</v>
@@ -13274,7 +13274,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H445" t="n">
         <v>4470</v>
@@ -13303,7 +13303,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H446" t="n">
         <v>504</v>
@@ -13332,7 +13332,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>5.10289669036865</v>
+        <v>5.10289716720581</v>
       </c>
       <c r="H447" t="n">
         <v>2883</v>
@@ -13361,7 +13361,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H448" t="n">
         <v>7543</v>
@@ -13390,7 +13390,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851566314697</v>
+        <v>5.18851613998413</v>
       </c>
       <c r="H449" t="n">
         <v>2920</v>
@@ -13419,7 +13419,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.20243549346924</v>
+        <v>5.2024359703064</v>
       </c>
       <c r="H450" t="n">
         <v>2913</v>
@@ -13506,7 +13506,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H453" t="n">
         <v>7910</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0980396270752</v>
+        <v>5.09803867340088</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13738,7 +13738,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763734817505</v>
+        <v>5.16763782501221</v>
       </c>
       <c r="H461" t="n">
         <v>2800</v>
@@ -13854,7 +13854,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H465" t="n">
         <v>3199</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H466" t="n">
         <v>2015</v>
@@ -13941,7 +13941,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>5.04584074020386</v>
+        <v>5.04584121704102</v>
       </c>
       <c r="H468" t="n">
         <v>7558</v>
@@ -13970,7 +13970,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H469" t="n">
         <v>1484</v>
@@ -14057,7 +14057,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H472" t="n">
         <v>10358</v>
@@ -14115,7 +14115,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404508590698</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H474" t="n">
         <v>6712</v>
@@ -14144,7 +14144,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404508590698</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H480" t="n">
         <v>10416</v>
@@ -14347,7 +14347,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H482" t="n">
         <v>2456</v>
@@ -14376,7 +14376,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H483" t="n">
         <v>6872</v>
@@ -14405,7 +14405,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H484" t="n">
         <v>2940</v>
@@ -14434,7 +14434,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H485" t="n">
         <v>672</v>
@@ -14463,7 +14463,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H486" t="n">
         <v>200</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.34986257553101</v>
+        <v>4.34986305236816</v>
       </c>
       <c r="H491" t="n">
         <v>11245</v>
@@ -14666,7 +14666,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896522521973</v>
+        <v>4.28896474838257</v>
       </c>
       <c r="H493" t="n">
         <v>5774</v>
@@ -14695,7 +14695,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887052536011</v>
+        <v>4.08887100219727</v>
       </c>
       <c r="H494" t="n">
         <v>1610</v>
@@ -14811,7 +14811,7 @@
         <v>5</v>
       </c>
       <c r="G498" t="n">
-        <v>4.34986257553101</v>
+        <v>4.34986305236816</v>
       </c>
       <c r="H498" t="n">
         <v>1568</v>
@@ -14840,7 +14840,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G499" t="n">
-        <v>4.14106941223145</v>
+        <v>4.1410698890686</v>
       </c>
       <c r="H499" t="n">
         <v>11007</v>
@@ -14927,7 +14927,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506443023682</v>
+        <v>4.31506395339966</v>
       </c>
       <c r="H502" t="n">
         <v>4690</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456792831421</v>
+        <v>4.18456840515137</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785261154175</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15043,7 +15043,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.50645732879639</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H506" t="n">
         <v>5490</v>
@@ -15101,7 +15101,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H508" t="n">
         <v>14843</v>
@@ -15130,7 +15130,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H509" t="n">
         <v>6520</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15188,7 +15188,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H511" t="n">
         <v>9671</v>
@@ -15246,7 +15246,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H513" t="n">
         <v>535</v>
@@ -15275,7 +15275,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G514" t="n">
-        <v>4.54125690460205</v>
+        <v>4.54125642776489</v>
       </c>
       <c r="H514" t="n">
         <v>2490</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15420,7 +15420,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H519" t="n">
         <v>2418</v>
@@ -15449,7 +15449,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H520" t="n">
         <v>140</v>
@@ -15478,7 +15478,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H522" t="n">
         <v>5441</v>
@@ -15594,7 +15594,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.50645732879639</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H525" t="n">
         <v>2013</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.50645732879639</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15826,7 +15826,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H533" t="n">
         <v>5756</v>
@@ -15855,7 +15855,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H534" t="n">
         <v>13104</v>
@@ -15884,7 +15884,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H535" t="n">
         <v>380</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15942,7 +15942,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.50645732879639</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H537" t="n">
         <v>8283</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785261154175</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785261154175</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16058,7 +16058,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H541" t="n">
         <v>1369</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16116,7 +16116,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>4.71525096893311</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H543" t="n">
         <v>300</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825393676758</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16174,7 +16174,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H545" t="n">
         <v>1820</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825393676758</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16319,7 +16319,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71525096893311</v>
+        <v>4.71525144577026</v>
       </c>
       <c r="H550" t="n">
         <v>3677</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16406,7 +16406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H553" t="n">
         <v>12566</v>
@@ -16435,7 +16435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H554" t="n">
         <v>4021</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206146240234</v>
+        <v>4.40206050872803</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16580,7 +16580,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G559" t="n">
-        <v>4.54125690460205</v>
+        <v>4.54125642776489</v>
       </c>
       <c r="H559" t="n">
         <v>3170</v>
@@ -16638,7 +16638,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865573883057</v>
+        <v>4.55865621566772</v>
       </c>
       <c r="H561" t="n">
         <v>8531</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305255889893</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16696,7 +16696,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H563" t="n">
         <v>7869</v>
@@ -16754,7 +16754,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H565" t="n">
         <v>4770</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16841,7 +16841,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H568" t="n">
         <v>22400</v>
@@ -16928,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H571" t="n">
         <v>855</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.8718466758728</v>
+        <v>4.87184619903564</v>
       </c>
       <c r="H572" t="n">
         <v>14439</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17102,7 +17102,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H577" t="n">
         <v>6090</v>
@@ -17131,7 +17131,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H578" t="n">
         <v>11230</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.95884370803833</v>
+        <v>4.95884323120117</v>
       </c>
       <c r="H579" t="n">
         <v>3281</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17305,7 +17305,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H584" t="n">
         <v>21315</v>
@@ -17392,7 +17392,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H587" t="n">
         <v>4942</v>
@@ -17421,7 +17421,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.30683279037476</v>
+        <v>5.3068323135376</v>
       </c>
       <c r="H588" t="n">
         <v>10524</v>
@@ -17479,7 +17479,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H590" t="n">
         <v>6044</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324052810669</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H597" t="n">
         <v>33122</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39383029937744</v>
+        <v>5.39382982254028</v>
       </c>
       <c r="H601" t="n">
         <v>124984</v>
@@ -17943,7 +17943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.5678243637085</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H606" t="n">
         <v>11629</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18001,7 +18001,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082733154297</v>
+        <v>5.48082780838013</v>
       </c>
       <c r="H608" t="n">
         <v>8454</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.4112286567688</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18059,7 +18059,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.5678243637085</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H610" t="n">
         <v>163362</v>
@@ -18117,7 +18117,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661800384521</v>
+        <v>5.77661752700806</v>
       </c>
       <c r="H612" t="n">
         <v>36365</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.9680118560791</v>
+        <v>5.96801233291626</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18320,7 +18320,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>6.30562353134155</v>
+        <v>6.30562305450439</v>
       </c>
       <c r="H619" t="n">
         <v>24808</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031042098999</v>
+        <v>7.00031137466431</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18436,7 +18436,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.83999824523926</v>
+        <v>6.83999729156494</v>
       </c>
       <c r="H623" t="n">
         <v>76240</v>
@@ -18465,7 +18465,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718536376953</v>
+        <v>7.10718584060669</v>
       </c>
       <c r="H624" t="n">
         <v>102683</v>
@@ -18494,7 +18494,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G625" t="n">
-        <v>6.89343547821045</v>
+        <v>6.89343500137329</v>
       </c>
       <c r="H625" t="n">
         <v>84822</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468591690063</v>
+        <v>6.96468544006348</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562274932861</v>
+        <v>6.87562322616577</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874814987183</v>
+        <v>7.90874671936035</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18697,7 +18697,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.1403112411499</v>
+        <v>8.14030933380127</v>
       </c>
       <c r="H632" t="n">
         <v>59783</v>
@@ -18755,7 +18755,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343425750732</v>
+        <v>9.17343521118164</v>
       </c>
       <c r="H634" t="n">
         <v>112604</v>
@@ -18900,7 +18900,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702877044678</v>
+        <v>9.30702972412109</v>
       </c>
       <c r="H639" t="n">
         <v>47607</v>
@@ -18929,7 +18929,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437252044678</v>
+        <v>9.08437156677246</v>
       </c>
       <c r="H640" t="n">
         <v>42073</v>
@@ -19103,7 +19103,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702877044678</v>
+        <v>9.30702972412109</v>
       </c>
       <c r="H646" t="n">
         <v>97578</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19161,7 +19161,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046474456787</v>
+        <v>9.93046569824219</v>
       </c>
       <c r="H648" t="n">
         <v>98237</v>
@@ -19219,7 +19219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109350204468</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H650" t="n">
         <v>160231</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19277,7 +19277,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H652" t="n">
         <v>199932</v>
@@ -19306,7 +19306,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H653" t="n">
         <v>91653</v>
@@ -19393,7 +19393,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H656" t="n">
         <v>32521</v>
@@ -19422,7 +19422,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>11.399995803833</v>
+        <v>11.3999967575073</v>
       </c>
       <c r="H657" t="n">
         <v>25340</v>
@@ -19451,7 +19451,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109350204468</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H658" t="n">
         <v>11498</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19625,7 +19625,7 @@
         <v>13</v>
       </c>
       <c r="G664" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H664" t="n">
         <v>25174</v>
@@ -19683,7 +19683,7 @@
         <v>13</v>
       </c>
       <c r="G666" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H666" t="n">
         <v>12852</v>
@@ -19741,7 +19741,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H668" t="n">
         <v>9685</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19857,7 +19857,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.4551515579224</v>
+        <v>11.455150604248</v>
       </c>
       <c r="H672" t="n">
         <v>11052</v>
@@ -19886,7 +19886,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>11.0957746505737</v>
+        <v>11.095775604248</v>
       </c>
       <c r="H673" t="n">
         <v>20518</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363967895508</v>
+        <v>10.7363958358765</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20002,7 +20002,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H677" t="n">
         <v>9507</v>
@@ -20060,7 +20060,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H679" t="n">
         <v>7332</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20118,7 +20118,7 @@
         <v>13</v>
       </c>
       <c r="G681" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H681" t="n">
         <v>6945</v>
@@ -20147,7 +20147,7 @@
         <v>13</v>
       </c>
       <c r="G682" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H682" t="n">
         <v>3572</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20205,7 +20205,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H684" t="n">
         <v>11051</v>
@@ -20234,7 +20234,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H685" t="n">
         <v>9237</v>
@@ -20321,7 +20321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449953079224</v>
+        <v>11.5449962615967</v>
       </c>
       <c r="H688" t="n">
         <v>8002</v>
@@ -20350,7 +20350,7 @@
         <v>13</v>
       </c>
       <c r="G689" t="n">
-        <v>11.6797609329224</v>
+        <v>11.6797618865967</v>
       </c>
       <c r="H689" t="n">
         <v>10841</v>
@@ -20379,7 +20379,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535947799683</v>
+        <v>12.3535938262939</v>
       </c>
       <c r="H690" t="n">
         <v>194061</v>
@@ -20408,7 +20408,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H691" t="n">
         <v>55853</v>
@@ -20437,7 +20437,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H692" t="n">
         <v>140958</v>
@@ -20466,7 +20466,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>13.3868036270142</v>
+        <v>13.3868045806885</v>
       </c>
       <c r="H693" t="n">
         <v>49176</v>
@@ -20495,7 +20495,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>14.3301696777344</v>
+        <v>14.3301706314087</v>
       </c>
       <c r="H694" t="n">
         <v>144504</v>
@@ -20582,7 +20582,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H697" t="n">
         <v>248766</v>
@@ -20611,7 +20611,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>17.2501125335693</v>
+        <v>17.2501106262207</v>
       </c>
       <c r="H698" t="n">
         <v>59019</v>
@@ -20640,7 +20640,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>16.8907337188721</v>
+        <v>16.8907318115234</v>
       </c>
       <c r="H699" t="n">
         <v>100713</v>
@@ -20669,7 +20669,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>17.879020690918</v>
+        <v>17.8790225982666</v>
       </c>
       <c r="H700" t="n">
         <v>65333</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180850982666</v>
+        <v>18.4180889129639</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20727,7 +20727,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H702" t="n">
         <v>62036</v>
@@ -20785,7 +20785,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H704" t="n">
         <v>50153</v>
@@ -20814,7 +20814,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.7442512512207</v>
+        <v>17.744255065918</v>
       </c>
       <c r="H705" t="n">
         <v>29563</v>
@@ -20843,7 +20843,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H706" t="n">
         <v>37684</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -21017,7 +21017,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H712" t="n">
         <v>12956</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21133,7 +21133,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.8907337188721</v>
+        <v>16.8907318115234</v>
       </c>
       <c r="H716" t="n">
         <v>64516</v>
@@ -21162,7 +21162,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H717" t="n">
         <v>48881</v>
@@ -21191,7 +21191,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051868438721</v>
+        <v>17.2051887512207</v>
       </c>
       <c r="H718" t="n">
         <v>51474</v>
@@ -21249,7 +21249,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H720" t="n">
         <v>23381</v>
@@ -21307,7 +21307,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H722" t="n">
         <v>31177</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H728" t="n">
         <v>20822</v>
@@ -21597,7 +21597,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H732" t="n">
         <v>11380</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21655,7 +21655,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2501125335693</v>
+        <v>17.2501106262207</v>
       </c>
       <c r="H734" t="n">
         <v>15613</v>
@@ -21684,7 +21684,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153411865234</v>
+        <v>17.1153430938721</v>
       </c>
       <c r="H735" t="n">
         <v>6538</v>
@@ -21713,7 +21713,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H736" t="n">
         <v>10110</v>
@@ -21742,7 +21742,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H737" t="n">
         <v>15411</v>
@@ -21800,7 +21800,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H739" t="n">
         <v>9553</v>
@@ -21858,7 +21858,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H741" t="n">
         <v>81245</v>
@@ -21887,7 +21887,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H742" t="n">
         <v>26368</v>
@@ -21945,7 +21945,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H744" t="n">
         <v>13809</v>
@@ -22148,7 +22148,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864311218262</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H751" t="n">
         <v>22548</v>
@@ -22177,7 +22177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110462188721</v>
+        <v>16.7110443115234</v>
       </c>
       <c r="H752" t="n">
         <v>38381</v>
@@ -22235,7 +22235,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>16.9356555938721</v>
+        <v>16.9356575012207</v>
       </c>
       <c r="H754" t="n">
         <v>36349</v>
@@ -22264,7 +22264,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H755" t="n">
         <v>10473</v>
@@ -22293,7 +22293,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H756" t="n">
         <v>13943</v>
@@ -22380,7 +22380,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661205291748</v>
+        <v>16.6661224365234</v>
       </c>
       <c r="H759" t="n">
         <v>32049</v>
@@ -22438,7 +22438,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.5313549041748</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H761" t="n">
         <v>15074</v>
@@ -22496,7 +22496,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H763" t="n">
         <v>17084</v>
@@ -22554,7 +22554,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778364181519</v>
+        <v>15.6778354644775</v>
       </c>
       <c r="H765" t="n">
         <v>16640</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22641,7 +22641,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.004002571106</v>
+        <v>15.0040035247803</v>
       </c>
       <c r="H768" t="n">
         <v>16692</v>
@@ -22670,7 +22670,7 @@
         <v>17</v>
       </c>
       <c r="G769" t="n">
-        <v>15.273533821106</v>
+        <v>15.2735357284546</v>
       </c>
       <c r="H769" t="n">
         <v>16809</v>
@@ -22699,7 +22699,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H770" t="n">
         <v>5930</v>
@@ -22728,7 +22728,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676773071289</v>
       </c>
       <c r="H771" t="n">
         <v>8915</v>
@@ -22757,7 +22757,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864311218262</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H772" t="n">
         <v>30917</v>
@@ -22815,7 +22815,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H774" t="n">
         <v>3354</v>
@@ -22844,7 +22844,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>16.3067455291748</v>
+        <v>16.3067436218262</v>
       </c>
       <c r="H775" t="n">
         <v>13090</v>
@@ -22989,7 +22989,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270561218262</v>
+        <v>16.1270599365234</v>
       </c>
       <c r="H780" t="n">
         <v>2753</v>
@@ -23163,7 +23163,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H786" t="n">
         <v>2004</v>
@@ -23221,7 +23221,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H788" t="n">
         <v>14768</v>
@@ -23308,7 +23308,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676773071289</v>
       </c>
       <c r="H791" t="n">
         <v>2124</v>
@@ -23366,7 +23366,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.7676782608032</v>
+        <v>15.7676773071289</v>
       </c>
       <c r="H793" t="n">
         <v>7639</v>
@@ -23395,7 +23395,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H794" t="n">
         <v>4856</v>
@@ -23424,7 +23424,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H795" t="n">
         <v>3584</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024457931519</v>
+        <v>15.9024438858032</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23511,7 +23511,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H798" t="n">
         <v>13711</v>
@@ -23540,7 +23540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778364181519</v>
+        <v>15.6778354644775</v>
       </c>
       <c r="H799" t="n">
         <v>4638</v>
@@ -23627,7 +23627,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286148071289</v>
+        <v>15.2286128997803</v>
       </c>
       <c r="H802" t="n">
         <v>5534</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879898071289</v>
+        <v>15.5879917144775</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23714,7 +23714,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H805" t="n">
         <v>5836</v>
@@ -23743,7 +23743,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H806" t="n">
         <v>7842</v>
@@ -23772,7 +23772,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141597747803</v>
+        <v>14.9141578674316</v>
       </c>
       <c r="H807" t="n">
         <v>18172</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -23830,7 +23830,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H809" t="n">
         <v>1995</v>
@@ -23859,7 +23859,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.183690071106</v>
+        <v>15.1836910247803</v>
       </c>
       <c r="H810" t="n">
         <v>3859</v>
@@ -23888,7 +23888,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590787887573</v>
+        <v>14.9590797424316</v>
       </c>
       <c r="H811" t="n">
         <v>1809</v>
@@ -23917,7 +23917,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>14.6895475387573</v>
+        <v>14.689546585083</v>
       </c>
       <c r="H812" t="n">
         <v>4915</v>
@@ -23946,7 +23946,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>14.5098571777344</v>
+        <v>14.5098581314087</v>
       </c>
       <c r="H813" t="n">
         <v>12514</v>
@@ -23975,7 +23975,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G814" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H814" t="n">
         <v>10409</v>
@@ -24004,7 +24004,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H815" t="n">
         <v>21544</v>
@@ -24091,7 +24091,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G818" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H818" t="n">
         <v>34207</v>
@@ -24120,7 +24120,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G819" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H819" t="n">
         <v>15464</v>
@@ -24149,7 +24149,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H820" t="n">
         <v>14476</v>
@@ -24178,7 +24178,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.5997037887573</v>
+        <v>14.599702835083</v>
       </c>
       <c r="H821" t="n">
         <v>12526</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504812240601</v>
+        <v>14.1504802703857</v>
       </c>
       <c r="H822" t="n">
         <v>17003</v>
@@ -24265,7 +24265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055583953857</v>
+        <v>14.1055593490601</v>
       </c>
       <c r="H824" t="n">
         <v>35205</v>
@@ -24323,7 +24323,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H826" t="n">
         <v>4142</v>
@@ -24352,7 +24352,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H827" t="n">
         <v>23439</v>
@@ -24381,7 +24381,7 @@
         <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H828" t="n">
         <v>13048</v>
@@ -24410,7 +24410,7 @@
         <v>15</v>
       </c>
       <c r="G829" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H829" t="n">
         <v>7670</v>
@@ -24439,7 +24439,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H830" t="n">
         <v>25666</v>
@@ -24468,7 +24468,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477392196655</v>
+        <v>12.8477382659912</v>
       </c>
       <c r="H831" t="n">
         <v>15063</v>
@@ -24497,7 +24497,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129716873169</v>
+        <v>12.7129726409912</v>
       </c>
       <c r="H832" t="n">
         <v>7112</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680507659912</v>
+        <v>12.6680498123169</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24555,7 +24555,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H834" t="n">
         <v>12679</v>
@@ -24671,7 +24671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G838" t="n">
-        <v>11.5899181365967</v>
+        <v>11.5899171829224</v>
       </c>
       <c r="H838" t="n">
         <v>13270</v>
@@ -24700,7 +24700,7 @@
         <v>15</v>
       </c>
       <c r="G839" t="n">
-        <v>13.4766492843628</v>
+        <v>13.4766483306885</v>
       </c>
       <c r="H839" t="n">
         <v>33921</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332841873169</v>
+        <v>12.5332822799683</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24758,7 +24758,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578935623169</v>
+        <v>12.7578945159912</v>
       </c>
       <c r="H841" t="n">
         <v>18683</v>
@@ -24787,7 +24787,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172714233398</v>
+        <v>13.1172723770142</v>
       </c>
       <c r="H842" t="n">
         <v>4865</v>
@@ -24816,7 +24816,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723495483398</v>
+        <v>13.0723485946655</v>
       </c>
       <c r="H843" t="n">
         <v>3970</v>
@@ -24845,7 +24845,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G844" t="n">
-        <v>13.1621942520142</v>
+        <v>13.1621932983398</v>
       </c>
       <c r="H844" t="n">
         <v>6802</v>
@@ -24874,7 +24874,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969608306885</v>
+        <v>13.2969598770142</v>
       </c>
       <c r="H845" t="n">
         <v>4249</v>
@@ -25019,7 +25019,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911033630371</v>
+        <v>13.7911043167114</v>
       </c>
       <c r="H850" t="n">
         <v>2038</v>
@@ -25077,7 +25077,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>14.1954021453857</v>
+        <v>14.1954030990601</v>
       </c>
       <c r="H852" t="n">
         <v>6891</v>
@@ -25106,7 +25106,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H853" t="n">
         <v>10148</v>
@@ -25135,7 +25135,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.273533821106</v>
+        <v>15.2735357284546</v>
       </c>
       <c r="H854" t="n">
         <v>51860</v>
@@ -25164,7 +25164,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.6329107284546</v>
+        <v>15.6329126358032</v>
       </c>
       <c r="H855" t="n">
         <v>45677</v>
@@ -25222,7 +25222,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H857" t="n">
         <v>10279</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993158340454</v>
+        <v>15.3993167877197</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25309,7 +25309,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>15.4532232284546</v>
+        <v>15.4532241821289</v>
       </c>
       <c r="H860" t="n">
         <v>4992</v>
@@ -25338,7 +25338,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657209396362</v>
+        <v>15.1657218933105</v>
       </c>
       <c r="H861" t="n">
         <v>7654</v>
@@ -25396,7 +25396,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G863" t="n">
-        <v>15.7766628265381</v>
+        <v>15.7766618728638</v>
       </c>
       <c r="H863" t="n">
         <v>44798</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407255172729</v>
+        <v>15.7407274246216</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25512,7 +25512,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250997543335</v>
+        <v>15.5251007080078</v>
       </c>
       <c r="H867" t="n">
         <v>7118</v>
@@ -25657,7 +25657,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368118286133</v>
+        <v>14.5368127822876</v>
       </c>
       <c r="H872" t="n">
         <v>5468</v>
@@ -25686,7 +25686,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H873" t="n">
         <v>5894</v>
@@ -25831,7 +25831,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H878" t="n">
         <v>3239</v>
@@ -25860,7 +25860,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G879" t="n">
-        <v>14.4289979934692</v>
+        <v>14.4289989471436</v>
       </c>
       <c r="H879" t="n">
         <v>8701</v>
@@ -25947,7 +25947,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135280609131</v>
+        <v>14.8135290145874</v>
       </c>
       <c r="H882" t="n">
         <v>7029</v>
@@ -25976,7 +25976,7 @@
         <v>16</v>
       </c>
       <c r="G883" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H883" t="n">
         <v>869</v>
@@ -26005,7 +26005,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H884" t="n">
         <v>2276</v>
@@ -26034,7 +26034,7 @@
         <v>16</v>
       </c>
       <c r="G885" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H885" t="n">
         <v>1989</v>
@@ -26121,7 +26121,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H888" t="n">
         <v>3111</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H890" t="n">
         <v>4619</v>
@@ -26208,7 +26208,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G891" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H891" t="n">
         <v>3839</v>
@@ -26411,7 +26411,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G898" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H898" t="n">
         <v>9737</v>
@@ -26643,7 +26643,7 @@
         <v>14</v>
       </c>
       <c r="G906" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H906" t="n">
         <v>8483</v>
@@ -26672,7 +26672,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G907" t="n">
-        <v>12.9824371337891</v>
+        <v>12.9824361801147</v>
       </c>
       <c r="H907" t="n">
         <v>3998</v>
@@ -26701,7 +26701,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>12.6345300674438</v>
+        <v>12.6345291137695</v>
       </c>
       <c r="H908" t="n">
         <v>11680</v>
@@ -26759,7 +26759,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G910" t="n">
-        <v>12.8908815383911</v>
+        <v>12.8908824920654</v>
       </c>
       <c r="H910" t="n">
         <v>845</v>
@@ -26846,7 +26846,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>12.5429735183716</v>
+        <v>12.5429744720459</v>
       </c>
       <c r="H913" t="n">
         <v>3259</v>
@@ -26875,7 +26875,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711511611938</v>
+        <v>12.6711521148682</v>
       </c>
       <c r="H914" t="n">
         <v>2839</v>
@@ -26991,7 +26991,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>13.0190582275391</v>
+        <v>13.0190591812134</v>
       </c>
       <c r="H918" t="n">
         <v>2344</v>
@@ -27107,7 +27107,7 @@
         <v>14</v>
       </c>
       <c r="G922" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H922" t="n">
         <v>4016</v>
@@ -27165,7 +27165,7 @@
         <v>14</v>
       </c>
       <c r="G924" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H924" t="n">
         <v>6097</v>
@@ -27194,7 +27194,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894617080688</v>
+        <v>12.6894626617432</v>
       </c>
       <c r="H925" t="n">
         <v>776</v>
@@ -27223,7 +27223,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514207839966</v>
+        <v>12.4514217376709</v>
       </c>
       <c r="H926" t="n">
         <v>3020</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359489440918</v>
+        <v>12.8359508514404</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27368,7 +27368,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>13.0739908218384</v>
+        <v>13.0739917755127</v>
       </c>
       <c r="H931" t="n">
         <v>824</v>
@@ -27455,7 +27455,7 @@
         <v>14</v>
       </c>
       <c r="G934" t="n">
-        <v>12.8176393508911</v>
+        <v>12.8176383972168</v>
       </c>
       <c r="H934" t="n">
         <v>399</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.092303276062</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27658,7 +27658,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>13.110613822937</v>
+        <v>13.1106128692627</v>
       </c>
       <c r="H941" t="n">
         <v>991</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.092303276062</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27774,7 +27774,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H945" t="n">
         <v>3109</v>
@@ -27861,7 +27861,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H948" t="n">
         <v>4180</v>
@@ -27919,7 +27919,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402849197388</v>
+        <v>14.7402839660645</v>
       </c>
       <c r="H950" t="n">
         <v>5635</v>
@@ -27948,7 +27948,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G951" t="n">
-        <v>14.8501491546631</v>
+        <v>14.8501482009888</v>
       </c>
       <c r="H951" t="n">
         <v>10192</v>
@@ -28035,7 +28035,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G954" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H954" t="n">
         <v>5306</v>
@@ -28064,7 +28064,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346046447754</v>
+        <v>13.9346055984497</v>
       </c>
       <c r="H955" t="n">
         <v>1552</v>
@@ -28151,7 +28151,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H958" t="n">
         <v>840</v>
@@ -28180,7 +28180,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G959" t="n">
-        <v>13.4951429367065</v>
+        <v>13.4951419830322</v>
       </c>
       <c r="H959" t="n">
         <v>2351</v>
@@ -28325,7 +28325,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H964" t="n">
         <v>2199</v>
@@ -28441,7 +28441,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303442001343</v>
+        <v>13.3303451538086</v>
       </c>
       <c r="H968" t="n">
         <v>853</v>
@@ -28644,7 +28644,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>13.7331848144531</v>
+        <v>13.7331838607788</v>
       </c>
       <c r="H975" t="n">
         <v>3867</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796701431274</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28760,7 +28760,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H979" t="n">
         <v>548</v>
@@ -28847,7 +28847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H982" t="n">
         <v>1433</v>
@@ -28876,7 +28876,7 @@
         <v>15</v>
       </c>
       <c r="G983" t="n">
-        <v>13.7331848144531</v>
+        <v>13.7331838607788</v>
       </c>
       <c r="H983" t="n">
         <v>3489</v>
@@ -28905,7 +28905,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H984" t="n">
         <v>2674</v>
@@ -29166,7 +29166,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H993" t="n">
         <v>3823</v>
@@ -29224,7 +29224,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H995" t="n">
         <v>776</v>
@@ -29253,7 +29253,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G996" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H996" t="n">
         <v>786</v>
@@ -29282,7 +29282,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G997" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H997" t="n">
         <v>1556</v>
@@ -29311,7 +29311,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G998" t="n">
-        <v>13.8613615036011</v>
+        <v>13.8613605499268</v>
       </c>
       <c r="H998" t="n">
         <v>2430</v>
@@ -29340,7 +29340,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514963150024</v>
+        <v>13.7514953613281</v>
       </c>
       <c r="H999" t="n">
         <v>1949</v>
@@ -29369,7 +29369,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1000" t="n">
         <v>1623</v>
@@ -29427,7 +29427,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712266921997</v>
+        <v>13.9712257385254</v>
       </c>
       <c r="H1002" t="n">
         <v>3350</v>
@@ -29456,7 +29456,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H1003" t="n">
         <v>748</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796701431274</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29514,7 +29514,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.0810918807983</v>
+        <v>14.081090927124</v>
       </c>
       <c r="H1005" t="n">
         <v>1238</v>
@@ -29543,7 +29543,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1006" t="n">
         <v>626</v>
@@ -29572,7 +29572,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1007" t="n">
         <v>1460</v>
@@ -29630,7 +29630,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.9417037963867</v>
+        <v>14.941704750061</v>
       </c>
       <c r="H1009" t="n">
         <v>11362</v>
@@ -29659,7 +29659,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.6670408248901</v>
+        <v>14.6670417785645</v>
       </c>
       <c r="H1010" t="n">
         <v>14618</v>
@@ -29717,7 +29717,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H1012" t="n">
         <v>11964</v>
@@ -29746,7 +29746,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.3374443054199</v>
+        <v>14.3374433517456</v>
       </c>
       <c r="H1013" t="n">
         <v>8822</v>
@@ -29775,7 +29775,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1014" t="n">
         <v>801</v>
@@ -29804,7 +29804,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1015" t="n">
         <v>6837</v>
@@ -29833,7 +29833,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H1016" t="n">
         <v>3081</v>
@@ -29978,7 +29978,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H1021" t="n">
         <v>924</v>
@@ -30326,7 +30326,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1033" t="n">
-        <v>13.9895362854004</v>
+        <v>13.9895372390747</v>
       </c>
       <c r="H1033" t="n">
         <v>1202</v>
@@ -30384,7 +30384,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1035" t="n">
         <v>7293</v>
@@ -30558,7 +30558,7 @@
         <v>16</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6487293243408</v>
+        <v>14.6487302780151</v>
       </c>
       <c r="H1041" t="n">
         <v>3209</v>
@@ -30761,7 +30761,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.1726446151733</v>
+        <v>14.1726455688477</v>
       </c>
       <c r="H1048" t="n">
         <v>3540</v>
@@ -30993,7 +30993,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1056" t="n">
-        <v>14.6304187774658</v>
+        <v>14.6304178237915</v>
       </c>
       <c r="H1056" t="n">
         <v>9312</v>
@@ -31080,7 +31080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1059" t="n">
         <v>2147</v>
@@ -31399,7 +31399,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1070" t="n">
         <v>4599</v>
@@ -31428,7 +31428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1071" t="n">
         <v>15327</v>
@@ -31515,7 +31515,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1074" t="n">
         <v>4278</v>
@@ -31544,7 +31544,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>14.2458906173706</v>
+        <v>14.2458896636963</v>
       </c>
       <c r="H1075" t="n">
         <v>4709</v>
@@ -31573,7 +31573,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1076" t="n">
         <v>5561</v>
@@ -31602,7 +31602,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1077" t="n">
-        <v>14.044469833374</v>
+        <v>14.0444707870483</v>
       </c>
       <c r="H1077" t="n">
         <v>8530</v>
@@ -31631,7 +31631,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1078" t="n">
         <v>11008</v>
@@ -31718,7 +31718,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1081" t="n">
         <v>104130</v>
@@ -31776,7 +31776,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H1083" t="n">
         <v>10646</v>
@@ -31892,7 +31892,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.161434173584</v>
+        <v>15.1614351272583</v>
       </c>
       <c r="H1087" t="n">
         <v>6067</v>
@@ -31921,7 +31921,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>15.0515699386597</v>
+        <v>15.051570892334</v>
       </c>
       <c r="H1088" t="n">
         <v>8528</v>
@@ -32008,7 +32008,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1091" t="n">
         <v>9320</v>
@@ -32124,7 +32124,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473840713501</v>
+        <v>15.7473850250244</v>
       </c>
       <c r="H1095" t="n">
         <v>11814</v>
@@ -32211,7 +32211,7 @@
         <v>17</v>
       </c>
       <c r="G1098" t="n">
-        <v>15.5642738342285</v>
+        <v>15.5642757415771</v>
       </c>
       <c r="H1098" t="n">
         <v>8931</v>
@@ -32240,7 +32240,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8023176193237</v>
+        <v>15.802318572998</v>
       </c>
       <c r="H1099" t="n">
         <v>6086</v>
@@ -32356,7 +32356,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>15.2896118164062</v>
+        <v>15.2896127700806</v>
       </c>
       <c r="H1103" t="n">
         <v>5347</v>
@@ -32385,7 +32385,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="n">
-        <v>15.5642738342285</v>
+        <v>15.5642757415771</v>
       </c>
       <c r="H1104" t="n">
         <v>4079</v>
@@ -32414,7 +32414,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572492599487</v>
+        <v>15.8572483062744</v>
       </c>
       <c r="H1105" t="n">
         <v>21663</v>
@@ -32443,7 +32443,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290735244751</v>
+        <v>15.7290725708008</v>
       </c>
       <c r="H1106" t="n">
         <v>5698</v>
@@ -32617,7 +32617,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.3699531555176</v>
+        <v>16.3699550628662</v>
       </c>
       <c r="H1112" t="n">
         <v>28938</v>
@@ -58781,6 +58781,35 @@
         <v>11289</v>
       </c>
       <c r="I2014" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2015" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2015" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="H2015" t="n">
+        <v>15034</v>
+      </c>
+      <c r="I2015" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8810818195343</v>
+        <v>2.88108229637146</v>
       </c>
       <c r="H2" t="n">
         <v>41400</v>
@@ -485,7 +485,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H4" t="n">
         <v>7200</v>
@@ -514,7 +514,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248680114746</v>
+        <v>2.90248703956604</v>
       </c>
       <c r="H5" t="n">
         <v>8550</v>
@@ -659,7 +659,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762376785278</v>
+        <v>2.90762424468994</v>
       </c>
       <c r="H10" t="n">
         <v>2250</v>
@@ -746,7 +746,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H13" t="n">
         <v>3600</v>
@@ -775,7 +775,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441948890686</v>
+        <v>2.83441972732544</v>
       </c>
       <c r="H20" t="n">
         <v>900</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8986337184906</v>
+        <v>2.89863419532776</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1123,7 +1123,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974389076233</v>
+        <v>2.79974412918091</v>
       </c>
       <c r="H26" t="n">
         <v>1800</v>
@@ -1210,7 +1210,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H29" t="n">
         <v>1800</v>
@@ -1239,7 +1239,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549601554871</v>
+        <v>2.76549625396729</v>
       </c>
       <c r="H30" t="n">
         <v>3150</v>
@@ -1355,7 +1355,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035928726196</v>
+        <v>2.7603588104248</v>
       </c>
       <c r="H34" t="n">
         <v>1800</v>
@@ -1384,7 +1384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399152755737</v>
+        <v>2.83399176597595</v>
       </c>
       <c r="H35" t="n">
         <v>7650</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1471,7 +1471,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368394851685</v>
+        <v>2.85368418693542</v>
       </c>
       <c r="H38" t="n">
         <v>6300</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385837554932</v>
+        <v>2.95385813713074</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823916435242</v>
+        <v>2.86823892593384</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9966676235199</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379179954529</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256887435913</v>
+        <v>3.34256911277771</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489611625671</v>
+        <v>3.30489659309387</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768544197083</v>
+        <v>3.2376856803894</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2109,7 +2109,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309681892395</v>
+        <v>3.25309705734253</v>
       </c>
       <c r="H60" t="n">
         <v>5400</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36482977867126</v>
+        <v>3.36483025550842</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2225,7 +2225,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873642921448</v>
+        <v>3.44873666763306</v>
       </c>
       <c r="H64" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757292747498</v>
+        <v>3.4675726890564</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2283,7 +2283,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098480224609</v>
+        <v>3.61098504066467</v>
       </c>
       <c r="H66" t="n">
         <v>38250</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630477905273</v>
+        <v>3.966304063797</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2399,7 +2399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533443450928</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H70" t="n">
         <v>59850</v>
@@ -2486,7 +2486,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G73" t="n">
-        <v>4.09087991714478</v>
+        <v>4.09087944030762</v>
       </c>
       <c r="H73" t="n">
         <v>33300</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.06690645217896</v>
+        <v>4.0669059753418</v>
       </c>
       <c r="H74" t="n">
         <v>18450</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279196739197</v>
+        <v>3.91279172897339</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2689,7 +2689,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407561302185</v>
+        <v>3.91407608985901</v>
       </c>
       <c r="H80" t="n">
         <v>4950</v>
@@ -2718,7 +2718,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553440093994</v>
+        <v>4.0155348777771</v>
       </c>
       <c r="H81" t="n">
         <v>1800</v>
@@ -2747,7 +2747,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.9564573764801</v>
+        <v>3.95645809173584</v>
       </c>
       <c r="H82" t="n">
         <v>2250</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566802978516</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0082573890686</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041068077087</v>
+        <v>3.87041091918945</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566802978516</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>4.57250022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>3.91493225097656</v>
+        <v>3.91493272781372</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -3037,7 +3037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H92" t="n">
         <v>6750</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533443450928</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H93" t="n">
         <v>10350</v>
@@ -3095,7 +3095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H96" t="n">
         <v>12600</v>
@@ -3182,7 +3182,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.0583438873291</v>
+        <v>4.05834436416626</v>
       </c>
       <c r="H97" t="n">
         <v>900</v>
@@ -3240,7 +3240,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H99" t="n">
         <v>8550</v>
@@ -3269,7 +3269,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H102" t="n">
         <v>4050</v>
@@ -3356,7 +3356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533443450928</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H103" t="n">
         <v>2250</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533443450928</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H104" t="n">
         <v>9450</v>
@@ -3501,7 +3501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H108" t="n">
         <v>11250</v>
@@ -3559,7 +3559,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H110" t="n">
         <v>21150</v>
@@ -3617,7 +3617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H112" t="n">
         <v>13950</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781080245972</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3704,7 +3704,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245861053467</v>
+        <v>4.21245908737183</v>
       </c>
       <c r="H115" t="n">
         <v>22950</v>
@@ -3733,7 +3733,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533443450928</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H116" t="n">
         <v>900</v>
@@ -3762,7 +3762,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H117" t="n">
         <v>5400</v>
@@ -3791,7 +3791,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H118" t="n">
         <v>6300</v>
@@ -3849,7 +3849,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H120" t="n">
         <v>11700</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781080245972</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781080245972</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -4023,7 +4023,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376337051392</v>
+        <v>4.32376384735107</v>
       </c>
       <c r="H126" t="n">
         <v>900</v>
@@ -4052,7 +4052,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H127" t="n">
         <v>10800</v>
@@ -4081,7 +4081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H128" t="n">
         <v>8100</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4168,7 +4168,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500179290771</v>
+        <v>4.49500226974487</v>
       </c>
       <c r="H131" t="n">
         <v>4950</v>
@@ -4197,7 +4197,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H132" t="n">
         <v>4050</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781080245972</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4255,7 +4255,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.4521918296814</v>
+        <v>4.45219230651855</v>
       </c>
       <c r="H134" t="n">
         <v>7200</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4429,7 +4429,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557350158691</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H140" t="n">
         <v>33750</v>
@@ -4458,7 +4458,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557350158691</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H141" t="n">
         <v>21150</v>
@@ -4487,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H142" t="n">
         <v>9900</v>
@@ -4516,7 +4516,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H143" t="n">
         <v>2250</v>
@@ -4545,7 +4545,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H144" t="n">
         <v>1350</v>
@@ -4603,7 +4603,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H146" t="n">
         <v>11250</v>
@@ -4661,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H148" t="n">
         <v>1350</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H149" t="n">
         <v>6750</v>
@@ -4719,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H152" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H154" t="n">
         <v>3150</v>
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H158" t="n">
         <v>1800</v>
@@ -4980,7 +4980,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433555603027</v>
+        <v>5.09433507919312</v>
       </c>
       <c r="H159" t="n">
         <v>2250</v>
@@ -5009,7 +5009,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H160" t="n">
         <v>7650</v>
@@ -5038,7 +5038,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H161" t="n">
         <v>102150</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5241,7 +5241,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H168" t="n">
         <v>10800</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424150466919</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5647,7 +5647,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.02076435089111</v>
+        <v>7.02076482772827</v>
       </c>
       <c r="H182" t="n">
         <v>31050</v>
@@ -5705,7 +5705,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671691894531</v>
+        <v>6.80671787261963</v>
       </c>
       <c r="H184" t="n">
         <v>3600</v>
@@ -5734,7 +5734,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H185" t="n">
         <v>15750</v>
@@ -5763,7 +5763,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H186" t="n">
         <v>4050</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514537811279</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266901016235</v>
+        <v>6.5926685333252</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919328689575</v>
+        <v>7.14919376373291</v>
       </c>
       <c r="H196" t="n">
         <v>13950</v>
@@ -6082,7 +6082,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638284683228</v>
+        <v>7.10638380050659</v>
       </c>
       <c r="H197" t="n">
         <v>15750</v>
@@ -6111,7 +6111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638284683228</v>
+        <v>7.10638380050659</v>
       </c>
       <c r="H198" t="n">
         <v>10800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514537811279</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6198,7 +6198,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671691894531</v>
+        <v>6.80671787261963</v>
       </c>
       <c r="H201" t="n">
         <v>11250</v>
@@ -6256,7 +6256,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H203" t="n">
         <v>2250</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266901016235</v>
+        <v>6.5926685333252</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6517,7 +6517,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H212" t="n">
         <v>4050</v>
@@ -6546,7 +6546,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390695571899</v>
+        <v>6.76390743255615</v>
       </c>
       <c r="H213" t="n">
         <v>3150</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862157821655</v>
+        <v>6.37862205505371</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6865,7 +6865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H224" t="n">
         <v>6100</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -6952,7 +6952,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H227" t="n">
         <v>19965</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424150466919</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300308227539</v>
+        <v>6.29300260543823</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7300,7 +7300,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H239" t="n">
         <v>7153</v>
@@ -7416,7 +7416,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H243" t="n">
         <v>3750</v>
@@ -7590,7 +7590,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H249" t="n">
         <v>5546</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7909,7 +7909,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H260" t="n">
         <v>10941</v>
@@ -7938,7 +7938,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H261" t="n">
         <v>2202</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333524703979</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8518,7 +8518,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895421981812</v>
+        <v>6.07895517349243</v>
       </c>
       <c r="H281" t="n">
         <v>14397</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771675109863</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490726470947</v>
+        <v>5.86490678787231</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.60805034637451</v>
+        <v>5.6080493927002</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9417,7 +9417,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H312" t="n">
         <v>1448</v>
@@ -9446,7 +9446,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H313" t="n">
         <v>8895</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647832870483</v>
+        <v>5.73647785186768</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9591,7 +9591,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H318" t="n">
         <v>25735</v>
@@ -9620,7 +9620,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557350158691</v>
+        <v>5.26557302474976</v>
       </c>
       <c r="H319" t="n">
         <v>5941</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995452880859</v>
+        <v>5.17995405197144</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750635147095</v>
       </c>
       <c r="H328" t="n">
         <v>14468</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051556587219</v>
+        <v>3.39051580429077</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -10026,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857228279114</v>
+        <v>2.56857252120972</v>
       </c>
       <c r="H333" t="n">
         <v>13836</v>
@@ -10113,7 +10113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.48295331001282</v>
+        <v>2.48295378684998</v>
       </c>
       <c r="H336" t="n">
         <v>8502</v>
@@ -10142,7 +10142,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H337" t="n">
         <v>1910</v>
@@ -10171,7 +10171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981070518494</v>
+        <v>2.73981046676636</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G339" t="n">
-        <v>3.23640108108521</v>
+        <v>3.23640131950378</v>
       </c>
       <c r="H339" t="n">
         <v>2830</v>
@@ -10229,7 +10229,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560145378113</v>
+        <v>3.95560097694397</v>
       </c>
       <c r="H340" t="n">
         <v>40606</v>
@@ -10316,7 +10316,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533443450928</v>
+        <v>4.19533491134644</v>
       </c>
       <c r="H343" t="n">
         <v>19120</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723909378052</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299217224121</v>
+        <v>3.73299169540405</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10432,7 +10432,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>3.51038217544556</v>
+        <v>3.51038241386414</v>
       </c>
       <c r="H347" t="n">
         <v>4841</v>
@@ -10490,7 +10490,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H349" t="n">
         <v>8462</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476367950439</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593528747559</v>
+        <v>3.65593457221985</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63881134986877</v>
+        <v>3.6388111114502</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10606,7 +10606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H353" t="n">
         <v>1950</v>
@@ -10635,7 +10635,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894402503967</v>
+        <v>3.51894426345825</v>
       </c>
       <c r="H354" t="n">
         <v>4650</v>
@@ -10664,7 +10664,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750635147095</v>
       </c>
       <c r="H355" t="n">
         <v>3470</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757292747498</v>
+        <v>3.4675726890564</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10722,7 +10722,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620111465454</v>
       </c>
       <c r="H357" t="n">
         <v>4102</v>
@@ -10751,7 +10751,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620111465454</v>
       </c>
       <c r="H358" t="n">
         <v>4270</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476367950439</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757292747498</v>
+        <v>3.4675726890564</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10838,7 +10838,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449689865112</v>
+        <v>3.66449666023254</v>
       </c>
       <c r="H361" t="n">
         <v>16600</v>
@@ -10867,7 +10867,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861066818237</v>
       </c>
       <c r="H362" t="n">
         <v>19084</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723909378052</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861114501953</v>
+        <v>3.81861066818237</v>
       </c>
       <c r="H364" t="n">
         <v>2419</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854480743408</v>
+        <v>3.8785445690155</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285806655884</v>
+        <v>3.85285878181458</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11041,7 +11041,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>4.74329662322998</v>
+        <v>4.74329710006714</v>
       </c>
       <c r="H368" t="n">
         <v>77313</v>
@@ -11070,7 +11070,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356435775757</v>
+        <v>4.50356340408325</v>
       </c>
       <c r="H369" t="n">
         <v>65581</v>
@@ -11186,7 +11186,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G373" t="n">
-        <v>4.82891607284546</v>
+        <v>4.8289155960083</v>
       </c>
       <c r="H373" t="n">
         <v>122121</v>
@@ -11215,7 +11215,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G374" t="n">
-        <v>4.6234302520752</v>
+        <v>4.62343072891235</v>
       </c>
       <c r="H374" t="n">
         <v>82279</v>
@@ -11273,7 +11273,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.4008207321167</v>
+        <v>4.40082025527954</v>
       </c>
       <c r="H376" t="n">
         <v>38510</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239274978638</v>
+        <v>4.27239179611206</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781080245972</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11534,7 +11534,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H385" t="n">
         <v>40025</v>
@@ -11766,7 +11766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.880286693573</v>
+        <v>4.88028717041016</v>
       </c>
       <c r="H393" t="n">
         <v>8696</v>
@@ -11969,7 +11969,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H400" t="n">
         <v>1473</v>
@@ -11998,7 +11998,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H401" t="n">
         <v>1401</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H417" t="n">
         <v>3912</v>
@@ -12520,7 +12520,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550668716431</v>
+        <v>5.32550716400146</v>
       </c>
       <c r="H419" t="n">
         <v>44555</v>
@@ -12549,7 +12549,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H420" t="n">
         <v>11461</v>
@@ -12607,7 +12607,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413558959961</v>
       </c>
       <c r="H422" t="n">
         <v>7415</v>
@@ -12636,7 +12636,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H423" t="n">
         <v>4800</v>
@@ -12665,7 +12665,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H424" t="n">
         <v>970</v>
@@ -12752,7 +12752,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.22276401519775</v>
+        <v>5.2227635383606</v>
       </c>
       <c r="H427" t="n">
         <v>5140</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440237045288</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -13071,7 +13071,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413463592529</v>
+        <v>5.27413558959961</v>
       </c>
       <c r="H438" t="n">
         <v>8401</v>
@@ -13129,7 +13129,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H440" t="n">
         <v>592</v>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H441" t="n">
         <v>915</v>
@@ -13245,7 +13245,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H444" t="n">
         <v>1100</v>
@@ -13303,7 +13303,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H446" t="n">
         <v>504</v>
@@ -13361,7 +13361,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714456558228</v>
+        <v>5.13714504241943</v>
       </c>
       <c r="H448" t="n">
         <v>7543</v>
@@ -13419,7 +13419,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.2024359703064</v>
+        <v>5.20243644714355</v>
       </c>
       <c r="H450" t="n">
         <v>2913</v>
@@ -13506,7 +13506,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H453" t="n">
         <v>7910</v>
@@ -13535,7 +13535,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023803710938</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H454" t="n">
         <v>900</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803867340088</v>
+        <v>5.0980396270752</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13738,7 +13738,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763782501221</v>
+        <v>5.16763734817505</v>
       </c>
       <c r="H461" t="n">
         <v>2800</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H466" t="n">
         <v>2015</v>
@@ -13941,7 +13941,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>5.04584121704102</v>
+        <v>5.04584169387817</v>
       </c>
       <c r="H468" t="n">
         <v>7558</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14057,7 +14057,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H472" t="n">
         <v>10358</v>
@@ -14086,7 +14086,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.8370475769043</v>
+        <v>4.83704710006714</v>
       </c>
       <c r="H473" t="n">
         <v>2696</v>
@@ -14115,7 +14115,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404413223267</v>
       </c>
       <c r="H474" t="n">
         <v>6712</v>
@@ -14144,7 +14144,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404413223267</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005006790161</v>
+        <v>4.75004959106445</v>
       </c>
       <c r="H477" t="n">
         <v>1841</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14318,7 +14318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H481" t="n">
         <v>6191</v>
@@ -14405,7 +14405,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H484" t="n">
         <v>2940</v>
@@ -14434,7 +14434,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H485" t="n">
         <v>672</v>
@@ -14463,7 +14463,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H486" t="n">
         <v>200</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H487" t="n">
         <v>537</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14550,7 +14550,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425939559937</v>
+        <v>4.45425987243652</v>
       </c>
       <c r="H489" t="n">
         <v>3075</v>
@@ -14724,7 +14724,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716861724854</v>
+        <v>4.16716909408569</v>
       </c>
       <c r="H495" t="n">
         <v>20644</v>
@@ -14782,7 +14782,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416564941406</v>
+        <v>4.25416612625122</v>
       </c>
       <c r="H497" t="n">
         <v>1064</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497020721436</v>
+        <v>4.1149697303772</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456840515137</v>
+        <v>4.18456792831421</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -14985,7 +14985,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.3063645362854</v>
+        <v>4.30636405944824</v>
       </c>
       <c r="H504" t="n">
         <v>10900</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43685960769653</v>
       </c>
       <c r="H507" t="n">
         <v>12706</v>
@@ -15101,7 +15101,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H508" t="n">
         <v>14843</v>
@@ -15130,7 +15130,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H509" t="n">
         <v>6520</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15217,7 +15217,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H512" t="n">
         <v>2873</v>
@@ -15304,7 +15304,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H515" t="n">
         <v>2290</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H517" t="n">
         <v>3170</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H518" t="n">
         <v>1170</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H523" t="n">
         <v>6233</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385711669922</v>
+        <v>4.52385759353638</v>
       </c>
       <c r="H524" t="n">
         <v>1255</v>
@@ -15652,7 +15652,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H527" t="n">
         <v>920</v>
@@ -15681,7 +15681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H528" t="n">
         <v>1750</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15739,7 +15739,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43685960769653</v>
       </c>
       <c r="H530" t="n">
         <v>10190</v>
@@ -15768,7 +15768,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G531" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H531" t="n">
         <v>7058</v>
@@ -15797,7 +15797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H532" t="n">
         <v>16579</v>
@@ -15971,7 +15971,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H538" t="n">
         <v>1392</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16058,7 +16058,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H541" t="n">
         <v>1369</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16174,7 +16174,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H545" t="n">
         <v>1820</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.57605600357056</v>
+        <v>4.5760555267334</v>
       </c>
       <c r="H549" t="n">
         <v>1333</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16406,7 +16406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H553" t="n">
         <v>12566</v>
@@ -16435,7 +16435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H554" t="n">
         <v>4021</v>
@@ -16464,7 +16464,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H555" t="n">
         <v>3530</v>
@@ -16493,7 +16493,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H556" t="n">
         <v>4770</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206050872803</v>
+        <v>4.40206098556519</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16551,7 +16551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43685960769653</v>
       </c>
       <c r="H558" t="n">
         <v>2505</v>
@@ -16609,7 +16609,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G560" t="n">
-        <v>4.48905897140503</v>
+        <v>4.48905849456787</v>
       </c>
       <c r="H560" t="n">
         <v>3592</v>
@@ -16696,7 +16696,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H563" t="n">
         <v>7869</v>
@@ -16754,7 +16754,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484964370728</v>
+        <v>4.78484916687012</v>
       </c>
       <c r="H565" t="n">
         <v>4770</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16841,7 +16841,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H568" t="n">
         <v>22400</v>
@@ -16928,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H571" t="n">
         <v>855</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17102,7 +17102,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H577" t="n">
         <v>6090</v>
@@ -17131,7 +17131,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H578" t="n">
         <v>11230</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17305,7 +17305,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H584" t="n">
         <v>21315</v>
@@ -17479,7 +17479,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H590" t="n">
         <v>6044</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17653,7 +17653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023803710938</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H596" t="n">
         <v>9629</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983575820923</v>
       </c>
       <c r="H597" t="n">
         <v>33122</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39382982254028</v>
+        <v>5.39382934570312</v>
       </c>
       <c r="H601" t="n">
         <v>124984</v>
@@ -17827,7 +17827,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>5.68962049484253</v>
+        <v>5.68962097167969</v>
       </c>
       <c r="H602" t="n">
         <v>98090</v>
@@ -17856,7 +17856,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>5.67222118377686</v>
+        <v>5.6722207069397</v>
       </c>
       <c r="H603" t="n">
         <v>155697</v>
@@ -17885,7 +17885,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68962049484253</v>
+        <v>5.68962097167969</v>
       </c>
       <c r="H604" t="n">
         <v>14365</v>
@@ -17943,7 +17943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H606" t="n">
         <v>11629</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.41122913360596</v>
+        <v>5.41122961044312</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18001,7 +18001,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082780838013</v>
+        <v>5.48082733154297</v>
       </c>
       <c r="H608" t="n">
         <v>8454</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.41122913360596</v>
+        <v>5.41122961044312</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18059,7 +18059,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.56782484054565</v>
+        <v>5.5678243637085</v>
       </c>
       <c r="H610" t="n">
         <v>163362</v>
@@ -18175,7 +18175,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881641387939</v>
+        <v>5.82881546020508</v>
       </c>
       <c r="H614" t="n">
         <v>16210</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801233291626</v>
+        <v>5.9680118560791</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281095504761</v>
+        <v>6.00281047821045</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281095504761</v>
+        <v>6.00281047821045</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031137466431</v>
+        <v>7.00031089782715</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18436,7 +18436,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.83999729156494</v>
+        <v>6.8399977684021</v>
       </c>
       <c r="H623" t="n">
         <v>76240</v>
@@ -18465,7 +18465,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718584060669</v>
+        <v>7.10718536376953</v>
       </c>
       <c r="H624" t="n">
         <v>102683</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468544006348</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874671936035</v>
+        <v>7.90874767303467</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968593597412</v>
+        <v>7.8196849822998</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18726,7 +18726,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.47874736785889</v>
+        <v>8.4787483215332</v>
       </c>
       <c r="H633" t="n">
         <v>83403</v>
@@ -18755,7 +18755,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343521118164</v>
+        <v>9.17343425750732</v>
       </c>
       <c r="H634" t="n">
         <v>112604</v>
@@ -18813,7 +18813,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249599456787</v>
+        <v>9.2624979019165</v>
       </c>
       <c r="H636" t="n">
         <v>208819</v>
@@ -18842,7 +18842,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249599456787</v>
+        <v>9.2624979019165</v>
       </c>
       <c r="H637" t="n">
         <v>116116</v>
@@ -18871,7 +18871,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890434265137</v>
+        <v>9.12890338897705</v>
       </c>
       <c r="H638" t="n">
         <v>117220</v>
@@ -18900,7 +18900,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702972412109</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H639" t="n">
         <v>47607</v>
@@ -18958,7 +18958,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.8171854019165</v>
+        <v>8.81718444824219</v>
       </c>
       <c r="H641" t="n">
         <v>40921</v>
@@ -18987,7 +18987,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937171936035</v>
+        <v>8.79937267303467</v>
       </c>
       <c r="H642" t="n">
         <v>24861</v>
@@ -19016,7 +19016,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G643" t="n">
-        <v>8.69249725341797</v>
+        <v>8.69249820709229</v>
       </c>
       <c r="H643" t="n">
         <v>30205</v>
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624713897705</v>
+        <v>8.90624809265137</v>
       </c>
       <c r="H645" t="n">
         <v>112321</v>
@@ -19103,7 +19103,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702972412109</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H646" t="n">
         <v>97578</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062232971191</v>
+        <v>9.44062328338623</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19161,7 +19161,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046569824219</v>
+        <v>9.93046474456787</v>
       </c>
       <c r="H648" t="n">
         <v>98237</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19277,7 +19277,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H652" t="n">
         <v>199932</v>
@@ -19306,7 +19306,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H653" t="n">
         <v>91653</v>
@@ -19364,7 +19364,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671829223633</v>
       </c>
       <c r="H655" t="n">
         <v>87639</v>
@@ -19393,7 +19393,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890584945679</v>
+        <v>11.4890594482422</v>
       </c>
       <c r="H656" t="n">
         <v>32521</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19567,7 +19567,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562456130981</v>
+        <v>11.7562465667725</v>
       </c>
       <c r="H662" t="n">
         <v>64255</v>
@@ -19596,7 +19596,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671829223633</v>
       </c>
       <c r="H663" t="n">
         <v>11952</v>
@@ -19654,7 +19654,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.859450340271</v>
+        <v>11.8594512939453</v>
       </c>
       <c r="H665" t="n">
         <v>38062</v>
@@ -19712,7 +19712,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H667" t="n">
         <v>20242</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19828,7 +19828,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H671" t="n">
         <v>3415</v>
@@ -19886,7 +19886,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>11.095775604248</v>
+        <v>11.0957736968994</v>
       </c>
       <c r="H673" t="n">
         <v>20518</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363958358765</v>
+        <v>10.7363967895508</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20031,7 +20031,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H678" t="n">
         <v>18194</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.7246837615967</v>
+        <v>11.724684715271</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20205,7 +20205,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.7696075439453</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H684" t="n">
         <v>11051</v>
@@ -20234,7 +20234,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.7696075439453</v>
+        <v>11.769606590271</v>
       </c>
       <c r="H685" t="n">
         <v>9237</v>
@@ -20292,7 +20292,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348400115967</v>
+        <v>11.6348390579224</v>
       </c>
       <c r="H687" t="n">
         <v>8053</v>
@@ -20321,7 +20321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449962615967</v>
+        <v>11.5449953079224</v>
       </c>
       <c r="H688" t="n">
         <v>8002</v>
@@ -20379,7 +20379,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535938262939</v>
+        <v>12.3535957336426</v>
       </c>
       <c r="H690" t="n">
         <v>194061</v>
@@ -20408,7 +20408,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="n">
         <v>55853</v>
@@ -20495,7 +20495,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>14.3301706314087</v>
+        <v>14.3301696777344</v>
       </c>
       <c r="H694" t="n">
         <v>144504</v>
@@ -20524,7 +20524,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H695" t="n">
         <v>297213</v>
@@ -20582,7 +20582,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.8340969085693</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H697" t="n">
         <v>248766</v>
@@ -20640,7 +20640,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>16.8907318115234</v>
+        <v>16.8907337188721</v>
       </c>
       <c r="H699" t="n">
         <v>100713</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180889129639</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20727,7 +20727,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.8340969085693</v>
+        <v>17.834098815918</v>
       </c>
       <c r="H702" t="n">
         <v>62036</v>
@@ -20756,7 +20756,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.923942565918</v>
+        <v>17.9239444732666</v>
       </c>
       <c r="H703" t="n">
         <v>17675</v>
@@ -20785,7 +20785,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H704" t="n">
         <v>50153</v>
@@ -20843,7 +20843,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H706" t="n">
         <v>37684</v>
@@ -20872,7 +20872,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399562835693</v>
       </c>
       <c r="H707" t="n">
         <v>16206</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -20930,7 +20930,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>17.7891750335693</v>
+        <v>17.789176940918</v>
       </c>
       <c r="H709" t="n">
         <v>27928</v>
@@ -20959,7 +20959,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>17.6094875335693</v>
+        <v>17.609489440918</v>
       </c>
       <c r="H710" t="n">
         <v>17019</v>
@@ -21017,7 +21017,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H712" t="n">
         <v>12956</v>
@@ -21075,7 +21075,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H714" t="n">
         <v>56021</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21133,7 +21133,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.8907318115234</v>
+        <v>16.8907337188721</v>
       </c>
       <c r="H716" t="n">
         <v>64516</v>
@@ -21162,7 +21162,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H717" t="n">
         <v>48881</v>
@@ -21249,7 +21249,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H720" t="n">
         <v>23381</v>
@@ -21307,7 +21307,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H722" t="n">
         <v>31177</v>
@@ -21336,7 +21336,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H723" t="n">
         <v>11585</v>
@@ -21394,7 +21394,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>17.1602668762207</v>
+        <v>17.1602687835693</v>
       </c>
       <c r="H725" t="n">
         <v>61724</v>
@@ -21423,7 +21423,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>17.1602668762207</v>
+        <v>17.1602687835693</v>
       </c>
       <c r="H726" t="n">
         <v>19578</v>
@@ -21452,7 +21452,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>17.1602668762207</v>
+        <v>17.1602687835693</v>
       </c>
       <c r="H727" t="n">
         <v>4990</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H728" t="n">
         <v>20822</v>
@@ -21539,7 +21539,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399562835693</v>
       </c>
       <c r="H730" t="n">
         <v>22860</v>
@@ -21568,7 +21568,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>17.3848762512207</v>
+        <v>17.3848781585693</v>
       </c>
       <c r="H731" t="n">
         <v>22850</v>
@@ -21597,7 +21597,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H732" t="n">
         <v>11380</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21684,7 +21684,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153430938721</v>
+        <v>17.1153450012207</v>
       </c>
       <c r="H735" t="n">
         <v>6538</v>
@@ -21713,7 +21713,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H736" t="n">
         <v>10110</v>
@@ -21742,7 +21742,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H737" t="n">
         <v>15411</v>
@@ -21771,7 +21771,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399543762207</v>
+        <v>17.3399562835693</v>
       </c>
       <c r="H738" t="n">
         <v>18846</v>
@@ -21800,7 +21800,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950305938721</v>
+        <v>17.2950325012207</v>
       </c>
       <c r="H739" t="n">
         <v>9553</v>
@@ -21829,7 +21829,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>17.1602668762207</v>
+        <v>17.1602687835693</v>
       </c>
       <c r="H740" t="n">
         <v>13774</v>
@@ -21858,7 +21858,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313529968262</v>
       </c>
       <c r="H741" t="n">
         <v>81245</v>
@@ -21887,7 +21887,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313529968262</v>
       </c>
       <c r="H742" t="n">
         <v>26368</v>
@@ -21945,7 +21945,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313529968262</v>
       </c>
       <c r="H744" t="n">
         <v>13809</v>
@@ -21974,7 +21974,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H745" t="n">
         <v>15308</v>
@@ -22003,7 +22003,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H746" t="n">
         <v>42523</v>
@@ -22032,7 +22032,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0821342468262</v>
+        <v>16.0821323394775</v>
       </c>
       <c r="H747" t="n">
         <v>11492</v>
@@ -22119,7 +22119,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H750" t="n">
         <v>10298</v>
@@ -22148,7 +22148,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864349365234</v>
+        <v>16.4864330291748</v>
       </c>
       <c r="H751" t="n">
         <v>22548</v>
@@ -22177,7 +22177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110443115234</v>
+        <v>16.7110424041748</v>
       </c>
       <c r="H752" t="n">
         <v>38381</v>
@@ -22264,7 +22264,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H755" t="n">
         <v>10473</v>
@@ -22322,7 +22322,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>16.3516674041748</v>
+        <v>16.3516654968262</v>
       </c>
       <c r="H757" t="n">
         <v>5194</v>
@@ -22351,7 +22351,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H758" t="n">
         <v>8367</v>
@@ -22380,7 +22380,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661224365234</v>
+        <v>16.6661205291748</v>
       </c>
       <c r="H759" t="n">
         <v>32049</v>
@@ -22438,7 +22438,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313529968262</v>
       </c>
       <c r="H761" t="n">
         <v>15074</v>
@@ -22554,7 +22554,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778345108032</v>
       </c>
       <c r="H765" t="n">
         <v>16640</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387701034546</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22612,7 +22612,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.3184566497803</v>
+        <v>15.3184576034546</v>
       </c>
       <c r="H767" t="n">
         <v>6092</v>
@@ -22641,7 +22641,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040035247803</v>
+        <v>15.0040016174316</v>
       </c>
       <c r="H768" t="n">
         <v>16692</v>
@@ -22757,7 +22757,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864349365234</v>
+        <v>16.4864330291748</v>
       </c>
       <c r="H772" t="n">
         <v>30917</v>
@@ -22873,7 +22873,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618236541748</v>
+        <v>16.2618217468262</v>
       </c>
       <c r="H776" t="n">
         <v>3032</v>
@@ -22902,7 +22902,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>16.0821342468262</v>
+        <v>16.0821323394775</v>
       </c>
       <c r="H777" t="n">
         <v>6129</v>
@@ -22931,7 +22931,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H778" t="n">
         <v>8343</v>
@@ -22960,7 +22960,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H779" t="n">
         <v>4290</v>
@@ -22989,7 +22989,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270599365234</v>
+        <v>16.1270542144775</v>
       </c>
       <c r="H780" t="n">
         <v>2753</v>
@@ -23018,7 +23018,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H781" t="n">
         <v>3445</v>
@@ -23047,7 +23047,7 @@
         <v>17.75</v>
       </c>
       <c r="G782" t="n">
-        <v>15.9473676681519</v>
+        <v>15.9473657608032</v>
       </c>
       <c r="H782" t="n">
         <v>3539</v>
@@ -23076,7 +23076,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H783" t="n">
         <v>3772</v>
@@ -23105,7 +23105,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H784" t="n">
         <v>9640</v>
@@ -23134,7 +23134,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H785" t="n">
         <v>2827</v>
@@ -23163,7 +23163,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H786" t="n">
         <v>2004</v>
@@ -23192,7 +23192,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H787" t="n">
         <v>1452</v>
@@ -23221,7 +23221,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H788" t="n">
         <v>14768</v>
@@ -23250,7 +23250,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>15.4083013534546</v>
+        <v>15.4083003997803</v>
       </c>
       <c r="H789" t="n">
         <v>6755</v>
@@ -23279,7 +23279,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126020431519</v>
+        <v>15.8126010894775</v>
       </c>
       <c r="H790" t="n">
         <v>9326</v>
@@ -23337,7 +23337,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922904968262</v>
+        <v>15.9922885894775</v>
       </c>
       <c r="H792" t="n">
         <v>6586</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024438858032</v>
+        <v>15.9024457931519</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23511,7 +23511,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H798" t="n">
         <v>13711</v>
@@ -23540,7 +23540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778345108032</v>
       </c>
       <c r="H799" t="n">
         <v>4638</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227554321289</v>
       </c>
       <c r="H800" t="n">
         <v>4924</v>
@@ -23598,7 +23598,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.3184566497803</v>
+        <v>15.3184576034546</v>
       </c>
       <c r="H801" t="n">
         <v>17725</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879917144775</v>
+        <v>15.5879898071289</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23685,7 +23685,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H804" t="n">
         <v>6910</v>
@@ -23772,7 +23772,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141578674316</v>
+        <v>14.914158821106</v>
       </c>
       <c r="H807" t="n">
         <v>18172</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387701034546</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -23859,7 +23859,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.1836910247803</v>
+        <v>15.1836919784546</v>
       </c>
       <c r="H810" t="n">
         <v>3859</v>
@@ -23888,7 +23888,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590797424316</v>
+        <v>14.9590787887573</v>
       </c>
       <c r="H811" t="n">
         <v>1809</v>
@@ -24004,7 +24004,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H815" t="n">
         <v>21544</v>
@@ -24062,7 +24062,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.554780960083</v>
+        <v>14.5547819137573</v>
       </c>
       <c r="H817" t="n">
         <v>53993</v>
@@ -24149,7 +24149,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H820" t="n">
         <v>14476</v>
@@ -24178,7 +24178,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.599702835083</v>
+        <v>14.5997018814087</v>
       </c>
       <c r="H821" t="n">
         <v>12526</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504802703857</v>
+        <v>14.1504812240601</v>
       </c>
       <c r="H822" t="n">
         <v>17003</v>
@@ -24236,7 +24236,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200124740601</v>
+        <v>14.4200134277344</v>
       </c>
       <c r="H823" t="n">
         <v>6212</v>
@@ -24265,7 +24265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055593490601</v>
+        <v>14.1055583953857</v>
       </c>
       <c r="H824" t="n">
         <v>35205</v>
@@ -24323,7 +24323,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114149093628</v>
       </c>
       <c r="H826" t="n">
         <v>4142</v>
@@ -24439,7 +24439,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H830" t="n">
         <v>25666</v>
@@ -24468,7 +24468,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477382659912</v>
+        <v>12.8477392196655</v>
       </c>
       <c r="H831" t="n">
         <v>15063</v>
@@ -24497,7 +24497,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129726409912</v>
+        <v>12.7129716873169</v>
       </c>
       <c r="H832" t="n">
         <v>7112</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680498123169</v>
+        <v>12.6680507659912</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24555,7 +24555,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H834" t="n">
         <v>12679</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332822799683</v>
+        <v>12.5332832336426</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24758,7 +24758,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578945159912</v>
+        <v>12.7578935623169</v>
       </c>
       <c r="H841" t="n">
         <v>18683</v>
@@ -24787,7 +24787,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172723770142</v>
+        <v>13.1172714233398</v>
       </c>
       <c r="H842" t="n">
         <v>4865</v>
@@ -24816,7 +24816,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723485946655</v>
+        <v>13.0723495483398</v>
       </c>
       <c r="H843" t="n">
         <v>3970</v>
@@ -24874,7 +24874,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969598770142</v>
+        <v>13.2969608306885</v>
       </c>
       <c r="H845" t="n">
         <v>4249</v>
@@ -24903,7 +24903,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>13.3418827056885</v>
+        <v>13.3418817520142</v>
       </c>
       <c r="H846" t="n">
         <v>2019</v>
@@ -24932,7 +24932,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664930343628</v>
+        <v>13.5664939880371</v>
       </c>
       <c r="H847" t="n">
         <v>9274</v>
@@ -25106,7 +25106,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H853" t="n">
         <v>10148</v>
@@ -25193,7 +25193,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.2196283340454</v>
+        <v>15.2196292877197</v>
       </c>
       <c r="H856" t="n">
         <v>17742</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.399317741394</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25280,7 +25280,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>15.5430679321289</v>
+        <v>15.5430660247803</v>
       </c>
       <c r="H859" t="n">
         <v>25099</v>
@@ -25338,7 +25338,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657218933105</v>
+        <v>15.1657209396362</v>
       </c>
       <c r="H861" t="n">
         <v>7654</v>
@@ -25425,7 +25425,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>16.118070602417</v>
+        <v>16.1180725097656</v>
       </c>
       <c r="H864" t="n">
         <v>30261</v>
@@ -25454,7 +25454,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563522338867</v>
+        <v>15.9563512802124</v>
       </c>
       <c r="H865" t="n">
         <v>11649</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407274246216</v>
+        <v>15.7407264709473</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25512,7 +25512,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5251007080078</v>
+        <v>15.5250997543335</v>
       </c>
       <c r="H867" t="n">
         <v>7118</v>
@@ -25541,7 +25541,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454103469849</v>
+        <v>15.3454113006592</v>
       </c>
       <c r="H868" t="n">
         <v>4337</v>
@@ -25599,7 +25599,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>14.644624710083</v>
+        <v>14.6446237564087</v>
       </c>
       <c r="H870" t="n">
         <v>3094</v>
@@ -25657,7 +25657,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368127822876</v>
+        <v>14.5368118286133</v>
       </c>
       <c r="H872" t="n">
         <v>5468</v>
@@ -25744,7 +25744,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>14.644624710083</v>
+        <v>14.6446237564087</v>
       </c>
       <c r="H875" t="n">
         <v>7498</v>
@@ -25831,7 +25831,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H878" t="n">
         <v>3239</v>
@@ -25918,7 +25918,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H881" t="n">
         <v>15130</v>
@@ -25947,7 +25947,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135290145874</v>
+        <v>14.8135280609131</v>
       </c>
       <c r="H882" t="n">
         <v>7029</v>
@@ -26005,7 +26005,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H884" t="n">
         <v>2276</v>
@@ -26121,7 +26121,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H888" t="n">
         <v>3111</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H890" t="n">
         <v>4619</v>
@@ -26382,7 +26382,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H897" t="n">
         <v>1992</v>
@@ -26614,7 +26614,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G905" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H905" t="n">
         <v>11888</v>
@@ -26730,7 +26730,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G909" t="n">
-        <v>12.8542604446411</v>
+        <v>12.8542613983154</v>
       </c>
       <c r="H909" t="n">
         <v>5740</v>
@@ -26875,7 +26875,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711521148682</v>
+        <v>12.6711511611938</v>
       </c>
       <c r="H914" t="n">
         <v>2839</v>
@@ -27194,7 +27194,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894626617432</v>
+        <v>12.6894617080688</v>
       </c>
       <c r="H925" t="n">
         <v>776</v>
@@ -27223,7 +27223,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="n">
         <v>3020</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359508514404</v>
+        <v>12.8359498977661</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27397,7 +27397,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G932" t="n">
-        <v>13.0556812286377</v>
+        <v>13.0556802749634</v>
       </c>
       <c r="H932" t="n">
         <v>1140</v>
@@ -27571,7 +27571,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G938" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H938" t="n">
         <v>11774</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27716,7 +27716,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H943" t="n">
         <v>1926</v>
@@ -27919,7 +27919,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402839660645</v>
+        <v>14.7402849197388</v>
       </c>
       <c r="H950" t="n">
         <v>5635</v>
@@ -27977,7 +27977,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H952" t="n">
         <v>5644</v>
@@ -28064,7 +28064,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346046447754</v>
       </c>
       <c r="H955" t="n">
         <v>1552</v>
@@ -28441,7 +28441,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303451538086</v>
+        <v>13.3303442001343</v>
       </c>
       <c r="H968" t="n">
         <v>853</v>
@@ -28499,7 +28499,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599407196045</v>
+        <v>13.6599397659302</v>
       </c>
       <c r="H970" t="n">
         <v>663</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28760,7 +28760,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H979" t="n">
         <v>548</v>
@@ -28992,7 +28992,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H987" t="n">
         <v>7766</v>
@@ -29021,7 +29021,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H988" t="n">
         <v>2745</v>
@@ -29224,7 +29224,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H995" t="n">
         <v>776</v>
@@ -29340,7 +29340,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="n">
         <v>1949</v>
@@ -29427,7 +29427,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="n">
         <v>3350</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29514,7 +29514,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.081090927124</v>
+        <v>14.0810918807983</v>
       </c>
       <c r="H1005" t="n">
         <v>1238</v>
@@ -29543,7 +29543,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1006" t="n">
         <v>626</v>
@@ -29572,7 +29572,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1007" t="n">
         <v>1460</v>
@@ -29601,7 +29601,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1008" t="n">
         <v>8629</v>
@@ -29630,7 +29630,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="n">
         <v>11362</v>
@@ -29775,7 +29775,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1014" t="n">
         <v>801</v>
@@ -29891,7 +29891,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909561157227</v>
       </c>
       <c r="H1018" t="n">
         <v>2476</v>
@@ -29920,7 +29920,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.9529151916504</v>
+        <v>13.9529142379761</v>
       </c>
       <c r="H1019" t="n">
         <v>2740</v>
@@ -30094,7 +30094,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909561157227</v>
       </c>
       <c r="H1025" t="n">
         <v>1900</v>
@@ -30152,7 +30152,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1027" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1027" t="n">
         <v>5708</v>
@@ -30181,7 +30181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909561157227</v>
       </c>
       <c r="H1028" t="n">
         <v>5343</v>
@@ -30384,7 +30384,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1035" t="n">
         <v>7293</v>
@@ -30442,7 +30442,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1037" t="n">
         <v>5201</v>
@@ -30471,7 +30471,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1038" t="n">
         <v>4882</v>
@@ -30500,7 +30500,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1039" t="n">
         <v>1448</v>
@@ -30529,7 +30529,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1040" t="n">
         <v>3156</v>
@@ -30674,7 +30674,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1045" t="n">
         <v>1335</v>
@@ -30703,7 +30703,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1046" t="n">
         <v>1062</v>
@@ -30790,7 +30790,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1049" t="n">
         <v>2797</v>
@@ -30877,7 +30877,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1052" t="n">
         <v>942</v>
@@ -31080,7 +31080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1059" t="n">
         <v>2147</v>
@@ -31109,7 +31109,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1060" t="n">
         <v>3908</v>
@@ -31167,7 +31167,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1062" t="n">
         <v>4440</v>
@@ -31370,7 +31370,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1069" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1069" t="n">
         <v>2207</v>
@@ -31399,7 +31399,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1070" t="n">
         <v>4599</v>
@@ -31428,7 +31428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1071" t="n">
         <v>15327</v>
@@ -31515,7 +31515,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1074" t="n">
         <v>4278</v>
@@ -31573,7 +31573,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1076" t="n">
         <v>5561</v>
@@ -31631,7 +31631,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1078" t="n">
         <v>11008</v>
@@ -31660,7 +31660,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1079" t="n">
         <v>7708</v>
@@ -31776,7 +31776,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H1083" t="n">
         <v>10646</v>
@@ -31892,7 +31892,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="n">
         <v>6067</v>
@@ -31979,7 +31979,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.960015296936</v>
+        <v>14.9600162506104</v>
       </c>
       <c r="H1090" t="n">
         <v>10574</v>
@@ -32066,7 +32066,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4361000061035</v>
+        <v>15.4360990524292</v>
       </c>
       <c r="H1093" t="n">
         <v>8188</v>
@@ -32095,7 +32095,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1094" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825881958008</v>
       </c>
       <c r="H1094" t="n">
         <v>4974</v>
@@ -32124,7 +32124,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473840713501</v>
       </c>
       <c r="H1095" t="n">
         <v>11814</v>
@@ -32182,7 +32182,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825881958008</v>
       </c>
       <c r="H1097" t="n">
         <v>6511</v>
@@ -32240,7 +32240,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="n">
         <v>6086</v>
@@ -32298,7 +32298,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1101" t="n">
-        <v>15.6375188827515</v>
+        <v>15.6375179290771</v>
       </c>
       <c r="H1101" t="n">
         <v>6442</v>
@@ -32414,7 +32414,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="n">
         <v>21663</v>
@@ -32443,7 +32443,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="n">
         <v>5698</v>
@@ -32501,7 +32501,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>16.2600898742676</v>
+        <v>16.2600917816162</v>
       </c>
       <c r="H1108" t="n">
         <v>12113</v>
@@ -32646,7 +32646,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1113" t="n">
         <v>19386</v>
@@ -32762,7 +32762,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1117" t="n">
         <v>9205</v>
@@ -32791,7 +32791,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309246063232</v>
+        <v>17.7309226989746</v>
       </c>
       <c r="H1118" t="n">
         <v>29414</v>
@@ -32820,7 +32820,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1119" t="n">
         <v>13971</v>
@@ -32849,7 +32849,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1120" t="n">
         <v>12199</v>
@@ -32878,7 +32878,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1121" t="n">
         <v>14919</v>
@@ -33052,7 +33052,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1127" t="n">
         <v>2398</v>
@@ -33081,7 +33081,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1128" t="n">
         <v>7274</v>
@@ -33110,7 +33110,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641819000244</v>
+        <v>16.9641799926758</v>
       </c>
       <c r="H1129" t="n">
         <v>6734</v>
@@ -33168,7 +33168,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1131" t="n">
         <v>3201</v>
@@ -33197,7 +33197,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683395385742</v>
+        <v>16.8683376312256</v>
       </c>
       <c r="H1132" t="n">
         <v>2268</v>
@@ -58810,6 +58810,35 @@
         <v>15034</v>
       </c>
       <c r="I2015" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2016" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2016" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>1.56500005722046</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="H2016" t="n">
+        <v>6762</v>
+      </c>
+      <c r="I2016" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108229637146</v>
+        <v>2.88108205795288</v>
       </c>
       <c r="H2" t="n">
         <v>41400</v>
@@ -456,7 +456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H3" t="n">
         <v>13950</v>
@@ -485,7 +485,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676808357239</v>
       </c>
       <c r="H4" t="n">
         <v>7200</v>
@@ -514,7 +514,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248703956604</v>
+        <v>2.90248680114746</v>
       </c>
       <c r="H5" t="n">
         <v>8550</v>
@@ -543,7 +543,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H6" t="n">
         <v>1350</v>
@@ -572,7 +572,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H7" t="n">
         <v>7200</v>
@@ -601,7 +601,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H8" t="n">
         <v>2700</v>
@@ -630,7 +630,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H9" t="n">
         <v>1350</v>
@@ -659,7 +659,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762424468994</v>
+        <v>2.90762400627136</v>
       </c>
       <c r="H10" t="n">
         <v>2250</v>
@@ -688,7 +688,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H11" t="n">
         <v>450</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H12" t="n">
         <v>1800</v>
@@ -746,7 +746,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676808357239</v>
       </c>
       <c r="H13" t="n">
         <v>3600</v>
@@ -775,7 +775,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676760673523</v>
+        <v>2.90676808357239</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441972732544</v>
+        <v>2.83441948890686</v>
       </c>
       <c r="H20" t="n">
         <v>900</v>
@@ -1007,7 +1007,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392495155334</v>
+        <v>2.89392518997192</v>
       </c>
       <c r="H22" t="n">
         <v>450</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1065,7 +1065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H24" t="n">
         <v>450</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863419532776</v>
+        <v>2.89863395690918</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1123,7 +1123,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974412918091</v>
+        <v>2.79974389076233</v>
       </c>
       <c r="H26" t="n">
         <v>1800</v>
@@ -1152,7 +1152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255313873291</v>
       </c>
       <c r="H27" t="n">
         <v>450</v>
@@ -1181,7 +1181,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601142883301</v>
+        <v>2.81601166725159</v>
       </c>
       <c r="H28" t="n">
         <v>450</v>
@@ -1210,7 +1210,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H29" t="n">
         <v>1800</v>
@@ -1268,7 +1268,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H31" t="n">
         <v>4950</v>
@@ -1297,7 +1297,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.8442656993866</v>
+        <v>2.84426593780518</v>
       </c>
       <c r="H32" t="n">
         <v>2700</v>
@@ -1355,7 +1355,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.7603588104248</v>
+        <v>2.76035928726196</v>
       </c>
       <c r="H34" t="n">
         <v>1800</v>
@@ -1384,7 +1384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399176597595</v>
+        <v>2.83399152755737</v>
       </c>
       <c r="H35" t="n">
         <v>7650</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1442,7 +1442,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H37" t="n">
         <v>5400</v>
@@ -1471,7 +1471,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G38" t="n">
-        <v>2.85368418693542</v>
+        <v>2.85368394851685</v>
       </c>
       <c r="H38" t="n">
         <v>6300</v>
@@ -1500,7 +1500,7 @@
         <v>3.40650010108948</v>
       </c>
       <c r="G39" t="n">
-        <v>2.91661429405212</v>
+        <v>2.91661405563354</v>
       </c>
       <c r="H39" t="n">
         <v>19350</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666810035706</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385813713074</v>
+        <v>2.9538586139679</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255313873291</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86823892593384</v>
+        <v>2.868239402771</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666810035706</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666810035706</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666810035706</v>
+        <v>2.99666786193848</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379179954529</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1964,7 +1964,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787263870239</v>
+        <v>3.19787240028381</v>
       </c>
       <c r="H55" t="n">
         <v>63900</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489659309387</v>
+        <v>3.30489611625671</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.2376856803894</v>
+        <v>3.23768520355225</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2109,7 +2109,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309705734253</v>
+        <v>3.25309681892395</v>
       </c>
       <c r="H60" t="n">
         <v>5400</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483025550842</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518602371216</v>
+        <v>3.815185546875</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.966304063797</v>
+        <v>3.96630430221558</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2370,7 +2370,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293298721313</v>
+        <v>4.04293346405029</v>
       </c>
       <c r="H69" t="n">
         <v>51750</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0669059753418</v>
+        <v>4.06690692901611</v>
       </c>
       <c r="H74" t="n">
         <v>18450</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279172897339</v>
+        <v>3.91279196739197</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2718,7 +2718,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.0155348777771</v>
+        <v>4.01553440093994</v>
       </c>
       <c r="H81" t="n">
         <v>1800</v>
@@ -2747,7 +2747,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.95645809173584</v>
+        <v>3.95645785331726</v>
       </c>
       <c r="H82" t="n">
         <v>2250</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2834,7 +2834,7 @@
         <v>4.52050018310547</v>
       </c>
       <c r="G85" t="n">
-        <v>3.87041091918945</v>
+        <v>3.87041068077087</v>
       </c>
       <c r="H85" t="n">
         <v>3150</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330761909485</v>
+        <v>3.96330714225769</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566802978516</v>
+        <v>3.89566826820374</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -3037,7 +3037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H92" t="n">
         <v>6750</v>
@@ -3095,7 +3095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H96" t="n">
         <v>12600</v>
@@ -3182,7 +3182,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G97" t="n">
-        <v>4.05834436416626</v>
+        <v>4.0583438873291</v>
       </c>
       <c r="H97" t="n">
         <v>900</v>
@@ -3240,7 +3240,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H99" t="n">
         <v>8550</v>
@@ -3269,7 +3269,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.17821168899536</v>
+        <v>4.1782112121582</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12683963775635</v>
+        <v>4.12684011459351</v>
       </c>
       <c r="H102" t="n">
         <v>4050</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3675,7 +3675,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3704,7 +3704,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>4.21245908737183</v>
+        <v>4.21245861053467</v>
       </c>
       <c r="H115" t="n">
         <v>22950</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095483779907</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4052,7 +4052,7 @@
         <v>5.25</v>
       </c>
       <c r="G127" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H127" t="n">
         <v>10800</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4168,7 +4168,7 @@
         <v>5.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49500226974487</v>
+        <v>4.49500179290771</v>
       </c>
       <c r="H131" t="n">
         <v>4950</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66624021530151</v>
+        <v>4.66623973846436</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4429,7 +4429,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557445526123</v>
       </c>
       <c r="H140" t="n">
         <v>33750</v>
@@ -4458,7 +4458,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557445526123</v>
       </c>
       <c r="H141" t="n">
         <v>21150</v>
@@ -4487,7 +4487,7 @@
         <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H142" t="n">
         <v>9900</v>
@@ -4516,7 +4516,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H143" t="n">
         <v>2250</v>
@@ -4661,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="G148" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H148" t="n">
         <v>1350</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H149" t="n">
         <v>6750</v>
@@ -4719,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="G150" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H154" t="n">
         <v>3150</v>
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H158" t="n">
         <v>1800</v>
@@ -5009,7 +5009,7 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H160" t="n">
         <v>7650</v>
@@ -5038,7 +5038,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H161" t="n">
         <v>102150</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5241,7 +5241,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="n">
         <v>10800</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424150466919</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828893661499</v>
       </c>
       <c r="H183" t="n">
         <v>23400</v>
@@ -5705,7 +5705,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>6.80671787261963</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H184" t="n">
         <v>3600</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514537811279</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.5926685333252</v>
+        <v>6.59266948699951</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514537811279</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233589172363</v>
+        <v>6.89233684539795</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6198,7 +6198,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>6.80671787261963</v>
+        <v>6.80671691894531</v>
       </c>
       <c r="H201" t="n">
         <v>11250</v>
@@ -6343,7 +6343,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.67828845977783</v>
+        <v>6.67828893661499</v>
       </c>
       <c r="H206" t="n">
         <v>4950</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952640533447</v>
+        <v>6.84952735900879</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.5926685333252</v>
+        <v>6.59266948699951</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862205505371</v>
+        <v>6.37862157821655</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6807,7 +6807,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H222" t="n">
         <v>7042</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6865,7 +6865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H224" t="n">
         <v>6100</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -6952,7 +6952,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="n">
         <v>19965</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424150466919</v>
+        <v>6.46424055099487</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7068,7 +7068,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H231" t="n">
         <v>55223</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300260543823</v>
+        <v>6.29300212860107</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7300,7 +7300,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G239" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H239" t="n">
         <v>7153</v>
@@ -7329,7 +7329,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H240" t="n">
         <v>10587</v>
@@ -7416,7 +7416,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G243" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H243" t="n">
         <v>3750</v>
@@ -7590,7 +7590,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H249" t="n">
         <v>5546</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7909,7 +7909,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H260" t="n">
         <v>10941</v>
@@ -7938,7 +7938,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G261" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H261" t="n">
         <v>2202</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8402,7 +8402,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>5.82209730148315</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H277" t="n">
         <v>1002</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333572387695</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8518,7 +8518,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>6.07895517349243</v>
+        <v>6.07895469665527</v>
       </c>
       <c r="H281" t="n">
         <v>14397</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.82209730148315</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H285" t="n">
         <v>5658</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771722793579</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8924,7 +8924,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G295" t="n">
-        <v>5.82209730148315</v>
+        <v>5.82209777832031</v>
       </c>
       <c r="H295" t="n">
         <v>3196</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928781509399</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6080493927002</v>
+        <v>5.60805034637451</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9417,7 +9417,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="n">
         <v>1448</v>
@@ -9446,7 +9446,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="n">
         <v>8895</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366884231567</v>
+        <v>5.69366931915283</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647785186768</v>
+        <v>5.73647880554199</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9591,7 +9591,7 @@
         <v>6</v>
       </c>
       <c r="G318" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H318" t="n">
         <v>25735</v>
@@ -9620,7 +9620,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557302474976</v>
+        <v>5.26557445526123</v>
       </c>
       <c r="H319" t="n">
         <v>5941</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995405197144</v>
+        <v>5.17995500564575</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750635147095</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H328" t="n">
         <v>14468</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051556587219</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -9968,7 +9968,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242022514343</v>
+        <v>2.96242046356201</v>
       </c>
       <c r="H331" t="n">
         <v>25097</v>
@@ -9997,7 +9997,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>2.91104865074158</v>
+        <v>2.91104888916016</v>
       </c>
       <c r="H332" t="n">
         <v>17685</v>
@@ -10026,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>2.56857252120972</v>
+        <v>2.56857228279114</v>
       </c>
       <c r="H333" t="n">
         <v>13836</v>
@@ -10113,7 +10113,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>2.48295378684998</v>
+        <v>2.48295331001282</v>
       </c>
       <c r="H336" t="n">
         <v>8502</v>
@@ -10142,7 +10142,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H337" t="n">
         <v>1910</v>
@@ -10171,7 +10171,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>2.73981046676636</v>
+        <v>2.73981070518494</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560097694397</v>
+        <v>3.95560145378113</v>
       </c>
       <c r="H340" t="n">
         <v>40606</v>
@@ -10287,7 +10287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971593856812</v>
+        <v>4.10971641540527</v>
       </c>
       <c r="H342" t="n">
         <v>27229</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723909378052</v>
+        <v>3.76723980903625</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299169540405</v>
+        <v>3.73299193382263</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10490,7 +10490,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H349" t="n">
         <v>8462</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476367950439</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593457221985</v>
+        <v>3.65593504905701</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10577,7 +10577,7 @@
         <v>4.25</v>
       </c>
       <c r="G352" t="n">
-        <v>3.6388111114502</v>
+        <v>3.63881087303162</v>
       </c>
       <c r="H352" t="n">
         <v>9864</v>
@@ -10606,7 +10606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.5446298122406</v>
+        <v>3.54462957382202</v>
       </c>
       <c r="H353" t="n">
         <v>1950</v>
@@ -10664,7 +10664,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750635147095</v>
+        <v>3.52750611305237</v>
       </c>
       <c r="H355" t="n">
         <v>3470</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10722,7 +10722,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.41620111465454</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H357" t="n">
         <v>4102</v>
@@ -10751,7 +10751,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.41620111465454</v>
+        <v>3.4162015914917</v>
       </c>
       <c r="H358" t="n">
         <v>4270</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476320266724</v>
+        <v>3.42476367950439</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.4675726890564</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10838,7 +10838,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>3.66449666023254</v>
+        <v>3.66449689865112</v>
       </c>
       <c r="H361" t="n">
         <v>16600</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723909378052</v>
+        <v>3.76723980903625</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.8785445690155</v>
+        <v>3.87854433059692</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285878181458</v>
+        <v>3.852858543396</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11070,7 +11070,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356340408325</v>
+        <v>4.50356388092041</v>
       </c>
       <c r="H369" t="n">
         <v>65581</v>
@@ -11186,7 +11186,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G373" t="n">
-        <v>4.8289155960083</v>
+        <v>4.82891654968262</v>
       </c>
       <c r="H373" t="n">
         <v>122121</v>
@@ -11273,7 +11273,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082025527954</v>
+        <v>4.40082120895386</v>
       </c>
       <c r="H376" t="n">
         <v>38510</v>
@@ -11302,7 +11302,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H377" t="n">
         <v>13190</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11447,7 +11447,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838251113892</v>
+        <v>5.30838298797607</v>
       </c>
       <c r="H382" t="n">
         <v>137190</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11534,7 +11534,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G385" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H385" t="n">
         <v>40025</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838251113892</v>
+        <v>5.30838298797607</v>
       </c>
       <c r="H387" t="n">
         <v>39972</v>
@@ -11679,7 +11679,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289764404297</v>
       </c>
       <c r="H390" t="n">
         <v>18684</v>
@@ -11766,7 +11766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.88028717041016</v>
+        <v>4.880286693573</v>
       </c>
       <c r="H393" t="n">
         <v>8696</v>
@@ -11853,7 +11853,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20563983917236</v>
+        <v>5.20564031600952</v>
       </c>
       <c r="H396" t="n">
         <v>4787</v>
@@ -11969,7 +11969,7 @@
         <v>6</v>
       </c>
       <c r="G400" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H400" t="n">
         <v>1473</v>
@@ -11998,7 +11998,7 @@
         <v>6</v>
       </c>
       <c r="G401" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H401" t="n">
         <v>1401</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303031921387</v>
+        <v>4.98303127288818</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12143,7 +12143,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H406" t="n">
         <v>2647</v>
@@ -12230,7 +12230,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H409" t="n">
         <v>4265</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12375,7 +12375,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H414" t="n">
         <v>1971</v>
@@ -12404,7 +12404,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H415" t="n">
         <v>4635</v>
@@ -12433,7 +12433,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H416" t="n">
         <v>12743</v>
@@ -12462,7 +12462,7 @@
         <v>6</v>
       </c>
       <c r="G417" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H417" t="n">
         <v>3912</v>
@@ -12520,7 +12520,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>5.32550716400146</v>
+        <v>5.32550668716431</v>
       </c>
       <c r="H419" t="n">
         <v>44555</v>
@@ -12549,7 +12549,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H420" t="n">
         <v>11461</v>
@@ -12607,7 +12607,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413558959961</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H422" t="n">
         <v>7415</v>
@@ -12636,7 +12636,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H423" t="n">
         <v>4800</v>
@@ -12665,7 +12665,7 @@
         <v>6</v>
       </c>
       <c r="G424" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H424" t="n">
         <v>970</v>
@@ -12723,7 +12723,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289764404297</v>
       </c>
       <c r="H426" t="n">
         <v>4511</v>
@@ -12752,7 +12752,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>5.2227635383606</v>
+        <v>5.22276401519775</v>
       </c>
       <c r="H427" t="n">
         <v>5140</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440189361572</v>
+        <v>5.03440284729004</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12839,7 +12839,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H430" t="n">
         <v>1010</v>
@@ -13071,7 +13071,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413558959961</v>
+        <v>5.27413511276245</v>
       </c>
       <c r="H438" t="n">
         <v>8401</v>
@@ -13129,7 +13129,7 @@
         <v>6</v>
       </c>
       <c r="G440" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H440" t="n">
         <v>592</v>
@@ -13158,7 +13158,7 @@
         <v>6</v>
       </c>
       <c r="G441" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H441" t="n">
         <v>915</v>
@@ -13187,7 +13187,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.1200213432312</v>
+        <v>5.12002182006836</v>
       </c>
       <c r="H442" t="n">
         <v>1564</v>
@@ -13245,7 +13245,7 @@
         <v>6</v>
       </c>
       <c r="G444" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H444" t="n">
         <v>1100</v>
@@ -13274,7 +13274,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289764404297</v>
       </c>
       <c r="H445" t="n">
         <v>4470</v>
@@ -13303,7 +13303,7 @@
         <v>6</v>
       </c>
       <c r="G446" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H446" t="n">
         <v>504</v>
@@ -13332,7 +13332,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>5.10289716720581</v>
+        <v>5.10289764404297</v>
       </c>
       <c r="H447" t="n">
         <v>2883</v>
@@ -13361,7 +13361,7 @@
         <v>6</v>
       </c>
       <c r="G448" t="n">
-        <v>5.13714504241943</v>
+        <v>5.13714456558228</v>
       </c>
       <c r="H448" t="n">
         <v>7543</v>
@@ -13419,7 +13419,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.20243644714355</v>
+        <v>5.2024359703064</v>
       </c>
       <c r="H450" t="n">
         <v>2913</v>
@@ -13448,7 +13448,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H451" t="n">
         <v>650</v>
@@ -13477,7 +13477,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H452" t="n">
         <v>930</v>
@@ -13506,7 +13506,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H453" t="n">
         <v>7910</v>
@@ -13535,7 +13535,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023803710938</v>
       </c>
       <c r="H454" t="n">
         <v>900</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0980396270752</v>
+        <v>5.09803867340088</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104211807251</v>
+        <v>5.01104259490967</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13738,7 +13738,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763734817505</v>
+        <v>5.16763782501221</v>
       </c>
       <c r="H461" t="n">
         <v>2800</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H466" t="n">
         <v>2015</v>
@@ -13941,7 +13941,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>5.04584169387817</v>
+        <v>5.04584121704102</v>
       </c>
       <c r="H468" t="n">
         <v>7558</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265075683594</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14086,7 +14086,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G473" t="n">
-        <v>4.83704710006714</v>
+        <v>4.8370475769043</v>
       </c>
       <c r="H473" t="n">
         <v>2696</v>
@@ -14115,7 +14115,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404413223267</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H474" t="n">
         <v>6712</v>
@@ -14144,7 +14144,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404413223267</v>
+        <v>4.92404460906982</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75004959106445</v>
+        <v>4.75005006790161</v>
       </c>
       <c r="H477" t="n">
         <v>1841</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265075683594</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14289,7 +14289,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H480" t="n">
         <v>10416</v>
@@ -14318,7 +14318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H481" t="n">
         <v>6191</v>
@@ -14347,7 +14347,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H482" t="n">
         <v>2456</v>
@@ -14405,7 +14405,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H484" t="n">
         <v>2940</v>
@@ -14434,7 +14434,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H485" t="n">
         <v>672</v>
@@ -14463,7 +14463,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H486" t="n">
         <v>200</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H487" t="n">
         <v>537</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14550,7 +14550,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425987243652</v>
+        <v>4.45425939559937</v>
       </c>
       <c r="H489" t="n">
         <v>3075</v>
@@ -14724,7 +14724,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716909408569</v>
+        <v>4.16716861724854</v>
       </c>
       <c r="H495" t="n">
         <v>20644</v>
@@ -14782,7 +14782,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G497" t="n">
-        <v>4.25416612625122</v>
+        <v>4.2541651725769</v>
       </c>
       <c r="H497" t="n">
         <v>1064</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.1149697303772</v>
+        <v>4.11497020721436</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456792831421</v>
+        <v>4.18456888198853</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -14985,7 +14985,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.30636405944824</v>
+        <v>4.3063645362854</v>
       </c>
       <c r="H504" t="n">
         <v>10900</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15043,7 +15043,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H506" t="n">
         <v>5490</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.43685960769653</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H507" t="n">
         <v>12706</v>
@@ -15101,7 +15101,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H508" t="n">
         <v>14843</v>
@@ -15130,7 +15130,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H509" t="n">
         <v>6520</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15188,7 +15188,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H511" t="n">
         <v>9671</v>
@@ -15246,7 +15246,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H513" t="n">
         <v>535</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H517" t="n">
         <v>3170</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H518" t="n">
         <v>1170</v>
@@ -15507,7 +15507,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H522" t="n">
         <v>5441</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H523" t="n">
         <v>6233</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385759353638</v>
+        <v>4.52385711669922</v>
       </c>
       <c r="H524" t="n">
         <v>1255</v>
@@ -15594,7 +15594,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H525" t="n">
         <v>2013</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165870666504</v>
+        <v>4.4716591835022</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15739,7 +15739,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>4.43685960769653</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H530" t="n">
         <v>10190</v>
@@ -15826,7 +15826,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H533" t="n">
         <v>5756</v>
@@ -15855,7 +15855,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H534" t="n">
         <v>13104</v>
@@ -15884,7 +15884,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H535" t="n">
         <v>380</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15942,7 +15942,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.50645780563354</v>
+        <v>4.5064582824707</v>
       </c>
       <c r="H537" t="n">
         <v>8283</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16058,7 +16058,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H541" t="n">
         <v>1369</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825393676758</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16174,7 +16174,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H545" t="n">
         <v>1820</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825393676758</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16406,7 +16406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H553" t="n">
         <v>12566</v>
@@ -16435,7 +16435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H554" t="n">
         <v>4021</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206098556519</v>
+        <v>4.40206050872803</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16551,7 +16551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>4.43685960769653</v>
+        <v>4.43686008453369</v>
       </c>
       <c r="H558" t="n">
         <v>2505</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305303573608</v>
+        <v>4.66305351257324</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16841,7 +16841,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H568" t="n">
         <v>22400</v>
@@ -16928,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H571" t="n">
         <v>855</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17102,7 +17102,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H577" t="n">
         <v>6090</v>
@@ -17131,7 +17131,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844142913818</v>
+        <v>5.02844190597534</v>
       </c>
       <c r="H578" t="n">
         <v>11230</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104211807251</v>
+        <v>5.01104259490967</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17305,7 +17305,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H584" t="n">
         <v>21315</v>
@@ -17363,7 +17363,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H586" t="n">
         <v>26713</v>
@@ -17450,7 +17450,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943300247192</v>
+        <v>5.28943347930908</v>
       </c>
       <c r="H589" t="n">
         <v>6920</v>
@@ -17479,7 +17479,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H590" t="n">
         <v>6044</v>
@@ -17508,7 +17508,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203369140625</v>
+        <v>5.27203321456909</v>
       </c>
       <c r="H591" t="n">
         <v>2345</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324005126953</v>
+        <v>5.06324100494385</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17653,7 +17653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023756027222</v>
+        <v>5.15023803710938</v>
       </c>
       <c r="H596" t="n">
         <v>9629</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983575820923</v>
+        <v>5.21983480453491</v>
       </c>
       <c r="H597" t="n">
         <v>33122</v>
@@ -17740,7 +17740,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203369140625</v>
+        <v>5.27203321456909</v>
       </c>
       <c r="H599" t="n">
         <v>16071</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.39382934570312</v>
+        <v>5.39382982254028</v>
       </c>
       <c r="H601" t="n">
         <v>124984</v>
@@ -17827,7 +17827,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>5.68962097167969</v>
+        <v>5.68962049484253</v>
       </c>
       <c r="H602" t="n">
         <v>98090</v>
@@ -17856,7 +17856,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>5.6722207069397</v>
+        <v>5.67222118377686</v>
       </c>
       <c r="H603" t="n">
         <v>155697</v>
@@ -17885,7 +17885,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68962097167969</v>
+        <v>5.68962049484253</v>
       </c>
       <c r="H604" t="n">
         <v>14365</v>
@@ -17972,7 +17972,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G607" t="n">
-        <v>5.41122961044312</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H607" t="n">
         <v>13558</v>
@@ -18030,7 +18030,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G609" t="n">
-        <v>5.41122961044312</v>
+        <v>5.41122913360596</v>
       </c>
       <c r="H609" t="n">
         <v>6107</v>
@@ -18117,7 +18117,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.77661752700806</v>
+        <v>5.7766170501709</v>
       </c>
       <c r="H612" t="n">
         <v>36365</v>
@@ -18146,7 +18146,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>5.79401683807373</v>
+        <v>5.79401731491089</v>
       </c>
       <c r="H613" t="n">
         <v>17964</v>
@@ -18175,7 +18175,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881546020508</v>
+        <v>5.82881641387939</v>
       </c>
       <c r="H614" t="n">
         <v>16210</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.9680118560791</v>
+        <v>5.96801233291626</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281143188477</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281143188477</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437356948853</v>
+        <v>6.23437309265137</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18378,7 +18378,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.5015606880188</v>
+        <v>6.50156116485596</v>
       </c>
       <c r="H621" t="n">
         <v>31678</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031089782715</v>
+        <v>7.00031137466431</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18436,7 +18436,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.8399977684021</v>
+        <v>6.83999729156494</v>
       </c>
       <c r="H623" t="n">
         <v>76240</v>
@@ -18465,7 +18465,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718536376953</v>
+        <v>7.10718584060669</v>
       </c>
       <c r="H624" t="n">
         <v>102683</v>
@@ -18494,7 +18494,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G625" t="n">
-        <v>6.89343500137329</v>
+        <v>6.89343452453613</v>
       </c>
       <c r="H625" t="n">
         <v>84822</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468591690063</v>
+        <v>6.96468544006348</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18610,7 +18610,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.48124742507935</v>
+        <v>7.4812479019165</v>
       </c>
       <c r="H629" t="n">
         <v>152384</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874767303467</v>
+        <v>7.90874671936035</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18697,7 +18697,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G632" t="n">
-        <v>8.14030933380127</v>
+        <v>8.14031028747559</v>
       </c>
       <c r="H632" t="n">
         <v>59783</v>
@@ -18726,7 +18726,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.4787483215332</v>
+        <v>8.47874736785889</v>
       </c>
       <c r="H633" t="n">
         <v>83403</v>
@@ -18755,7 +18755,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343425750732</v>
+        <v>9.17343616485596</v>
       </c>
       <c r="H634" t="n">
         <v>112604</v>
@@ -18813,7 +18813,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.2624979019165</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H636" t="n">
         <v>208819</v>
@@ -18842,7 +18842,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.2624979019165</v>
+        <v>9.26249599456787</v>
       </c>
       <c r="H637" t="n">
         <v>116116</v>
@@ -18871,7 +18871,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890338897705</v>
+        <v>9.12890434265137</v>
       </c>
       <c r="H638" t="n">
         <v>117220</v>
@@ -18900,7 +18900,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702877044678</v>
+        <v>9.30702972412109</v>
       </c>
       <c r="H639" t="n">
         <v>47607</v>
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624809265137</v>
+        <v>8.90624713897705</v>
       </c>
       <c r="H645" t="n">
         <v>112321</v>
@@ -19103,7 +19103,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702877044678</v>
+        <v>9.30702972412109</v>
       </c>
       <c r="H646" t="n">
         <v>97578</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19161,7 +19161,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>9.93046474456787</v>
+        <v>9.93046569824219</v>
       </c>
       <c r="H648" t="n">
         <v>98237</v>
@@ -19190,7 +19190,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G649" t="n">
-        <v>10.5093717575073</v>
+        <v>10.5093727111816</v>
       </c>
       <c r="H649" t="n">
         <v>113895</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19277,7 +19277,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890575408936</v>
       </c>
       <c r="H652" t="n">
         <v>199932</v>
@@ -19306,7 +19306,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890575408936</v>
       </c>
       <c r="H653" t="n">
         <v>91653</v>
@@ -19335,7 +19335,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.845308303833</v>
+        <v>11.8453092575073</v>
       </c>
       <c r="H654" t="n">
         <v>47177</v>
@@ -19364,7 +19364,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671829223633</v>
+        <v>11.6671848297119</v>
       </c>
       <c r="H655" t="n">
         <v>87639</v>
@@ -19393,7 +19393,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890594482422</v>
+        <v>11.4890575408936</v>
       </c>
       <c r="H656" t="n">
         <v>32521</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19567,7 +19567,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G662" t="n">
-        <v>11.7562465667725</v>
+        <v>11.7562456130981</v>
       </c>
       <c r="H662" t="n">
         <v>64255</v>
@@ -19596,7 +19596,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671829223633</v>
+        <v>11.6671848297119</v>
       </c>
       <c r="H663" t="n">
         <v>11952</v>
@@ -19654,7 +19654,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.8594512939453</v>
+        <v>11.859450340271</v>
       </c>
       <c r="H665" t="n">
         <v>38062</v>
@@ -19712,7 +19712,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G667" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H667" t="n">
         <v>20242</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19828,7 +19828,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G671" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H671" t="n">
         <v>3415</v>
@@ -19886,7 +19886,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>11.0957736968994</v>
+        <v>11.095775604248</v>
       </c>
       <c r="H673" t="n">
         <v>20518</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363967895508</v>
+        <v>10.7363958358765</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20031,7 +20031,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H678" t="n">
         <v>18194</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.724684715271</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20205,7 +20205,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H684" t="n">
         <v>11051</v>
@@ -20234,7 +20234,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>11.769606590271</v>
+        <v>11.7696075439453</v>
       </c>
       <c r="H685" t="n">
         <v>9237</v>
@@ -20292,7 +20292,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>11.6348390579224</v>
+        <v>11.6348400115967</v>
       </c>
       <c r="H687" t="n">
         <v>8053</v>
@@ -20321,7 +20321,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>11.5449953079224</v>
+        <v>11.5449962615967</v>
       </c>
       <c r="H688" t="n">
         <v>8002</v>
@@ -20379,7 +20379,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535957336426</v>
+        <v>12.3535938262939</v>
       </c>
       <c r="H690" t="n">
         <v>194061</v>
@@ -20408,7 +20408,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H691" t="n">
         <v>55853</v>
@@ -20495,7 +20495,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G694" t="n">
-        <v>14.3301696777344</v>
+        <v>14.3301706314087</v>
       </c>
       <c r="H694" t="n">
         <v>144504</v>
@@ -20524,7 +20524,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H695" t="n">
         <v>297213</v>
@@ -20582,7 +20582,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H697" t="n">
         <v>248766</v>
@@ -20640,7 +20640,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>16.8907337188721</v>
+        <v>16.8907318115234</v>
       </c>
       <c r="H699" t="n">
         <v>100713</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180850982666</v>
+        <v>18.4180889129639</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20727,7 +20727,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>17.834098815918</v>
+        <v>17.8340969085693</v>
       </c>
       <c r="H702" t="n">
         <v>62036</v>
@@ -20756,7 +20756,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.9239444732666</v>
+        <v>17.923942565918</v>
       </c>
       <c r="H703" t="n">
         <v>17675</v>
@@ -20785,7 +20785,7 @@
         <v>19.25</v>
       </c>
       <c r="G704" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H704" t="n">
         <v>50153</v>
@@ -20843,7 +20843,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H706" t="n">
         <v>37684</v>
@@ -20872,7 +20872,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>17.3399562835693</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H707" t="n">
         <v>16206</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -20930,7 +20930,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>17.789176940918</v>
+        <v>17.7891750335693</v>
       </c>
       <c r="H709" t="n">
         <v>27928</v>
@@ -20959,7 +20959,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>17.609489440918</v>
+        <v>17.6094875335693</v>
       </c>
       <c r="H710" t="n">
         <v>17019</v>
@@ -21017,7 +21017,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H712" t="n">
         <v>12956</v>
@@ -21075,7 +21075,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H714" t="n">
         <v>56021</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21133,7 +21133,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.8907337188721</v>
+        <v>16.8907318115234</v>
       </c>
       <c r="H716" t="n">
         <v>64516</v>
@@ -21162,7 +21162,7 @@
         <v>19.25</v>
       </c>
       <c r="G717" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H717" t="n">
         <v>48881</v>
@@ -21249,7 +21249,7 @@
         <v>19.25</v>
       </c>
       <c r="G720" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H720" t="n">
         <v>23381</v>
@@ -21307,7 +21307,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4297981262207</v>
+        <v>17.4298000335693</v>
       </c>
       <c r="H722" t="n">
         <v>31177</v>
@@ -21336,7 +21336,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>17.3848781585693</v>
+        <v>17.3848762512207</v>
       </c>
       <c r="H723" t="n">
         <v>11585</v>
@@ -21394,7 +21394,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>17.1602687835693</v>
+        <v>17.1602668762207</v>
       </c>
       <c r="H725" t="n">
         <v>61724</v>
@@ -21423,7 +21423,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>17.1602687835693</v>
+        <v>17.1602668762207</v>
       </c>
       <c r="H726" t="n">
         <v>19578</v>
@@ -21452,7 +21452,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>17.1602687835693</v>
+        <v>17.1602668762207</v>
       </c>
       <c r="H727" t="n">
         <v>4990</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H728" t="n">
         <v>20822</v>
@@ -21539,7 +21539,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>17.3399562835693</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H730" t="n">
         <v>22860</v>
@@ -21568,7 +21568,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>17.3848781585693</v>
+        <v>17.3848762512207</v>
       </c>
       <c r="H731" t="n">
         <v>22850</v>
@@ -21597,7 +21597,7 @@
         <v>19.25</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H732" t="n">
         <v>11380</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704212188721</v>
+        <v>17.0704231262207</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21684,7 +21684,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153450012207</v>
+        <v>17.1153430938721</v>
       </c>
       <c r="H735" t="n">
         <v>6538</v>
@@ -21713,7 +21713,7 @@
         <v>19.25</v>
       </c>
       <c r="G736" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H736" t="n">
         <v>10110</v>
@@ -21742,7 +21742,7 @@
         <v>19.25</v>
       </c>
       <c r="G737" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H737" t="n">
         <v>15411</v>
@@ -21771,7 +21771,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>17.3399562835693</v>
+        <v>17.3399543762207</v>
       </c>
       <c r="H738" t="n">
         <v>18846</v>
@@ -21800,7 +21800,7 @@
         <v>19.25</v>
       </c>
       <c r="G739" t="n">
-        <v>17.2950325012207</v>
+        <v>17.2950305938721</v>
       </c>
       <c r="H739" t="n">
         <v>9553</v>
@@ -21829,7 +21829,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>17.1602687835693</v>
+        <v>17.1602668762207</v>
       </c>
       <c r="H740" t="n">
         <v>13774</v>
@@ -21858,7 +21858,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>16.5313529968262</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H741" t="n">
         <v>81245</v>
@@ -21887,7 +21887,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>16.5313529968262</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H742" t="n">
         <v>26368</v>
@@ -21945,7 +21945,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>16.5313529968262</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H744" t="n">
         <v>13809</v>
@@ -21974,7 +21974,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H745" t="n">
         <v>15308</v>
@@ -22003,7 +22003,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H746" t="n">
         <v>42523</v>
@@ -22032,7 +22032,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H747" t="n">
         <v>11492</v>
@@ -22119,7 +22119,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H750" t="n">
         <v>10298</v>
@@ -22148,7 +22148,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4864330291748</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H751" t="n">
         <v>22548</v>
@@ -22177,7 +22177,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>16.7110424041748</v>
+        <v>16.7110443115234</v>
       </c>
       <c r="H752" t="n">
         <v>38381</v>
@@ -22264,7 +22264,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008880615234</v>
+        <v>16.8008899688721</v>
       </c>
       <c r="H755" t="n">
         <v>10473</v>
@@ -22322,7 +22322,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>16.3516654968262</v>
+        <v>16.3516674041748</v>
       </c>
       <c r="H757" t="n">
         <v>5194</v>
@@ -22351,7 +22351,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H758" t="n">
         <v>8367</v>
@@ -22380,7 +22380,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>16.6661205291748</v>
+        <v>16.6661224365234</v>
       </c>
       <c r="H759" t="n">
         <v>32049</v>
@@ -22438,7 +22438,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.5313529968262</v>
+        <v>16.5313568115234</v>
       </c>
       <c r="H761" t="n">
         <v>15074</v>
@@ -22554,7 +22554,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778345108032</v>
+        <v>15.6778354644775</v>
       </c>
       <c r="H765" t="n">
         <v>16640</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22612,7 +22612,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G767" t="n">
-        <v>15.3184576034546</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H767" t="n">
         <v>6092</v>
@@ -22641,7 +22641,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>15.0040016174316</v>
+        <v>15.0040035247803</v>
       </c>
       <c r="H768" t="n">
         <v>16692</v>
@@ -22757,7 +22757,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>16.4864330291748</v>
+        <v>16.4864349365234</v>
       </c>
       <c r="H772" t="n">
         <v>30917</v>
@@ -22873,7 +22873,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.2618217468262</v>
+        <v>16.2618236541748</v>
       </c>
       <c r="H776" t="n">
         <v>3032</v>
@@ -22902,7 +22902,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>16.0821323394775</v>
+        <v>16.0821342468262</v>
       </c>
       <c r="H777" t="n">
         <v>6129</v>
@@ -22931,7 +22931,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H778" t="n">
         <v>8343</v>
@@ -22960,7 +22960,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719779968262</v>
       </c>
       <c r="H779" t="n">
         <v>4290</v>
@@ -22989,7 +22989,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270542144775</v>
+        <v>16.1270599365234</v>
       </c>
       <c r="H780" t="n">
         <v>2753</v>
@@ -23018,7 +23018,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H781" t="n">
         <v>3445</v>
@@ -23047,7 +23047,7 @@
         <v>17.75</v>
       </c>
       <c r="G782" t="n">
-        <v>15.9473657608032</v>
+        <v>15.9473676681519</v>
       </c>
       <c r="H782" t="n">
         <v>3539</v>
@@ -23076,7 +23076,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H783" t="n">
         <v>3772</v>
@@ -23105,7 +23105,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H784" t="n">
         <v>9640</v>
@@ -23134,7 +23134,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H785" t="n">
         <v>2827</v>
@@ -23163,7 +23163,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H786" t="n">
         <v>2004</v>
@@ -23192,7 +23192,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H787" t="n">
         <v>1452</v>
@@ -23221,7 +23221,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H788" t="n">
         <v>14768</v>
@@ -23250,7 +23250,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>15.4083003997803</v>
+        <v>15.4083013534546</v>
       </c>
       <c r="H789" t="n">
         <v>6755</v>
@@ -23279,7 +23279,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126010894775</v>
+        <v>15.8126020431519</v>
       </c>
       <c r="H790" t="n">
         <v>9326</v>
@@ -23337,7 +23337,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>15.9922885894775</v>
+        <v>15.9922904968262</v>
       </c>
       <c r="H792" t="n">
         <v>6586</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024457931519</v>
+        <v>15.9024438858032</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23511,7 +23511,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981460571289</v>
+        <v>15.4981451034546</v>
       </c>
       <c r="H798" t="n">
         <v>13711</v>
@@ -23540,7 +23540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778345108032</v>
+        <v>15.6778354644775</v>
       </c>
       <c r="H799" t="n">
         <v>4638</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227554321289</v>
+        <v>15.7227573394775</v>
       </c>
       <c r="H800" t="n">
         <v>4924</v>
@@ -23598,7 +23598,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>15.3184576034546</v>
+        <v>15.3184566497803</v>
       </c>
       <c r="H801" t="n">
         <v>17725</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879898071289</v>
+        <v>15.5879917144775</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23685,7 +23685,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H804" t="n">
         <v>6910</v>
@@ -23772,7 +23772,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.914158821106</v>
+        <v>14.9141578674316</v>
       </c>
       <c r="H807" t="n">
         <v>18172</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387691497803</v>
+        <v>15.1387701034546</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -23859,7 +23859,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G810" t="n">
-        <v>15.1836919784546</v>
+        <v>15.1836910247803</v>
       </c>
       <c r="H810" t="n">
         <v>3859</v>
@@ -23888,7 +23888,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>14.9590787887573</v>
+        <v>14.9590797424316</v>
       </c>
       <c r="H811" t="n">
         <v>1809</v>
@@ -24004,7 +24004,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H815" t="n">
         <v>21544</v>
@@ -24062,7 +24062,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.5547819137573</v>
+        <v>14.554780960083</v>
       </c>
       <c r="H817" t="n">
         <v>53993</v>
@@ -24149,7 +24149,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H820" t="n">
         <v>14476</v>
@@ -24178,7 +24178,7 @@
         <v>16.25</v>
       </c>
       <c r="G821" t="n">
-        <v>14.5997018814087</v>
+        <v>14.599702835083</v>
       </c>
       <c r="H821" t="n">
         <v>12526</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504812240601</v>
+        <v>14.1504802703857</v>
       </c>
       <c r="H822" t="n">
         <v>17003</v>
@@ -24236,7 +24236,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200134277344</v>
+        <v>14.4200124740601</v>
       </c>
       <c r="H823" t="n">
         <v>6212</v>
@@ -24265,7 +24265,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>14.1055583953857</v>
+        <v>14.1055593490601</v>
       </c>
       <c r="H824" t="n">
         <v>35205</v>
@@ -24323,7 +24323,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114149093628</v>
+        <v>13.6114139556885</v>
       </c>
       <c r="H826" t="n">
         <v>4142</v>
@@ -24439,7 +24439,7 @@
         <v>14</v>
       </c>
       <c r="G830" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H830" t="n">
         <v>25666</v>
@@ -24468,7 +24468,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8477392196655</v>
+        <v>12.8477382659912</v>
       </c>
       <c r="H831" t="n">
         <v>15063</v>
@@ -24497,7 +24497,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129716873169</v>
+        <v>12.7129726409912</v>
       </c>
       <c r="H832" t="n">
         <v>7112</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680507659912</v>
+        <v>12.6680498123169</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24555,7 +24555,7 @@
         <v>14</v>
       </c>
       <c r="G834" t="n">
-        <v>12.5782060623169</v>
+        <v>12.5782051086426</v>
       </c>
       <c r="H834" t="n">
         <v>12679</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332832336426</v>
+        <v>12.5332822799683</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24758,7 +24758,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578935623169</v>
+        <v>12.7578945159912</v>
       </c>
       <c r="H841" t="n">
         <v>18683</v>
@@ -24787,7 +24787,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>13.1172714233398</v>
+        <v>13.1172723770142</v>
       </c>
       <c r="H842" t="n">
         <v>4865</v>
@@ -24816,7 +24816,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>13.0723495483398</v>
+        <v>13.0723485946655</v>
       </c>
       <c r="H843" t="n">
         <v>3970</v>
@@ -24874,7 +24874,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>13.2969608306885</v>
+        <v>13.2969598770142</v>
       </c>
       <c r="H845" t="n">
         <v>4249</v>
@@ -24903,7 +24903,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>13.3418817520142</v>
+        <v>13.3418827056885</v>
       </c>
       <c r="H846" t="n">
         <v>2019</v>
@@ -24932,7 +24932,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>13.5664939880371</v>
+        <v>13.5664930343628</v>
       </c>
       <c r="H847" t="n">
         <v>9274</v>
@@ -25106,7 +25106,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H853" t="n">
         <v>10148</v>
@@ -25193,7 +25193,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G856" t="n">
-        <v>15.2196292877197</v>
+        <v>15.2196283340454</v>
       </c>
       <c r="H856" t="n">
         <v>17742</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.399317741394</v>
+        <v>15.3993167877197</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25280,7 +25280,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>15.5430660247803</v>
+        <v>15.5430679321289</v>
       </c>
       <c r="H859" t="n">
         <v>25099</v>
@@ -25338,7 +25338,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657209396362</v>
+        <v>15.1657218933105</v>
       </c>
       <c r="H861" t="n">
         <v>7654</v>
@@ -25425,7 +25425,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>16.1180725097656</v>
+        <v>16.118070602417</v>
       </c>
       <c r="H864" t="n">
         <v>30261</v>
@@ -25454,7 +25454,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563512802124</v>
+        <v>15.9563522338867</v>
       </c>
       <c r="H865" t="n">
         <v>11649</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407264709473</v>
+        <v>15.7407274246216</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25512,7 +25512,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5250997543335</v>
+        <v>15.5251007080078</v>
       </c>
       <c r="H867" t="n">
         <v>7118</v>
@@ -25541,7 +25541,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454113006592</v>
+        <v>15.3454103469849</v>
       </c>
       <c r="H868" t="n">
         <v>4337</v>
@@ -25599,7 +25599,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>14.6446237564087</v>
+        <v>14.644624710083</v>
       </c>
       <c r="H870" t="n">
         <v>3094</v>
@@ -25657,7 +25657,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368118286133</v>
+        <v>14.5368127822876</v>
       </c>
       <c r="H872" t="n">
         <v>5468</v>
@@ -25744,7 +25744,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>14.6446237564087</v>
+        <v>14.644624710083</v>
       </c>
       <c r="H875" t="n">
         <v>7498</v>
@@ -25831,7 +25831,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750915527344</v>
+        <v>14.3750925064087</v>
       </c>
       <c r="H878" t="n">
         <v>3239</v>
@@ -25918,7 +25918,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>14.9233922958374</v>
+        <v>14.9233932495117</v>
       </c>
       <c r="H881" t="n">
         <v>15130</v>
@@ -25947,7 +25947,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135280609131</v>
+        <v>14.8135290145874</v>
       </c>
       <c r="H882" t="n">
         <v>7029</v>
@@ -26005,7 +26005,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H884" t="n">
         <v>2276</v>
@@ -26121,7 +26121,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H888" t="n">
         <v>3111</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H890" t="n">
         <v>4619</v>
@@ -26382,7 +26382,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>14.9233922958374</v>
+        <v>14.9233932495117</v>
       </c>
       <c r="H897" t="n">
         <v>1992</v>
@@ -26614,7 +26614,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G905" t="n">
-        <v>13.2204790115356</v>
+        <v>13.2204780578613</v>
       </c>
       <c r="H905" t="n">
         <v>11888</v>
@@ -26730,7 +26730,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G909" t="n">
-        <v>12.8542613983154</v>
+        <v>12.8542604446411</v>
       </c>
       <c r="H909" t="n">
         <v>5740</v>
@@ -26875,7 +26875,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711511611938</v>
+        <v>12.6711521148682</v>
       </c>
       <c r="H914" t="n">
         <v>2839</v>
@@ -27194,7 +27194,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894617080688</v>
+        <v>12.6894626617432</v>
       </c>
       <c r="H925" t="n">
         <v>776</v>
@@ -27223,7 +27223,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514207839966</v>
+        <v>12.4514217376709</v>
       </c>
       <c r="H926" t="n">
         <v>3020</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359498977661</v>
+        <v>12.8359508514404</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27397,7 +27397,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G932" t="n">
-        <v>13.0556802749634</v>
+        <v>13.0556812286377</v>
       </c>
       <c r="H932" t="n">
         <v>1140</v>
@@ -27571,7 +27571,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G938" t="n">
-        <v>13.2204790115356</v>
+        <v>13.2204780578613</v>
       </c>
       <c r="H938" t="n">
         <v>11774</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923023223877</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923023223877</v>
+        <v>13.0923013687134</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27716,7 +27716,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>13.2204790115356</v>
+        <v>13.2204780578613</v>
       </c>
       <c r="H943" t="n">
         <v>1926</v>
@@ -27919,7 +27919,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402849197388</v>
+        <v>14.7402839660645</v>
       </c>
       <c r="H950" t="n">
         <v>5635</v>
@@ -27977,7 +27977,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9233922958374</v>
+        <v>14.9233932495117</v>
       </c>
       <c r="H952" t="n">
         <v>5644</v>
@@ -28064,7 +28064,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346046447754</v>
+        <v>13.9346055984497</v>
       </c>
       <c r="H955" t="n">
         <v>1552</v>
@@ -28441,7 +28441,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303442001343</v>
+        <v>13.3303451538086</v>
       </c>
       <c r="H968" t="n">
         <v>853</v>
@@ -28499,7 +28499,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599397659302</v>
+        <v>13.6599407196045</v>
       </c>
       <c r="H970" t="n">
         <v>663</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796710968018</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28760,7 +28760,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H979" t="n">
         <v>548</v>
@@ -28992,7 +28992,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H987" t="n">
         <v>7766</v>
@@ -29021,7 +29021,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H988" t="n">
         <v>2745</v>
@@ -29224,7 +29224,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H995" t="n">
         <v>776</v>
@@ -29340,7 +29340,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514963150024</v>
+        <v>13.7514953613281</v>
       </c>
       <c r="H999" t="n">
         <v>1949</v>
@@ -29427,7 +29427,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712266921997</v>
+        <v>13.9712257385254</v>
       </c>
       <c r="H1002" t="n">
         <v>3350</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796710968018</v>
+        <v>13.8796720504761</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29514,7 +29514,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.0810918807983</v>
+        <v>14.081090927124</v>
       </c>
       <c r="H1005" t="n">
         <v>1238</v>
@@ -29543,7 +29543,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1006" t="n">
         <v>626</v>
@@ -29572,7 +29572,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1007" t="n">
         <v>1460</v>
@@ -29601,7 +29601,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1008" t="n">
         <v>8629</v>
@@ -29630,7 +29630,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.9417037963867</v>
+        <v>14.941704750061</v>
       </c>
       <c r="H1009" t="n">
         <v>11362</v>
@@ -29775,7 +29775,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1014" t="n">
         <v>801</v>
@@ -29891,7 +29891,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.1909561157227</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1018" t="n">
         <v>2476</v>
@@ -29920,7 +29920,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.9529142379761</v>
+        <v>13.9529151916504</v>
       </c>
       <c r="H1019" t="n">
         <v>2740</v>
@@ -30094,7 +30094,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.1909561157227</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1025" t="n">
         <v>1900</v>
@@ -30152,7 +30152,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1027" t="n">
-        <v>14.3557558059692</v>
+        <v>14.3557548522949</v>
       </c>
       <c r="H1027" t="n">
         <v>5708</v>
@@ -30181,7 +30181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.1909561157227</v>
+        <v>14.190957069397</v>
       </c>
       <c r="H1028" t="n">
         <v>5343</v>
@@ -30384,7 +30384,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1035" t="n">
         <v>7293</v>
@@ -30442,7 +30442,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1037" t="n">
         <v>5201</v>
@@ -30471,7 +30471,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1038" t="n">
         <v>4882</v>
@@ -30500,7 +30500,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1039" t="n">
         <v>1448</v>
@@ -30529,7 +30529,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.3557558059692</v>
+        <v>14.3557548522949</v>
       </c>
       <c r="H1040" t="n">
         <v>3156</v>
@@ -30674,7 +30674,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1045" t="n">
         <v>1335</v>
@@ -30703,7 +30703,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1046" t="n">
         <v>1062</v>
@@ -30790,7 +30790,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.3557558059692</v>
+        <v>14.3557548522949</v>
       </c>
       <c r="H1049" t="n">
         <v>2797</v>
@@ -30877,7 +30877,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1052" t="n">
         <v>942</v>
@@ -31080,7 +31080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1059" t="n">
         <v>2147</v>
@@ -31109,7 +31109,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1060" t="n">
         <v>3908</v>
@@ -31167,7 +31167,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656209945679</v>
+        <v>14.4656200408936</v>
       </c>
       <c r="H1062" t="n">
         <v>4440</v>
@@ -31370,7 +31370,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1069" t="n">
-        <v>14.3557558059692</v>
+        <v>14.3557548522949</v>
       </c>
       <c r="H1069" t="n">
         <v>2207</v>
@@ -31399,7 +31399,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1070" t="n">
         <v>4599</v>
@@ -31428,7 +31428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571746826172</v>
+        <v>14.5571756362915</v>
       </c>
       <c r="H1071" t="n">
         <v>15327</v>
@@ -31515,7 +31515,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642002105713</v>
+        <v>14.2642011642456</v>
       </c>
       <c r="H1074" t="n">
         <v>4278</v>
@@ -31573,7 +31573,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360244750977</v>
+        <v>14.1360235214233</v>
       </c>
       <c r="H1076" t="n">
         <v>5561</v>
@@ -31631,7 +31631,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191337585449</v>
+        <v>14.3191347122192</v>
       </c>
       <c r="H1078" t="n">
         <v>11008</v>
@@ -31660,7 +31660,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388641357422</v>
+        <v>14.5388650894165</v>
       </c>
       <c r="H1079" t="n">
         <v>7708</v>
@@ -31776,7 +31776,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952175140381</v>
+        <v>14.7952165603638</v>
       </c>
       <c r="H1083" t="n">
         <v>10646</v>
@@ -31892,7 +31892,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.161434173584</v>
+        <v>15.1614351272583</v>
       </c>
       <c r="H1087" t="n">
         <v>6067</v>
@@ -31979,7 +31979,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.9600162506104</v>
+        <v>14.960015296936</v>
       </c>
       <c r="H1090" t="n">
         <v>10574</v>
@@ -32066,7 +32066,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4360990524292</v>
+        <v>15.4361000061035</v>
       </c>
       <c r="H1093" t="n">
         <v>8188</v>
@@ -32095,7 +32095,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1094" t="n">
-        <v>15.5825881958008</v>
+        <v>15.5825872421265</v>
       </c>
       <c r="H1094" t="n">
         <v>4974</v>
@@ -32124,7 +32124,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473840713501</v>
+        <v>15.7473850250244</v>
       </c>
       <c r="H1095" t="n">
         <v>11814</v>
@@ -32182,7 +32182,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.5825881958008</v>
+        <v>15.5825872421265</v>
       </c>
       <c r="H1097" t="n">
         <v>6511</v>
@@ -32240,7 +32240,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.8023176193237</v>
+        <v>15.802318572998</v>
       </c>
       <c r="H1099" t="n">
         <v>6086</v>
@@ -32298,7 +32298,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1101" t="n">
-        <v>15.6375179290771</v>
+        <v>15.6375188827515</v>
       </c>
       <c r="H1101" t="n">
         <v>6442</v>
@@ -32414,7 +32414,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572492599487</v>
+        <v>15.8572483062744</v>
       </c>
       <c r="H1105" t="n">
         <v>21663</v>
@@ -32443,7 +32443,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290735244751</v>
+        <v>15.7290725708008</v>
       </c>
       <c r="H1106" t="n">
         <v>5698</v>
@@ -32501,7 +32501,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>16.2600917816162</v>
+        <v>16.2600898742676</v>
       </c>
       <c r="H1108" t="n">
         <v>12113</v>
@@ -32646,7 +32646,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.060022354126</v>
+        <v>17.0600242614746</v>
       </c>
       <c r="H1113" t="n">
         <v>19386</v>
@@ -32762,7 +32762,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.395471572876</v>
+        <v>17.3954734802246</v>
       </c>
       <c r="H1117" t="n">
         <v>9205</v>
@@ -32791,7 +32791,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309226989746</v>
+        <v>17.7309246063232</v>
       </c>
       <c r="H1118" t="n">
         <v>29414</v>
@@ -32820,7 +32820,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392360687256</v>
+        <v>17.5392379760742</v>
       </c>
       <c r="H1119" t="n">
         <v>13971</v>
@@ -32849,7 +32849,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392360687256</v>
+        <v>17.5392379760742</v>
       </c>
       <c r="H1120" t="n">
         <v>12199</v>
@@ -32878,7 +32878,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.395471572876</v>
+        <v>17.3954734802246</v>
       </c>
       <c r="H1121" t="n">
         <v>14919</v>
@@ -33052,7 +33052,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.395471572876</v>
+        <v>17.3954734802246</v>
       </c>
       <c r="H1127" t="n">
         <v>2398</v>
@@ -33081,7 +33081,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.060022354126</v>
+        <v>17.0600242614746</v>
       </c>
       <c r="H1128" t="n">
         <v>7274</v>
@@ -33110,7 +33110,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641799926758</v>
+        <v>16.9641819000244</v>
       </c>
       <c r="H1129" t="n">
         <v>6734</v>
@@ -33168,7 +33168,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.060022354126</v>
+        <v>17.0600242614746</v>
       </c>
       <c r="H1131" t="n">
         <v>3201</v>
@@ -33197,7 +33197,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683376312256</v>
+        <v>16.8683395385742</v>
       </c>
       <c r="H1132" t="n">
         <v>2268</v>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88108205795288</v>
+        <v>2.88108229637146</v>
       </c>
       <c r="H2" t="n">
         <v>41400</v>
@@ -485,7 +485,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676808357239</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H4" t="n">
         <v>7200</v>
@@ -514,7 +514,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.90248680114746</v>
+        <v>2.90248703956604</v>
       </c>
       <c r="H5" t="n">
         <v>8550</v>
@@ -746,7 +746,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676808357239</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H13" t="n">
         <v>3600</v>
@@ -775,7 +775,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676808357239</v>
+        <v>2.90676784515381</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>2.89392518997192</v>
+        <v>2.89392495155334</v>
       </c>
       <c r="H22" t="n">
         <v>450</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062068939209</v>
+        <v>2.91062045097351</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863395690918</v>
+        <v>2.89863419532776</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1152,7 +1152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255313873291</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H27" t="n">
         <v>450</v>
@@ -1181,7 +1181,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601166725159</v>
+        <v>2.81601119041443</v>
       </c>
       <c r="H28" t="n">
         <v>450</v>
@@ -1239,7 +1239,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549625396729</v>
+        <v>2.76549649238586</v>
       </c>
       <c r="H30" t="n">
         <v>3150</v>
@@ -1326,7 +1326,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>2.82542967796326</v>
+        <v>2.82542943954468</v>
       </c>
       <c r="H33" t="n">
         <v>2250</v>
@@ -1355,7 +1355,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76035928726196</v>
+        <v>2.76035904884338</v>
       </c>
       <c r="H34" t="n">
         <v>1800</v>
@@ -1384,7 +1384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399152755737</v>
+        <v>2.83399176597595</v>
       </c>
       <c r="H35" t="n">
         <v>7650</v>
@@ -1413,7 +1413,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G36" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H36" t="n">
         <v>16200</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666786193848</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.9538586139679</v>
+        <v>2.95385813713074</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255313873291</v>
+        <v>2.84255337715149</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1616,7 +1616,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G43" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H43" t="n">
         <v>9000</v>
@@ -1645,7 +1645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>2.868239402771</v>
+        <v>2.86823916435242</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>3.51300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>3.00779819488525</v>
+        <v>3.00779843330383</v>
       </c>
       <c r="H46" t="n">
         <v>7650</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666786193848</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666786193848</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666786193848</v>
+        <v>2.99666810035706</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379203796387</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379203796387</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379156112671</v>
+        <v>3.01379203796387</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256911277771</v>
+        <v>3.34256935119629</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489611625671</v>
+        <v>3.30489635467529</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768520355225</v>
+        <v>3.23768591880798</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2109,7 +2109,7 @@
         <v>3.79949998855591</v>
       </c>
       <c r="G60" t="n">
-        <v>3.25309681892395</v>
+        <v>3.25309705734253</v>
       </c>
       <c r="H60" t="n">
         <v>5400</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36482977867126</v>
+        <v>3.36483001708984</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.407639503479</v>
+        <v>3.40763926506042</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2225,7 +2225,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G64" t="n">
-        <v>3.44873666763306</v>
+        <v>3.44873642921448</v>
       </c>
       <c r="H64" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2283,7 +2283,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098504066467</v>
+        <v>3.61098480224609</v>
       </c>
       <c r="H66" t="n">
         <v>38250</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.815185546875</v>
+        <v>3.81518650054932</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.96630430221558</v>
+        <v>3.966304063797</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2370,7 +2370,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293346405029</v>
+        <v>4.04293251037598</v>
       </c>
       <c r="H69" t="n">
         <v>51750</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095483779907</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2515,7 +2515,7 @@
         <v>4.75</v>
       </c>
       <c r="G74" t="n">
-        <v>4.06690692901611</v>
+        <v>4.06690645217896</v>
       </c>
       <c r="H74" t="n">
         <v>18450</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128771781921</v>
+        <v>3.98128724098206</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2573,7 +2573,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G76" t="n">
-        <v>4.02409696578979</v>
+        <v>4.02409648895264</v>
       </c>
       <c r="H76" t="n">
         <v>450</v>
@@ -2602,7 +2602,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.93847751617432</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H77" t="n">
         <v>5850</v>
@@ -2631,7 +2631,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.93847751617432</v>
+        <v>3.9384777545929</v>
       </c>
       <c r="H78" t="n">
         <v>18900</v>
@@ -2718,7 +2718,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>4.01553440093994</v>
+        <v>4.0155348777771</v>
       </c>
       <c r="H81" t="n">
         <v>1800</v>
@@ -2747,7 +2747,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G82" t="n">
-        <v>3.95645785331726</v>
+        <v>3.9564573764801</v>
       </c>
       <c r="H82" t="n">
         <v>2250</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566850662231</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.0082573890686</v>
+        <v>4.00825691223145</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330714225769</v>
+        <v>3.96330761909485</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566826820374</v>
+        <v>3.89566850662231</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2979,7 +2979,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H90" t="n">
         <v>17550</v>
@@ -3008,7 +3008,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H91" t="n">
         <v>4950</v>
@@ -3037,7 +3037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H92" t="n">
         <v>6750</v>
@@ -3095,7 +3095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H98" t="n">
         <v>8100</v>
@@ -3240,7 +3240,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H99" t="n">
         <v>8550</v>
@@ -3269,7 +3269,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.1782112121582</v>
+        <v>4.17821168899536</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108751296997</v>
+        <v>4.16108703613281</v>
       </c>
       <c r="H101" t="n">
         <v>4050</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095483779907</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095483779907</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095483779907</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3530,7 +3530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062028884888</v>
       </c>
       <c r="H109" t="n">
         <v>27450</v>
@@ -3588,7 +3588,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062028884888</v>
       </c>
       <c r="H111" t="n">
         <v>4500</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3675,7 +3675,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3820,7 +3820,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H119" t="n">
         <v>9450</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -3936,7 +3936,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H123" t="n">
         <v>3600</v>
@@ -3965,7 +3965,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938234329224</v>
+        <v>4.40938282012939</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095483779907</v>
+        <v>4.28095436096191</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4023,7 +4023,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>4.32376384735107</v>
+        <v>4.32376432418823</v>
       </c>
       <c r="H126" t="n">
         <v>900</v>
@@ -4139,7 +4139,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062028884888</v>
       </c>
       <c r="H130" t="n">
         <v>1350</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4342,7 +4342,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H137" t="n">
         <v>69750</v>
@@ -4371,7 +4371,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H138" t="n">
         <v>18000</v>
@@ -4400,7 +4400,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H139" t="n">
         <v>3150</v>
@@ -4429,7 +4429,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>5.26557445526123</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H140" t="n">
         <v>33750</v>
@@ -4458,7 +4458,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>5.26557445526123</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H141" t="n">
         <v>21150</v>
@@ -4545,7 +4545,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G144" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H144" t="n">
         <v>1350</v>
@@ -4603,7 +4603,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G146" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H146" t="n">
         <v>11250</v>
@@ -4748,7 +4748,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871658325195</v>
+        <v>5.00871610641479</v>
       </c>
       <c r="H151" t="n">
         <v>1800</v>
@@ -4777,7 +4777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H152" t="n">
         <v>13500</v>
@@ -4980,7 +4980,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09433507919312</v>
+        <v>5.09433460235596</v>
       </c>
       <c r="H159" t="n">
         <v>2250</v>
@@ -5067,7 +5067,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G162" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H162" t="n">
         <v>20250</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H163" t="n">
         <v>7650</v>
@@ -5125,7 +5125,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H164" t="n">
         <v>38250</v>
@@ -5154,7 +5154,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G165" t="n">
-        <v>5.60805034637451</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H165" t="n">
         <v>18000</v>
@@ -5183,7 +5183,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H166" t="n">
         <v>10800</v>
@@ -5212,7 +5212,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H167" t="n">
         <v>14850</v>
@@ -5241,7 +5241,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H168" t="n">
         <v>10800</v>
@@ -5270,7 +5270,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G169" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H169" t="n">
         <v>9450</v>
@@ -5328,7 +5328,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H171" t="n">
         <v>8100</v>
@@ -5386,7 +5386,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H173" t="n">
         <v>26100</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5502,7 +5502,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H177" t="n">
         <v>27450</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>6.67828893661499</v>
+        <v>6.67828845977783</v>
       </c>
       <c r="H183" t="n">
         <v>23400</v>
@@ -5734,7 +5734,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H185" t="n">
         <v>15750</v>
@@ -5763,7 +5763,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H186" t="n">
         <v>4050</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.59266948699951</v>
+        <v>6.5926685333252</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919376373291</v>
+        <v>7.14919424057007</v>
       </c>
       <c r="H196" t="n">
         <v>13950</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514633178711</v>
+        <v>6.93514585494995</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233684539795</v>
+        <v>6.89233636856079</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6256,7 +6256,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H203" t="n">
         <v>2250</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547897338867</v>
+        <v>6.63547945022583</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6343,7 +6343,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.67828893661499</v>
+        <v>6.67828845977783</v>
       </c>
       <c r="H206" t="n">
         <v>4950</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952735900879</v>
+        <v>6.84952688217163</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.59266948699951</v>
+        <v>6.5926685333252</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6517,7 +6517,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H212" t="n">
         <v>4050</v>
@@ -6546,7 +6546,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>6.76390743255615</v>
+        <v>6.76390695571899</v>
       </c>
       <c r="H213" t="n">
         <v>3150</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54985952377319</v>
+        <v>6.54986000061035</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6720,7 +6720,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>6.37862157821655</v>
+        <v>6.37862110137939</v>
       </c>
       <c r="H219" t="n">
         <v>8033</v>
@@ -6749,7 +6749,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G220" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H220" t="n">
         <v>23636</v>
@@ -6778,7 +6778,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G221" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H221" t="n">
         <v>2400</v>
@@ -6807,7 +6807,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H222" t="n">
         <v>7042</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6923,7 +6923,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H226" t="n">
         <v>12417</v>
@@ -6952,7 +6952,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H227" t="n">
         <v>19965</v>
@@ -6981,7 +6981,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H228" t="n">
         <v>3719</v>
@@ -7068,7 +7068,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H231" t="n">
         <v>55223</v>
@@ -7097,7 +7097,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019359588623</v>
       </c>
       <c r="H232" t="n">
         <v>20785</v>
@@ -7126,7 +7126,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>6.29300212860107</v>
+        <v>6.29300260543823</v>
       </c>
       <c r="H233" t="n">
         <v>9795</v>
@@ -7184,7 +7184,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H235" t="n">
         <v>2494</v>
@@ -7242,7 +7242,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H237" t="n">
         <v>3630</v>
@@ -7271,7 +7271,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>6.25019311904907</v>
+        <v>6.25019359588623</v>
       </c>
       <c r="H238" t="n">
         <v>4610</v>
@@ -7329,7 +7329,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738315582275</v>
+        <v>6.20738363265991</v>
       </c>
       <c r="H240" t="n">
         <v>10587</v>
@@ -7445,7 +7445,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G244" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H244" t="n">
         <v>1353</v>
@@ -7474,7 +7474,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H245" t="n">
         <v>3000</v>
@@ -7503,7 +7503,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>6.16457366943359</v>
+        <v>6.16457414627075</v>
       </c>
       <c r="H246" t="n">
         <v>12575</v>
@@ -7619,7 +7619,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052671432495</v>
       </c>
       <c r="H250" t="n">
         <v>4710</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7735,7 +7735,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H254" t="n">
         <v>9240</v>
@@ -7764,7 +7764,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>5.60805034637451</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H255" t="n">
         <v>6920</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7967,7 +7967,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H262" t="n">
         <v>2060</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8025,7 +8025,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052671432495</v>
       </c>
       <c r="H264" t="n">
         <v>1575</v>
@@ -8054,7 +8054,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H265" t="n">
         <v>998</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8141,7 +8141,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052671432495</v>
       </c>
       <c r="H268" t="n">
         <v>2072</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8199,7 +8199,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614521026611</v>
+        <v>6.03614568710327</v>
       </c>
       <c r="H270" t="n">
         <v>12160</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8286,7 +8286,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H273" t="n">
         <v>6625</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333572387695</v>
+        <v>5.99333620071411</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8547,7 +8547,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052671432495</v>
       </c>
       <c r="H282" t="n">
         <v>3735</v>
@@ -8576,7 +8576,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052671432495</v>
       </c>
       <c r="H283" t="n">
         <v>5807</v>
@@ -8605,7 +8605,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052623748779</v>
+        <v>5.95052671432495</v>
       </c>
       <c r="H284" t="n">
         <v>498</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771722793579</v>
+        <v>5.90771627426147</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490678787231</v>
+        <v>5.86490631103516</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9040,7 +9040,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H299" t="n">
         <v>2360</v>
@@ -9098,7 +9098,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H301" t="n">
         <v>2357</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928781509399</v>
+        <v>5.77928733825684</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9185,7 +9185,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>5.60805034637451</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H304" t="n">
         <v>2769</v>
@@ -9214,7 +9214,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H305" t="n">
         <v>395</v>
@@ -9243,7 +9243,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H306" t="n">
         <v>6889</v>
@@ -9272,7 +9272,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>5.60805034637451</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H307" t="n">
         <v>2484</v>
@@ -9301,7 +9301,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H308" t="n">
         <v>3433</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H309" t="n">
         <v>714</v>
@@ -9359,7 +9359,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>5.60805034637451</v>
+        <v>5.60804986953735</v>
       </c>
       <c r="H310" t="n">
         <v>1050</v>
@@ -9388,7 +9388,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H311" t="n">
         <v>1072</v>
@@ -9417,7 +9417,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H312" t="n">
         <v>1448</v>
@@ -9446,7 +9446,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56524038314819</v>
+        <v>5.56523990631104</v>
       </c>
       <c r="H313" t="n">
         <v>8895</v>
@@ -9475,7 +9475,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243089675903</v>
+        <v>5.52243041992188</v>
       </c>
       <c r="H314" t="n">
         <v>1549</v>
@@ -9533,7 +9533,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.73647880554199</v>
+        <v>5.73647832870483</v>
       </c>
       <c r="H316" t="n">
         <v>1719</v>
@@ -9562,7 +9562,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.65085935592651</v>
+        <v>5.65085887908936</v>
       </c>
       <c r="H317" t="n">
         <v>4780</v>
@@ -9620,7 +9620,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>5.26557445526123</v>
+        <v>5.26557350158691</v>
       </c>
       <c r="H319" t="n">
         <v>5941</v>
@@ -9649,7 +9649,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H320" t="n">
         <v>9329</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995500564575</v>
+        <v>5.17995452880859</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9794,7 +9794,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062028884888</v>
       </c>
       <c r="H325" t="n">
         <v>7622</v>
@@ -9823,7 +9823,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062028884888</v>
       </c>
       <c r="H326" t="n">
         <v>6905</v>
@@ -9852,7 +9852,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H327" t="n">
         <v>5844</v>
@@ -9881,7 +9881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750587463379</v>
       </c>
       <c r="H328" t="n">
         <v>14468</v>
@@ -9910,7 +9910,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874453544617</v>
+        <v>3.69874501228333</v>
       </c>
       <c r="H329" t="n">
         <v>7210</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051556587219</v>
+        <v>3.39051580429077</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -10229,7 +10229,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560145378113</v>
+        <v>3.95560073852539</v>
       </c>
       <c r="H340" t="n">
         <v>40606</v>
@@ -10258,7 +10258,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062076568604</v>
+        <v>4.58062028884888</v>
       </c>
       <c r="H341" t="n">
         <v>24606</v>
@@ -10287,7 +10287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G342" t="n">
-        <v>4.10971641540527</v>
+        <v>4.10971593856812</v>
       </c>
       <c r="H342" t="n">
         <v>27229</v>
@@ -10345,7 +10345,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710594177246</v>
+        <v>3.88710641860962</v>
       </c>
       <c r="H344" t="n">
         <v>14534</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299193382263</v>
+        <v>3.73299169540405</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10461,7 +10461,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743929862976</v>
+        <v>3.58743977546692</v>
       </c>
       <c r="H348" t="n">
         <v>5375</v>
@@ -10490,7 +10490,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H349" t="n">
         <v>8462</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476367950439</v>
+        <v>3.42476344108582</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593504905701</v>
+        <v>3.65593481063843</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10606,7 +10606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G353" t="n">
-        <v>3.54462957382202</v>
+        <v>3.5446298122406</v>
       </c>
       <c r="H353" t="n">
         <v>1950</v>
@@ -10664,7 +10664,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750611305237</v>
+        <v>3.52750587463379</v>
       </c>
       <c r="H355" t="n">
         <v>3470</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10722,7 +10722,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620111465454</v>
       </c>
       <c r="H357" t="n">
         <v>4102</v>
@@ -10751,7 +10751,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>3.4162015914917</v>
+        <v>3.41620111465454</v>
       </c>
       <c r="H358" t="n">
         <v>4270</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476367950439</v>
+        <v>3.42476344108582</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757316589355</v>
+        <v>3.46757292747498</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.76723980903625</v>
+        <v>3.7672393321991</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10954,7 +10954,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>3.81004881858826</v>
+        <v>3.81004905700684</v>
       </c>
       <c r="H365" t="n">
         <v>3480</v>
@@ -10983,7 +10983,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G366" t="n">
-        <v>3.87854433059692</v>
+        <v>3.8785445690155</v>
       </c>
       <c r="H366" t="n">
         <v>4865</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.852858543396</v>
+        <v>3.85285878181458</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11070,7 +11070,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356388092041</v>
+        <v>4.50356292724609</v>
       </c>
       <c r="H369" t="n">
         <v>65581</v>
@@ -11099,7 +11099,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H370" t="n">
         <v>55309</v>
@@ -11128,7 +11128,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.39400243759155</v>
+        <v>5.39400196075439</v>
       </c>
       <c r="H371" t="n">
         <v>176118</v>
@@ -11157,7 +11157,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34263038635254</v>
+        <v>5.34262990951538</v>
       </c>
       <c r="H372" t="n">
         <v>50751</v>
@@ -11186,7 +11186,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G373" t="n">
-        <v>4.82891654968262</v>
+        <v>4.82891607284546</v>
       </c>
       <c r="H373" t="n">
         <v>122121</v>
@@ -11273,7 +11273,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.40082120895386</v>
+        <v>4.40082025527954</v>
       </c>
       <c r="H376" t="n">
         <v>38510</v>
@@ -11302,7 +11302,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657333374023</v>
+        <v>4.36657285690308</v>
       </c>
       <c r="H377" t="n">
         <v>13190</v>
@@ -11331,7 +11331,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26383018493652</v>
+        <v>4.26382970809937</v>
       </c>
       <c r="H378" t="n">
         <v>10379</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.27239179611206</v>
+        <v>4.2723913192749</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781127929688</v>
+        <v>4.53781175613403</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11418,7 +11418,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055442810059</v>
+        <v>4.64055395126343</v>
       </c>
       <c r="H381" t="n">
         <v>28041</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11563,7 +11563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34263038635254</v>
+        <v>5.34262990951538</v>
       </c>
       <c r="H386" t="n">
         <v>87258</v>
@@ -11650,7 +11650,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H389" t="n">
         <v>10104</v>
@@ -11708,7 +11708,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015449523926</v>
+        <v>5.00015497207642</v>
       </c>
       <c r="H391" t="n">
         <v>16426</v>
@@ -11737,7 +11737,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015449523926</v>
+        <v>5.00015497207642</v>
       </c>
       <c r="H392" t="n">
         <v>5797</v>
@@ -11766,7 +11766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G393" t="n">
-        <v>4.880286693573</v>
+        <v>4.88028717041016</v>
       </c>
       <c r="H393" t="n">
         <v>8696</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426921844482</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11824,7 +11824,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H395" t="n">
         <v>6353</v>
@@ -11853,7 +11853,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20564031600952</v>
+        <v>5.20563983917236</v>
       </c>
       <c r="H396" t="n">
         <v>4787</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303127288818</v>
+        <v>4.98303079605103</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12143,7 +12143,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H406" t="n">
         <v>2647</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426921844482</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12230,7 +12230,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H409" t="n">
         <v>4265</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12375,7 +12375,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H414" t="n">
         <v>1971</v>
@@ -12404,7 +12404,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H415" t="n">
         <v>4635</v>
@@ -12433,7 +12433,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H416" t="n">
         <v>12743</v>
@@ -12491,7 +12491,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H418" t="n">
         <v>1185</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440284729004</v>
+        <v>5.03440141677856</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12839,7 +12839,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H430" t="n">
         <v>1010</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426921844482</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426921844482</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12955,7 +12955,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H434" t="n">
         <v>528</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426921844482</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426826477051</v>
+        <v>5.15426921844482</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13187,7 +13187,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002182006836</v>
+        <v>5.12002086639404</v>
       </c>
       <c r="H442" t="n">
         <v>1564</v>
@@ -13216,7 +13216,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>5.1713924407959</v>
+        <v>5.17139196395874</v>
       </c>
       <c r="H443" t="n">
         <v>260</v>
@@ -13448,7 +13448,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H451" t="n">
         <v>650</v>
@@ -13477,7 +13477,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H452" t="n">
         <v>930</v>
@@ -13506,7 +13506,7 @@
         <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H453" t="n">
         <v>7910</v>
@@ -13535,7 +13535,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G454" t="n">
-        <v>5.15023803710938</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H454" t="n">
         <v>900</v>
@@ -13564,7 +13564,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503713607788</v>
       </c>
       <c r="H455" t="n">
         <v>845</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.09803867340088</v>
+        <v>5.0980396270752</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13651,7 +13651,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G458" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H458" t="n">
         <v>3600</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104164123535</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13709,7 +13709,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H460" t="n">
         <v>2330</v>
@@ -13738,7 +13738,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763782501221</v>
+        <v>5.16763687133789</v>
       </c>
       <c r="H461" t="n">
         <v>2800</v>
@@ -13767,7 +13767,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G462" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08064031600952</v>
       </c>
       <c r="H462" t="n">
         <v>2675</v>
@@ -13796,7 +13796,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G463" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08064031600952</v>
       </c>
       <c r="H463" t="n">
         <v>1000</v>
@@ -13825,7 +13825,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G464" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H464" t="n">
         <v>4200</v>
@@ -13912,7 +13912,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H467" t="n">
         <v>500</v>
@@ -13999,7 +13999,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H470" t="n">
         <v>4279</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14115,7 +14115,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G474" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404413223267</v>
       </c>
       <c r="H474" t="n">
         <v>6712</v>
@@ -14144,7 +14144,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.92404460906982</v>
+        <v>4.92404413223267</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H476" t="n">
         <v>4010</v>
@@ -14202,7 +14202,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75005006790161</v>
+        <v>4.75004959106445</v>
       </c>
       <c r="H477" t="n">
         <v>1841</v>
@@ -14231,7 +14231,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H478" t="n">
         <v>2892</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.73265075683594</v>
+        <v>4.7326512336731</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14289,7 +14289,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H480" t="n">
         <v>10416</v>
@@ -14347,7 +14347,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H482" t="n">
         <v>2456</v>
@@ -14405,7 +14405,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H484" t="n">
         <v>2940</v>
@@ -14434,7 +14434,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H485" t="n">
         <v>672</v>
@@ -14463,7 +14463,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H486" t="n">
         <v>200</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14550,7 +14550,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425939559937</v>
+        <v>4.45425987243652</v>
       </c>
       <c r="H489" t="n">
         <v>3075</v>
@@ -14666,7 +14666,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896474838257</v>
+        <v>4.28896427154541</v>
       </c>
       <c r="H493" t="n">
         <v>5774</v>
@@ -14724,7 +14724,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716861724854</v>
+        <v>4.16716909408569</v>
       </c>
       <c r="H495" t="n">
         <v>20644</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.11497020721436</v>
+        <v>4.1149697303772</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14956,7 +14956,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>4.18456888198853</v>
+        <v>4.18456792831421</v>
       </c>
       <c r="H503" t="n">
         <v>2940</v>
@@ -14985,7 +14985,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.3063645362854</v>
+        <v>4.30636358261108</v>
       </c>
       <c r="H504" t="n">
         <v>10900</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15043,7 +15043,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G506" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H506" t="n">
         <v>5490</v>
@@ -15101,7 +15101,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H508" t="n">
         <v>14843</v>
@@ -15130,7 +15130,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H509" t="n">
         <v>6520</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15188,7 +15188,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H511" t="n">
         <v>9671</v>
@@ -15217,7 +15217,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605504989624</v>
       </c>
       <c r="H512" t="n">
         <v>2873</v>
@@ -15246,7 +15246,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H513" t="n">
         <v>535</v>
@@ -15304,7 +15304,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605504989624</v>
       </c>
       <c r="H515" t="n">
         <v>2290</v>
@@ -15333,7 +15333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H516" t="n">
         <v>6185</v>
@@ -15507,7 +15507,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H522" t="n">
         <v>5441</v>
@@ -15594,7 +15594,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H525" t="n">
         <v>2013</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605504989624</v>
       </c>
       <c r="H528" t="n">
         <v>1750</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.4716591835022</v>
+        <v>4.47165870666504</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15797,7 +15797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605504989624</v>
       </c>
       <c r="H532" t="n">
         <v>16579</v>
@@ -15826,7 +15826,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H533" t="n">
         <v>5756</v>
@@ -15855,7 +15855,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H534" t="n">
         <v>13104</v>
@@ -15884,7 +15884,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345531463623</v>
+        <v>4.59345483779907</v>
       </c>
       <c r="H535" t="n">
         <v>380</v>
@@ -15913,7 +15913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G536" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H536" t="n">
         <v>3659</v>
@@ -15942,7 +15942,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>4.5064582824707</v>
+        <v>4.50645780563354</v>
       </c>
       <c r="H537" t="n">
         <v>8283</v>
@@ -15971,7 +15971,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605504989624</v>
       </c>
       <c r="H538" t="n">
         <v>1392</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785165786743</v>
+        <v>4.69785213470459</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16058,7 +16058,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H541" t="n">
         <v>1369</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16174,7 +16174,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H545" t="n">
         <v>1820</v>
@@ -16203,7 +16203,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H546" t="n">
         <v>8745</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825393676758</v>
+        <v>4.62825441360474</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16261,7 +16261,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H548" t="n">
         <v>1400</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.5760555267334</v>
+        <v>4.57605504989624</v>
       </c>
       <c r="H549" t="n">
         <v>1333</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045282363892</v>
+        <v>4.68045234680176</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16406,7 +16406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H553" t="n">
         <v>12566</v>
@@ -16435,7 +16435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6108546257019</v>
+        <v>4.61085510253906</v>
       </c>
       <c r="H554" t="n">
         <v>4021</v>
@@ -16522,7 +16522,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G557" t="n">
-        <v>4.40206050872803</v>
+        <v>4.40206146240234</v>
       </c>
       <c r="H557" t="n">
         <v>7501</v>
@@ -16667,7 +16667,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>4.66305351257324</v>
+        <v>4.66305303573608</v>
       </c>
       <c r="H562" t="n">
         <v>61009</v>
@@ -16725,7 +16725,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744985580444</v>
+        <v>4.76744937896729</v>
       </c>
       <c r="H564" t="n">
         <v>16117</v>
@@ -16783,7 +16783,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>5.08063983917236</v>
+        <v>5.08064031600952</v>
       </c>
       <c r="H566" t="n">
         <v>45160</v>
@@ -16812,7 +16812,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H567" t="n">
         <v>25506</v>
@@ -16841,7 +16841,7 @@
         <v>6</v>
       </c>
       <c r="G568" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H568" t="n">
         <v>22400</v>
@@ -16870,7 +16870,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H569" t="n">
         <v>16615</v>
@@ -16899,7 +16899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503713607788</v>
       </c>
       <c r="H570" t="n">
         <v>4750</v>
@@ -16928,7 +16928,7 @@
         <v>6</v>
       </c>
       <c r="G571" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H571" t="n">
         <v>855</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.87184619903564</v>
+        <v>4.8718466758728</v>
       </c>
       <c r="H572" t="n">
         <v>14439</v>
@@ -16986,7 +16986,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H573" t="n">
         <v>11120</v>
@@ -17015,7 +17015,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H574" t="n">
         <v>10615</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H576" t="n">
         <v>6736</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664529800415</v>
+        <v>4.90664482116699</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104259490967</v>
+        <v>5.01104164123535</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17247,7 +17247,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G582" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17276,7 +17276,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H583" t="n">
         <v>68126</v>
@@ -17305,7 +17305,7 @@
         <v>6</v>
       </c>
       <c r="G584" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H584" t="n">
         <v>21315</v>
@@ -17334,7 +17334,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G585" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H585" t="n">
         <v>18151</v>
@@ -17363,7 +17363,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H586" t="n">
         <v>26713</v>
@@ -17450,7 +17450,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28943347930908</v>
+        <v>5.28943300247192</v>
       </c>
       <c r="H589" t="n">
         <v>6920</v>
@@ -17479,7 +17479,7 @@
         <v>6</v>
       </c>
       <c r="G590" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H590" t="n">
         <v>6044</v>
@@ -17508,7 +17508,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>5.27203321456909</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H591" t="n">
         <v>2345</v>
@@ -17537,7 +17537,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503665924072</v>
+        <v>5.18503713607788</v>
       </c>
       <c r="H592" t="n">
         <v>6452</v>
@@ -17566,7 +17566,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G593" t="n">
-        <v>5.13283824920654</v>
+        <v>5.1328387260437</v>
       </c>
       <c r="H593" t="n">
         <v>3697</v>
@@ -17595,7 +17595,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.976243019104</v>
+        <v>4.97624349594116</v>
       </c>
       <c r="H594" t="n">
         <v>12574</v>
@@ -17624,7 +17624,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G595" t="n">
-        <v>5.06324100494385</v>
+        <v>5.06324005126953</v>
       </c>
       <c r="H595" t="n">
         <v>3486</v>
@@ -17653,7 +17653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.15023803710938</v>
+        <v>5.15023756027222</v>
       </c>
       <c r="H596" t="n">
         <v>9629</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.21983480453491</v>
+        <v>5.21983528137207</v>
       </c>
       <c r="H597" t="n">
         <v>33122</v>
@@ -17711,7 +17711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H598" t="n">
         <v>15675</v>
@@ -17740,7 +17740,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>5.27203321456909</v>
+        <v>5.27203369140625</v>
       </c>
       <c r="H599" t="n">
         <v>16071</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.23723459243774</v>
+        <v>5.2372350692749</v>
       </c>
       <c r="H600" t="n">
         <v>2830</v>
@@ -17943,7 +17943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.5678243637085</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H606" t="n">
         <v>11629</v>
@@ -18001,7 +18001,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G608" t="n">
-        <v>5.48082733154297</v>
+        <v>5.48082685470581</v>
       </c>
       <c r="H608" t="n">
         <v>8454</v>
@@ -18059,7 +18059,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>5.5678243637085</v>
+        <v>5.56782484054565</v>
       </c>
       <c r="H610" t="n">
         <v>163362</v>
@@ -18088,7 +18088,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G611" t="n">
-        <v>5.81141662597656</v>
+        <v>5.81141710281372</v>
       </c>
       <c r="H611" t="n">
         <v>67041</v>
@@ -18117,7 +18117,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G612" t="n">
-        <v>5.7766170501709</v>
+        <v>5.77661800384521</v>
       </c>
       <c r="H612" t="n">
         <v>36365</v>
@@ -18146,7 +18146,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>5.79401731491089</v>
+        <v>5.79401683807373</v>
       </c>
       <c r="H613" t="n">
         <v>17964</v>
@@ -18175,7 +18175,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.82881641387939</v>
+        <v>5.82881593704224</v>
       </c>
       <c r="H614" t="n">
         <v>16210</v>
@@ -18204,7 +18204,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G615" t="n">
-        <v>5.81141662597656</v>
+        <v>5.81141710281372</v>
       </c>
       <c r="H615" t="n">
         <v>25918</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.96801233291626</v>
+        <v>5.9680118560791</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281143188477</v>
+        <v>6.00281047821045</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281143188477</v>
+        <v>6.00281047821045</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18349,7 +18349,7 @@
         <v>7</v>
       </c>
       <c r="G620" t="n">
-        <v>6.23437309265137</v>
+        <v>6.23437356948853</v>
       </c>
       <c r="H620" t="n">
         <v>23823</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031137466431</v>
+        <v>7.00031089782715</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18465,7 +18465,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G624" t="n">
-        <v>7.10718584060669</v>
+        <v>7.10718536376953</v>
       </c>
       <c r="H624" t="n">
         <v>102683</v>
@@ -18494,7 +18494,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G625" t="n">
-        <v>6.89343452453613</v>
+        <v>6.89343500137329</v>
       </c>
       <c r="H625" t="n">
         <v>84822</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468544006348</v>
+        <v>6.96468591690063</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562322616577</v>
+        <v>6.87562274932861</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18581,7 +18581,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>7.08937311172485</v>
+        <v>7.0893726348877</v>
       </c>
       <c r="H628" t="n">
         <v>61294</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.8196849822998</v>
+        <v>7.81968402862549</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18726,7 +18726,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.47874736785889</v>
+        <v>8.4787483215332</v>
       </c>
       <c r="H633" t="n">
         <v>83403</v>
@@ -18755,7 +18755,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343616485596</v>
+        <v>9.17343521118164</v>
       </c>
       <c r="H634" t="n">
         <v>112604</v>
@@ -18784,7 +18784,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>9.97499656677246</v>
+        <v>9.97499752044678</v>
       </c>
       <c r="H635" t="n">
         <v>152319</v>
@@ -18813,7 +18813,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G636" t="n">
-        <v>9.26249599456787</v>
+        <v>9.26249694824219</v>
       </c>
       <c r="H636" t="n">
         <v>208819</v>
@@ -18842,7 +18842,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>9.26249599456787</v>
+        <v>9.26249694824219</v>
       </c>
       <c r="H637" t="n">
         <v>116116</v>
@@ -18871,7 +18871,7 @@
         <v>10.25</v>
       </c>
       <c r="G638" t="n">
-        <v>9.12890434265137</v>
+        <v>9.12890338897705</v>
       </c>
       <c r="H638" t="n">
         <v>117220</v>
@@ -18900,7 +18900,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>9.30702972412109</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H639" t="n">
         <v>47607</v>
@@ -18929,7 +18929,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437156677246</v>
+        <v>9.08437252044678</v>
       </c>
       <c r="H640" t="n">
         <v>42073</v>
@@ -18958,7 +18958,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718444824219</v>
+        <v>8.81718349456787</v>
       </c>
       <c r="H641" t="n">
         <v>40921</v>
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624713897705</v>
+        <v>8.90624809265137</v>
       </c>
       <c r="H645" t="n">
         <v>112321</v>
@@ -19103,7 +19103,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>9.30702972412109</v>
+        <v>9.30702877044678</v>
       </c>
       <c r="H646" t="n">
         <v>97578</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062232971191</v>
+        <v>9.44062328338623</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19219,7 +19219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109340667725</v>
+        <v>11.3109331130981</v>
       </c>
       <c r="H650" t="n">
         <v>160231</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19277,7 +19277,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>11.4890575408936</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H652" t="n">
         <v>199932</v>
@@ -19306,7 +19306,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>11.4890575408936</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H653" t="n">
         <v>91653</v>
@@ -19335,7 +19335,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453092575073</v>
+        <v>11.8453102111816</v>
       </c>
       <c r="H654" t="n">
         <v>47177</v>
@@ -19364,7 +19364,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671848297119</v>
+        <v>11.6671838760376</v>
       </c>
       <c r="H655" t="n">
         <v>87639</v>
@@ -19393,7 +19393,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>11.4890575408936</v>
+        <v>11.4890584945679</v>
       </c>
       <c r="H656" t="n">
         <v>32521</v>
@@ -19422,7 +19422,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>11.3999967575073</v>
+        <v>11.3999977111816</v>
       </c>
       <c r="H657" t="n">
         <v>25340</v>
@@ -19451,7 +19451,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109340667725</v>
+        <v>11.3109331130981</v>
       </c>
       <c r="H658" t="n">
         <v>11498</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781221389771</v>
+        <v>11.5781211853027</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19538,7 +19538,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335903167725</v>
+        <v>11.5335893630981</v>
       </c>
       <c r="H661" t="n">
         <v>13950</v>
@@ -19596,7 +19596,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671848297119</v>
+        <v>11.6671838760376</v>
       </c>
       <c r="H663" t="n">
         <v>11952</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19886,7 +19886,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>11.095775604248</v>
+        <v>11.0957736968994</v>
       </c>
       <c r="H673" t="n">
         <v>20518</v>
@@ -19915,7 +19915,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>10.7363958358765</v>
+        <v>10.7363967895508</v>
       </c>
       <c r="H674" t="n">
         <v>51956</v>
@@ -19944,7 +19944,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.410228729248</v>
+        <v>11.4102296829224</v>
       </c>
       <c r="H675" t="n">
         <v>30625</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.7246837615967</v>
+        <v>11.7246856689453</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20379,7 +20379,7 @@
         <v>13.75</v>
       </c>
       <c r="G690" t="n">
-        <v>12.3535938262939</v>
+        <v>12.3535947799683</v>
       </c>
       <c r="H690" t="n">
         <v>194061</v>
@@ -20524,7 +20524,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H695" t="n">
         <v>297213</v>
@@ -20698,7 +20698,7 @@
         <v>20.5</v>
       </c>
       <c r="G701" t="n">
-        <v>18.4180889129639</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="H701" t="n">
         <v>114226</v>
@@ -20756,7 +20756,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G703" t="n">
-        <v>17.923942565918</v>
+        <v>17.9239444732666</v>
       </c>
       <c r="H703" t="n">
         <v>17675</v>
@@ -20814,7 +20814,7 @@
         <v>19.75</v>
       </c>
       <c r="G705" t="n">
-        <v>17.744255065918</v>
+        <v>17.7442531585693</v>
       </c>
       <c r="H705" t="n">
         <v>29563</v>
@@ -20843,7 +20843,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H706" t="n">
         <v>37684</v>
@@ -20901,7 +20901,7 @@
         <v>19</v>
       </c>
       <c r="G708" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H708" t="n">
         <v>21001</v>
@@ -21017,7 +21017,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H712" t="n">
         <v>12956</v>
@@ -21075,7 +21075,7 @@
         <v>17.5</v>
       </c>
       <c r="G714" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H714" t="n">
         <v>56021</v>
@@ -21104,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="G715" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H715" t="n">
         <v>53734</v>
@@ -21191,7 +21191,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.2051887512207</v>
+        <v>17.2051868438721</v>
       </c>
       <c r="H718" t="n">
         <v>51474</v>
@@ -21307,7 +21307,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>17.4298000335693</v>
+        <v>17.4297981262207</v>
       </c>
       <c r="H722" t="n">
         <v>31177</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H728" t="n">
         <v>20822</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.0704231262207</v>
+        <v>17.0704212188721</v>
       </c>
       <c r="H733" t="n">
         <v>11843</v>
@@ -21684,7 +21684,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>17.1153430938721</v>
+        <v>17.1153450012207</v>
       </c>
       <c r="H735" t="n">
         <v>6538</v>
@@ -21858,7 +21858,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H741" t="n">
         <v>81245</v>
@@ -21887,7 +21887,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H742" t="n">
         <v>26368</v>
@@ -21945,7 +21945,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H744" t="n">
         <v>13809</v>
@@ -22119,7 +22119,7 @@
         <v>18</v>
       </c>
       <c r="G750" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H750" t="n">
         <v>10298</v>
@@ -22264,7 +22264,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>16.8008899688721</v>
+        <v>16.8008880615234</v>
       </c>
       <c r="H755" t="n">
         <v>10473</v>
@@ -22322,7 +22322,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>16.3516674041748</v>
+        <v>16.3516654968262</v>
       </c>
       <c r="H757" t="n">
         <v>5194</v>
@@ -22438,7 +22438,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>16.5313568115234</v>
+        <v>16.5313549041748</v>
       </c>
       <c r="H761" t="n">
         <v>15074</v>
@@ -22554,7 +22554,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H765" t="n">
         <v>16640</v>
@@ -22583,7 +22583,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.1387701034546</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H766" t="n">
         <v>25194</v>
@@ -22960,7 +22960,7 @@
         <v>18</v>
       </c>
       <c r="G779" t="n">
-        <v>16.1719779968262</v>
+        <v>16.1719799041748</v>
       </c>
       <c r="H779" t="n">
         <v>4290</v>
@@ -22989,7 +22989,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1270599365234</v>
+        <v>16.1270561218262</v>
       </c>
       <c r="H780" t="n">
         <v>2753</v>
@@ -23018,7 +23018,7 @@
         <v>17.5</v>
       </c>
       <c r="G781" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H781" t="n">
         <v>3445</v>
@@ -23047,7 +23047,7 @@
         <v>17.75</v>
       </c>
       <c r="G782" t="n">
-        <v>15.9473676681519</v>
+        <v>15.9473657608032</v>
       </c>
       <c r="H782" t="n">
         <v>3539</v>
@@ -23105,7 +23105,7 @@
         <v>17.5</v>
       </c>
       <c r="G784" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H784" t="n">
         <v>9640</v>
@@ -23134,7 +23134,7 @@
         <v>17.5</v>
       </c>
       <c r="G785" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H785" t="n">
         <v>2827</v>
@@ -23163,7 +23163,7 @@
         <v>17.25</v>
       </c>
       <c r="G786" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H786" t="n">
         <v>2004</v>
@@ -23221,7 +23221,7 @@
         <v>17.25</v>
       </c>
       <c r="G788" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H788" t="n">
         <v>14768</v>
@@ -23250,7 +23250,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>15.4083013534546</v>
+        <v>15.4083003997803</v>
       </c>
       <c r="H789" t="n">
         <v>6755</v>
@@ -23279,7 +23279,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8126020431519</v>
+        <v>15.8126010894775</v>
       </c>
       <c r="H790" t="n">
         <v>9326</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>15.9024438858032</v>
+        <v>15.9024457931519</v>
       </c>
       <c r="H797" t="n">
         <v>18920</v>
@@ -23511,7 +23511,7 @@
         <v>17.25</v>
       </c>
       <c r="G798" t="n">
-        <v>15.4981451034546</v>
+        <v>15.4981460571289</v>
       </c>
       <c r="H798" t="n">
         <v>13711</v>
@@ -23540,7 +23540,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>15.6778354644775</v>
+        <v>15.6778364181519</v>
       </c>
       <c r="H799" t="n">
         <v>4638</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>15.7227573394775</v>
+        <v>15.7227563858032</v>
       </c>
       <c r="H800" t="n">
         <v>4924</v>
@@ -23627,7 +23627,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>15.2286128997803</v>
+        <v>15.2286138534546</v>
       </c>
       <c r="H802" t="n">
         <v>5534</v>
@@ -23656,7 +23656,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G803" t="n">
-        <v>15.5879917144775</v>
+        <v>15.5879898071289</v>
       </c>
       <c r="H803" t="n">
         <v>8803</v>
@@ -23772,7 +23772,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>14.9141578674316</v>
+        <v>14.914158821106</v>
       </c>
       <c r="H807" t="n">
         <v>18172</v>
@@ -23801,7 +23801,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.1387701034546</v>
+        <v>15.1387691497803</v>
       </c>
       <c r="H808" t="n">
         <v>4804</v>
@@ -24004,7 +24004,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114158630371</v>
       </c>
       <c r="H815" t="n">
         <v>21544</v>
@@ -24062,7 +24062,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>14.554780960083</v>
+        <v>14.5547819137573</v>
       </c>
       <c r="H817" t="n">
         <v>53993</v>
@@ -24149,7 +24149,7 @@
         <v>16</v>
       </c>
       <c r="G820" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H820" t="n">
         <v>14476</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>14.1504802703857</v>
+        <v>14.1504812240601</v>
       </c>
       <c r="H822" t="n">
         <v>17003</v>
@@ -24236,7 +24236,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>14.4200124740601</v>
+        <v>14.4200134277344</v>
       </c>
       <c r="H823" t="n">
         <v>6212</v>
@@ -24323,7 +24323,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>13.6114139556885</v>
+        <v>13.6114158630371</v>
       </c>
       <c r="H826" t="n">
         <v>4142</v>
@@ -24497,7 +24497,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.7129726409912</v>
+        <v>12.7129716873169</v>
       </c>
       <c r="H832" t="n">
         <v>7112</v>
@@ -24526,7 +24526,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>12.6680498123169</v>
+        <v>12.6680507659912</v>
       </c>
       <c r="H833" t="n">
         <v>3601</v>
@@ -24729,7 +24729,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>12.5332822799683</v>
+        <v>12.5332832336426</v>
       </c>
       <c r="H840" t="n">
         <v>12716</v>
@@ -24758,7 +24758,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>12.7578945159912</v>
+        <v>12.7578935623169</v>
       </c>
       <c r="H841" t="n">
         <v>18683</v>
@@ -25019,7 +25019,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>13.7911043167114</v>
+        <v>13.7911033630371</v>
       </c>
       <c r="H850" t="n">
         <v>2038</v>
@@ -25106,7 +25106,7 @@
         <v>16</v>
       </c>
       <c r="G853" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H853" t="n">
         <v>10148</v>
@@ -25251,7 +25251,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3993167877197</v>
+        <v>15.399317741394</v>
       </c>
       <c r="H858" t="n">
         <v>11868</v>
@@ -25338,7 +25338,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1657218933105</v>
+        <v>15.1657209396362</v>
       </c>
       <c r="H861" t="n">
         <v>7654</v>
@@ -25454,7 +25454,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G865" t="n">
-        <v>15.9563522338867</v>
+        <v>15.9563512802124</v>
       </c>
       <c r="H865" t="n">
         <v>11649</v>
@@ -25483,7 +25483,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G866" t="n">
-        <v>15.7407274246216</v>
+        <v>15.7407264709473</v>
       </c>
       <c r="H866" t="n">
         <v>7261</v>
@@ -25512,7 +25512,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G867" t="n">
-        <v>15.5251007080078</v>
+        <v>15.5250997543335</v>
       </c>
       <c r="H867" t="n">
         <v>7118</v>
@@ -25541,7 +25541,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G868" t="n">
-        <v>15.3454103469849</v>
+        <v>15.3454093933105</v>
       </c>
       <c r="H868" t="n">
         <v>4337</v>
@@ -25599,7 +25599,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>14.644624710083</v>
+        <v>14.6446237564087</v>
       </c>
       <c r="H870" t="n">
         <v>3094</v>
@@ -25657,7 +25657,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G872" t="n">
-        <v>14.5368127822876</v>
+        <v>14.5368118286133</v>
       </c>
       <c r="H872" t="n">
         <v>5468</v>
@@ -25744,7 +25744,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>14.644624710083</v>
+        <v>14.6446237564087</v>
       </c>
       <c r="H875" t="n">
         <v>7498</v>
@@ -25831,7 +25831,7 @@
         <v>16</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3750925064087</v>
+        <v>14.3750915527344</v>
       </c>
       <c r="H878" t="n">
         <v>3239</v>
@@ -25918,7 +25918,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H881" t="n">
         <v>15130</v>
@@ -25947,7 +25947,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>14.8135290145874</v>
+        <v>14.8135280609131</v>
       </c>
       <c r="H882" t="n">
         <v>7029</v>
@@ -26005,7 +26005,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H884" t="n">
         <v>2276</v>
@@ -26121,7 +26121,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G888" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H888" t="n">
         <v>3111</v>
@@ -26179,7 +26179,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H890" t="n">
         <v>4619</v>
@@ -26382,7 +26382,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H897" t="n">
         <v>1992</v>
@@ -26614,7 +26614,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G905" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H905" t="n">
         <v>11888</v>
@@ -26730,7 +26730,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G909" t="n">
-        <v>12.8542604446411</v>
+        <v>12.8542613983154</v>
       </c>
       <c r="H909" t="n">
         <v>5740</v>
@@ -26875,7 +26875,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>12.6711521148682</v>
+        <v>12.6711511611938</v>
       </c>
       <c r="H914" t="n">
         <v>2839</v>
@@ -27194,7 +27194,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G925" t="n">
-        <v>12.6894626617432</v>
+        <v>12.6894617080688</v>
       </c>
       <c r="H925" t="n">
         <v>776</v>
@@ -27223,7 +27223,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>12.4514217376709</v>
+        <v>12.4514207839966</v>
       </c>
       <c r="H926" t="n">
         <v>3020</v>
@@ -27310,7 +27310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G929" t="n">
-        <v>12.8359508514404</v>
+        <v>12.8359498977661</v>
       </c>
       <c r="H929" t="n">
         <v>754</v>
@@ -27397,7 +27397,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G932" t="n">
-        <v>13.0556812286377</v>
+        <v>13.0556802749634</v>
       </c>
       <c r="H932" t="n">
         <v>1140</v>
@@ -27571,7 +27571,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G938" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H938" t="n">
         <v>11774</v>
@@ -27629,7 +27629,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H940" t="n">
         <v>646</v>
@@ -27687,7 +27687,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G942" t="n">
-        <v>13.0923013687134</v>
+        <v>13.0923023223877</v>
       </c>
       <c r="H942" t="n">
         <v>2409</v>
@@ -27716,7 +27716,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>13.2204780578613</v>
+        <v>13.2204790115356</v>
       </c>
       <c r="H943" t="n">
         <v>1926</v>
@@ -27919,7 +27919,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>14.7402839660645</v>
+        <v>14.7402849197388</v>
       </c>
       <c r="H950" t="n">
         <v>5635</v>
@@ -27977,7 +27977,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9233932495117</v>
+        <v>14.9233922958374</v>
       </c>
       <c r="H952" t="n">
         <v>5644</v>
@@ -28064,7 +28064,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G955" t="n">
-        <v>13.9346055984497</v>
+        <v>13.9346046447754</v>
       </c>
       <c r="H955" t="n">
         <v>1552</v>
@@ -28441,7 +28441,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G968" t="n">
-        <v>13.3303451538086</v>
+        <v>13.3303442001343</v>
       </c>
       <c r="H968" t="n">
         <v>853</v>
@@ -28499,7 +28499,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G970" t="n">
-        <v>13.6599407196045</v>
+        <v>13.6599397659302</v>
       </c>
       <c r="H970" t="n">
         <v>663</v>
@@ -28702,7 +28702,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H977" t="n">
         <v>1418</v>
@@ -28760,7 +28760,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G979" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H979" t="n">
         <v>548</v>
@@ -28992,7 +28992,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G987" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H987" t="n">
         <v>7766</v>
@@ -29021,7 +29021,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G988" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H988" t="n">
         <v>2745</v>
@@ -29224,7 +29224,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G995" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H995" t="n">
         <v>776</v>
@@ -29340,7 +29340,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>13.7514953613281</v>
+        <v>13.7514963150024</v>
       </c>
       <c r="H999" t="n">
         <v>1949</v>
@@ -29427,7 +29427,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.9712257385254</v>
+        <v>13.9712266921997</v>
       </c>
       <c r="H1002" t="n">
         <v>3350</v>
@@ -29485,7 +29485,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.8796720504761</v>
+        <v>13.8796710968018</v>
       </c>
       <c r="H1004" t="n">
         <v>938</v>
@@ -29514,7 +29514,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.081090927124</v>
+        <v>14.0810918807983</v>
       </c>
       <c r="H1005" t="n">
         <v>1238</v>
@@ -29543,7 +29543,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1006" t="n">
         <v>626</v>
@@ -29572,7 +29572,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1007" t="n">
         <v>1460</v>
@@ -29601,7 +29601,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1008" t="n">
         <v>8629</v>
@@ -29630,7 +29630,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.941704750061</v>
+        <v>14.9417037963867</v>
       </c>
       <c r="H1009" t="n">
         <v>11362</v>
@@ -29775,7 +29775,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1014" t="n">
         <v>801</v>
@@ -29891,7 +29891,7 @@
         <v>15.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909561157227</v>
       </c>
       <c r="H1018" t="n">
         <v>2476</v>
@@ -29920,7 +29920,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.9529151916504</v>
+        <v>13.9529142379761</v>
       </c>
       <c r="H1019" t="n">
         <v>2740</v>
@@ -30094,7 +30094,7 @@
         <v>15.5</v>
       </c>
       <c r="G1025" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909561157227</v>
       </c>
       <c r="H1025" t="n">
         <v>1900</v>
@@ -30152,7 +30152,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1027" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1027" t="n">
         <v>5708</v>
@@ -30181,7 +30181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1028" t="n">
-        <v>14.190957069397</v>
+        <v>14.1909561157227</v>
       </c>
       <c r="H1028" t="n">
         <v>5343</v>
@@ -30384,7 +30384,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1035" t="n">
         <v>7293</v>
@@ -30442,7 +30442,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1037" t="n">
         <v>5201</v>
@@ -30471,7 +30471,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1038" t="n">
         <v>4882</v>
@@ -30500,7 +30500,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1039" t="n">
         <v>1448</v>
@@ -30529,7 +30529,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1040" t="n">
         <v>3156</v>
@@ -30674,7 +30674,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1045" t="n">
         <v>1335</v>
@@ -30703,7 +30703,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1046" t="n">
         <v>1062</v>
@@ -30790,7 +30790,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1049" t="n">
         <v>2797</v>
@@ -30877,7 +30877,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1052" t="n">
         <v>942</v>
@@ -31080,7 +31080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1059" t="n">
         <v>2147</v>
@@ -31109,7 +31109,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1060" t="n">
         <v>3908</v>
@@ -31167,7 +31167,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>14.4656200408936</v>
+        <v>14.4656209945679</v>
       </c>
       <c r="H1062" t="n">
         <v>4440</v>
@@ -31370,7 +31370,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1069" t="n">
-        <v>14.3557548522949</v>
+        <v>14.3557558059692</v>
       </c>
       <c r="H1069" t="n">
         <v>2207</v>
@@ -31399,7 +31399,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1070" t="n">
         <v>4599</v>
@@ -31428,7 +31428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1071" t="n">
-        <v>14.5571756362915</v>
+        <v>14.5571746826172</v>
       </c>
       <c r="H1071" t="n">
         <v>15327</v>
@@ -31515,7 +31515,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1074" t="n">
-        <v>14.2642011642456</v>
+        <v>14.2642002105713</v>
       </c>
       <c r="H1074" t="n">
         <v>4278</v>
@@ -31573,7 +31573,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1076" t="n">
-        <v>14.1360235214233</v>
+        <v>14.1360244750977</v>
       </c>
       <c r="H1076" t="n">
         <v>5561</v>
@@ -31631,7 +31631,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1078" t="n">
-        <v>14.3191347122192</v>
+        <v>14.3191337585449</v>
       </c>
       <c r="H1078" t="n">
         <v>11008</v>
@@ -31660,7 +31660,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1079" t="n">
-        <v>14.5388650894165</v>
+        <v>14.5388641357422</v>
       </c>
       <c r="H1079" t="n">
         <v>7708</v>
@@ -31776,7 +31776,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>14.7952165603638</v>
+        <v>14.7952175140381</v>
       </c>
       <c r="H1083" t="n">
         <v>10646</v>
@@ -31892,7 +31892,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1087" t="n">
-        <v>15.1614351272583</v>
+        <v>15.161434173584</v>
       </c>
       <c r="H1087" t="n">
         <v>6067</v>
@@ -31979,7 +31979,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>14.960015296936</v>
+        <v>14.9600162506104</v>
       </c>
       <c r="H1090" t="n">
         <v>10574</v>
@@ -32066,7 +32066,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1093" t="n">
-        <v>15.4361000061035</v>
+        <v>15.4360990524292</v>
       </c>
       <c r="H1093" t="n">
         <v>8188</v>
@@ -32095,7 +32095,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1094" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825881958008</v>
       </c>
       <c r="H1094" t="n">
         <v>4974</v>
@@ -32124,7 +32124,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>15.7473850250244</v>
+        <v>15.7473840713501</v>
       </c>
       <c r="H1095" t="n">
         <v>11814</v>
@@ -32182,7 +32182,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1097" t="n">
-        <v>15.5825872421265</v>
+        <v>15.5825881958008</v>
       </c>
       <c r="H1097" t="n">
         <v>6511</v>
@@ -32240,7 +32240,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1099" t="n">
-        <v>15.802318572998</v>
+        <v>15.8023176193237</v>
       </c>
       <c r="H1099" t="n">
         <v>6086</v>
@@ -32298,7 +32298,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1101" t="n">
-        <v>15.6375188827515</v>
+        <v>15.6375179290771</v>
       </c>
       <c r="H1101" t="n">
         <v>6442</v>
@@ -32414,7 +32414,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1105" t="n">
-        <v>15.8572483062744</v>
+        <v>15.8572492599487</v>
       </c>
       <c r="H1105" t="n">
         <v>21663</v>
@@ -32443,7 +32443,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>15.7290725708008</v>
+        <v>15.7290735244751</v>
       </c>
       <c r="H1106" t="n">
         <v>5698</v>
@@ -32501,7 +32501,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1108" t="n">
-        <v>16.2600898742676</v>
+        <v>16.2600917816162</v>
       </c>
       <c r="H1108" t="n">
         <v>12113</v>
@@ -32646,7 +32646,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1113" t="n">
         <v>19386</v>
@@ -32762,7 +32762,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1117" t="n">
         <v>9205</v>
@@ -32791,7 +32791,7 @@
         <v>18.5</v>
       </c>
       <c r="G1118" t="n">
-        <v>17.7309246063232</v>
+        <v>17.7309226989746</v>
       </c>
       <c r="H1118" t="n">
         <v>29414</v>
@@ -32820,7 +32820,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1119" t="n">
         <v>13971</v>
@@ -32849,7 +32849,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>17.5392379760742</v>
+        <v>17.5392360687256</v>
       </c>
       <c r="H1120" t="n">
         <v>12199</v>
@@ -32878,7 +32878,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1121" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1121" t="n">
         <v>14919</v>
@@ -33052,7 +33052,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>17.3954734802246</v>
+        <v>17.395471572876</v>
       </c>
       <c r="H1127" t="n">
         <v>2398</v>
@@ -33081,7 +33081,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1128" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1128" t="n">
         <v>7274</v>
@@ -33110,7 +33110,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>16.9641819000244</v>
+        <v>16.9641799926758</v>
       </c>
       <c r="H1129" t="n">
         <v>6734</v>
@@ -33168,7 +33168,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>17.0600242614746</v>
+        <v>17.060022354126</v>
       </c>
       <c r="H1131" t="n">
         <v>3201</v>
@@ -33197,7 +33197,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>16.8683395385742</v>
+        <v>16.8683376312256</v>
       </c>
       <c r="H1132" t="n">
         <v>2268</v>
@@ -58839,6 +58839,64 @@
         <v>6762</v>
       </c>
       <c r="I2016" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2017" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2017" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="H2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2017" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2018" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2018" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="H2018" t="n">
+        <v>3458</v>
+      </c>
+      <c r="I2018" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDAC.MI.xlsx
+++ b/data/EDAC.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H4" t="n">
         <v>7200</v>
@@ -659,7 +659,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G10" t="n">
-        <v>2.90762400627136</v>
+        <v>2.90762376785278</v>
       </c>
       <c r="H10" t="n">
         <v>2250</v>
@@ -746,7 +746,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H13" t="n">
         <v>3600</v>
@@ -775,7 +775,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.90676784515381</v>
+        <v>2.90676760673523</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H15" t="n">
         <v>5400</v>
@@ -833,7 +833,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G16" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H16" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G17" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H17" t="n">
         <v>450</v>
@@ -891,7 +891,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G18" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H18" t="n">
         <v>900</v>
@@ -920,7 +920,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G19" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.31049990653992</v>
       </c>
       <c r="G20" t="n">
-        <v>2.83441948890686</v>
+        <v>2.83441972732544</v>
       </c>
       <c r="H20" t="n">
         <v>900</v>
@@ -1036,7 +1036,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91062045097351</v>
+        <v>2.91062068939209</v>
       </c>
       <c r="H23" t="n">
         <v>450</v>
@@ -1094,7 +1094,7 @@
         <v>3.38549995422363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.89863419532776</v>
+        <v>2.89863395690918</v>
       </c>
       <c r="H25" t="n">
         <v>1350</v>
@@ -1123,7 +1123,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.79974389076233</v>
+        <v>2.79974365234375</v>
       </c>
       <c r="H26" t="n">
         <v>1800</v>
@@ -1152,7 +1152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255313873291</v>
       </c>
       <c r="H27" t="n">
         <v>450</v>
@@ -1181,7 +1181,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>2.81601119041443</v>
+        <v>2.81601166725159</v>
       </c>
       <c r="H28" t="n">
         <v>450</v>
@@ -1239,7 +1239,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76549649238586</v>
+        <v>2.76549625396729</v>
       </c>
       <c r="H30" t="n">
         <v>3150</v>
@@ -1297,7 +1297,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G32" t="n">
-        <v>2.84426593780518</v>
+        <v>2.8442656993866</v>
       </c>
       <c r="H32" t="n">
         <v>2700</v>
@@ -1384,7 +1384,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83399176597595</v>
+        <v>2.83399152755737</v>
       </c>
       <c r="H35" t="n">
         <v>7650</v>
@@ -1529,7 +1529,7 @@
         <v>3.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H40" t="n">
         <v>2250</v>
@@ -1558,7 +1558,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95385813713074</v>
+        <v>2.95385837554932</v>
       </c>
       <c r="H41" t="n">
         <v>2250</v>
@@ -1587,7 +1587,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84255337715149</v>
+        <v>2.84255313873291</v>
       </c>
       <c r="H42" t="n">
         <v>3600</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H47" t="n">
         <v>900</v>
@@ -1761,7 +1761,7 @@
         <v>3.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H48" t="n">
         <v>900</v>
@@ -1790,7 +1790,7 @@
         <v>3.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99666810035706</v>
+        <v>2.9966676235199</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>3.01379203796387</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H50" t="n">
         <v>12600</v>
@@ -1848,7 +1848,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>3.01379203796387</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01379203796387</v>
+        <v>3.01379156112671</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1906,7 +1906,7 @@
         <v>3.54949998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>3.03904938697815</v>
+        <v>3.03904914855957</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1935,7 +1935,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G54" t="n">
-        <v>3.34256935119629</v>
+        <v>3.34256911277771</v>
       </c>
       <c r="H54" t="n">
         <v>9450</v>
@@ -1964,7 +1964,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G55" t="n">
-        <v>3.19787240028381</v>
+        <v>3.19787287712097</v>
       </c>
       <c r="H55" t="n">
         <v>63900</v>
@@ -1993,7 +1993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>3.30489635467529</v>
+        <v>3.30489683151245</v>
       </c>
       <c r="H56" t="n">
         <v>12600</v>
@@ -2022,7 +2022,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35626816749573</v>
+        <v>3.35626840591431</v>
       </c>
       <c r="H57" t="n">
         <v>20250</v>
@@ -2080,7 +2080,7 @@
         <v>3.78150010108948</v>
       </c>
       <c r="G59" t="n">
-        <v>3.23768591880798</v>
+        <v>3.23768544197083</v>
       </c>
       <c r="H59" t="n">
         <v>8100</v>
@@ -2138,7 +2138,7 @@
         <v>3.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3.21071553230286</v>
+        <v>3.21071529388428</v>
       </c>
       <c r="H61" t="n">
         <v>11700</v>
@@ -2167,7 +2167,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.36483001708984</v>
+        <v>3.36482977867126</v>
       </c>
       <c r="H62" t="n">
         <v>9450</v>
@@ -2196,7 +2196,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.40763926506042</v>
+        <v>3.40763974189758</v>
       </c>
       <c r="H63" t="n">
         <v>13500</v>
@@ -2254,7 +2254,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H65" t="n">
         <v>23400</v>
@@ -2283,7 +2283,7 @@
         <v>4.21750020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>3.61098480224609</v>
+        <v>3.61098504066467</v>
       </c>
       <c r="H66" t="n">
         <v>38250</v>
@@ -2312,7 +2312,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G67" t="n">
-        <v>3.81518650054932</v>
+        <v>3.81518626213074</v>
       </c>
       <c r="H67" t="n">
         <v>22050</v>
@@ -2341,7 +2341,7 @@
         <v>4.63250017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.966304063797</v>
+        <v>3.96630430221558</v>
       </c>
       <c r="H68" t="n">
         <v>85950</v>
@@ -2370,7 +2370,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G69" t="n">
-        <v>4.04293251037598</v>
+        <v>4.04293346405029</v>
       </c>
       <c r="H69" t="n">
         <v>51750</v>
@@ -2399,7 +2399,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H70" t="n">
         <v>59850</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H71" t="n">
         <v>44550</v>
@@ -2457,7 +2457,7 @@
         <v>4.9524998664856</v>
       </c>
       <c r="G72" t="n">
-        <v>4.24028539657593</v>
+        <v>4.24028491973877</v>
       </c>
       <c r="H72" t="n">
         <v>10800</v>
@@ -2544,7 +2544,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G75" t="n">
-        <v>3.98128724098206</v>
+        <v>3.98128771781921</v>
       </c>
       <c r="H75" t="n">
         <v>16200</v>
@@ -2602,7 +2602,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847799301147</v>
       </c>
       <c r="H77" t="n">
         <v>5850</v>
@@ -2631,7 +2631,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.9384777545929</v>
+        <v>3.93847799301147</v>
       </c>
       <c r="H78" t="n">
         <v>18900</v>
@@ -2660,7 +2660,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G79" t="n">
-        <v>3.91279196739197</v>
+        <v>3.91279220581055</v>
       </c>
       <c r="H79" t="n">
         <v>5400</v>
@@ -2689,7 +2689,7 @@
         <v>4.57149982452393</v>
       </c>
       <c r="G80" t="n">
-        <v>3.91407608985901</v>
+        <v>3.91407585144043</v>
       </c>
       <c r="H80" t="n">
         <v>4950</v>
@@ -2776,7 +2776,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>3.89566850662231</v>
+        <v>3.89566874504089</v>
       </c>
       <c r="H83" t="n">
         <v>5400</v>
@@ -2805,7 +2805,7 @@
         <v>4.68149995803833</v>
       </c>
       <c r="G84" t="n">
-        <v>4.00825691223145</v>
+        <v>4.0082573890686</v>
       </c>
       <c r="H84" t="n">
         <v>8550</v>
@@ -2863,7 +2863,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96330761909485</v>
+        <v>3.96330714225769</v>
       </c>
       <c r="H86" t="n">
         <v>2700</v>
@@ -2892,7 +2892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89566850662231</v>
+        <v>3.89566874504089</v>
       </c>
       <c r="H87" t="n">
         <v>5400</v>
@@ -2979,7 +2979,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G90" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H90" t="n">
         <v>17550</v>
@@ -3008,7 +3008,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G91" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H91" t="n">
         <v>4950</v>
@@ -3037,7 +3037,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>4.17821168899536</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H92" t="n">
         <v>6750</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H93" t="n">
         <v>10350</v>
@@ -3095,7 +3095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.17821168899536</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H94" t="n">
         <v>3150</v>
@@ -3124,7 +3124,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>4.17821168899536</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G96" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H96" t="n">
         <v>12600</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H98" t="n">
         <v>8100</v>
@@ -3240,7 +3240,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G99" t="n">
-        <v>4.17821168899536</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H99" t="n">
         <v>8550</v>
@@ -3269,7 +3269,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>4.17821168899536</v>
+        <v>4.17821073532104</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G101" t="n">
-        <v>4.16108703613281</v>
+        <v>4.16108751296997</v>
       </c>
       <c r="H101" t="n">
         <v>4050</v>
@@ -3327,7 +3327,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.12684011459351</v>
+        <v>4.12683963775635</v>
       </c>
       <c r="H102" t="n">
         <v>4050</v>
@@ -3356,7 +3356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H103" t="n">
         <v>2250</v>
@@ -3385,7 +3385,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H104" t="n">
         <v>9450</v>
@@ -3414,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H105" t="n">
         <v>7650</v>
@@ -3443,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H106" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H107" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G108" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H108" t="n">
         <v>11250</v>
@@ -3530,7 +3530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H109" t="n">
         <v>27450</v>
@@ -3588,7 +3588,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G111" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H111" t="n">
         <v>4500</v>
@@ -3617,7 +3617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H112" t="n">
         <v>13950</v>
@@ -3646,7 +3646,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H113" t="n">
         <v>5850</v>
@@ -3675,7 +3675,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3733,7 +3733,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H116" t="n">
         <v>900</v>
@@ -3762,7 +3762,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H117" t="n">
         <v>5400</v>
@@ -3791,7 +3791,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H118" t="n">
         <v>6300</v>
@@ -3820,7 +3820,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938186645508</v>
       </c>
       <c r="H119" t="n">
         <v>9450</v>
@@ -3849,7 +3849,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H120" t="n">
         <v>11700</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H121" t="n">
         <v>1350</v>
@@ -3907,7 +3907,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H122" t="n">
         <v>1800</v>
@@ -3936,7 +3936,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938186645508</v>
       </c>
       <c r="H123" t="n">
         <v>3600</v>
@@ -3965,7 +3965,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.40938282012939</v>
+        <v>4.40938186645508</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>4.28095436096191</v>
+        <v>4.28095388412476</v>
       </c>
       <c r="H125" t="n">
         <v>11700</v>
@@ -4081,7 +4081,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H128" t="n">
         <v>8100</v>
@@ -4110,7 +4110,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4139,7 +4139,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G130" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H130" t="n">
         <v>1350</v>
@@ -4226,7 +4226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G133" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H133" t="n">
         <v>17550</v>
@@ -4255,7 +4255,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.45219230651855</v>
+        <v>4.4521918296814</v>
       </c>
       <c r="H134" t="n">
         <v>7200</v>
@@ -4284,7 +4284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>4.66623973846436</v>
+        <v>4.66624021530151</v>
       </c>
       <c r="H135" t="n">
         <v>34650</v>
@@ -4342,7 +4342,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H137" t="n">
         <v>69750</v>
@@ -4371,7 +4371,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H138" t="n">
         <v>18000</v>
@@ -4400,7 +4400,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H139" t="n">
         <v>3150</v>
@@ -4748,7 +4748,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.00871610641479</v>
+        <v>5.00871658325195</v>
       </c>
       <c r="H151" t="n">
         <v>1800</v>
@@ -5096,7 +5096,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52242994308472</v>
       </c>
       <c r="H163" t="n">
         <v>7650</v>
@@ -5241,7 +5241,7 @@
         <v>6.5</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H168" t="n">
         <v>10800</v>
@@ -5299,7 +5299,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H170" t="n">
         <v>4050</v>
@@ -5328,7 +5328,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52242994308472</v>
       </c>
       <c r="H171" t="n">
         <v>8100</v>
@@ -5357,7 +5357,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H172" t="n">
         <v>39600</v>
@@ -5415,7 +5415,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H174" t="n">
         <v>13050</v>
@@ -5444,7 +5444,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H175" t="n">
         <v>33300</v>
@@ -5473,7 +5473,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G176" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H176" t="n">
         <v>12600</v>
@@ -5502,7 +5502,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G177" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H177" t="n">
         <v>27450</v>
@@ -5531,7 +5531,7 @@
         <v>8</v>
       </c>
       <c r="G178" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H178" t="n">
         <v>24750</v>
@@ -5560,7 +5560,7 @@
         <v>8</v>
       </c>
       <c r="G179" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H179" t="n">
         <v>37350</v>
@@ -5589,7 +5589,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H180" t="n">
         <v>13500</v>
@@ -5618,7 +5618,7 @@
         <v>7.75</v>
       </c>
       <c r="G181" t="n">
-        <v>6.63547945022583</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H181" t="n">
         <v>15300</v>
@@ -5792,7 +5792,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H187" t="n">
         <v>2700</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H188" t="n">
         <v>19350</v>
@@ -5850,7 +5850,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H189" t="n">
         <v>4050</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H190" t="n">
         <v>15750</v>
@@ -5908,7 +5908,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>6.5926685333252</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H191" t="n">
         <v>16650</v>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H195" t="n">
         <v>37800</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.14919424057007</v>
+        <v>7.14919376373291</v>
       </c>
       <c r="H196" t="n">
         <v>13950</v>
@@ -6082,7 +6082,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>7.10638380050659</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H197" t="n">
         <v>15750</v>
@@ -6111,7 +6111,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>7.10638380050659</v>
+        <v>7.10638427734375</v>
       </c>
       <c r="H198" t="n">
         <v>10800</v>
@@ -6140,7 +6140,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G199" t="n">
-        <v>6.93514585494995</v>
+        <v>6.93514633178711</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>6.89233636856079</v>
+        <v>6.89233589172363</v>
       </c>
       <c r="H200" t="n">
         <v>6750</v>
@@ -6285,7 +6285,7 @@
         <v>7.75</v>
       </c>
       <c r="G204" t="n">
-        <v>6.63547945022583</v>
+        <v>6.63547849655151</v>
       </c>
       <c r="H204" t="n">
         <v>9900</v>
@@ -6314,7 +6314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84952688217163</v>
+        <v>6.84952640533447</v>
       </c>
       <c r="H207" t="n">
         <v>4950</v>
@@ -6401,7 +6401,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>6.5926685333252</v>
+        <v>6.59266901016235</v>
       </c>
       <c r="H208" t="n">
         <v>15750</v>
@@ -6430,7 +6430,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H209" t="n">
         <v>8100</v>
@@ -6459,7 +6459,7 @@
         <v>7.5</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42143106460571</v>
+        <v>6.42143058776855</v>
       </c>
       <c r="H210" t="n">
         <v>6300</v>
@@ -6575,7 +6575,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H214" t="n">
         <v>5850</v>
@@ -6604,7 +6604,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H215" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H216" t="n">
         <v>13430</v>
@@ -6662,7 +6662,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G217" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H217" t="n">
         <v>7527</v>
@@ -6691,7 +6691,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.54986000061035</v>
+        <v>6.54985952377319</v>
       </c>
       <c r="H218" t="n">
         <v>600</v>
@@ -6749,7 +6749,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G220" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H220" t="n">
         <v>23636</v>
@@ -6778,7 +6778,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G221" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H221" t="n">
         <v>2400</v>
@@ -6807,7 +6807,7 @@
         <v>7.25</v>
       </c>
       <c r="G222" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H222" t="n">
         <v>7042</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="G223" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H223" t="n">
         <v>3075</v>
@@ -6894,7 +6894,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H225" t="n">
         <v>7622</v>
@@ -6952,7 +6952,7 @@
         <v>6.5</v>
       </c>
       <c r="G227" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H227" t="n">
         <v>19965</v>
@@ -7010,7 +7010,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G229" t="n">
-        <v>6.46424055099487</v>
+        <v>6.46424102783203</v>
       </c>
       <c r="H229" t="n">
         <v>24801</v>
@@ -7068,7 +7068,7 @@
         <v>7.25</v>
       </c>
       <c r="G231" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H231" t="n">
         <v>55223</v>
@@ -7184,7 +7184,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H235" t="n">
         <v>2494</v>
@@ -7242,7 +7242,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H237" t="n">
         <v>3630</v>
@@ -7329,7 +7329,7 @@
         <v>7.25</v>
       </c>
       <c r="G240" t="n">
-        <v>6.20738363265991</v>
+        <v>6.20738315582275</v>
       </c>
       <c r="H240" t="n">
         <v>10587</v>
@@ -7445,7 +7445,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G244" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H244" t="n">
         <v>1353</v>
@@ -7474,7 +7474,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H245" t="n">
         <v>3000</v>
@@ -7503,7 +7503,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G246" t="n">
-        <v>6.16457414627075</v>
+        <v>6.16457366943359</v>
       </c>
       <c r="H246" t="n">
         <v>12575</v>
@@ -7619,7 +7619,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>5.95052671432495</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H250" t="n">
         <v>4710</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G251" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H251" t="n">
         <v>5435</v>
@@ -7677,7 +7677,7 @@
         <v>7</v>
       </c>
       <c r="G252" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H252" t="n">
         <v>4850</v>
@@ -7706,7 +7706,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H253" t="n">
         <v>2172</v>
@@ -7793,7 +7793,7 @@
         <v>6.75</v>
       </c>
       <c r="G256" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H256" t="n">
         <v>4368</v>
@@ -7822,7 +7822,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G257" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H257" t="n">
         <v>2667</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="G258" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H258" t="n">
         <v>5935</v>
@@ -7880,7 +7880,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H259" t="n">
         <v>1600</v>
@@ -7967,7 +7967,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H262" t="n">
         <v>2060</v>
@@ -7996,7 +7996,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H263" t="n">
         <v>3055</v>
@@ -8025,7 +8025,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>5.95052671432495</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H264" t="n">
         <v>1575</v>
@@ -8054,7 +8054,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H265" t="n">
         <v>998</v>
@@ -8083,7 +8083,7 @@
         <v>7</v>
       </c>
       <c r="G266" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H266" t="n">
         <v>300</v>
@@ -8112,7 +8112,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H267" t="n">
         <v>5285</v>
@@ -8141,7 +8141,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.95052671432495</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H268" t="n">
         <v>2072</v>
@@ -8170,7 +8170,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H269" t="n">
         <v>5514</v>
@@ -8199,7 +8199,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G270" t="n">
-        <v>6.03614568710327</v>
+        <v>6.03614521026611</v>
       </c>
       <c r="H270" t="n">
         <v>12160</v>
@@ -8228,7 +8228,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H271" t="n">
         <v>4430</v>
@@ -8257,7 +8257,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H272" t="n">
         <v>2125</v>
@@ -8315,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="G274" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H274" t="n">
         <v>2450</v>
@@ -8344,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G275" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H275" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H276" t="n">
         <v>316</v>
@@ -8431,7 +8431,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H278" t="n">
         <v>1282</v>
@@ -8460,7 +8460,7 @@
         <v>7</v>
       </c>
       <c r="G279" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H279" t="n">
         <v>6367</v>
@@ -8489,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="G280" t="n">
-        <v>5.99333620071411</v>
+        <v>5.99333524703979</v>
       </c>
       <c r="H280" t="n">
         <v>1065</v>
@@ -8547,7 +8547,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G282" t="n">
-        <v>5.95052671432495</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H282" t="n">
         <v>3735</v>
@@ -8576,7 +8576,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G283" t="n">
-        <v>5.95052671432495</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H283" t="n">
         <v>5807</v>
@@ -8605,7 +8605,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>5.95052671432495</v>
+        <v>5.95052576065063</v>
       </c>
       <c r="H284" t="n">
         <v>498</v>
@@ -8663,7 +8663,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G286" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H286" t="n">
         <v>3644</v>
@@ -8692,7 +8692,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H287" t="n">
         <v>1646</v>
@@ -8721,7 +8721,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>5.90771627426147</v>
+        <v>5.90771675109863</v>
       </c>
       <c r="H288" t="n">
         <v>3648</v>
@@ -8750,7 +8750,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H289" t="n">
         <v>3551</v>
@@ -8779,7 +8779,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H290" t="n">
         <v>1490</v>
@@ -8808,7 +8808,7 @@
         <v>6.75</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H291" t="n">
         <v>2030</v>
@@ -8837,7 +8837,7 @@
         <v>6.75</v>
       </c>
       <c r="G292" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H292" t="n">
         <v>720</v>
@@ -8866,7 +8866,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>5.86490631103516</v>
+        <v>5.86490726470947</v>
       </c>
       <c r="H293" t="n">
         <v>2474</v>
@@ -8895,7 +8895,7 @@
         <v>6.75</v>
       </c>
       <c r="G294" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H294" t="n">
         <v>4848</v>
@@ -8953,7 +8953,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H296" t="n">
         <v>5050</v>
@@ -8982,7 +8982,7 @@
         <v>6.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H297" t="n">
         <v>1260</v>
@@ -9011,7 +9011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H298" t="n">
         <v>2312</v>
@@ -9069,7 +9069,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H300" t="n">
         <v>2253</v>
@@ -9127,7 +9127,7 @@
         <v>6.75</v>
       </c>
       <c r="G302" t="n">
-        <v>5.77928733825684</v>
+        <v>5.77928829193115</v>
       </c>
       <c r="H302" t="n">
         <v>2854</v>
@@ -9156,7 +9156,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H303" t="n">
         <v>2414</v>
@@ -9417,7 +9417,7 @@
         <v>6.5</v>
       </c>
       <c r="G312" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H312" t="n">
         <v>1448</v>
@@ -9446,7 +9446,7 @@
         <v>6.5</v>
       </c>
       <c r="G313" t="n">
-        <v>5.56523990631104</v>
+        <v>5.56524038314819</v>
       </c>
       <c r="H313" t="n">
         <v>8895</v>
@@ -9475,7 +9475,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G314" t="n">
-        <v>5.52243041992188</v>
+        <v>5.52242994308472</v>
       </c>
       <c r="H314" t="n">
         <v>1549</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69366931915283</v>
+        <v>5.69366884231567</v>
       </c>
       <c r="H315" t="n">
         <v>27565</v>
@@ -9678,7 +9678,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>5.17995452880859</v>
+        <v>5.17995500564575</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9736,7 +9736,7 @@
         <v>5.5</v>
       </c>
       <c r="G323" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70904922485352</v>
       </c>
       <c r="H323" t="n">
         <v>13319</v>
@@ -9765,7 +9765,7 @@
         <v>5.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.70904970169067</v>
+        <v>4.70904922485352</v>
       </c>
       <c r="H324" t="n">
         <v>7596</v>
@@ -9794,7 +9794,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G325" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H325" t="n">
         <v>7622</v>
@@ -9823,7 +9823,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H326" t="n">
         <v>6905</v>
@@ -9852,7 +9852,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H327" t="n">
         <v>5844</v>
@@ -9881,7 +9881,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G328" t="n">
-        <v>3.52750587463379</v>
+        <v>3.52750563621521</v>
       </c>
       <c r="H328" t="n">
         <v>14468</v>
@@ -9910,7 +9910,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>3.69874501228333</v>
+        <v>3.69874453544617</v>
       </c>
       <c r="H329" t="n">
         <v>7210</v>
@@ -9939,7 +9939,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>3.39051580429077</v>
+        <v>3.39051556587219</v>
       </c>
       <c r="H330" t="n">
         <v>26799</v>
@@ -9968,7 +9968,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G331" t="n">
-        <v>2.96242046356201</v>
+        <v>2.96242022514343</v>
       </c>
       <c r="H331" t="n">
         <v>25097</v>
@@ -10084,7 +10084,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G335" t="n">
-        <v>2.43158173561096</v>
+        <v>2.43158197402954</v>
       </c>
       <c r="H335" t="n">
         <v>3740</v>
@@ -10229,7 +10229,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>3.95560073852539</v>
+        <v>3.95560121536255</v>
       </c>
       <c r="H340" t="n">
         <v>40606</v>
@@ -10258,7 +10258,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58062028884888</v>
+        <v>4.58062076568604</v>
       </c>
       <c r="H341" t="n">
         <v>24606</v>
@@ -10316,7 +10316,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.19533491134644</v>
+        <v>4.19533443450928</v>
       </c>
       <c r="H343" t="n">
         <v>19120</v>
@@ -10345,7 +10345,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.88710641860962</v>
+        <v>3.88710618019104</v>
       </c>
       <c r="H344" t="n">
         <v>14534</v>
@@ -10374,7 +10374,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723909378052</v>
       </c>
       <c r="H345" t="n">
         <v>6178</v>
@@ -10403,7 +10403,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G346" t="n">
-        <v>3.73299169540405</v>
+        <v>3.73299217224121</v>
       </c>
       <c r="H346" t="n">
         <v>3880</v>
@@ -10461,7 +10461,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>3.58743977546692</v>
+        <v>3.58743929862976</v>
       </c>
       <c r="H348" t="n">
         <v>5375</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H350" t="n">
         <v>8602</v>
@@ -10548,7 +10548,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>3.65593481063843</v>
+        <v>3.65593457221985</v>
       </c>
       <c r="H351" t="n">
         <v>25907</v>
@@ -10635,7 +10635,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>3.51894426345825</v>
+        <v>3.51894450187683</v>
       </c>
       <c r="H354" t="n">
         <v>4650</v>
@@ -10664,7 +10664,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.52750587463379</v>
+        <v>3.52750563621521</v>
       </c>
       <c r="H355" t="n">
         <v>3470</v>
@@ -10693,7 +10693,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H356" t="n">
         <v>7150</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.42476344108582</v>
+        <v>3.42476320266724</v>
       </c>
       <c r="H359" t="n">
         <v>3100</v>
@@ -10809,7 +10809,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>3.46757292747498</v>
+        <v>3.46757316589355</v>
       </c>
       <c r="H360" t="n">
         <v>6825</v>
@@ -10867,7 +10867,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>3.81861066818237</v>
+        <v>3.81861114501953</v>
       </c>
       <c r="H362" t="n">
         <v>19084</v>
@@ -10896,7 +10896,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>3.7672393321991</v>
+        <v>3.76723909378052</v>
       </c>
       <c r="H363" t="n">
         <v>20856</v>
@@ -10925,7 +10925,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>3.81861066818237</v>
+        <v>3.81861114501953</v>
       </c>
       <c r="H364" t="n">
         <v>2419</v>
@@ -11012,7 +11012,7 @@
         <v>4.5</v>
       </c>
       <c r="G367" t="n">
-        <v>3.85285878181458</v>
+        <v>3.85285830497742</v>
       </c>
       <c r="H367" t="n">
         <v>8160</v>
@@ -11070,7 +11070,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G369" t="n">
-        <v>4.50356292724609</v>
+        <v>4.50356340408325</v>
       </c>
       <c r="H369" t="n">
         <v>65581</v>
@@ -11157,7 +11157,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.34262990951538</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H372" t="n">
         <v>50751</v>
@@ -11302,7 +11302,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>4.36657285690308</v>
+        <v>4.36657333374023</v>
       </c>
       <c r="H377" t="n">
         <v>13190</v>
@@ -11331,7 +11331,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>4.26382970809937</v>
+        <v>4.26383018493652</v>
       </c>
       <c r="H378" t="n">
         <v>10379</v>
@@ -11360,7 +11360,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>4.2723913192749</v>
+        <v>4.27239179611206</v>
       </c>
       <c r="H379" t="n">
         <v>13357</v>
@@ -11389,7 +11389,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>4.53781175613403</v>
+        <v>4.53781127929688</v>
       </c>
       <c r="H380" t="n">
         <v>26820</v>
@@ -11418,7 +11418,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64055395126343</v>
+        <v>4.64055442810059</v>
       </c>
       <c r="H381" t="n">
         <v>28041</v>
@@ -11447,7 +11447,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838251113892</v>
       </c>
       <c r="H382" t="n">
         <v>137190</v>
@@ -11505,7 +11505,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G384" t="n">
-        <v>4.98303079605103</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H384" t="n">
         <v>22125</v>
@@ -11563,7 +11563,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>5.34262990951538</v>
+        <v>5.3426308631897</v>
       </c>
       <c r="H386" t="n">
         <v>87258</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.30838298797607</v>
+        <v>5.30838251113892</v>
       </c>
       <c r="H387" t="n">
         <v>39972</v>
@@ -11621,7 +11621,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G388" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H388" t="n">
         <v>21205</v>
@@ -11650,7 +11650,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H389" t="n">
         <v>10104</v>
@@ -11679,7 +11679,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.10289764404297</v>
+        <v>5.10289621353149</v>
       </c>
       <c r="H390" t="n">
         <v>18684</v>
@@ -11708,7 +11708,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G391" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H391" t="n">
         <v>16426</v>
@@ -11737,7 +11737,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G392" t="n">
-        <v>5.00015497207642</v>
+        <v>5.00015449523926</v>
       </c>
       <c r="H392" t="n">
         <v>5797</v>
@@ -11795,7 +11795,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G394" t="n">
-        <v>5.15426921844482</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H394" t="n">
         <v>23884</v>
@@ -11824,7 +11824,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H395" t="n">
         <v>6353</v>
@@ -11853,7 +11853,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>5.20563983917236</v>
+        <v>5.20564031600952</v>
       </c>
       <c r="H396" t="n">
         <v>4787</v>
@@ -11882,7 +11882,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G397" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H397" t="n">
         <v>5833</v>
@@ -12056,7 +12056,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G403" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H403" t="n">
         <v>4080</v>
@@ -12085,7 +12085,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G404" t="n">
-        <v>4.98303079605103</v>
+        <v>4.98303031921387</v>
       </c>
       <c r="H404" t="n">
         <v>5550</v>
@@ -12143,7 +12143,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G406" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H406" t="n">
         <v>2647</v>
@@ -12172,7 +12172,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>5.15426921844482</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H407" t="n">
         <v>1812</v>
@@ -12230,7 +12230,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H409" t="n">
         <v>4265</v>
@@ -12317,7 +12317,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H412" t="n">
         <v>395</v>
@@ -12375,7 +12375,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H414" t="n">
         <v>1971</v>
@@ -12404,7 +12404,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G415" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H415" t="n">
         <v>4635</v>
@@ -12433,7 +12433,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H416" t="n">
         <v>12743</v>
@@ -12491,7 +12491,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H418" t="n">
         <v>1185</v>
@@ -12578,7 +12578,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G421" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H421" t="n">
         <v>10486</v>
@@ -12607,7 +12607,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G422" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413558959961</v>
       </c>
       <c r="H422" t="n">
         <v>7415</v>
@@ -12694,7 +12694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G425" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H425" t="n">
         <v>3416</v>
@@ -12723,7 +12723,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>5.10289764404297</v>
+        <v>5.10289621353149</v>
       </c>
       <c r="H426" t="n">
         <v>4511</v>
@@ -12781,7 +12781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G428" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H428" t="n">
         <v>8205</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.03440141677856</v>
+        <v>5.03440189361572</v>
       </c>
       <c r="H429" t="n">
         <v>5203</v>
@@ -12839,7 +12839,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G430" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H430" t="n">
         <v>1010</v>
@@ -12868,7 +12868,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.15426921844482</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H431" t="n">
         <v>751</v>
@@ -12926,7 +12926,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>5.15426921844482</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H433" t="n">
         <v>2489</v>
@@ -12955,7 +12955,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H434" t="n">
         <v>528</v>
@@ -12984,7 +12984,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G435" t="n">
-        <v>5.15426921844482</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H435" t="n">
         <v>2314</v>
@@ -13013,7 +13013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G436" t="n">
-        <v>5.15426921844482</v>
+        <v>5.15426874160767</v>
       </c>
       <c r="H436" t="n">
         <v>2092</v>
@@ -13071,7 +13071,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>5.27413511276245</v>
+        <v>5.27413558959961</v>
       </c>
       <c r="H438" t="n">
         <v>8401</v>
@@ -13187,7 +13187,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>5.12002086639404</v>
+        <v>5.1200213432312</v>
       </c>
       <c r="H442" t="n">
         <v>1564</v>
@@ -13216,7 +13216,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>5.17139196395874</v>
+        <v>5.1713924407959</v>
       </c>
       <c r="H443" t="n">
         <v>260</v>
@@ -13274,7 +13274,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.10289764404297</v>
+        <v>5.10289621353149</v>
       </c>
       <c r="H445" t="n">
         <v>4470</v>
@@ -13332,7 +13332,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>5.10289764404297</v>
+        <v>5.10289621353149</v>
       </c>
       <c r="H447" t="n">
         <v>2883</v>
@@ -13390,7 +13390,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G449" t="n">
-        <v>5.18851613998413</v>
+        <v>5.18851566314697</v>
       </c>
       <c r="H449" t="n">
         <v>2920</v>
@@ -13419,7 +13419,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>5.2024359703064</v>
+        <v>5.20243549346924</v>
       </c>
       <c r="H450" t="n">
         <v>2913</v>
@@ -13564,7 +13564,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>5.18503713607788</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H455" t="n">
         <v>845</v>
@@ -13593,7 +13593,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G456" t="n">
-        <v>5.11543846130371</v>
+        <v>5.11543941497803</v>
       </c>
       <c r="H456" t="n">
         <v>3723</v>
@@ -13622,7 +13622,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G457" t="n">
-        <v>5.0980396270752</v>
+        <v>5.09803915023804</v>
       </c>
       <c r="H457" t="n">
         <v>3203</v>
@@ -13680,7 +13680,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>5.01104164123535</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H459" t="n">
         <v>2350</v>
@@ -13709,7 +13709,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G460" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H460" t="n">
         <v>2330</v>
@@ -13738,7 +13738,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>5.16763687133789</v>
+        <v>5.16763782501221</v>
       </c>
       <c r="H461" t="n">
         <v>2800</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H466" t="n">
         <v>2015</v>
@@ -13999,7 +13999,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H470" t="n">
         <v>4279</v>
@@ -14028,7 +14028,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265075683594</v>
       </c>
       <c r="H471" t="n">
         <v>9623</v>
@@ -14057,7 +14057,7 @@
         <v>5.5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H472" t="n">
         <v>10358</v>
@@ -14173,7 +14173,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H476" t="n">
         <v>4010</v>
@@ -14231,7 +14231,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H478" t="n">
         <v>2892</v>
@@ -14260,7 +14260,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>4.7326512336731</v>
+        <v>4.73265075683594</v>
       </c>
       <c r="H479" t="n">
         <v>889</v>
@@ -14289,7 +14289,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H480" t="n">
         <v>10416</v>
@@ -14318,7 +14318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G481" t="n">
-        <v>4.52385711669922</v>
+        <v>4.5238561630249</v>
       </c>
       <c r="H481" t="n">
         <v>6191</v>
@@ -14347,7 +14347,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G482" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H482" t="n">
         <v>2456</v>
@@ -14376,7 +14376,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G483" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H483" t="n">
         <v>6872</v>
@@ -14405,7 +14405,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H484" t="n">
         <v>2940</v>
@@ -14434,7 +14434,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H485" t="n">
         <v>672</v>
@@ -14463,7 +14463,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H486" t="n">
         <v>200</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>4.52385711669922</v>
+        <v>4.5238561630249</v>
       </c>
       <c r="H487" t="n">
         <v>537</v>
@@ -14521,7 +14521,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G488" t="n">
-        <v>4.47165870666504</v>
+        <v>4.47165822982788</v>
       </c>
       <c r="H488" t="n">
         <v>2906</v>
@@ -14550,7 +14550,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G489" t="n">
-        <v>4.45425987243652</v>
+        <v>4.45425939559937</v>
       </c>
       <c r="H489" t="n">
         <v>3075</v>
@@ -14666,7 +14666,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G493" t="n">
-        <v>4.28896427154541</v>
+        <v>4.28896474838257</v>
       </c>
       <c r="H493" t="n">
         <v>5774</v>
@@ -14695,7 +14695,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.08887100219727</v>
+        <v>4.08887147903442</v>
       </c>
       <c r="H494" t="n">
         <v>1610</v>
@@ -14724,7 +14724,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>4.16716909408569</v>
+        <v>4.16716861724854</v>
       </c>
       <c r="H495" t="n">
         <v>20644</v>
@@ -14869,7 +14869,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>4.1149697303772</v>
+        <v>4.11497068405151</v>
       </c>
       <c r="H500" t="n">
         <v>6862</v>
@@ -14927,7 +14927,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31506395339966</v>
+        <v>4.31506443023682</v>
       </c>
       <c r="H502" t="n">
         <v>4690</v>
@@ -14985,7 +14985,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.30636358261108</v>
+        <v>4.30636405944824</v>
       </c>
       <c r="H504" t="n">
         <v>10900</v>
@@ -15014,7 +15014,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H505" t="n">
         <v>25986</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43686056137085</v>
       </c>
       <c r="H507" t="n">
         <v>12706</v>
@@ -15101,7 +15101,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H508" t="n">
         <v>14843</v>
@@ -15130,7 +15130,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H509" t="n">
         <v>6520</v>
@@ -15159,7 +15159,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H510" t="n">
         <v>524</v>
@@ -15188,7 +15188,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G511" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H511" t="n">
         <v>9671</v>
@@ -15217,7 +15217,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G512" t="n">
-        <v>4.57605504989624</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H512" t="n">
         <v>2873</v>
@@ -15246,7 +15246,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G513" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H513" t="n">
         <v>535</v>
@@ -15275,7 +15275,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G514" t="n">
-        <v>4.54125642776489</v>
+        <v>4.54125690460205</v>
       </c>
       <c r="H514" t="n">
         <v>2490</v>
@@ -15304,7 +15304,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>4.57605504989624</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H515" t="n">
         <v>2290</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>4.52385711669922</v>
+        <v>4.5238561630249</v>
       </c>
       <c r="H517" t="n">
         <v>3170</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.52385711669922</v>
+        <v>4.5238561630249</v>
       </c>
       <c r="H518" t="n">
         <v>1170</v>
@@ -15420,7 +15420,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H519" t="n">
         <v>2418</v>
@@ -15449,7 +15449,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H520" t="n">
         <v>140</v>
@@ -15478,7 +15478,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H522" t="n">
         <v>5441</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.52385711669922</v>
+        <v>4.5238561630249</v>
       </c>
       <c r="H523" t="n">
         <v>6233</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.52385711669922</v>
+        <v>4.5238561630249</v>
       </c>
       <c r="H524" t="n">
         <v>1255</v>
@@ -15681,7 +15681,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G528" t="n">
-        <v>4.57605504989624</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H528" t="n">
         <v>1750</v>
@@ -15710,7 +15710,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>4.47165870666504</v>
+        <v>4.47165822982788</v>
       </c>
       <c r="H529" t="n">
         <v>2863</v>
@@ -15739,7 +15739,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G530" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43686056137085</v>
       </c>
       <c r="H530" t="n">
         <v>10190</v>
@@ -15797,7 +15797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G532" t="n">
-        <v>4.57605504989624</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H532" t="n">
         <v>16579</v>
@@ -15826,7 +15826,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G533" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H533" t="n">
         <v>5756</v>
@@ -15855,7 +15855,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G534" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H534" t="n">
         <v>13104</v>
@@ -15884,7 +15884,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.59345483779907</v>
+        <v>4.59345531463623</v>
       </c>
       <c r="H535" t="n">
         <v>380</v>
@@ -15971,7 +15971,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G538" t="n">
-        <v>4.57605504989624</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H538" t="n">
         <v>1392</v>
@@ -16000,7 +16000,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H539" t="n">
         <v>11117</v>
@@ -16029,7 +16029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>4.69785213470459</v>
+        <v>4.69785165786743</v>
       </c>
       <c r="H540" t="n">
         <v>5151</v>
@@ -16058,7 +16058,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G541" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H541" t="n">
         <v>1369</v>
@@ -16087,7 +16087,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G542" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H542" t="n">
         <v>1100</v>
@@ -16145,7 +16145,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G544" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825489044189</v>
       </c>
       <c r="H544" t="n">
         <v>855</v>
@@ -16174,7 +16174,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H545" t="n">
         <v>1820</v>
@@ -16203,7 +16203,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H546" t="n">
         <v>8745</v>
@@ -16232,7 +16232,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G547" t="n">
-        <v>4.62825441360474</v>
+        <v>4.62825489044189</v>
       </c>
       <c r="H547" t="n">
         <v>14044</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.57605504989624</v>
+        <v>4.57605600357056</v>
       </c>
       <c r="H549" t="n">
         <v>1333</v>
@@ -16348,7 +16348,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H551" t="n">
         <v>2327</v>
@@ -16377,7 +16377,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.68045234680176</v>
+        <v>4.68045282363892</v>
       </c>
       <c r="H552" t="n">
         <v>1922</v>
@@ -16406,7 +16406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H553" t="n">
         <v>12566</v>
@@ -16435,7 +16435,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>4.61085510253906</v>
+        <v>4.6108546257019</v>
       </c>
       <c r="H554" t="n">
         <v>4021</v>
@@ -16551,7 +16551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>4.43686008453369</v>
+        <v>4.43686056137085</v>
       </c>
       <c r="H558" t="n">
         <v>2505</v>
@@ -16580,7 +16580,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G559" t="n">
-        <v>4.54125642776489</v>
+        <v>4.54125690460205</v>
       </c>
       <c r="H559" t="n">
         <v>3170</v>
@@ -16638,7 +16638,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>4.55865621566772</v>
+        <v>4.55865573883057</v>
       </c>
       <c r="H561" t="n">
         <v>8531</v>
@@ -16696,7 +16696,7 @@
         <v>5.5</v>
       </c>
       <c r="G563" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H563" t="n">
         <v>7869</v>
@@ -16725,7 +16725,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76744937896729</v>
+        <v>4.76744985580444</v>
       </c>
       <c r="H564" t="n">
         <v>16117</v>
@@ -16754,7 +16754,7 @@
         <v>5.5</v>
       </c>
       <c r="G565" t="n">
-        <v>4.78484916687012</v>
+        <v>4.78484964370728</v>
       </c>
       <c r="H565" t="n">
         <v>4770</v>
@@ -16899,7 +16899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>5.18503713607788</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H570" t="n">
         <v>4750</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>4.8718466758728</v>
+        <v>4.87184619903564</v>
       </c>
       <c r="H572" t="n">
         <v>14439</v>
@@ -16986,7 +16986,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G573" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H573" t="n">
         <v>11120</v>
@@ -17015,7 +17015,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G574" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H574" t="n">
         <v>10615</v>
@@ -17044,7 +17044,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G575" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H575" t="n">
         <v>7152</v>
@@ -17102,7 +17102,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G577" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H577" t="n">
         <v>6090</v>
@@ -17131,7 +17131,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G578" t="n">
-        <v>5.02844190597534</v>
+        <v>5.02844142913818</v>
       </c>
       <c r="H578" t="n">
         <v>11230</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.90664482116699</v>
+        <v>4.90664529800415</v>
       </c>
       <c r="H580" t="n">
         <v>3904</v>
@@ -17218,7 +17218,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G581" t="n">
-        <v>5.01104164123535</v>
+        <v>5.01104211807251</v>
       </c>
       <c r="H581" t="n">
         <v>3082</v>
@@ -17392,7 +17392,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H587" t="n">
         <v>4942</v>
@@ -17421,7 +17421,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.3068323135376</v>
+        <v>5.30683279037476</v>
       </c>
       <c r="H588" t="n">
         <v>10524</v>
@@ -17537,7 +17537,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>5.18503713607788</v>
+        <v>5.18503665924072</v>
       </c>
       <c r="H592" t="n">
         <v>6452</v>
@@ -17595,7 +17595,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>4.97624349594116</v>
+        <v>4.976243019104</v>
       </c>
       <c r="H594" t="n">
         <v>12574</v>
@@ -18233,7 +18233,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G616" t="n">
-        <v>5.9680118560791</v>
+        <v>5.96801233291626</v>
       </c>
       <c r="H616" t="n">
         <v>25482</v>
@@ -18262,7 +18262,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H617" t="n">
         <v>94802</v>
@@ -18291,7 +18291,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>6.00281047821045</v>
+        <v>6.00281095504761</v>
       </c>
       <c r="H618" t="n">
         <v>68179</v>
@@ -18407,7 +18407,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G622" t="n">
-        <v>7.00031089782715</v>
+        <v>7.00031137466431</v>
       </c>
       <c r="H622" t="n">
         <v>164588</v>
@@ -18436,7 +18436,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G623" t="n">
-        <v>6.83999729156494</v>
+        <v>6.8399977684021</v>
       </c>
       <c r="H623" t="n">
         <v>76240</v>
@@ -18523,7 +18523,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="n">
-        <v>6.96468591690063</v>
+        <v>6.96468496322632</v>
       </c>
       <c r="H626" t="n">
         <v>31285</v>
@@ -18552,7 +18552,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G627" t="n">
-        <v>6.87562274932861</v>
+        <v>6.87562322616577</v>
       </c>
       <c r="H627" t="n">
         <v>13853</v>
@@ -18581,7 +18581,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G628" t="n">
-        <v>7.0893726348877</v>
+        <v>7.08937311172485</v>
       </c>
       <c r="H628" t="n">
         <v>61294</v>
@@ -18610,7 +18610,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G629" t="n">
-        <v>7.4812479019165</v>
+        <v>7.48124694824219</v>
       </c>
       <c r="H629" t="n">
         <v>152384</v>
@@ -18639,7 +18639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G630" t="n">
-        <v>7.90874671936035</v>
+        <v>7.90874767303467</v>
       </c>
       <c r="H630" t="n">
         <v>133034</v>
@@ -18668,7 +18668,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.81968402862549</v>
+        <v>7.81968450546265</v>
       </c>
       <c r="H631" t="n">
         <v>70456</v>
@@ -18726,7 +18726,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G633" t="n">
-        <v>8.4787483215332</v>
+        <v>8.47874736785889</v>
       </c>
       <c r="H633" t="n">
         <v>83403</v>
@@ -18755,7 +18755,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>9.17343521118164</v>
+        <v>9.17343616485596</v>
       </c>
       <c r="H634" t="n">
         <v>112604</v>
@@ -18784,7 +18784,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>9.97499752044678</v>
+        <v>9.97499656677246</v>
       </c>
       <c r="H635" t="n">
         <v>152319</v>
@@ -18929,7 +18929,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>9.08437252044678</v>
+        <v>9.08437156677246</v>
       </c>
       <c r="H640" t="n">
         <v>42073</v>
@@ -18958,7 +18958,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G641" t="n">
-        <v>8.81718349456787</v>
+        <v>8.81718444824219</v>
       </c>
       <c r="H641" t="n">
         <v>40921</v>
@@ -18987,7 +18987,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G642" t="n">
-        <v>8.79937267303467</v>
+        <v>8.79937362670898</v>
       </c>
       <c r="H642" t="n">
         <v>24861</v>
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="G645" t="n">
-        <v>8.90624809265137</v>
+        <v>8.90624713897705</v>
       </c>
       <c r="H645" t="n">
         <v>112321</v>
@@ -19132,7 +19132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>9.44062328338623</v>
+        <v>9.44062232971191</v>
       </c>
       <c r="H647" t="n">
         <v>42066</v>
@@ -19219,7 +19219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>11.3109331130981</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H650" t="n">
         <v>160231</v>
@@ -19248,7 +19248,7 @@
         <v>13</v>
       </c>
       <c r="G651" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H651" t="n">
         <v>147714</v>
@@ -19335,7 +19335,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8453102111816</v>
+        <v>11.845308303833</v>
       </c>
       <c r="H654" t="n">
         <v>47177</v>
@@ -19364,7 +19364,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671848297119</v>
       </c>
       <c r="H655" t="n">
         <v>87639</v>
@@ -19422,7 +19422,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G657" t="n">
-        <v>11.3999977111816</v>
+        <v>11.3999967575073</v>
       </c>
       <c r="H657" t="n">
         <v>25340</v>
@@ -19451,7 +19451,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.3109331130981</v>
+        <v>11.3109340667725</v>
       </c>
       <c r="H658" t="n">
         <v>11498</v>
@@ -19480,7 +19480,7 @@
         <v>13</v>
       </c>
       <c r="G659" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H659" t="n">
         <v>38033</v>
@@ -19509,7 +19509,7 @@
         <v>13</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5781211853027</v>
+        <v>11.5781221389771</v>
       </c>
       <c r="H660" t="n">
         <v>32324</v>
@@ -19538,7 +19538,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>11.5335893630981</v>
+        <v>11.5335903167725</v>
       </c>
       <c r="H661" t="n">
         <v>13950</v>
@@ -19596,7 +19596,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>11.6671838760376</v>
+        <v>11.6671848297119</v>
       </c>
       <c r="H663" t="n">
         <v>11952</v>
@@ -19770,7 +19770,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>11.7246856689453</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H669" t="n">
         <v>11757</v>
@@ -19799,7 +19799,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>11.7246856689453</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H670" t="n">
         <v>12493</v>
@@ -19857,7 +19857,7 @@
         <v>12.75</v>
       </c>
       <c r="G672" t="n">
-        <v>11.455150604248</v>
+        <v>11.4551515579224</v>
       </c>
       <c r="H672" t="n">
         <v>11052</v>
@@ -19886,7 +19886,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>11.0957736968994</v>
+        <v>11.095775604248</v>
       </c>
       <c r="H673" t="n">
         <v>20518</v>
@@ -19944,7 +19944,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G675" t="n">
-        <v>11.4102296829224</v>
+        <v>11.410228729248</v>
       </c>
       <c r="H675" t="n">
         <v>30625</v>
@@ -19973,7 +19973,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>11.7246856689453</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H676" t="n">
         <v>35214</v>
@@ -20089,7 +20089,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.7246856689453</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H680" t="n">
         <v>13624</v>
@@ -20176,7 +20176,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G683" t="n">
-        <v>11.7246856689453</v>
+        <v>11.7246837615967</v>
       </c>
       <c r="H683" t="n">
         <v>11527</v>
@@ -20408,7 +20408,7 @@
         <v>14</v>
       </c>
       <c r="G691" t="n">
-        <v>12.5782051086426</v>
+        <v>12.5782060623169</v>
       </c>
       <c r="H691" t="n">
         <v>55853</v>
@@ -20524,7 +20524,7 @@
         <v>18</v>
       </c>
       <c r="G695" t="n">
-        <v>16.1719799041748</v>
+        <v>16.1719760894775</v>
       </c>
       <c r="H695" t="n">
 